--- a/artfynd/A 47938-2025 artfynd.xlsx
+++ b/artfynd/A 47938-2025 artfynd.xlsx
@@ -6270,10 +6270,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129011373</v>
+        <v>129011372</v>
       </c>
       <c r="B57" t="n">
-        <v>91540</v>
+        <v>57723</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6281,30 +6281,31 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6312,10 +6313,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>409435</v>
+        <v>409796</v>
       </c>
       <c r="R57" t="n">
-        <v>6782383</v>
+        <v>6782327</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6347,7 +6348,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6357,12 +6358,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:14</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>4 st på samma tall</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6371,7 +6367,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6390,10 +6385,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129011372</v>
+        <v>129032889</v>
       </c>
       <c r="B58" t="n">
-        <v>57723</v>
+        <v>79034</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6401,42 +6396,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>409796</v>
+        <v>409164</v>
       </c>
       <c r="R58" t="n">
-        <v>6782327</v>
+        <v>6782308</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6466,19 +6453,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>11:10</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6493,22 +6470,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129032889</v>
+        <v>129011375</v>
       </c>
       <c r="B59" t="n">
-        <v>79034</v>
+        <v>78791</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6516,21 +6493,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6540,10 +6517,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>409164</v>
+        <v>409335</v>
       </c>
       <c r="R59" t="n">
-        <v>6782308</v>
+        <v>6782352</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6573,9 +6550,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6590,22 +6577,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129011375</v>
+        <v>129032403</v>
       </c>
       <c r="B60" t="n">
-        <v>78791</v>
+        <v>79034</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6613,21 +6600,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6637,10 +6624,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>409335</v>
+        <v>409021</v>
       </c>
       <c r="R60" t="n">
-        <v>6782352</v>
+        <v>6782365</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6670,19 +6657,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>14:40</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>14:40</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6697,22 +6674,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129032403</v>
+        <v>129011373</v>
       </c>
       <c r="B61" t="n">
-        <v>79034</v>
+        <v>91540</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6720,34 +6697,41 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>409021</v>
+        <v>409435</v>
       </c>
       <c r="R61" t="n">
-        <v>6782365</v>
+        <v>6782383</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6777,29 +6761,45 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>4 st på samma tall</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -7515,10 +7515,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129032874</v>
+        <v>129032867</v>
       </c>
       <c r="B69" t="n">
-        <v>91538</v>
+        <v>57723</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7526,21 +7526,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7550,10 +7550,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>409405</v>
+        <v>409693</v>
       </c>
       <c r="R69" t="n">
-        <v>6782366</v>
+        <v>6782357</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7612,7 +7612,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129032867</v>
+        <v>129032396</v>
       </c>
       <c r="B70" t="n">
         <v>57723</v>
@@ -7641,16 +7641,24 @@
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>409693</v>
+        <v>409753</v>
       </c>
       <c r="R70" t="n">
-        <v>6782357</v>
+        <v>6782323</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7697,22 +7705,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129032396</v>
+        <v>129032874</v>
       </c>
       <c r="B71" t="n">
-        <v>57723</v>
+        <v>91538</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7720,42 +7728,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>409753</v>
+        <v>409405</v>
       </c>
       <c r="R71" t="n">
-        <v>6782323</v>
+        <v>6782366</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7802,12 +7802,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>

--- a/artfynd/A 47938-2025 artfynd.xlsx
+++ b/artfynd/A 47938-2025 artfynd.xlsx
@@ -1180,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129032907</v>
+        <v>129032394</v>
       </c>
       <c r="B7" t="n">
-        <v>79034</v>
+        <v>79624</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>409686</v>
+        <v>409553</v>
       </c>
       <c r="R7" t="n">
-        <v>6782351</v>
+        <v>6782378</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1265,19 +1265,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129011389</v>
+        <v>129032907</v>
       </c>
       <c r="B8" t="n">
         <v>79034</v>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>409278</v>
+        <v>409686</v>
       </c>
       <c r="R8" t="n">
-        <v>6782361</v>
+        <v>6782351</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1345,19 +1345,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>15:18</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>15:18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1372,19 +1362,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129032919</v>
+        <v>129011389</v>
       </c>
       <c r="B9" t="n">
         <v>79034</v>
@@ -1419,10 +1409,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>409358</v>
+        <v>409278</v>
       </c>
       <c r="R9" t="n">
-        <v>6782291</v>
+        <v>6782361</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1452,9 +1442,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1469,22 +1469,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129032394</v>
+        <v>129032919</v>
       </c>
       <c r="B10" t="n">
-        <v>79624</v>
+        <v>79034</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1492,21 +1492,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>409553</v>
+        <v>409358</v>
       </c>
       <c r="R10" t="n">
-        <v>6782378</v>
+        <v>6782291</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1566,12 +1566,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1785,7 +1785,7 @@
         <v>129032398</v>
       </c>
       <c r="B13" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1879,10 +1879,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129011378</v>
+        <v>129032392</v>
       </c>
       <c r="B14" t="n">
-        <v>79034</v>
+        <v>79653</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1890,21 +1890,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1914,10 +1914,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>408984</v>
+        <v>409554</v>
       </c>
       <c r="R14" t="n">
-        <v>6782347</v>
+        <v>6782380</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1947,19 +1947,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>16:10</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>16:10</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1974,22 +1964,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129032392</v>
+        <v>129011378</v>
       </c>
       <c r="B15" t="n">
-        <v>79653</v>
+        <v>79034</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1997,21 +1987,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2021,10 +2011,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>409554</v>
+        <v>408984</v>
       </c>
       <c r="R15" t="n">
-        <v>6782380</v>
+        <v>6782347</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2054,9 +2044,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2071,12 +2071,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2280,7 +2280,7 @@
         <v>129011376</v>
       </c>
       <c r="B18" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2384,10 +2384,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129032868</v>
+        <v>129032885</v>
       </c>
       <c r="B19" t="n">
-        <v>57723</v>
+        <v>79034</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2395,21 +2395,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2419,10 +2419,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>409688</v>
+        <v>409078</v>
       </c>
       <c r="R19" t="n">
-        <v>6782303</v>
+        <v>6782312</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2481,7 +2481,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129032885</v>
+        <v>129011400</v>
       </c>
       <c r="B20" t="n">
         <v>79034</v>
@@ -2516,10 +2516,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>409078</v>
+        <v>409643</v>
       </c>
       <c r="R20" t="n">
-        <v>6782312</v>
+        <v>6782378</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2549,9 +2549,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2566,19 +2576,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129011400</v>
+        <v>129032892</v>
       </c>
       <c r="B21" t="n">
         <v>79034</v>
@@ -2613,10 +2623,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>409643</v>
+        <v>409244</v>
       </c>
       <c r="R21" t="n">
-        <v>6782378</v>
+        <v>6782381</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2646,19 +2656,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>12:59</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>12:59</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2673,22 +2673,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129032892</v>
+        <v>129032868</v>
       </c>
       <c r="B22" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2696,21 +2696,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2720,10 +2720,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>409244</v>
+        <v>409688</v>
       </c>
       <c r="R22" t="n">
-        <v>6782381</v>
+        <v>6782303</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2785,7 +2785,7 @@
         <v>129032399</v>
       </c>
       <c r="B23" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>129011374</v>
       </c>
       <c r="B24" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2999,10 +2999,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129032395</v>
+        <v>129011383</v>
       </c>
       <c r="B25" t="n">
-        <v>57723</v>
+        <v>79034</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3010,42 +3010,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>409759</v>
+        <v>409028</v>
       </c>
       <c r="R25" t="n">
-        <v>6782358</v>
+        <v>6782350</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3075,9 +3067,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3092,22 +3094,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129032393</v>
+        <v>129011395</v>
       </c>
       <c r="B26" t="n">
-        <v>79624</v>
+        <v>79034</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3115,21 +3117,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3139,10 +3141,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>409554</v>
+        <v>409555</v>
       </c>
       <c r="R26" t="n">
-        <v>6782380</v>
+        <v>6782356</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3172,9 +3174,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3189,19 +3201,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129011383</v>
+        <v>129011407</v>
       </c>
       <c r="B27" t="n">
         <v>79034</v>
@@ -3236,10 +3248,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>409028</v>
+        <v>409795</v>
       </c>
       <c r="R27" t="n">
-        <v>6782350</v>
+        <v>6782327</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3271,7 +3283,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3281,7 +3293,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3308,10 +3320,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129011395</v>
+        <v>129032395</v>
       </c>
       <c r="B28" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3319,34 +3331,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>409555</v>
+        <v>409759</v>
       </c>
       <c r="R28" t="n">
-        <v>6782356</v>
+        <v>6782358</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3376,19 +3396,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>13:17</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>13:17</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3403,22 +3413,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129011407</v>
+        <v>129032393</v>
       </c>
       <c r="B29" t="n">
-        <v>79034</v>
+        <v>79624</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3426,21 +3436,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3450,10 +3460,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>409795</v>
+        <v>409554</v>
       </c>
       <c r="R29" t="n">
-        <v>6782327</v>
+        <v>6782380</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3483,19 +3493,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>11:12</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>11:12</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3510,22 +3510,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129032913</v>
+        <v>129011369</v>
       </c>
       <c r="B30" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3533,34 +3533,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>409757</v>
+        <v>409683</v>
       </c>
       <c r="R30" t="n">
-        <v>6782355</v>
+        <v>6782391</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3590,9 +3598,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3607,19 +3625,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129032406</v>
+        <v>129032913</v>
       </c>
       <c r="B31" t="n">
         <v>79034</v>
@@ -3654,10 +3672,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>409253</v>
+        <v>409757</v>
       </c>
       <c r="R31" t="n">
-        <v>6782372</v>
+        <v>6782355</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3704,19 +3722,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129032882</v>
+        <v>129032406</v>
       </c>
       <c r="B32" t="n">
         <v>79034</v>
@@ -3751,10 +3769,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>408992</v>
+        <v>409253</v>
       </c>
       <c r="R32" t="n">
-        <v>6782394</v>
+        <v>6782372</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3801,19 +3819,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129011391</v>
+        <v>129032882</v>
       </c>
       <c r="B33" t="n">
         <v>79034</v>
@@ -3848,10 +3866,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>409349</v>
+        <v>408992</v>
       </c>
       <c r="R33" t="n">
-        <v>6782383</v>
+        <v>6782394</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3881,19 +3899,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>14:34</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>14:34</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3908,19 +3916,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129032878</v>
+        <v>129011391</v>
       </c>
       <c r="B34" t="n">
         <v>79034</v>
@@ -3955,10 +3963,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>408966</v>
+        <v>409349</v>
       </c>
       <c r="R34" t="n">
-        <v>6782283</v>
+        <v>6782383</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3988,9 +3996,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4005,22 +4023,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129011369</v>
+        <v>129032878</v>
       </c>
       <c r="B35" t="n">
-        <v>57723</v>
+        <v>79034</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4028,42 +4046,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>409683</v>
+        <v>408966</v>
       </c>
       <c r="R35" t="n">
-        <v>6782391</v>
+        <v>6782283</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4093,19 +4103,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>12:56</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>12:56</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4120,12 +4120,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -5647,10 +5647,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129011401</v>
+        <v>129032866</v>
       </c>
       <c r="B51" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5658,21 +5658,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5682,10 +5682,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>409663</v>
+        <v>409757</v>
       </c>
       <c r="R51" t="n">
-        <v>6782385</v>
+        <v>6782386</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5715,19 +5715,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>12:58</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>12:58</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5742,19 +5732,19 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129032899</v>
+        <v>129011401</v>
       </c>
       <c r="B52" t="n">
         <v>79034</v>
@@ -5789,10 +5779,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>409397</v>
+        <v>409663</v>
       </c>
       <c r="R52" t="n">
-        <v>6782272</v>
+        <v>6782385</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5822,9 +5812,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5839,19 +5839,19 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129011386</v>
+        <v>129032899</v>
       </c>
       <c r="B53" t="n">
         <v>79034</v>
@@ -5886,10 +5886,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>409210</v>
+        <v>409397</v>
       </c>
       <c r="R53" t="n">
-        <v>6782365</v>
+        <v>6782272</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5919,19 +5919,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>15:26</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>15:26</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5946,19 +5936,19 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129011409</v>
+        <v>129011386</v>
       </c>
       <c r="B54" t="n">
         <v>79034</v>
@@ -5993,10 +5983,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>409202</v>
+        <v>409210</v>
       </c>
       <c r="R54" t="n">
-        <v>6782367</v>
+        <v>6782365</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6047,7 +6037,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6066,7 +6055,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129011396</v>
+        <v>129011409</v>
       </c>
       <c r="B55" t="n">
         <v>79034</v>
@@ -6101,10 +6090,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>409584</v>
+        <v>409202</v>
       </c>
       <c r="R55" t="n">
-        <v>6782395</v>
+        <v>6782367</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6136,7 +6125,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6146,7 +6135,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6155,6 +6144,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6173,10 +6163,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129032866</v>
+        <v>129011396</v>
       </c>
       <c r="B56" t="n">
-        <v>57723</v>
+        <v>79034</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6184,21 +6174,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6208,10 +6198,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>409757</v>
+        <v>409584</v>
       </c>
       <c r="R56" t="n">
-        <v>6782386</v>
+        <v>6782395</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6241,9 +6231,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6258,22 +6258,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129011372</v>
+        <v>129032889</v>
       </c>
       <c r="B57" t="n">
-        <v>57723</v>
+        <v>79034</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6281,42 +6281,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>409796</v>
+        <v>409164</v>
       </c>
       <c r="R57" t="n">
-        <v>6782327</v>
+        <v>6782308</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6346,19 +6338,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>11:10</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6373,19 +6355,19 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129032889</v>
+        <v>129032403</v>
       </c>
       <c r="B58" t="n">
         <v>79034</v>
@@ -6420,10 +6402,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>409164</v>
+        <v>409021</v>
       </c>
       <c r="R58" t="n">
-        <v>6782308</v>
+        <v>6782365</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6470,12 +6452,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -6589,10 +6571,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129032403</v>
+        <v>129011372</v>
       </c>
       <c r="B60" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6600,34 +6582,42 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>409021</v>
+        <v>409796</v>
       </c>
       <c r="R60" t="n">
-        <v>6782365</v>
+        <v>6782327</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6657,9 +6647,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6674,12 +6674,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -6689,7 +6689,7 @@
         <v>129011373</v>
       </c>
       <c r="B61" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6809,7 +6809,7 @@
         <v>129032400</v>
       </c>
       <c r="B62" t="n">
-        <v>91975</v>
+        <v>91978</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6903,10 +6903,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129011387</v>
+        <v>129032872</v>
       </c>
       <c r="B63" t="n">
-        <v>79034</v>
+        <v>78791</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6914,21 +6914,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6938,10 +6938,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>409232</v>
+        <v>409594</v>
       </c>
       <c r="R63" t="n">
-        <v>6782353</v>
+        <v>6782294</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6971,19 +6971,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>15:22</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>15:22</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6998,22 +6988,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129032872</v>
+        <v>129032396</v>
       </c>
       <c r="B64" t="n">
-        <v>78791</v>
+        <v>57723</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7021,34 +7011,42 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>409594</v>
+        <v>409753</v>
       </c>
       <c r="R64" t="n">
-        <v>6782294</v>
+        <v>6782323</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7095,22 +7093,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129032886</v>
+        <v>129032867</v>
       </c>
       <c r="B65" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7118,21 +7116,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7142,10 +7140,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>409108</v>
+        <v>409693</v>
       </c>
       <c r="R65" t="n">
-        <v>6782395</v>
+        <v>6782357</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7204,10 +7202,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129011384</v>
+        <v>129032874</v>
       </c>
       <c r="B66" t="n">
-        <v>79034</v>
+        <v>91541</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7215,21 +7213,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7239,10 +7237,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>409068</v>
+        <v>409405</v>
       </c>
       <c r="R66" t="n">
-        <v>6782377</v>
+        <v>6782366</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7272,19 +7270,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>15:43</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>15:43</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7299,19 +7287,19 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129011379</v>
+        <v>129011387</v>
       </c>
       <c r="B67" t="n">
         <v>79034</v>
@@ -7346,10 +7334,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>408991</v>
+        <v>409232</v>
       </c>
       <c r="R67" t="n">
-        <v>6782360</v>
+        <v>6782353</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7381,7 +7369,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7391,7 +7379,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7418,7 +7406,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129032914</v>
+        <v>129032886</v>
       </c>
       <c r="B68" t="n">
         <v>79034</v>
@@ -7453,10 +7441,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>409759</v>
+        <v>409108</v>
       </c>
       <c r="R68" t="n">
-        <v>6782343</v>
+        <v>6782395</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7515,10 +7503,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129032867</v>
+        <v>129011384</v>
       </c>
       <c r="B69" t="n">
-        <v>57723</v>
+        <v>79034</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7526,21 +7514,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7550,10 +7538,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>409693</v>
+        <v>409068</v>
       </c>
       <c r="R69" t="n">
-        <v>6782357</v>
+        <v>6782377</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7583,9 +7571,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7600,22 +7598,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129032396</v>
+        <v>129011379</v>
       </c>
       <c r="B70" t="n">
-        <v>57723</v>
+        <v>79034</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7623,42 +7621,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>409753</v>
+        <v>408991</v>
       </c>
       <c r="R70" t="n">
-        <v>6782323</v>
+        <v>6782360</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7688,9 +7678,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7705,22 +7705,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129032874</v>
+        <v>129032914</v>
       </c>
       <c r="B71" t="n">
-        <v>91538</v>
+        <v>79034</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7728,21 +7728,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7752,10 +7752,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>409405</v>
+        <v>409759</v>
       </c>
       <c r="R71" t="n">
-        <v>6782366</v>
+        <v>6782343</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7817,7 +7817,7 @@
         <v>129032873</v>
       </c>
       <c r="B72" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8303,10 +8303,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129032893</v>
+        <v>129032402</v>
       </c>
       <c r="B77" t="n">
-        <v>79034</v>
+        <v>91541</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8314,21 +8314,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8338,10 +8338,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>409280</v>
+        <v>409767</v>
       </c>
       <c r="R77" t="n">
-        <v>6782382</v>
+        <v>6782352</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8388,19 +8388,19 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129011404</v>
+        <v>129032893</v>
       </c>
       <c r="B78" t="n">
         <v>79034</v>
@@ -8435,10 +8435,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>409736</v>
+        <v>409280</v>
       </c>
       <c r="R78" t="n">
-        <v>6782394</v>
+        <v>6782382</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8468,19 +8468,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>11:59</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>11:59</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8495,19 +8485,19 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129032901</v>
+        <v>129011404</v>
       </c>
       <c r="B79" t="n">
         <v>79034</v>
@@ -8542,10 +8532,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>409528</v>
+        <v>409736</v>
       </c>
       <c r="R79" t="n">
-        <v>6782292</v>
+        <v>6782394</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8575,9 +8565,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8592,19 +8592,19 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129032888</v>
+        <v>129032901</v>
       </c>
       <c r="B80" t="n">
         <v>79034</v>
@@ -8639,10 +8639,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>409127</v>
+        <v>409528</v>
       </c>
       <c r="R80" t="n">
-        <v>6782290</v>
+        <v>6782292</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8701,10 +8701,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129032402</v>
+        <v>129032888</v>
       </c>
       <c r="B81" t="n">
-        <v>91538</v>
+        <v>79034</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8712,21 +8712,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8736,10 +8736,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>409767</v>
+        <v>409127</v>
       </c>
       <c r="R81" t="n">
-        <v>6782352</v>
+        <v>6782290</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8786,12 +8786,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
@@ -9186,10 +9186,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129032898</v>
+        <v>129032870</v>
       </c>
       <c r="B86" t="n">
-        <v>79034</v>
+        <v>91543</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9197,31 +9197,42 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>409390</v>
+        <v>409530</v>
       </c>
       <c r="R86" t="n">
         <v>6782289</v>
@@ -9265,6 +9276,7 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9283,10 +9295,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129032918</v>
+        <v>129011370</v>
       </c>
       <c r="B87" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9294,34 +9306,42 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>409363</v>
+        <v>409759</v>
       </c>
       <c r="R87" t="n">
-        <v>6782377</v>
+        <v>6782330</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9351,9 +9371,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9368,22 +9398,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129032870</v>
+        <v>129032898</v>
       </c>
       <c r="B88" t="n">
-        <v>91540</v>
+        <v>79034</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9391,42 +9421,31 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>409530</v>
+        <v>409390</v>
       </c>
       <c r="R88" t="n">
         <v>6782289</v>
@@ -9470,7 +9489,6 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -9489,10 +9507,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129011370</v>
+        <v>129032918</v>
       </c>
       <c r="B89" t="n">
-        <v>57723</v>
+        <v>79034</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9500,42 +9518,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>409759</v>
+        <v>409363</v>
       </c>
       <c r="R89" t="n">
-        <v>6782330</v>
+        <v>6782377</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9565,19 +9575,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>11:48</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9592,12 +9592,12 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
@@ -10808,10 +10808,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129011377</v>
+        <v>129032401</v>
       </c>
       <c r="B102" t="n">
-        <v>79034</v>
+        <v>91541</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10819,21 +10819,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10843,10 +10843,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>408995</v>
+        <v>409226</v>
       </c>
       <c r="R102" t="n">
-        <v>6782299</v>
+        <v>6782376</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10876,19 +10876,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z102" t="inlineStr">
-        <is>
-          <t>16:13</t>
-        </is>
-      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB102" t="inlineStr">
-        <is>
-          <t>16:13</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10903,19 +10893,19 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129011402</v>
+        <v>129011377</v>
       </c>
       <c r="B103" t="n">
         <v>79034</v>
@@ -10950,10 +10940,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>409671</v>
+        <v>408995</v>
       </c>
       <c r="R103" t="n">
-        <v>6782390</v>
+        <v>6782299</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10985,7 +10975,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -10995,7 +10985,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11022,7 +11012,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129011385</v>
+        <v>129011402</v>
       </c>
       <c r="B104" t="n">
         <v>79034</v>
@@ -11057,10 +11047,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>409214</v>
+        <v>409671</v>
       </c>
       <c r="R104" t="n">
-        <v>6782345</v>
+        <v>6782390</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11092,7 +11082,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11102,7 +11092,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11129,7 +11119,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129032877</v>
+        <v>129011385</v>
       </c>
       <c r="B105" t="n">
         <v>79034</v>
@@ -11164,10 +11154,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>408994</v>
+        <v>409214</v>
       </c>
       <c r="R105" t="n">
-        <v>6782293</v>
+        <v>6782345</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11197,9 +11187,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11214,19 +11214,19 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129032904</v>
+        <v>129032877</v>
       </c>
       <c r="B106" t="n">
         <v>79034</v>
@@ -11261,10 +11261,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>409568</v>
+        <v>408994</v>
       </c>
       <c r="R106" t="n">
-        <v>6782383</v>
+        <v>6782293</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11323,7 +11323,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129032915</v>
+        <v>129032904</v>
       </c>
       <c r="B107" t="n">
         <v>79034</v>
@@ -11358,10 +11358,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>409765</v>
+        <v>409568</v>
       </c>
       <c r="R107" t="n">
-        <v>6782330</v>
+        <v>6782383</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11420,10 +11420,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129032401</v>
+        <v>129032915</v>
       </c>
       <c r="B108" t="n">
-        <v>91538</v>
+        <v>79034</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11431,21 +11431,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11455,10 +11455,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>409226</v>
+        <v>409765</v>
       </c>
       <c r="R108" t="n">
-        <v>6782376</v>
+        <v>6782330</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11505,12 +11505,12 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>

--- a/artfynd/A 47938-2025 artfynd.xlsx
+++ b/artfynd/A 47938-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129032920</v>
+        <v>129011403</v>
       </c>
       <c r="B2" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>409793</v>
+        <v>409706</v>
       </c>
       <c r="R2" t="n">
-        <v>6782448</v>
+        <v>6782359</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -743,9 +743,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -760,22 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129011405</v>
+        <v>129032920</v>
       </c>
       <c r="B3" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>409747</v>
+        <v>409793</v>
       </c>
       <c r="R3" t="n">
-        <v>6782328</v>
+        <v>6782448</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -840,19 +850,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>11:47</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:47</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,22 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129032876</v>
+        <v>129011405</v>
       </c>
       <c r="B4" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>408997</v>
+        <v>409747</v>
       </c>
       <c r="R4" t="n">
-        <v>6782283</v>
+        <v>6782328</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -947,9 +947,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -964,22 +974,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129011403</v>
+        <v>129032876</v>
       </c>
       <c r="B5" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1011,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>409706</v>
+        <v>408997</v>
       </c>
       <c r="R5" t="n">
-        <v>6782359</v>
+        <v>6782283</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1044,19 +1054,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>12:06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,12 +1071,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1086,7 +1086,7 @@
         <v>129032905</v>
       </c>
       <c r="B6" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>129032394</v>
       </c>
       <c r="B7" t="n">
-        <v>79624</v>
+        <v>79625</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>129032907</v>
       </c>
       <c r="B8" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1377,7 +1377,7 @@
         <v>129011389</v>
       </c>
       <c r="B9" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>129032919</v>
       </c>
       <c r="B10" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>129011398</v>
       </c>
       <c r="B11" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1685,10 +1685,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129032894</v>
+        <v>129032398</v>
       </c>
       <c r="B12" t="n">
-        <v>79034</v>
+        <v>91546</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1696,21 +1696,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1720,10 +1720,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>409292</v>
+        <v>409482</v>
       </c>
       <c r="R12" t="n">
-        <v>6782306</v>
+        <v>6782335</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1770,22 +1770,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129032398</v>
+        <v>129032894</v>
       </c>
       <c r="B13" t="n">
-        <v>91543</v>
+        <v>79035</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1793,21 +1793,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1817,10 +1817,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>409482</v>
+        <v>409292</v>
       </c>
       <c r="R13" t="n">
-        <v>6782335</v>
+        <v>6782306</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1867,22 +1867,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129032392</v>
+        <v>129011378</v>
       </c>
       <c r="B14" t="n">
-        <v>79653</v>
+        <v>79035</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1890,21 +1890,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1914,10 +1914,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>409554</v>
+        <v>408984</v>
       </c>
       <c r="R14" t="n">
-        <v>6782380</v>
+        <v>6782347</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1947,9 +1947,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1964,22 +1974,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129011378</v>
+        <v>129032909</v>
       </c>
       <c r="B15" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2011,10 +2021,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>408984</v>
+        <v>409727</v>
       </c>
       <c r="R15" t="n">
-        <v>6782347</v>
+        <v>6782352</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2044,19 +2054,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>16:10</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>16:10</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2071,22 +2071,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129032897</v>
+        <v>129032392</v>
       </c>
       <c r="B16" t="n">
-        <v>79034</v>
+        <v>79654</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2094,21 +2094,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2118,10 +2118,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>409469</v>
+        <v>409554</v>
       </c>
       <c r="R16" t="n">
-        <v>6782371</v>
+        <v>6782380</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2168,22 +2168,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129032909</v>
+        <v>129032897</v>
       </c>
       <c r="B17" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>409727</v>
+        <v>409469</v>
       </c>
       <c r="R17" t="n">
-        <v>6782352</v>
+        <v>6782371</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2277,10 +2277,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129011376</v>
+        <v>129032885</v>
       </c>
       <c r="B18" t="n">
-        <v>91541</v>
+        <v>79035</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2288,21 +2288,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2312,10 +2312,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>409774</v>
+        <v>409078</v>
       </c>
       <c r="R18" t="n">
-        <v>6782323</v>
+        <v>6782312</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2345,19 +2345,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>11:31</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>11:31</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2372,22 +2362,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129032885</v>
+        <v>129032892</v>
       </c>
       <c r="B19" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2419,10 +2409,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>409078</v>
+        <v>409244</v>
       </c>
       <c r="R19" t="n">
-        <v>6782312</v>
+        <v>6782381</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2484,7 +2474,7 @@
         <v>129011400</v>
       </c>
       <c r="B20" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2588,10 +2578,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129032892</v>
+        <v>129011376</v>
       </c>
       <c r="B21" t="n">
-        <v>79034</v>
+        <v>91544</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2599,21 +2589,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2623,10 +2613,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>409244</v>
+        <v>409774</v>
       </c>
       <c r="R21" t="n">
-        <v>6782381</v>
+        <v>6782323</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2656,9 +2646,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2673,12 +2673,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2785,7 +2785,7 @@
         <v>129032399</v>
       </c>
       <c r="B23" t="n">
-        <v>91543</v>
+        <v>91546</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>129011374</v>
       </c>
       <c r="B24" t="n">
-        <v>91543</v>
+        <v>91546</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2999,10 +2999,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129011383</v>
+        <v>129011395</v>
       </c>
       <c r="B25" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3034,10 +3034,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>409028</v>
+        <v>409555</v>
       </c>
       <c r="R25" t="n">
-        <v>6782350</v>
+        <v>6782356</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3069,7 +3069,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3106,10 +3106,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129011395</v>
+        <v>129011407</v>
       </c>
       <c r="B26" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3141,10 +3141,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>409555</v>
+        <v>409795</v>
       </c>
       <c r="R26" t="n">
-        <v>6782356</v>
+        <v>6782327</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3176,7 +3176,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3213,10 +3213,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129011407</v>
+        <v>129011383</v>
       </c>
       <c r="B27" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3248,10 +3248,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>409795</v>
+        <v>409028</v>
       </c>
       <c r="R27" t="n">
-        <v>6782327</v>
+        <v>6782350</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3283,7 +3283,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3293,7 +3293,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3428,7 +3428,7 @@
         <v>129032393</v>
       </c>
       <c r="B29" t="n">
-        <v>79624</v>
+        <v>79625</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3522,10 +3522,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129011369</v>
+        <v>129011391</v>
       </c>
       <c r="B30" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3533,42 +3533,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>409683</v>
+        <v>409349</v>
       </c>
       <c r="R30" t="n">
-        <v>6782391</v>
+        <v>6782383</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3600,7 +3592,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3610,7 +3602,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3640,7 +3632,7 @@
         <v>129032913</v>
       </c>
       <c r="B31" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3737,7 +3729,7 @@
         <v>129032406</v>
       </c>
       <c r="B32" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3834,7 +3826,7 @@
         <v>129032882</v>
       </c>
       <c r="B33" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3928,10 +3920,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129011391</v>
+        <v>129032878</v>
       </c>
       <c r="B34" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3963,10 +3955,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>409349</v>
+        <v>408966</v>
       </c>
       <c r="R34" t="n">
-        <v>6782383</v>
+        <v>6782283</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3996,19 +3988,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>14:34</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>14:34</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4023,22 +4005,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129032878</v>
+        <v>129011369</v>
       </c>
       <c r="B35" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4046,34 +4028,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>408966</v>
+        <v>409683</v>
       </c>
       <c r="R35" t="n">
-        <v>6782283</v>
+        <v>6782391</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4103,9 +4093,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4120,22 +4120,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129032887</v>
+        <v>129011381</v>
       </c>
       <c r="B36" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4167,10 +4167,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>409176</v>
+        <v>409010</v>
       </c>
       <c r="R36" t="n">
-        <v>6782420</v>
+        <v>6782383</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4200,9 +4200,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4217,22 +4227,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129011381</v>
+        <v>129032887</v>
       </c>
       <c r="B37" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4264,10 +4274,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>409010</v>
+        <v>409176</v>
       </c>
       <c r="R37" t="n">
-        <v>6782383</v>
+        <v>6782420</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4297,19 +4307,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>16:06</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>16:06</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4324,22 +4324,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129032891</v>
+        <v>129011392</v>
       </c>
       <c r="B38" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4371,10 +4371,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>409241</v>
+        <v>409361</v>
       </c>
       <c r="R38" t="n">
-        <v>6782372</v>
+        <v>6782401</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4404,9 +4404,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4421,22 +4431,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129011392</v>
+        <v>129032906</v>
       </c>
       <c r="B39" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4468,10 +4478,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>409361</v>
+        <v>409684</v>
       </c>
       <c r="R39" t="n">
-        <v>6782401</v>
+        <v>6782322</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4501,19 +4511,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>14:31</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>14:31</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4528,22 +4528,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129032911</v>
+        <v>129032891</v>
       </c>
       <c r="B40" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4575,10 +4575,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>409777</v>
+        <v>409241</v>
       </c>
       <c r="R40" t="n">
-        <v>6782445</v>
+        <v>6782372</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4637,10 +4637,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129032906</v>
+        <v>129032911</v>
       </c>
       <c r="B41" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4672,10 +4672,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>409684</v>
+        <v>409777</v>
       </c>
       <c r="R41" t="n">
-        <v>6782322</v>
+        <v>6782445</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4737,7 +4737,7 @@
         <v>129032407</v>
       </c>
       <c r="B42" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4834,7 +4834,7 @@
         <v>129032910</v>
       </c>
       <c r="B43" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         <v>129011394</v>
       </c>
       <c r="B44" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5038,7 +5038,7 @@
         <v>129011399</v>
       </c>
       <c r="B45" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5145,7 +5145,7 @@
         <v>129011408</v>
       </c>
       <c r="B46" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5249,10 +5249,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129032883</v>
+        <v>129032884</v>
       </c>
       <c r="B47" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5284,10 +5284,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>409010</v>
+        <v>409039</v>
       </c>
       <c r="R47" t="n">
-        <v>6782399</v>
+        <v>6782290</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5346,10 +5346,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129011380</v>
+        <v>129032883</v>
       </c>
       <c r="B48" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5381,10 +5381,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>408984</v>
+        <v>409010</v>
       </c>
       <c r="R48" t="n">
-        <v>6782385</v>
+        <v>6782399</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5414,19 +5414,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>16:07</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>16:07</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5441,22 +5431,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129032884</v>
+        <v>129011380</v>
       </c>
       <c r="B49" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5488,10 +5478,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>409039</v>
+        <v>408984</v>
       </c>
       <c r="R49" t="n">
-        <v>6782290</v>
+        <v>6782385</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5521,9 +5511,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5538,12 +5538,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -5647,10 +5647,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129032866</v>
+        <v>129011409</v>
       </c>
       <c r="B51" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5658,21 +5658,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5682,10 +5682,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>409757</v>
+        <v>409202</v>
       </c>
       <c r="R51" t="n">
-        <v>6782386</v>
+        <v>6782367</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5715,29 +5715,40 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -5747,7 +5758,7 @@
         <v>129011401</v>
       </c>
       <c r="B52" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5854,7 +5865,7 @@
         <v>129032899</v>
       </c>
       <c r="B53" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5948,10 +5959,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129011386</v>
+        <v>129011396</v>
       </c>
       <c r="B54" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5983,10 +5994,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>409210</v>
+        <v>409584</v>
       </c>
       <c r="R54" t="n">
-        <v>6782365</v>
+        <v>6782395</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6018,7 +6029,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6028,7 +6039,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6055,10 +6066,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129011409</v>
+        <v>129011386</v>
       </c>
       <c r="B55" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6090,10 +6101,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>409202</v>
+        <v>409210</v>
       </c>
       <c r="R55" t="n">
-        <v>6782367</v>
+        <v>6782365</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6144,7 +6155,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6163,10 +6173,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129011396</v>
+        <v>129032866</v>
       </c>
       <c r="B56" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6174,21 +6184,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6198,10 +6208,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>409584</v>
+        <v>409757</v>
       </c>
       <c r="R56" t="n">
-        <v>6782395</v>
+        <v>6782386</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6231,19 +6241,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>13:11</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>13:11</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6258,12 +6258,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -6273,7 +6273,7 @@
         <v>129032889</v>
       </c>
       <c r="B57" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6367,10 +6367,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129032403</v>
+        <v>129011375</v>
       </c>
       <c r="B58" t="n">
-        <v>79034</v>
+        <v>78792</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6378,21 +6378,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6402,10 +6402,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>409021</v>
+        <v>409335</v>
       </c>
       <c r="R58" t="n">
-        <v>6782365</v>
+        <v>6782352</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6435,9 +6435,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6452,22 +6462,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129011375</v>
+        <v>129032403</v>
       </c>
       <c r="B59" t="n">
-        <v>78791</v>
+        <v>79035</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6475,21 +6485,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6499,10 +6509,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>409335</v>
+        <v>409021</v>
       </c>
       <c r="R59" t="n">
-        <v>6782352</v>
+        <v>6782365</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6532,19 +6542,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>14:40</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>14:40</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6559,22 +6559,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129011372</v>
+        <v>129011373</v>
       </c>
       <c r="B60" t="n">
-        <v>57723</v>
+        <v>91546</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6582,31 +6582,30 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -6614,10 +6613,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>409796</v>
+        <v>409435</v>
       </c>
       <c r="R60" t="n">
-        <v>6782327</v>
+        <v>6782383</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6649,7 +6648,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6659,7 +6658,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>4 st på samma tall</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6668,6 +6672,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6686,10 +6691,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129011373</v>
+        <v>129011372</v>
       </c>
       <c r="B61" t="n">
-        <v>91543</v>
+        <v>57723</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6697,30 +6702,31 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -6728,10 +6734,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>409435</v>
+        <v>409796</v>
       </c>
       <c r="R61" t="n">
-        <v>6782383</v>
+        <v>6782327</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6763,7 +6769,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -6773,12 +6779,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:14</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>4 st på samma tall</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6787,7 +6788,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6809,7 +6809,7 @@
         <v>129032400</v>
       </c>
       <c r="B62" t="n">
-        <v>91978</v>
+        <v>91981</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6903,10 +6903,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129032872</v>
+        <v>129032874</v>
       </c>
       <c r="B63" t="n">
-        <v>78791</v>
+        <v>91544</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6914,21 +6914,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6446</v>
+        <v>5432</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6938,10 +6938,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>409594</v>
+        <v>409405</v>
       </c>
       <c r="R63" t="n">
-        <v>6782294</v>
+        <v>6782366</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7000,10 +7000,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129032396</v>
+        <v>129011387</v>
       </c>
       <c r="B64" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7011,42 +7011,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>409753</v>
+        <v>409232</v>
       </c>
       <c r="R64" t="n">
-        <v>6782323</v>
+        <v>6782353</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7076,9 +7068,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7093,22 +7095,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129032867</v>
+        <v>129032872</v>
       </c>
       <c r="B65" t="n">
-        <v>57723</v>
+        <v>78792</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7116,21 +7118,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7140,10 +7142,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>409693</v>
+        <v>409594</v>
       </c>
       <c r="R65" t="n">
-        <v>6782357</v>
+        <v>6782294</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7202,10 +7204,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129032874</v>
+        <v>129032914</v>
       </c>
       <c r="B66" t="n">
-        <v>91541</v>
+        <v>79035</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7213,21 +7215,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7237,10 +7239,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>409405</v>
+        <v>409759</v>
       </c>
       <c r="R66" t="n">
-        <v>6782366</v>
+        <v>6782343</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7299,10 +7301,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129011387</v>
+        <v>129032396</v>
       </c>
       <c r="B67" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7310,34 +7312,42 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>409232</v>
+        <v>409753</v>
       </c>
       <c r="R67" t="n">
-        <v>6782353</v>
+        <v>6782323</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7367,19 +7377,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>15:22</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>15:22</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7394,22 +7394,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129032886</v>
+        <v>129032867</v>
       </c>
       <c r="B68" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7417,21 +7417,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7441,10 +7441,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>409108</v>
+        <v>409693</v>
       </c>
       <c r="R68" t="n">
-        <v>6782395</v>
+        <v>6782357</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7503,10 +7503,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129011384</v>
+        <v>129032886</v>
       </c>
       <c r="B69" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7538,10 +7538,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>409068</v>
+        <v>409108</v>
       </c>
       <c r="R69" t="n">
-        <v>6782377</v>
+        <v>6782395</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7571,19 +7571,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>15:43</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>15:43</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7598,22 +7588,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129011379</v>
+        <v>129011384</v>
       </c>
       <c r="B70" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7645,10 +7635,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>408991</v>
+        <v>409068</v>
       </c>
       <c r="R70" t="n">
-        <v>6782360</v>
+        <v>6782377</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7680,7 +7670,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -7690,7 +7680,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7717,10 +7707,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129032914</v>
+        <v>129011379</v>
       </c>
       <c r="B71" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7752,10 +7742,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>409759</v>
+        <v>408991</v>
       </c>
       <c r="R71" t="n">
-        <v>6782343</v>
+        <v>6782360</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7785,9 +7775,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7802,22 +7802,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129032873</v>
+        <v>129032902</v>
       </c>
       <c r="B72" t="n">
-        <v>91523</v>
+        <v>79035</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7825,37 +7825,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>409075</v>
+        <v>409549</v>
       </c>
       <c r="R72" t="n">
-        <v>6782317</v>
+        <v>6782286</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7896,7 +7893,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -7915,10 +7911,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129032896</v>
+        <v>129032917</v>
       </c>
       <c r="B73" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7950,10 +7946,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>409331</v>
+        <v>409360</v>
       </c>
       <c r="R73" t="n">
-        <v>6782342</v>
+        <v>6782355</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8012,10 +8008,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129032902</v>
+        <v>129032900</v>
       </c>
       <c r="B74" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8047,7 +8043,7 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>409549</v>
+        <v>409449</v>
       </c>
       <c r="R74" t="n">
         <v>6782286</v>
@@ -8109,10 +8105,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129032917</v>
+        <v>129032873</v>
       </c>
       <c r="B75" t="n">
-        <v>79034</v>
+        <v>91526</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8120,34 +8116,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>409360</v>
+        <v>409075</v>
       </c>
       <c r="R75" t="n">
-        <v>6782355</v>
+        <v>6782317</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8188,6 +8187,7 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8206,10 +8206,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129032900</v>
+        <v>129032896</v>
       </c>
       <c r="B76" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8241,10 +8241,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>409449</v>
+        <v>409331</v>
       </c>
       <c r="R76" t="n">
-        <v>6782286</v>
+        <v>6782342</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8306,7 +8306,7 @@
         <v>129032402</v>
       </c>
       <c r="B77" t="n">
-        <v>91541</v>
+        <v>91544</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8403,7 +8403,7 @@
         <v>129032893</v>
       </c>
       <c r="B78" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8500,7 +8500,7 @@
         <v>129011404</v>
       </c>
       <c r="B79" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8604,10 +8604,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129032901</v>
+        <v>129032888</v>
       </c>
       <c r="B80" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8639,10 +8639,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>409528</v>
+        <v>409127</v>
       </c>
       <c r="R80" t="n">
-        <v>6782292</v>
+        <v>6782290</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8701,10 +8701,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129032888</v>
+        <v>129032901</v>
       </c>
       <c r="B81" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8736,10 +8736,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>409127</v>
+        <v>409528</v>
       </c>
       <c r="R81" t="n">
-        <v>6782290</v>
+        <v>6782292</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8798,10 +8798,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129032908</v>
+        <v>129032879</v>
       </c>
       <c r="B82" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8833,10 +8833,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>409715</v>
+        <v>408909</v>
       </c>
       <c r="R82" t="n">
-        <v>6782363</v>
+        <v>6782332</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8895,10 +8895,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129032879</v>
+        <v>129032916</v>
       </c>
       <c r="B83" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8930,10 +8930,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>408909</v>
+        <v>409812</v>
       </c>
       <c r="R83" t="n">
-        <v>6782332</v>
+        <v>6782309</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8992,10 +8992,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129032409</v>
+        <v>129032908</v>
       </c>
       <c r="B84" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9027,10 +9027,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>409782</v>
+        <v>409715</v>
       </c>
       <c r="R84" t="n">
-        <v>6782339</v>
+        <v>6782363</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9077,22 +9077,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129032916</v>
+        <v>129032409</v>
       </c>
       <c r="B85" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9124,10 +9124,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>409812</v>
+        <v>409782</v>
       </c>
       <c r="R85" t="n">
-        <v>6782309</v>
+        <v>6782339</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9174,22 +9174,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129032870</v>
+        <v>129032898</v>
       </c>
       <c r="B86" t="n">
-        <v>91543</v>
+        <v>79035</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9197,42 +9197,31 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>409530</v>
+        <v>409390</v>
       </c>
       <c r="R86" t="n">
         <v>6782289</v>
@@ -9276,7 +9265,6 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9295,10 +9283,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129011370</v>
+        <v>129032918</v>
       </c>
       <c r="B87" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9306,42 +9294,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>409759</v>
+        <v>409363</v>
       </c>
       <c r="R87" t="n">
-        <v>6782330</v>
+        <v>6782377</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9371,19 +9351,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>11:48</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9398,22 +9368,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129032898</v>
+        <v>129032870</v>
       </c>
       <c r="B88" t="n">
-        <v>79034</v>
+        <v>91546</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9421,31 +9391,42 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>409390</v>
+        <v>409530</v>
       </c>
       <c r="R88" t="n">
         <v>6782289</v>
@@ -9489,6 +9470,7 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -9507,10 +9489,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129032918</v>
+        <v>129011370</v>
       </c>
       <c r="B89" t="n">
-        <v>79034</v>
+        <v>57723</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9518,34 +9500,42 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>409363</v>
+        <v>409759</v>
       </c>
       <c r="R89" t="n">
-        <v>6782377</v>
+        <v>6782330</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9575,9 +9565,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9592,12 +9592,12 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
@@ -9607,7 +9607,7 @@
         <v>129011393</v>
       </c>
       <c r="B90" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9714,7 +9714,7 @@
         <v>129032895</v>
       </c>
       <c r="B91" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9811,7 +9811,7 @@
         <v>129032903</v>
       </c>
       <c r="B92" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9908,7 +9908,7 @@
         <v>129032880</v>
       </c>
       <c r="B93" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10005,7 +10005,7 @@
         <v>129032405</v>
       </c>
       <c r="B94" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10102,7 +10102,7 @@
         <v>129011388</v>
       </c>
       <c r="B95" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10206,10 +10206,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129011406</v>
+        <v>129032408</v>
       </c>
       <c r="B96" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10241,10 +10241,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>409759</v>
+        <v>409749</v>
       </c>
       <c r="R96" t="n">
-        <v>6782314</v>
+        <v>6782325</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10274,19 +10274,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z96" t="inlineStr">
-        <is>
-          <t>11:41</t>
-        </is>
-      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB96" t="inlineStr">
-        <is>
-          <t>11:41</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10301,22 +10291,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129032408</v>
+        <v>129032912</v>
       </c>
       <c r="B97" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10348,10 +10338,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>409749</v>
+        <v>409762</v>
       </c>
       <c r="R97" t="n">
-        <v>6782325</v>
+        <v>6782335</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10398,22 +10388,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129032912</v>
+        <v>129032875</v>
       </c>
       <c r="B98" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10445,10 +10435,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>409762</v>
+        <v>409034</v>
       </c>
       <c r="R98" t="n">
-        <v>6782335</v>
+        <v>6782261</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10507,10 +10497,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129032890</v>
+        <v>129011390</v>
       </c>
       <c r="B99" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10542,10 +10532,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>409228</v>
+        <v>409349</v>
       </c>
       <c r="R99" t="n">
-        <v>6782298</v>
+        <v>6782376</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10575,9 +10565,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10592,22 +10592,22 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129032875</v>
+        <v>129011406</v>
       </c>
       <c r="B100" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10639,10 +10639,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>409034</v>
+        <v>409759</v>
       </c>
       <c r="R100" t="n">
-        <v>6782261</v>
+        <v>6782314</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10672,9 +10672,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10689,22 +10699,22 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129011390</v>
+        <v>129032890</v>
       </c>
       <c r="B101" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10736,10 +10746,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>409349</v>
+        <v>409228</v>
       </c>
       <c r="R101" t="n">
-        <v>6782376</v>
+        <v>6782298</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10769,19 +10779,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z101" t="inlineStr">
-        <is>
-          <t>14:34</t>
-        </is>
-      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB101" t="inlineStr">
-        <is>
-          <t>14:34</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10796,22 +10796,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129032401</v>
+        <v>129011385</v>
       </c>
       <c r="B102" t="n">
-        <v>91541</v>
+        <v>79035</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10819,21 +10819,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10843,10 +10843,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>409226</v>
+        <v>409214</v>
       </c>
       <c r="R102" t="n">
-        <v>6782376</v>
+        <v>6782345</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10876,9 +10876,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10893,22 +10903,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129011377</v>
+        <v>129032904</v>
       </c>
       <c r="B103" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10940,10 +10950,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>408995</v>
+        <v>409568</v>
       </c>
       <c r="R103" t="n">
-        <v>6782299</v>
+        <v>6782383</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10973,19 +10983,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z103" t="inlineStr">
-        <is>
-          <t>16:13</t>
-        </is>
-      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB103" t="inlineStr">
-        <is>
-          <t>16:13</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11000,22 +11000,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129011402</v>
+        <v>129032915</v>
       </c>
       <c r="B104" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11047,10 +11047,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>409671</v>
+        <v>409765</v>
       </c>
       <c r="R104" t="n">
-        <v>6782390</v>
+        <v>6782330</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11080,19 +11080,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z104" t="inlineStr">
-        <is>
-          <t>12:57</t>
-        </is>
-      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB104" t="inlineStr">
-        <is>
-          <t>12:57</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11107,22 +11097,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129011385</v>
+        <v>129011377</v>
       </c>
       <c r="B105" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11154,10 +11144,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>409214</v>
+        <v>408995</v>
       </c>
       <c r="R105" t="n">
-        <v>6782345</v>
+        <v>6782299</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11189,7 +11179,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11199,7 +11189,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11226,10 +11216,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129032877</v>
+        <v>129011402</v>
       </c>
       <c r="B106" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11261,10 +11251,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>408994</v>
+        <v>409671</v>
       </c>
       <c r="R106" t="n">
-        <v>6782293</v>
+        <v>6782390</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11294,9 +11284,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11311,22 +11311,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129032904</v>
+        <v>129032877</v>
       </c>
       <c r="B107" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11358,10 +11358,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>409568</v>
+        <v>408994</v>
       </c>
       <c r="R107" t="n">
-        <v>6782383</v>
+        <v>6782293</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11420,10 +11420,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129032915</v>
+        <v>129032401</v>
       </c>
       <c r="B108" t="n">
-        <v>79034</v>
+        <v>91544</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11431,21 +11431,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11455,10 +11455,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>409765</v>
+        <v>409226</v>
       </c>
       <c r="R108" t="n">
-        <v>6782330</v>
+        <v>6782376</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11505,12 +11505,12 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>

--- a/artfynd/A 47938-2025 artfynd.xlsx
+++ b/artfynd/A 47938-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129011403</v>
+        <v>129032920</v>
       </c>
       <c r="B2" t="n">
         <v>79035</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>409706</v>
+        <v>409793</v>
       </c>
       <c r="R2" t="n">
-        <v>6782359</v>
+        <v>6782448</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -743,19 +743,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>12:06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,19 +760,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129032920</v>
+        <v>129011405</v>
       </c>
       <c r="B3" t="n">
         <v>79035</v>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>409793</v>
+        <v>409747</v>
       </c>
       <c r="R3" t="n">
-        <v>6782448</v>
+        <v>6782328</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -850,9 +840,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,19 +867,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129011405</v>
+        <v>129032876</v>
       </c>
       <c r="B4" t="n">
         <v>79035</v>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>409747</v>
+        <v>408997</v>
       </c>
       <c r="R4" t="n">
-        <v>6782328</v>
+        <v>6782283</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -947,19 +947,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>11:47</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>11:47</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -974,19 +964,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129032876</v>
+        <v>129011403</v>
       </c>
       <c r="B5" t="n">
         <v>79035</v>
@@ -1021,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>408997</v>
+        <v>409706</v>
       </c>
       <c r="R5" t="n">
-        <v>6782283</v>
+        <v>6782359</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1054,9 +1044,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,12 +1071,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1180,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129032394</v>
+        <v>129032907</v>
       </c>
       <c r="B7" t="n">
-        <v>79625</v>
+        <v>79035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>409553</v>
+        <v>409686</v>
       </c>
       <c r="R7" t="n">
-        <v>6782378</v>
+        <v>6782351</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1265,19 +1265,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129032907</v>
+        <v>129011389</v>
       </c>
       <c r="B8" t="n">
         <v>79035</v>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>409686</v>
+        <v>409278</v>
       </c>
       <c r="R8" t="n">
-        <v>6782351</v>
+        <v>6782361</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1345,9 +1345,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1362,19 +1372,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129011389</v>
+        <v>129032919</v>
       </c>
       <c r="B9" t="n">
         <v>79035</v>
@@ -1409,10 +1419,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>409278</v>
+        <v>409358</v>
       </c>
       <c r="R9" t="n">
-        <v>6782361</v>
+        <v>6782291</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1442,19 +1452,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>15:18</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>15:18</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1469,22 +1469,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129032919</v>
+        <v>129032394</v>
       </c>
       <c r="B10" t="n">
-        <v>79035</v>
+        <v>79625</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1492,21 +1492,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>409358</v>
+        <v>409553</v>
       </c>
       <c r="R10" t="n">
-        <v>6782291</v>
+        <v>6782378</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1566,22 +1566,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129011398</v>
+        <v>129032398</v>
       </c>
       <c r="B11" t="n">
-        <v>79035</v>
+        <v>91546</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1589,21 +1589,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1613,10 +1613,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>409596</v>
+        <v>409482</v>
       </c>
       <c r="R11" t="n">
-        <v>6782395</v>
+        <v>6782335</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1646,19 +1646,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>13:08</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>13:08</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1673,22 +1663,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129032398</v>
+        <v>129011398</v>
       </c>
       <c r="B12" t="n">
-        <v>91546</v>
+        <v>79035</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1696,21 +1686,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1720,10 +1710,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>409482</v>
+        <v>409596</v>
       </c>
       <c r="R12" t="n">
-        <v>6782335</v>
+        <v>6782395</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1753,9 +1743,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1770,12 +1770,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1986,7 +1986,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129032909</v>
+        <v>129032897</v>
       </c>
       <c r="B15" t="n">
         <v>79035</v>
@@ -2021,10 +2021,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>409727</v>
+        <v>409469</v>
       </c>
       <c r="R15" t="n">
-        <v>6782352</v>
+        <v>6782371</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2083,10 +2083,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129032392</v>
+        <v>129032909</v>
       </c>
       <c r="B16" t="n">
-        <v>79654</v>
+        <v>79035</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2094,21 +2094,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2118,10 +2118,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>409554</v>
+        <v>409727</v>
       </c>
       <c r="R16" t="n">
-        <v>6782380</v>
+        <v>6782352</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2168,22 +2168,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129032897</v>
+        <v>129032392</v>
       </c>
       <c r="B17" t="n">
-        <v>79035</v>
+        <v>79654</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2191,21 +2191,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>409469</v>
+        <v>409554</v>
       </c>
       <c r="R17" t="n">
-        <v>6782371</v>
+        <v>6782380</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2265,22 +2265,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129032885</v>
+        <v>129011376</v>
       </c>
       <c r="B18" t="n">
-        <v>79035</v>
+        <v>91544</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2288,21 +2288,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2312,10 +2312,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>409078</v>
+        <v>409774</v>
       </c>
       <c r="R18" t="n">
-        <v>6782312</v>
+        <v>6782323</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2345,9 +2345,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2362,19 +2372,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129032892</v>
+        <v>129032885</v>
       </c>
       <c r="B19" t="n">
         <v>79035</v>
@@ -2409,10 +2419,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>409244</v>
+        <v>409078</v>
       </c>
       <c r="R19" t="n">
-        <v>6782381</v>
+        <v>6782312</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2578,10 +2588,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129011376</v>
+        <v>129032892</v>
       </c>
       <c r="B21" t="n">
-        <v>91544</v>
+        <v>79035</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2589,21 +2599,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2613,10 +2623,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>409774</v>
+        <v>409244</v>
       </c>
       <c r="R21" t="n">
-        <v>6782323</v>
+        <v>6782381</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2646,19 +2656,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>11:31</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>11:31</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2673,12 +2673,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2999,7 +2999,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129011395</v>
+        <v>129011383</v>
       </c>
       <c r="B25" t="n">
         <v>79035</v>
@@ -3034,10 +3034,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>409555</v>
+        <v>409028</v>
       </c>
       <c r="R25" t="n">
-        <v>6782356</v>
+        <v>6782350</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3069,7 +3069,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3106,7 +3106,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129011407</v>
+        <v>129011395</v>
       </c>
       <c r="B26" t="n">
         <v>79035</v>
@@ -3141,10 +3141,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>409795</v>
+        <v>409555</v>
       </c>
       <c r="R26" t="n">
-        <v>6782327</v>
+        <v>6782356</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3176,7 +3176,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3213,7 +3213,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129011383</v>
+        <v>129011407</v>
       </c>
       <c r="B27" t="n">
         <v>79035</v>
@@ -3248,10 +3248,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>409028</v>
+        <v>409795</v>
       </c>
       <c r="R27" t="n">
-        <v>6782350</v>
+        <v>6782327</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3283,7 +3283,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3293,7 +3293,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3522,7 +3522,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129011391</v>
+        <v>129032913</v>
       </c>
       <c r="B30" t="n">
         <v>79035</v>
@@ -3557,10 +3557,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>409349</v>
+        <v>409757</v>
       </c>
       <c r="R30" t="n">
-        <v>6782383</v>
+        <v>6782355</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3590,19 +3590,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>14:34</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>14:34</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3617,19 +3607,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129032913</v>
+        <v>129032406</v>
       </c>
       <c r="B31" t="n">
         <v>79035</v>
@@ -3664,10 +3654,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>409757</v>
+        <v>409253</v>
       </c>
       <c r="R31" t="n">
-        <v>6782355</v>
+        <v>6782372</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3714,19 +3704,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129032406</v>
+        <v>129032882</v>
       </c>
       <c r="B32" t="n">
         <v>79035</v>
@@ -3761,10 +3751,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>409253</v>
+        <v>408992</v>
       </c>
       <c r="R32" t="n">
-        <v>6782372</v>
+        <v>6782394</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3811,19 +3801,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129032882</v>
+        <v>129011391</v>
       </c>
       <c r="B33" t="n">
         <v>79035</v>
@@ -3858,10 +3848,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>408992</v>
+        <v>409349</v>
       </c>
       <c r="R33" t="n">
-        <v>6782394</v>
+        <v>6782383</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3891,9 +3881,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3908,12 +3908,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4132,7 +4132,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129011381</v>
+        <v>129032887</v>
       </c>
       <c r="B36" t="n">
         <v>79035</v>
@@ -4167,10 +4167,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>409010</v>
+        <v>409176</v>
       </c>
       <c r="R36" t="n">
-        <v>6782383</v>
+        <v>6782420</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4200,19 +4200,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>16:06</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>16:06</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4227,19 +4217,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129032887</v>
+        <v>129011381</v>
       </c>
       <c r="B37" t="n">
         <v>79035</v>
@@ -4274,10 +4264,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>409176</v>
+        <v>409010</v>
       </c>
       <c r="R37" t="n">
-        <v>6782420</v>
+        <v>6782383</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4307,9 +4297,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4324,19 +4324,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129011392</v>
+        <v>129032891</v>
       </c>
       <c r="B38" t="n">
         <v>79035</v>
@@ -4371,10 +4371,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>409361</v>
+        <v>409241</v>
       </c>
       <c r="R38" t="n">
-        <v>6782401</v>
+        <v>6782372</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4404,19 +4404,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>14:31</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>14:31</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4431,19 +4421,19 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129032906</v>
+        <v>129011392</v>
       </c>
       <c r="B39" t="n">
         <v>79035</v>
@@ -4478,10 +4468,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>409684</v>
+        <v>409361</v>
       </c>
       <c r="R39" t="n">
-        <v>6782322</v>
+        <v>6782401</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4511,9 +4501,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4528,19 +4528,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129032891</v>
+        <v>129032911</v>
       </c>
       <c r="B40" t="n">
         <v>79035</v>
@@ -4575,10 +4575,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>409241</v>
+        <v>409777</v>
       </c>
       <c r="R40" t="n">
-        <v>6782372</v>
+        <v>6782445</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4637,7 +4637,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129032911</v>
+        <v>129032906</v>
       </c>
       <c r="B41" t="n">
         <v>79035</v>
@@ -4672,10 +4672,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>409777</v>
+        <v>409684</v>
       </c>
       <c r="R41" t="n">
-        <v>6782445</v>
+        <v>6782322</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5142,10 +5142,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129011408</v>
+        <v>129032869</v>
       </c>
       <c r="B46" t="n">
-        <v>79035</v>
+        <v>57723</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5153,21 +5153,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5177,10 +5177,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>409801</v>
+        <v>409754</v>
       </c>
       <c r="R46" t="n">
-        <v>6782315</v>
+        <v>6782356</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5210,19 +5210,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>11:08</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>11:08</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5237,19 +5227,19 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129032884</v>
+        <v>129011408</v>
       </c>
       <c r="B47" t="n">
         <v>79035</v>
@@ -5284,10 +5274,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>409039</v>
+        <v>409801</v>
       </c>
       <c r="R47" t="n">
-        <v>6782290</v>
+        <v>6782315</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5317,9 +5307,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5334,12 +5334,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -5550,10 +5550,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129032869</v>
+        <v>129032884</v>
       </c>
       <c r="B50" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5561,21 +5561,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5585,10 +5585,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>409754</v>
+        <v>409039</v>
       </c>
       <c r="R50" t="n">
-        <v>6782356</v>
+        <v>6782290</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5647,10 +5647,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129011409</v>
+        <v>129032866</v>
       </c>
       <c r="B51" t="n">
-        <v>79035</v>
+        <v>57723</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5658,21 +5658,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5682,10 +5682,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>409202</v>
+        <v>409757</v>
       </c>
       <c r="R51" t="n">
-        <v>6782367</v>
+        <v>6782386</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5715,40 +5715,29 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>15:26</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>15:26</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -5959,7 +5948,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129011396</v>
+        <v>129011386</v>
       </c>
       <c r="B54" t="n">
         <v>79035</v>
@@ -5994,10 +5983,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>409584</v>
+        <v>409210</v>
       </c>
       <c r="R54" t="n">
-        <v>6782395</v>
+        <v>6782365</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6029,7 +6018,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6039,7 +6028,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6066,7 +6055,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129011386</v>
+        <v>129011409</v>
       </c>
       <c r="B55" t="n">
         <v>79035</v>
@@ -6101,10 +6090,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>409210</v>
+        <v>409202</v>
       </c>
       <c r="R55" t="n">
-        <v>6782365</v>
+        <v>6782367</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6155,6 +6144,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6173,10 +6163,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129032866</v>
+        <v>129011396</v>
       </c>
       <c r="B56" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6184,21 +6174,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6208,10 +6198,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>409757</v>
+        <v>409584</v>
       </c>
       <c r="R56" t="n">
-        <v>6782386</v>
+        <v>6782395</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6241,9 +6231,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6258,22 +6258,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129032889</v>
+        <v>129011373</v>
       </c>
       <c r="B57" t="n">
-        <v>79035</v>
+        <v>91546</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6281,34 +6281,41 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>409164</v>
+        <v>409435</v>
       </c>
       <c r="R57" t="n">
-        <v>6782308</v>
+        <v>6782383</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6338,39 +6345,55 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>4 st på samma tall</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129011375</v>
+        <v>129032889</v>
       </c>
       <c r="B58" t="n">
-        <v>78792</v>
+        <v>79035</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6378,21 +6401,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6402,10 +6425,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>409335</v>
+        <v>409164</v>
       </c>
       <c r="R58" t="n">
-        <v>6782352</v>
+        <v>6782308</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6435,19 +6458,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>14:40</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>14:40</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6462,22 +6475,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129032403</v>
+        <v>129011375</v>
       </c>
       <c r="B59" t="n">
-        <v>79035</v>
+        <v>78792</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6485,21 +6498,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6509,10 +6522,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>409021</v>
+        <v>409335</v>
       </c>
       <c r="R59" t="n">
-        <v>6782365</v>
+        <v>6782352</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6542,9 +6555,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6559,22 +6582,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129011373</v>
+        <v>129032403</v>
       </c>
       <c r="B60" t="n">
-        <v>91546</v>
+        <v>79035</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6582,41 +6605,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>409435</v>
+        <v>409021</v>
       </c>
       <c r="R60" t="n">
-        <v>6782383</v>
+        <v>6782365</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6646,45 +6662,29 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>4 st på samma tall</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -7204,7 +7204,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129032914</v>
+        <v>129032886</v>
       </c>
       <c r="B66" t="n">
         <v>79035</v>
@@ -7239,10 +7239,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>409759</v>
+        <v>409108</v>
       </c>
       <c r="R66" t="n">
-        <v>6782343</v>
+        <v>6782395</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7301,10 +7301,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129032396</v>
+        <v>129011384</v>
       </c>
       <c r="B67" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7312,42 +7312,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>409753</v>
+        <v>409068</v>
       </c>
       <c r="R67" t="n">
-        <v>6782323</v>
+        <v>6782377</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7377,9 +7369,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7394,22 +7396,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129032867</v>
+        <v>129011379</v>
       </c>
       <c r="B68" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7417,21 +7419,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7441,10 +7443,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>409693</v>
+        <v>408991</v>
       </c>
       <c r="R68" t="n">
-        <v>6782357</v>
+        <v>6782360</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7474,9 +7476,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7491,19 +7503,19 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129032886</v>
+        <v>129032914</v>
       </c>
       <c r="B69" t="n">
         <v>79035</v>
@@ -7538,10 +7550,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>409108</v>
+        <v>409759</v>
       </c>
       <c r="R69" t="n">
-        <v>6782395</v>
+        <v>6782343</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7600,10 +7612,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129011384</v>
+        <v>129032396</v>
       </c>
       <c r="B70" t="n">
-        <v>79035</v>
+        <v>57723</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7611,34 +7623,42 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>409068</v>
+        <v>409753</v>
       </c>
       <c r="R70" t="n">
-        <v>6782377</v>
+        <v>6782323</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7668,19 +7688,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>15:43</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>15:43</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7695,22 +7705,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129011379</v>
+        <v>129032867</v>
       </c>
       <c r="B71" t="n">
-        <v>79035</v>
+        <v>57723</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7718,21 +7728,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7742,10 +7752,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>408991</v>
+        <v>409693</v>
       </c>
       <c r="R71" t="n">
-        <v>6782360</v>
+        <v>6782357</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7775,19 +7785,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>16:09</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>16:09</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7802,22 +7802,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129032902</v>
+        <v>129032873</v>
       </c>
       <c r="B72" t="n">
-        <v>79035</v>
+        <v>91526</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7825,34 +7825,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>409549</v>
+        <v>409075</v>
       </c>
       <c r="R72" t="n">
-        <v>6782286</v>
+        <v>6782317</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7893,6 +7896,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -7911,7 +7915,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129032917</v>
+        <v>129032896</v>
       </c>
       <c r="B73" t="n">
         <v>79035</v>
@@ -7946,10 +7950,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>409360</v>
+        <v>409331</v>
       </c>
       <c r="R73" t="n">
-        <v>6782355</v>
+        <v>6782342</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8008,7 +8012,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129032900</v>
+        <v>129032902</v>
       </c>
       <c r="B74" t="n">
         <v>79035</v>
@@ -8043,7 +8047,7 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>409449</v>
+        <v>409549</v>
       </c>
       <c r="R74" t="n">
         <v>6782286</v>
@@ -8105,10 +8109,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129032873</v>
+        <v>129032917</v>
       </c>
       <c r="B75" t="n">
-        <v>91526</v>
+        <v>79035</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8116,37 +8120,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>409075</v>
+        <v>409360</v>
       </c>
       <c r="R75" t="n">
-        <v>6782317</v>
+        <v>6782355</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8187,7 +8188,6 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8206,7 +8206,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129032896</v>
+        <v>129032900</v>
       </c>
       <c r="B76" t="n">
         <v>79035</v>
@@ -8241,10 +8241,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>409331</v>
+        <v>409449</v>
       </c>
       <c r="R76" t="n">
-        <v>6782342</v>
+        <v>6782286</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8604,7 +8604,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129032888</v>
+        <v>129032901</v>
       </c>
       <c r="B80" t="n">
         <v>79035</v>
@@ -8639,10 +8639,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>409127</v>
+        <v>409528</v>
       </c>
       <c r="R80" t="n">
-        <v>6782290</v>
+        <v>6782292</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8701,7 +8701,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129032901</v>
+        <v>129032888</v>
       </c>
       <c r="B81" t="n">
         <v>79035</v>
@@ -8736,10 +8736,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>409528</v>
+        <v>409127</v>
       </c>
       <c r="R81" t="n">
-        <v>6782292</v>
+        <v>6782290</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8798,7 +8798,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129032879</v>
+        <v>129032908</v>
       </c>
       <c r="B82" t="n">
         <v>79035</v>
@@ -8833,10 +8833,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>408909</v>
+        <v>409715</v>
       </c>
       <c r="R82" t="n">
-        <v>6782332</v>
+        <v>6782363</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8895,7 +8895,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129032916</v>
+        <v>129032879</v>
       </c>
       <c r="B83" t="n">
         <v>79035</v>
@@ -8930,10 +8930,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>409812</v>
+        <v>408909</v>
       </c>
       <c r="R83" t="n">
-        <v>6782309</v>
+        <v>6782332</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8992,7 +8992,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129032908</v>
+        <v>129032409</v>
       </c>
       <c r="B84" t="n">
         <v>79035</v>
@@ -9027,10 +9027,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>409715</v>
+        <v>409782</v>
       </c>
       <c r="R84" t="n">
-        <v>6782363</v>
+        <v>6782339</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9077,19 +9077,19 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129032409</v>
+        <v>129032916</v>
       </c>
       <c r="B85" t="n">
         <v>79035</v>
@@ -9124,10 +9124,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>409782</v>
+        <v>409812</v>
       </c>
       <c r="R85" t="n">
-        <v>6782339</v>
+        <v>6782309</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9174,22 +9174,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129032898</v>
+        <v>129011370</v>
       </c>
       <c r="B86" t="n">
-        <v>79035</v>
+        <v>57723</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9197,34 +9197,42 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>409390</v>
+        <v>409759</v>
       </c>
       <c r="R86" t="n">
-        <v>6782289</v>
+        <v>6782330</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9254,9 +9262,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9271,22 +9289,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129032918</v>
+        <v>129032870</v>
       </c>
       <c r="B87" t="n">
-        <v>79035</v>
+        <v>91546</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9294,34 +9312,45 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>409363</v>
+        <v>409530</v>
       </c>
       <c r="R87" t="n">
-        <v>6782377</v>
+        <v>6782289</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9362,6 +9391,7 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9380,10 +9410,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129032870</v>
+        <v>129032898</v>
       </c>
       <c r="B88" t="n">
-        <v>91546</v>
+        <v>79035</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9391,42 +9421,31 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>409530</v>
+        <v>409390</v>
       </c>
       <c r="R88" t="n">
         <v>6782289</v>
@@ -9470,7 +9489,6 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -9489,10 +9507,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129011370</v>
+        <v>129032918</v>
       </c>
       <c r="B89" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9500,42 +9518,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>409759</v>
+        <v>409363</v>
       </c>
       <c r="R89" t="n">
-        <v>6782330</v>
+        <v>6782377</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9565,19 +9575,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>11:48</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9592,12 +9592,12 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
@@ -10206,7 +10206,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129032408</v>
+        <v>129011406</v>
       </c>
       <c r="B96" t="n">
         <v>79035</v>
@@ -10241,10 +10241,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>409749</v>
+        <v>409759</v>
       </c>
       <c r="R96" t="n">
-        <v>6782325</v>
+        <v>6782314</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10274,9 +10274,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10291,19 +10301,19 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129032912</v>
+        <v>129032408</v>
       </c>
       <c r="B97" t="n">
         <v>79035</v>
@@ -10338,10 +10348,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>409762</v>
+        <v>409749</v>
       </c>
       <c r="R97" t="n">
-        <v>6782335</v>
+        <v>6782325</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10388,19 +10398,19 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129032875</v>
+        <v>129032912</v>
       </c>
       <c r="B98" t="n">
         <v>79035</v>
@@ -10435,10 +10445,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>409034</v>
+        <v>409762</v>
       </c>
       <c r="R98" t="n">
-        <v>6782261</v>
+        <v>6782335</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10497,7 +10507,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129011390</v>
+        <v>129032890</v>
       </c>
       <c r="B99" t="n">
         <v>79035</v>
@@ -10532,10 +10542,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>409349</v>
+        <v>409228</v>
       </c>
       <c r="R99" t="n">
-        <v>6782376</v>
+        <v>6782298</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10565,19 +10575,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>14:34</t>
-        </is>
-      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>14:34</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10592,19 +10592,19 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129011406</v>
+        <v>129032875</v>
       </c>
       <c r="B100" t="n">
         <v>79035</v>
@@ -10639,10 +10639,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>409759</v>
+        <v>409034</v>
       </c>
       <c r="R100" t="n">
-        <v>6782314</v>
+        <v>6782261</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10672,19 +10672,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>11:41</t>
-        </is>
-      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>11:41</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10699,19 +10689,19 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129032890</v>
+        <v>129011390</v>
       </c>
       <c r="B101" t="n">
         <v>79035</v>
@@ -10746,10 +10736,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>409228</v>
+        <v>409349</v>
       </c>
       <c r="R101" t="n">
-        <v>6782298</v>
+        <v>6782376</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10779,9 +10769,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10796,22 +10796,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129011385</v>
+        <v>129032401</v>
       </c>
       <c r="B102" t="n">
-        <v>79035</v>
+        <v>91544</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10819,21 +10819,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10843,10 +10843,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>409214</v>
+        <v>409226</v>
       </c>
       <c r="R102" t="n">
-        <v>6782345</v>
+        <v>6782376</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10876,19 +10876,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z102" t="inlineStr">
-        <is>
-          <t>15:29</t>
-        </is>
-      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB102" t="inlineStr">
-        <is>
-          <t>15:29</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10903,19 +10893,19 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129032904</v>
+        <v>129011377</v>
       </c>
       <c r="B103" t="n">
         <v>79035</v>
@@ -10950,10 +10940,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>409568</v>
+        <v>408995</v>
       </c>
       <c r="R103" t="n">
-        <v>6782383</v>
+        <v>6782299</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10983,9 +10973,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11000,19 +11000,19 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129032915</v>
+        <v>129011402</v>
       </c>
       <c r="B104" t="n">
         <v>79035</v>
@@ -11047,10 +11047,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>409765</v>
+        <v>409671</v>
       </c>
       <c r="R104" t="n">
-        <v>6782330</v>
+        <v>6782390</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11080,9 +11080,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11097,19 +11107,19 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129011377</v>
+        <v>129011385</v>
       </c>
       <c r="B105" t="n">
         <v>79035</v>
@@ -11144,10 +11154,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>408995</v>
+        <v>409214</v>
       </c>
       <c r="R105" t="n">
-        <v>6782299</v>
+        <v>6782345</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11179,7 +11189,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11189,7 +11199,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11216,7 +11226,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129011402</v>
+        <v>129032877</v>
       </c>
       <c r="B106" t="n">
         <v>79035</v>
@@ -11251,10 +11261,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>409671</v>
+        <v>408994</v>
       </c>
       <c r="R106" t="n">
-        <v>6782390</v>
+        <v>6782293</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11284,19 +11294,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z106" t="inlineStr">
-        <is>
-          <t>12:57</t>
-        </is>
-      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB106" t="inlineStr">
-        <is>
-          <t>12:57</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11311,19 +11311,19 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129032877</v>
+        <v>129032904</v>
       </c>
       <c r="B107" t="n">
         <v>79035</v>
@@ -11358,10 +11358,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>408994</v>
+        <v>409568</v>
       </c>
       <c r="R107" t="n">
-        <v>6782293</v>
+        <v>6782383</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11420,10 +11420,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129032401</v>
+        <v>129032915</v>
       </c>
       <c r="B108" t="n">
-        <v>91544</v>
+        <v>79035</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11431,21 +11431,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11455,10 +11455,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>409226</v>
+        <v>409765</v>
       </c>
       <c r="R108" t="n">
-        <v>6782376</v>
+        <v>6782330</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11505,12 +11505,12 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>

--- a/artfynd/A 47938-2025 artfynd.xlsx
+++ b/artfynd/A 47938-2025 artfynd.xlsx
@@ -3522,10 +3522,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129032913</v>
+        <v>129011369</v>
       </c>
       <c r="B30" t="n">
-        <v>79035</v>
+        <v>57723</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3533,34 +3533,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>409757</v>
+        <v>409683</v>
       </c>
       <c r="R30" t="n">
-        <v>6782355</v>
+        <v>6782391</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3590,9 +3598,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3607,19 +3625,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129032406</v>
+        <v>129032913</v>
       </c>
       <c r="B31" t="n">
         <v>79035</v>
@@ -3654,10 +3672,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>409253</v>
+        <v>409757</v>
       </c>
       <c r="R31" t="n">
-        <v>6782372</v>
+        <v>6782355</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3704,19 +3722,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129032882</v>
+        <v>129032406</v>
       </c>
       <c r="B32" t="n">
         <v>79035</v>
@@ -3751,10 +3769,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>408992</v>
+        <v>409253</v>
       </c>
       <c r="R32" t="n">
-        <v>6782394</v>
+        <v>6782372</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3801,19 +3819,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129011391</v>
+        <v>129032882</v>
       </c>
       <c r="B33" t="n">
         <v>79035</v>
@@ -3848,10 +3866,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>409349</v>
+        <v>408992</v>
       </c>
       <c r="R33" t="n">
-        <v>6782383</v>
+        <v>6782394</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3881,19 +3899,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>14:34</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>14:34</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3908,19 +3916,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129032878</v>
+        <v>129011391</v>
       </c>
       <c r="B34" t="n">
         <v>79035</v>
@@ -3955,10 +3963,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>408966</v>
+        <v>409349</v>
       </c>
       <c r="R34" t="n">
-        <v>6782283</v>
+        <v>6782383</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3988,9 +3996,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4005,22 +4023,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129011369</v>
+        <v>129032878</v>
       </c>
       <c r="B35" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4028,42 +4046,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>409683</v>
+        <v>408966</v>
       </c>
       <c r="R35" t="n">
-        <v>6782391</v>
+        <v>6782283</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4093,19 +4103,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>12:56</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>12:56</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4120,12 +4120,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -7000,10 +7000,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129011387</v>
+        <v>129032396</v>
       </c>
       <c r="B64" t="n">
-        <v>79035</v>
+        <v>57723</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7011,34 +7011,42 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>409232</v>
+        <v>409753</v>
       </c>
       <c r="R64" t="n">
-        <v>6782353</v>
+        <v>6782323</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7068,19 +7076,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>15:22</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>15:22</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7095,22 +7093,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129032872</v>
+        <v>129032867</v>
       </c>
       <c r="B65" t="n">
-        <v>78792</v>
+        <v>57723</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7118,21 +7116,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7142,10 +7140,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>409594</v>
+        <v>409693</v>
       </c>
       <c r="R65" t="n">
-        <v>6782294</v>
+        <v>6782357</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7204,7 +7202,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129032886</v>
+        <v>129011387</v>
       </c>
       <c r="B66" t="n">
         <v>79035</v>
@@ -7239,10 +7237,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>409108</v>
+        <v>409232</v>
       </c>
       <c r="R66" t="n">
-        <v>6782395</v>
+        <v>6782353</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7272,9 +7270,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7289,22 +7297,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129011384</v>
+        <v>129032872</v>
       </c>
       <c r="B67" t="n">
-        <v>79035</v>
+        <v>78792</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7312,21 +7320,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7336,10 +7344,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>409068</v>
+        <v>409594</v>
       </c>
       <c r="R67" t="n">
-        <v>6782377</v>
+        <v>6782294</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7369,19 +7377,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>15:43</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>15:43</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7396,19 +7394,19 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129011379</v>
+        <v>129032886</v>
       </c>
       <c r="B68" t="n">
         <v>79035</v>
@@ -7443,10 +7441,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>408991</v>
+        <v>409108</v>
       </c>
       <c r="R68" t="n">
-        <v>6782360</v>
+        <v>6782395</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7476,19 +7474,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>16:09</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>16:09</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7503,19 +7491,19 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129032914</v>
+        <v>129011384</v>
       </c>
       <c r="B69" t="n">
         <v>79035</v>
@@ -7550,10 +7538,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>409759</v>
+        <v>409068</v>
       </c>
       <c r="R69" t="n">
-        <v>6782343</v>
+        <v>6782377</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7583,9 +7571,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7600,22 +7598,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129032396</v>
+        <v>129011379</v>
       </c>
       <c r="B70" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7623,42 +7621,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>409753</v>
+        <v>408991</v>
       </c>
       <c r="R70" t="n">
-        <v>6782323</v>
+        <v>6782360</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7688,9 +7678,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7705,22 +7705,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129032867</v>
+        <v>129032914</v>
       </c>
       <c r="B71" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7728,21 +7728,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7752,10 +7752,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>409693</v>
+        <v>409759</v>
       </c>
       <c r="R71" t="n">
-        <v>6782357</v>
+        <v>6782343</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -10808,10 +10808,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129032401</v>
+        <v>129011377</v>
       </c>
       <c r="B102" t="n">
-        <v>91544</v>
+        <v>79035</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10819,21 +10819,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10843,10 +10843,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>409226</v>
+        <v>408995</v>
       </c>
       <c r="R102" t="n">
-        <v>6782376</v>
+        <v>6782299</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10876,9 +10876,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10893,19 +10903,19 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129011377</v>
+        <v>129011402</v>
       </c>
       <c r="B103" t="n">
         <v>79035</v>
@@ -10940,10 +10950,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>408995</v>
+        <v>409671</v>
       </c>
       <c r="R103" t="n">
-        <v>6782299</v>
+        <v>6782390</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10975,7 +10985,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -10985,7 +10995,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11012,7 +11022,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129011402</v>
+        <v>129011385</v>
       </c>
       <c r="B104" t="n">
         <v>79035</v>
@@ -11047,10 +11057,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>409671</v>
+        <v>409214</v>
       </c>
       <c r="R104" t="n">
-        <v>6782390</v>
+        <v>6782345</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11082,7 +11092,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11092,7 +11102,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11119,7 +11129,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129011385</v>
+        <v>129032877</v>
       </c>
       <c r="B105" t="n">
         <v>79035</v>
@@ -11154,10 +11164,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>409214</v>
+        <v>408994</v>
       </c>
       <c r="R105" t="n">
-        <v>6782345</v>
+        <v>6782293</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11187,19 +11197,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z105" t="inlineStr">
-        <is>
-          <t>15:29</t>
-        </is>
-      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB105" t="inlineStr">
-        <is>
-          <t>15:29</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11214,19 +11214,19 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129032877</v>
+        <v>129032904</v>
       </c>
       <c r="B106" t="n">
         <v>79035</v>
@@ -11261,10 +11261,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>408994</v>
+        <v>409568</v>
       </c>
       <c r="R106" t="n">
-        <v>6782293</v>
+        <v>6782383</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11323,7 +11323,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129032904</v>
+        <v>129032915</v>
       </c>
       <c r="B107" t="n">
         <v>79035</v>
@@ -11358,10 +11358,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>409568</v>
+        <v>409765</v>
       </c>
       <c r="R107" t="n">
-        <v>6782383</v>
+        <v>6782330</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11420,10 +11420,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129032915</v>
+        <v>129032401</v>
       </c>
       <c r="B108" t="n">
-        <v>79035</v>
+        <v>91544</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11431,21 +11431,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11455,10 +11455,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>409765</v>
+        <v>409226</v>
       </c>
       <c r="R108" t="n">
-        <v>6782330</v>
+        <v>6782376</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11505,12 +11505,12 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>

--- a/artfynd/A 47938-2025 artfynd.xlsx
+++ b/artfynd/A 47938-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129032920</v>
+        <v>129011405</v>
       </c>
       <c r="B2" t="n">
         <v>79035</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>409793</v>
+        <v>409747</v>
       </c>
       <c r="R2" t="n">
-        <v>6782448</v>
+        <v>6782328</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -743,9 +743,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -760,19 +770,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129011405</v>
+        <v>129011403</v>
       </c>
       <c r="B3" t="n">
         <v>79035</v>
@@ -807,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>409747</v>
+        <v>409706</v>
       </c>
       <c r="R3" t="n">
-        <v>6782328</v>
+        <v>6782359</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -842,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -852,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129032876</v>
+        <v>129032920</v>
       </c>
       <c r="B4" t="n">
         <v>79035</v>
@@ -914,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>408997</v>
+        <v>409793</v>
       </c>
       <c r="R4" t="n">
-        <v>6782283</v>
+        <v>6782448</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,7 +986,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129011403</v>
+        <v>129032876</v>
       </c>
       <c r="B5" t="n">
         <v>79035</v>
@@ -1011,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>409706</v>
+        <v>408997</v>
       </c>
       <c r="R5" t="n">
-        <v>6782359</v>
+        <v>6782283</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1044,19 +1054,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>12:06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,12 +1071,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1180,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129032907</v>
+        <v>129032394</v>
       </c>
       <c r="B7" t="n">
-        <v>79035</v>
+        <v>79625</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>409686</v>
+        <v>409553</v>
       </c>
       <c r="R7" t="n">
-        <v>6782351</v>
+        <v>6782378</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1265,19 +1265,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129011389</v>
+        <v>129032907</v>
       </c>
       <c r="B8" t="n">
         <v>79035</v>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>409278</v>
+        <v>409686</v>
       </c>
       <c r="R8" t="n">
-        <v>6782361</v>
+        <v>6782351</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1345,19 +1345,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>15:18</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>15:18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1372,12 +1362,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1481,10 +1471,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129032394</v>
+        <v>129011389</v>
       </c>
       <c r="B10" t="n">
-        <v>79625</v>
+        <v>79035</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1492,21 +1482,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1516,10 +1506,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>409553</v>
+        <v>409278</v>
       </c>
       <c r="R10" t="n">
-        <v>6782378</v>
+        <v>6782361</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1549,9 +1539,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1566,12 +1566,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1675,7 +1675,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129011398</v>
+        <v>129032894</v>
       </c>
       <c r="B12" t="n">
         <v>79035</v>
@@ -1710,10 +1710,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>409596</v>
+        <v>409292</v>
       </c>
       <c r="R12" t="n">
-        <v>6782395</v>
+        <v>6782306</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1743,19 +1743,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>13:08</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>13:08</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1770,19 +1760,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129032894</v>
+        <v>129011398</v>
       </c>
       <c r="B13" t="n">
         <v>79035</v>
@@ -1817,10 +1807,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>409292</v>
+        <v>409596</v>
       </c>
       <c r="R13" t="n">
-        <v>6782306</v>
+        <v>6782395</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1850,9 +1840,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1867,19 +1867,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129011378</v>
+        <v>129032909</v>
       </c>
       <c r="B14" t="n">
         <v>79035</v>
@@ -1914,10 +1914,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>408984</v>
+        <v>409727</v>
       </c>
       <c r="R14" t="n">
-        <v>6782347</v>
+        <v>6782352</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1947,19 +1947,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>16:10</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>16:10</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1974,19 +1964,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129032897</v>
+        <v>129011378</v>
       </c>
       <c r="B15" t="n">
         <v>79035</v>
@@ -2021,10 +2011,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>409469</v>
+        <v>408984</v>
       </c>
       <c r="R15" t="n">
-        <v>6782371</v>
+        <v>6782347</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2054,9 +2044,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2071,22 +2071,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129032909</v>
+        <v>129032392</v>
       </c>
       <c r="B16" t="n">
-        <v>79035</v>
+        <v>79654</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2094,21 +2094,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2118,10 +2118,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>409727</v>
+        <v>409554</v>
       </c>
       <c r="R16" t="n">
-        <v>6782352</v>
+        <v>6782380</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2168,22 +2168,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129032392</v>
+        <v>129032897</v>
       </c>
       <c r="B17" t="n">
-        <v>79654</v>
+        <v>79035</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2191,21 +2191,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>409554</v>
+        <v>409469</v>
       </c>
       <c r="R17" t="n">
-        <v>6782380</v>
+        <v>6782371</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2265,12 +2265,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2384,7 +2384,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129032885</v>
+        <v>129032892</v>
       </c>
       <c r="B19" t="n">
         <v>79035</v>
@@ -2419,10 +2419,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>409078</v>
+        <v>409244</v>
       </c>
       <c r="R19" t="n">
-        <v>6782312</v>
+        <v>6782381</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2588,10 +2588,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129032892</v>
+        <v>129032868</v>
       </c>
       <c r="B21" t="n">
-        <v>79035</v>
+        <v>57723</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2599,21 +2599,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2623,10 +2623,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>409244</v>
+        <v>409688</v>
       </c>
       <c r="R21" t="n">
-        <v>6782381</v>
+        <v>6782303</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2685,10 +2685,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129032868</v>
+        <v>129032885</v>
       </c>
       <c r="B22" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2696,21 +2696,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2720,10 +2720,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>409688</v>
+        <v>409078</v>
       </c>
       <c r="R22" t="n">
-        <v>6782303</v>
+        <v>6782312</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2782,10 +2782,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129032399</v>
+        <v>129011395</v>
       </c>
       <c r="B23" t="n">
-        <v>91546</v>
+        <v>79035</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2793,21 +2793,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2817,10 +2817,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>409492</v>
+        <v>409555</v>
       </c>
       <c r="R23" t="n">
-        <v>6782346</v>
+        <v>6782356</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2850,9 +2850,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2867,22 +2877,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129011374</v>
+        <v>129011407</v>
       </c>
       <c r="B24" t="n">
-        <v>91546</v>
+        <v>79035</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2890,41 +2900,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>409475</v>
+        <v>409795</v>
       </c>
       <c r="R24" t="n">
-        <v>6782342</v>
+        <v>6782327</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2956,7 +2959,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -2966,12 +2969,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:57</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>hackspetthål under tickorna</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2980,7 +2978,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -2999,10 +2996,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129011383</v>
+        <v>129032395</v>
       </c>
       <c r="B25" t="n">
-        <v>79035</v>
+        <v>57723</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3010,34 +3007,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>409028</v>
+        <v>409759</v>
       </c>
       <c r="R25" t="n">
-        <v>6782350</v>
+        <v>6782358</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3067,19 +3072,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>16:04</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>16:04</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3094,19 +3089,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129011395</v>
+        <v>129011383</v>
       </c>
       <c r="B26" t="n">
         <v>79035</v>
@@ -3141,10 +3136,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>409555</v>
+        <v>409028</v>
       </c>
       <c r="R26" t="n">
-        <v>6782356</v>
+        <v>6782350</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3176,7 +3171,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3186,7 +3181,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3213,10 +3208,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129011407</v>
+        <v>129032399</v>
       </c>
       <c r="B27" t="n">
-        <v>79035</v>
+        <v>91546</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3224,21 +3219,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3248,10 +3243,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>409795</v>
+        <v>409492</v>
       </c>
       <c r="R27" t="n">
-        <v>6782327</v>
+        <v>6782346</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3281,19 +3276,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>11:12</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>11:12</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3308,22 +3293,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129032395</v>
+        <v>129011374</v>
       </c>
       <c r="B28" t="n">
-        <v>57723</v>
+        <v>91546</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3331,31 +3316,30 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3363,10 +3347,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>409759</v>
+        <v>409475</v>
       </c>
       <c r="R28" t="n">
-        <v>6782358</v>
+        <v>6782342</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3396,29 +3380,45 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>hackspetthål under tickorna</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3522,10 +3522,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129011369</v>
+        <v>129032913</v>
       </c>
       <c r="B30" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3533,42 +3533,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>409683</v>
+        <v>409757</v>
       </c>
       <c r="R30" t="n">
-        <v>6782391</v>
+        <v>6782355</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3598,19 +3590,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>12:56</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>12:56</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3625,19 +3607,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129032913</v>
+        <v>129032406</v>
       </c>
       <c r="B31" t="n">
         <v>79035</v>
@@ -3672,10 +3654,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>409757</v>
+        <v>409253</v>
       </c>
       <c r="R31" t="n">
-        <v>6782355</v>
+        <v>6782372</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3722,19 +3704,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129032406</v>
+        <v>129032882</v>
       </c>
       <c r="B32" t="n">
         <v>79035</v>
@@ -3769,10 +3751,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>409253</v>
+        <v>408992</v>
       </c>
       <c r="R32" t="n">
-        <v>6782372</v>
+        <v>6782394</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3819,19 +3801,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129032882</v>
+        <v>129032878</v>
       </c>
       <c r="B33" t="n">
         <v>79035</v>
@@ -3866,10 +3848,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>408992</v>
+        <v>408966</v>
       </c>
       <c r="R33" t="n">
-        <v>6782394</v>
+        <v>6782283</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3928,10 +3910,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129011391</v>
+        <v>129011369</v>
       </c>
       <c r="B34" t="n">
-        <v>79035</v>
+        <v>57723</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3939,34 +3921,42 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>409349</v>
+        <v>409683</v>
       </c>
       <c r="R34" t="n">
-        <v>6782383</v>
+        <v>6782391</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3998,7 +3988,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4008,7 +3998,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4035,7 +4025,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129032878</v>
+        <v>129011391</v>
       </c>
       <c r="B35" t="n">
         <v>79035</v>
@@ -4070,10 +4060,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>408966</v>
+        <v>409349</v>
       </c>
       <c r="R35" t="n">
-        <v>6782283</v>
+        <v>6782383</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4103,9 +4093,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4120,19 +4120,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129032887</v>
+        <v>129011381</v>
       </c>
       <c r="B36" t="n">
         <v>79035</v>
@@ -4167,10 +4167,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>409176</v>
+        <v>409010</v>
       </c>
       <c r="R36" t="n">
-        <v>6782420</v>
+        <v>6782383</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4200,9 +4200,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4217,19 +4227,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129011381</v>
+        <v>129032887</v>
       </c>
       <c r="B37" t="n">
         <v>79035</v>
@@ -4264,10 +4274,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>409010</v>
+        <v>409176</v>
       </c>
       <c r="R37" t="n">
-        <v>6782383</v>
+        <v>6782420</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4297,19 +4307,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>16:06</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>16:06</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4324,19 +4324,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129032891</v>
+        <v>129011392</v>
       </c>
       <c r="B38" t="n">
         <v>79035</v>
@@ -4371,10 +4371,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>409241</v>
+        <v>409361</v>
       </c>
       <c r="R38" t="n">
-        <v>6782372</v>
+        <v>6782401</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4404,9 +4404,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4421,19 +4431,19 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129011392</v>
+        <v>129011394</v>
       </c>
       <c r="B39" t="n">
         <v>79035</v>
@@ -4468,10 +4478,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>409361</v>
+        <v>409543</v>
       </c>
       <c r="R39" t="n">
-        <v>6782401</v>
+        <v>6782361</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4503,7 +4513,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4513,7 +4523,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4540,7 +4550,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129032911</v>
+        <v>129011399</v>
       </c>
       <c r="B40" t="n">
         <v>79035</v>
@@ -4575,10 +4585,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>409777</v>
+        <v>409609</v>
       </c>
       <c r="R40" t="n">
-        <v>6782445</v>
+        <v>6782404</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4608,9 +4618,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4625,19 +4645,19 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129032906</v>
+        <v>129032891</v>
       </c>
       <c r="B41" t="n">
         <v>79035</v>
@@ -4672,10 +4692,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>409684</v>
+        <v>409241</v>
       </c>
       <c r="R41" t="n">
-        <v>6782322</v>
+        <v>6782372</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4734,7 +4754,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129032407</v>
+        <v>129032911</v>
       </c>
       <c r="B42" t="n">
         <v>79035</v>
@@ -4769,10 +4789,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>409659</v>
+        <v>409777</v>
       </c>
       <c r="R42" t="n">
-        <v>6782436</v>
+        <v>6782445</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4819,19 +4839,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129032910</v>
+        <v>129032906</v>
       </c>
       <c r="B43" t="n">
         <v>79035</v>
@@ -4866,10 +4886,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>409744</v>
+        <v>409684</v>
       </c>
       <c r="R43" t="n">
-        <v>6782394</v>
+        <v>6782322</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4928,7 +4948,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129011394</v>
+        <v>129032407</v>
       </c>
       <c r="B44" t="n">
         <v>79035</v>
@@ -4963,10 +4983,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>409543</v>
+        <v>409659</v>
       </c>
       <c r="R44" t="n">
-        <v>6782361</v>
+        <v>6782436</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4996,19 +5016,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>13:27</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>13:27</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5023,19 +5033,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129011399</v>
+        <v>129032910</v>
       </c>
       <c r="B45" t="n">
         <v>79035</v>
@@ -5070,10 +5080,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>409609</v>
+        <v>409744</v>
       </c>
       <c r="R45" t="n">
-        <v>6782404</v>
+        <v>6782394</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5103,19 +5113,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>13:06</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>13:06</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5130,22 +5130,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129032869</v>
+        <v>129032883</v>
       </c>
       <c r="B46" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5153,21 +5153,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5177,10 +5177,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>409754</v>
+        <v>409010</v>
       </c>
       <c r="R46" t="n">
-        <v>6782356</v>
+        <v>6782399</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5239,7 +5239,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129011408</v>
+        <v>129032884</v>
       </c>
       <c r="B47" t="n">
         <v>79035</v>
@@ -5274,10 +5274,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>409801</v>
+        <v>409039</v>
       </c>
       <c r="R47" t="n">
-        <v>6782315</v>
+        <v>6782290</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5307,19 +5307,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>11:08</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>11:08</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5334,19 +5324,19 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129032883</v>
+        <v>129011408</v>
       </c>
       <c r="B48" t="n">
         <v>79035</v>
@@ -5381,10 +5371,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>409010</v>
+        <v>409801</v>
       </c>
       <c r="R48" t="n">
-        <v>6782399</v>
+        <v>6782315</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5414,9 +5404,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5431,12 +5431,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5550,10 +5550,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129032884</v>
+        <v>129032869</v>
       </c>
       <c r="B50" t="n">
-        <v>79035</v>
+        <v>57723</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5561,21 +5561,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5585,10 +5585,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>409039</v>
+        <v>409754</v>
       </c>
       <c r="R50" t="n">
-        <v>6782290</v>
+        <v>6782356</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5647,10 +5647,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129032866</v>
+        <v>129011401</v>
       </c>
       <c r="B51" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5658,21 +5658,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5682,10 +5682,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>409757</v>
+        <v>409663</v>
       </c>
       <c r="R51" t="n">
-        <v>6782386</v>
+        <v>6782385</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5715,9 +5715,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5732,19 +5742,19 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129011401</v>
+        <v>129011386</v>
       </c>
       <c r="B52" t="n">
         <v>79035</v>
@@ -5779,10 +5789,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>409663</v>
+        <v>409210</v>
       </c>
       <c r="R52" t="n">
-        <v>6782385</v>
+        <v>6782365</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5814,7 +5824,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -5824,7 +5834,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5851,7 +5861,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129032899</v>
+        <v>129011409</v>
       </c>
       <c r="B53" t="n">
         <v>79035</v>
@@ -5886,10 +5896,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>409397</v>
+        <v>409202</v>
       </c>
       <c r="R53" t="n">
-        <v>6782272</v>
+        <v>6782367</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5919,36 +5929,47 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129011386</v>
+        <v>129032899</v>
       </c>
       <c r="B54" t="n">
         <v>79035</v>
@@ -5983,10 +6004,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>409210</v>
+        <v>409397</v>
       </c>
       <c r="R54" t="n">
-        <v>6782365</v>
+        <v>6782272</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6016,19 +6037,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>15:26</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>15:26</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6043,19 +6054,19 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129011409</v>
+        <v>129011396</v>
       </c>
       <c r="B55" t="n">
         <v>79035</v>
@@ -6090,10 +6101,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>409202</v>
+        <v>409584</v>
       </c>
       <c r="R55" t="n">
-        <v>6782367</v>
+        <v>6782395</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6125,7 +6136,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6135,7 +6146,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6144,7 +6155,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6163,10 +6173,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129011396</v>
+        <v>129032866</v>
       </c>
       <c r="B56" t="n">
-        <v>79035</v>
+        <v>57723</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6174,21 +6184,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6198,10 +6208,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>409584</v>
+        <v>409757</v>
       </c>
       <c r="R56" t="n">
-        <v>6782395</v>
+        <v>6782386</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6231,19 +6241,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>13:11</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>13:11</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6258,22 +6258,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129011373</v>
+        <v>129032889</v>
       </c>
       <c r="B57" t="n">
-        <v>91546</v>
+        <v>79035</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6281,41 +6281,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>409435</v>
+        <v>409164</v>
       </c>
       <c r="R57" t="n">
-        <v>6782383</v>
+        <v>6782308</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6345,52 +6338,36 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>4 st på samma tall</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129032889</v>
+        <v>129032403</v>
       </c>
       <c r="B58" t="n">
         <v>79035</v>
@@ -6425,10 +6402,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>409164</v>
+        <v>409021</v>
       </c>
       <c r="R58" t="n">
-        <v>6782308</v>
+        <v>6782365</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6475,12 +6452,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -6594,10 +6571,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129032403</v>
+        <v>129011373</v>
       </c>
       <c r="B60" t="n">
-        <v>79035</v>
+        <v>91546</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6605,34 +6582,41 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>409021</v>
+        <v>409435</v>
       </c>
       <c r="R60" t="n">
-        <v>6782365</v>
+        <v>6782383</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6662,29 +6646,45 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>4 st på samma tall</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -7000,10 +7000,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129032396</v>
+        <v>129032886</v>
       </c>
       <c r="B64" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7011,42 +7011,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>409753</v>
+        <v>409108</v>
       </c>
       <c r="R64" t="n">
-        <v>6782323</v>
+        <v>6782395</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7093,22 +7085,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129032867</v>
+        <v>129011379</v>
       </c>
       <c r="B65" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7116,21 +7108,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7140,10 +7132,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>409693</v>
+        <v>408991</v>
       </c>
       <c r="R65" t="n">
-        <v>6782357</v>
+        <v>6782360</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7173,9 +7165,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7190,19 +7192,19 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129011387</v>
+        <v>129032914</v>
       </c>
       <c r="B66" t="n">
         <v>79035</v>
@@ -7237,10 +7239,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>409232</v>
+        <v>409759</v>
       </c>
       <c r="R66" t="n">
-        <v>6782353</v>
+        <v>6782343</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7270,19 +7272,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>15:22</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>15:22</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7297,22 +7289,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129032872</v>
+        <v>129032396</v>
       </c>
       <c r="B67" t="n">
-        <v>78792</v>
+        <v>57723</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7320,34 +7312,42 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>409594</v>
+        <v>409753</v>
       </c>
       <c r="R67" t="n">
-        <v>6782294</v>
+        <v>6782323</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7394,22 +7394,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129032886</v>
+        <v>129032867</v>
       </c>
       <c r="B68" t="n">
-        <v>79035</v>
+        <v>57723</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7417,21 +7417,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7441,10 +7441,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>409108</v>
+        <v>409693</v>
       </c>
       <c r="R68" t="n">
-        <v>6782395</v>
+        <v>6782357</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7503,7 +7503,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129011384</v>
+        <v>129011387</v>
       </c>
       <c r="B69" t="n">
         <v>79035</v>
@@ -7538,10 +7538,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>409068</v>
+        <v>409232</v>
       </c>
       <c r="R69" t="n">
-        <v>6782377</v>
+        <v>6782353</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7573,7 +7573,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7583,7 +7583,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7610,7 +7610,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129011379</v>
+        <v>129011384</v>
       </c>
       <c r="B70" t="n">
         <v>79035</v>
@@ -7645,10 +7645,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>408991</v>
+        <v>409068</v>
       </c>
       <c r="R70" t="n">
-        <v>6782360</v>
+        <v>6782377</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7680,7 +7680,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -7690,7 +7690,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7717,10 +7717,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129032914</v>
+        <v>129032872</v>
       </c>
       <c r="B71" t="n">
-        <v>79035</v>
+        <v>78792</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7728,21 +7728,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7752,10 +7752,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>409759</v>
+        <v>409594</v>
       </c>
       <c r="R71" t="n">
-        <v>6782343</v>
+        <v>6782294</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8992,7 +8992,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129032409</v>
+        <v>129032916</v>
       </c>
       <c r="B84" t="n">
         <v>79035</v>
@@ -9027,10 +9027,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>409782</v>
+        <v>409812</v>
       </c>
       <c r="R84" t="n">
-        <v>6782339</v>
+        <v>6782309</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9077,19 +9077,19 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129032916</v>
+        <v>129032409</v>
       </c>
       <c r="B85" t="n">
         <v>79035</v>
@@ -9124,10 +9124,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>409812</v>
+        <v>409782</v>
       </c>
       <c r="R85" t="n">
-        <v>6782309</v>
+        <v>6782339</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9174,22 +9174,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129011370</v>
+        <v>129032898</v>
       </c>
       <c r="B86" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9197,42 +9197,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>409759</v>
+        <v>409390</v>
       </c>
       <c r="R86" t="n">
-        <v>6782330</v>
+        <v>6782289</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9262,19 +9254,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>11:48</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9289,22 +9271,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129032870</v>
+        <v>129032918</v>
       </c>
       <c r="B87" t="n">
-        <v>91546</v>
+        <v>79035</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9312,45 +9294,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>409530</v>
+        <v>409363</v>
       </c>
       <c r="R87" t="n">
-        <v>6782289</v>
+        <v>6782377</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9391,7 +9362,6 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9410,10 +9380,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129032898</v>
+        <v>129032870</v>
       </c>
       <c r="B88" t="n">
-        <v>79035</v>
+        <v>91546</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9421,31 +9391,42 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>409390</v>
+        <v>409530</v>
       </c>
       <c r="R88" t="n">
         <v>6782289</v>
@@ -9489,6 +9470,7 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -9507,10 +9489,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129032918</v>
+        <v>129011370</v>
       </c>
       <c r="B89" t="n">
-        <v>79035</v>
+        <v>57723</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9518,34 +9500,42 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>409363</v>
+        <v>409759</v>
       </c>
       <c r="R89" t="n">
-        <v>6782377</v>
+        <v>6782330</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9575,9 +9565,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9592,19 +9592,19 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129011393</v>
+        <v>129032895</v>
       </c>
       <c r="B90" t="n">
         <v>79035</v>
@@ -9639,10 +9639,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>409472</v>
+        <v>409310</v>
       </c>
       <c r="R90" t="n">
-        <v>6782351</v>
+        <v>6782326</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9672,19 +9672,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>14:05</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>14:05</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9699,19 +9689,19 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129032895</v>
+        <v>129032903</v>
       </c>
       <c r="B91" t="n">
         <v>79035</v>
@@ -9746,10 +9736,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>409310</v>
+        <v>409582</v>
       </c>
       <c r="R91" t="n">
-        <v>6782326</v>
+        <v>6782297</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9808,7 +9798,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129032903</v>
+        <v>129032880</v>
       </c>
       <c r="B92" t="n">
         <v>79035</v>
@@ -9843,10 +9833,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>409582</v>
+        <v>408901</v>
       </c>
       <c r="R92" t="n">
-        <v>6782297</v>
+        <v>6782390</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9905,7 +9895,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129032880</v>
+        <v>129032405</v>
       </c>
       <c r="B93" t="n">
         <v>79035</v>
@@ -9940,10 +9930,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>408901</v>
+        <v>409048</v>
       </c>
       <c r="R93" t="n">
-        <v>6782390</v>
+        <v>6782365</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9990,19 +9980,19 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129032405</v>
+        <v>129011393</v>
       </c>
       <c r="B94" t="n">
         <v>79035</v>
@@ -10037,10 +10027,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>409048</v>
+        <v>409472</v>
       </c>
       <c r="R94" t="n">
-        <v>6782365</v>
+        <v>6782351</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10070,9 +10060,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10087,12 +10087,12 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
@@ -10206,7 +10206,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129011406</v>
+        <v>129032912</v>
       </c>
       <c r="B96" t="n">
         <v>79035</v>
@@ -10241,10 +10241,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>409759</v>
+        <v>409762</v>
       </c>
       <c r="R96" t="n">
-        <v>6782314</v>
+        <v>6782335</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10274,19 +10274,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z96" t="inlineStr">
-        <is>
-          <t>11:41</t>
-        </is>
-      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB96" t="inlineStr">
-        <is>
-          <t>11:41</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10301,19 +10291,19 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129032408</v>
+        <v>129032890</v>
       </c>
       <c r="B97" t="n">
         <v>79035</v>
@@ -10348,10 +10338,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>409749</v>
+        <v>409228</v>
       </c>
       <c r="R97" t="n">
-        <v>6782325</v>
+        <v>6782298</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10398,19 +10388,19 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129032912</v>
+        <v>129032875</v>
       </c>
       <c r="B98" t="n">
         <v>79035</v>
@@ -10445,10 +10435,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>409762</v>
+        <v>409034</v>
       </c>
       <c r="R98" t="n">
-        <v>6782335</v>
+        <v>6782261</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10507,7 +10497,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129032890</v>
+        <v>129011390</v>
       </c>
       <c r="B99" t="n">
         <v>79035</v>
@@ -10542,10 +10532,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>409228</v>
+        <v>409349</v>
       </c>
       <c r="R99" t="n">
-        <v>6782298</v>
+        <v>6782376</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10575,9 +10565,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10592,19 +10592,19 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129032875</v>
+        <v>129011406</v>
       </c>
       <c r="B100" t="n">
         <v>79035</v>
@@ -10639,10 +10639,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>409034</v>
+        <v>409759</v>
       </c>
       <c r="R100" t="n">
-        <v>6782261</v>
+        <v>6782314</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10672,9 +10672,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10689,19 +10699,19 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129011390</v>
+        <v>129032408</v>
       </c>
       <c r="B101" t="n">
         <v>79035</v>
@@ -10736,10 +10746,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>409349</v>
+        <v>409749</v>
       </c>
       <c r="R101" t="n">
-        <v>6782376</v>
+        <v>6782325</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10769,19 +10779,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z101" t="inlineStr">
-        <is>
-          <t>14:34</t>
-        </is>
-      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB101" t="inlineStr">
-        <is>
-          <t>14:34</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10796,22 +10796,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129011377</v>
+        <v>129032401</v>
       </c>
       <c r="B102" t="n">
-        <v>79035</v>
+        <v>91544</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10819,21 +10819,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10843,10 +10843,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>408995</v>
+        <v>409226</v>
       </c>
       <c r="R102" t="n">
-        <v>6782299</v>
+        <v>6782376</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10876,19 +10876,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z102" t="inlineStr">
-        <is>
-          <t>16:13</t>
-        </is>
-      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB102" t="inlineStr">
-        <is>
-          <t>16:13</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10903,19 +10893,19 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129011402</v>
+        <v>129011377</v>
       </c>
       <c r="B103" t="n">
         <v>79035</v>
@@ -10950,10 +10940,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>409671</v>
+        <v>408995</v>
       </c>
       <c r="R103" t="n">
-        <v>6782390</v>
+        <v>6782299</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10985,7 +10975,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -10995,7 +10985,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11022,7 +11012,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129011385</v>
+        <v>129032877</v>
       </c>
       <c r="B104" t="n">
         <v>79035</v>
@@ -11057,10 +11047,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>409214</v>
+        <v>408994</v>
       </c>
       <c r="R104" t="n">
-        <v>6782345</v>
+        <v>6782293</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11090,19 +11080,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z104" t="inlineStr">
-        <is>
-          <t>15:29</t>
-        </is>
-      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB104" t="inlineStr">
-        <is>
-          <t>15:29</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11117,19 +11097,19 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129032877</v>
+        <v>129032904</v>
       </c>
       <c r="B105" t="n">
         <v>79035</v>
@@ -11164,10 +11144,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>408994</v>
+        <v>409568</v>
       </c>
       <c r="R105" t="n">
-        <v>6782293</v>
+        <v>6782383</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11226,7 +11206,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129032904</v>
+        <v>129032915</v>
       </c>
       <c r="B106" t="n">
         <v>79035</v>
@@ -11261,10 +11241,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>409568</v>
+        <v>409765</v>
       </c>
       <c r="R106" t="n">
-        <v>6782383</v>
+        <v>6782330</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11323,7 +11303,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129032915</v>
+        <v>129011402</v>
       </c>
       <c r="B107" t="n">
         <v>79035</v>
@@ -11358,10 +11338,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>409765</v>
+        <v>409671</v>
       </c>
       <c r="R107" t="n">
-        <v>6782330</v>
+        <v>6782390</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11391,9 +11371,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11408,22 +11398,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129032401</v>
+        <v>129011385</v>
       </c>
       <c r="B108" t="n">
-        <v>91544</v>
+        <v>79035</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11431,21 +11421,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11455,10 +11445,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>409226</v>
+        <v>409214</v>
       </c>
       <c r="R108" t="n">
-        <v>6782376</v>
+        <v>6782345</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11488,9 +11478,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11505,12 +11505,12 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>

--- a/artfynd/A 47938-2025 artfynd.xlsx
+++ b/artfynd/A 47938-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129011405</v>
+        <v>129032920</v>
       </c>
       <c r="B2" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>409747</v>
+        <v>409793</v>
       </c>
       <c r="R2" t="n">
-        <v>6782328</v>
+        <v>6782448</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -743,19 +743,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>11:47</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>11:47</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129011403</v>
+        <v>129011405</v>
       </c>
       <c r="B3" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>409706</v>
+        <v>409747</v>
       </c>
       <c r="R3" t="n">
-        <v>6782359</v>
+        <v>6782328</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +842,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +852,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129032920</v>
+        <v>129032876</v>
       </c>
       <c r="B4" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>409793</v>
+        <v>408997</v>
       </c>
       <c r="R4" t="n">
-        <v>6782448</v>
+        <v>6782283</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,10 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129032876</v>
+        <v>129011403</v>
       </c>
       <c r="B5" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1021,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>408997</v>
+        <v>409706</v>
       </c>
       <c r="R5" t="n">
-        <v>6782283</v>
+        <v>6782359</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1054,9 +1044,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,12 +1071,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1086,7 +1086,7 @@
         <v>129032905</v>
       </c>
       <c r="B6" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1180,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129032394</v>
+        <v>129032907</v>
       </c>
       <c r="B7" t="n">
-        <v>79625</v>
+        <v>79039</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>409553</v>
+        <v>409686</v>
       </c>
       <c r="R7" t="n">
-        <v>6782378</v>
+        <v>6782351</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1265,22 +1265,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129032907</v>
+        <v>129011389</v>
       </c>
       <c r="B8" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>409686</v>
+        <v>409278</v>
       </c>
       <c r="R8" t="n">
-        <v>6782351</v>
+        <v>6782361</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1345,9 +1345,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1362,12 +1372,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1377,7 +1387,7 @@
         <v>129032919</v>
       </c>
       <c r="B9" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1471,10 +1481,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129011389</v>
+        <v>129032394</v>
       </c>
       <c r="B10" t="n">
-        <v>79035</v>
+        <v>79629</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1482,21 +1492,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1506,10 +1516,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>409278</v>
+        <v>409553</v>
       </c>
       <c r="R10" t="n">
-        <v>6782361</v>
+        <v>6782378</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1539,19 +1549,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>15:18</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>15:18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1566,12 +1566,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1581,7 +1581,7 @@
         <v>129032398</v>
       </c>
       <c r="B11" t="n">
-        <v>91546</v>
+        <v>91553</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1675,10 +1675,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129032894</v>
+        <v>129011398</v>
       </c>
       <c r="B12" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1710,10 +1710,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>409292</v>
+        <v>409596</v>
       </c>
       <c r="R12" t="n">
-        <v>6782306</v>
+        <v>6782395</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1743,9 +1743,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1760,22 +1770,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129011398</v>
+        <v>129032894</v>
       </c>
       <c r="B13" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1807,10 +1817,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>409596</v>
+        <v>409292</v>
       </c>
       <c r="R13" t="n">
-        <v>6782395</v>
+        <v>6782306</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1840,19 +1850,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>13:08</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>13:08</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1867,22 +1867,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129032909</v>
+        <v>129011378</v>
       </c>
       <c r="B14" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1914,10 +1914,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>409727</v>
+        <v>408984</v>
       </c>
       <c r="R14" t="n">
-        <v>6782352</v>
+        <v>6782347</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1947,9 +1947,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1964,22 +1974,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129011378</v>
+        <v>129032392</v>
       </c>
       <c r="B15" t="n">
-        <v>79035</v>
+        <v>79658</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1987,21 +1997,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2011,10 +2021,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>408984</v>
+        <v>409554</v>
       </c>
       <c r="R15" t="n">
-        <v>6782347</v>
+        <v>6782380</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2044,19 +2054,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>16:10</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>16:10</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2071,22 +2071,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129032392</v>
+        <v>129032897</v>
       </c>
       <c r="B16" t="n">
-        <v>79654</v>
+        <v>79039</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2094,21 +2094,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2118,10 +2118,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>409554</v>
+        <v>409469</v>
       </c>
       <c r="R16" t="n">
-        <v>6782380</v>
+        <v>6782371</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2168,22 +2168,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129032897</v>
+        <v>129032909</v>
       </c>
       <c r="B17" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>409469</v>
+        <v>409727</v>
       </c>
       <c r="R17" t="n">
-        <v>6782371</v>
+        <v>6782352</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2280,7 +2280,7 @@
         <v>129011376</v>
       </c>
       <c r="B18" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2384,10 +2384,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129032892</v>
+        <v>129032885</v>
       </c>
       <c r="B19" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2419,10 +2419,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>409244</v>
+        <v>409078</v>
       </c>
       <c r="R19" t="n">
-        <v>6782381</v>
+        <v>6782312</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2484,7 +2484,7 @@
         <v>129011400</v>
       </c>
       <c r="B20" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2588,10 +2588,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129032868</v>
+        <v>129032892</v>
       </c>
       <c r="B21" t="n">
-        <v>57723</v>
+        <v>79039</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2599,21 +2599,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2623,10 +2623,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>409688</v>
+        <v>409244</v>
       </c>
       <c r="R21" t="n">
-        <v>6782303</v>
+        <v>6782381</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2685,10 +2685,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129032885</v>
+        <v>129032868</v>
       </c>
       <c r="B22" t="n">
-        <v>79035</v>
+        <v>57725</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2696,21 +2696,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2720,10 +2720,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>409078</v>
+        <v>409688</v>
       </c>
       <c r="R22" t="n">
-        <v>6782312</v>
+        <v>6782303</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2782,10 +2782,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129011395</v>
+        <v>129011383</v>
       </c>
       <c r="B23" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2817,10 +2817,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>409555</v>
+        <v>409028</v>
       </c>
       <c r="R23" t="n">
-        <v>6782356</v>
+        <v>6782350</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2852,7 +2852,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2889,10 +2889,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129011407</v>
+        <v>129011395</v>
       </c>
       <c r="B24" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2924,10 +2924,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>409795</v>
+        <v>409555</v>
       </c>
       <c r="R24" t="n">
-        <v>6782327</v>
+        <v>6782356</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2996,10 +2996,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129032395</v>
+        <v>129011407</v>
       </c>
       <c r="B25" t="n">
-        <v>57723</v>
+        <v>79039</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3007,42 +3007,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>409759</v>
+        <v>409795</v>
       </c>
       <c r="R25" t="n">
-        <v>6782358</v>
+        <v>6782327</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3072,9 +3064,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3089,22 +3091,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129011383</v>
+        <v>129032393</v>
       </c>
       <c r="B26" t="n">
-        <v>79035</v>
+        <v>79629</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3112,21 +3114,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3136,10 +3138,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>409028</v>
+        <v>409554</v>
       </c>
       <c r="R26" t="n">
-        <v>6782350</v>
+        <v>6782380</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3169,19 +3171,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>16:04</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>16:04</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3196,12 +3188,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3211,7 +3203,7 @@
         <v>129032399</v>
       </c>
       <c r="B27" t="n">
-        <v>91546</v>
+        <v>91553</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3308,7 +3300,7 @@
         <v>129011374</v>
       </c>
       <c r="B28" t="n">
-        <v>91546</v>
+        <v>91553</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3425,10 +3417,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129032393</v>
+        <v>129032395</v>
       </c>
       <c r="B29" t="n">
-        <v>79625</v>
+        <v>57725</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3436,34 +3428,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>409554</v>
+        <v>409759</v>
       </c>
       <c r="R29" t="n">
-        <v>6782380</v>
+        <v>6782358</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3525,7 +3525,7 @@
         <v>129032913</v>
       </c>
       <c r="B30" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3622,7 +3622,7 @@
         <v>129032406</v>
       </c>
       <c r="B31" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         <v>129032882</v>
       </c>
       <c r="B32" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3813,10 +3813,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129032878</v>
+        <v>129011391</v>
       </c>
       <c r="B33" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3848,10 +3848,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>408966</v>
+        <v>409349</v>
       </c>
       <c r="R33" t="n">
-        <v>6782283</v>
+        <v>6782383</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3881,9 +3881,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3898,22 +3908,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129011369</v>
+        <v>129032878</v>
       </c>
       <c r="B34" t="n">
-        <v>57723</v>
+        <v>79039</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3921,42 +3931,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>409683</v>
+        <v>408966</v>
       </c>
       <c r="R34" t="n">
-        <v>6782391</v>
+        <v>6782283</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3986,19 +3988,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>12:56</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>12:56</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4013,22 +4005,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129011391</v>
+        <v>129011369</v>
       </c>
       <c r="B35" t="n">
-        <v>79035</v>
+        <v>57725</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4036,34 +4028,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>409349</v>
+        <v>409683</v>
       </c>
       <c r="R35" t="n">
-        <v>6782383</v>
+        <v>6782391</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4095,7 +4095,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4105,7 +4105,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4132,10 +4132,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129011381</v>
+        <v>129032887</v>
       </c>
       <c r="B36" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4167,10 +4167,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>409010</v>
+        <v>409176</v>
       </c>
       <c r="R36" t="n">
-        <v>6782383</v>
+        <v>6782420</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4200,19 +4200,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>16:06</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>16:06</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4227,22 +4217,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129032887</v>
+        <v>129011381</v>
       </c>
       <c r="B37" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4274,10 +4264,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>409176</v>
+        <v>409010</v>
       </c>
       <c r="R37" t="n">
-        <v>6782420</v>
+        <v>6782383</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4307,9 +4297,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4324,22 +4324,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129011392</v>
+        <v>129032891</v>
       </c>
       <c r="B38" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4371,10 +4371,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>409361</v>
+        <v>409241</v>
       </c>
       <c r="R38" t="n">
-        <v>6782401</v>
+        <v>6782372</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4404,19 +4404,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>14:31</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>14:31</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4431,22 +4421,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129011394</v>
+        <v>129011392</v>
       </c>
       <c r="B39" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4478,10 +4468,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>409543</v>
+        <v>409361</v>
       </c>
       <c r="R39" t="n">
-        <v>6782361</v>
+        <v>6782401</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4513,7 +4503,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4523,7 +4513,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4550,10 +4540,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129011399</v>
+        <v>129032911</v>
       </c>
       <c r="B40" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4585,10 +4575,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>409609</v>
+        <v>409777</v>
       </c>
       <c r="R40" t="n">
-        <v>6782404</v>
+        <v>6782445</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4618,19 +4608,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>13:06</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>13:06</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4645,22 +4625,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129032891</v>
+        <v>129032906</v>
       </c>
       <c r="B41" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4692,10 +4672,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>409241</v>
+        <v>409684</v>
       </c>
       <c r="R41" t="n">
-        <v>6782372</v>
+        <v>6782322</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4754,10 +4734,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129032911</v>
+        <v>129032407</v>
       </c>
       <c r="B42" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4789,10 +4769,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>409777</v>
+        <v>409659</v>
       </c>
       <c r="R42" t="n">
-        <v>6782445</v>
+        <v>6782436</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4839,22 +4819,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129032906</v>
+        <v>129032910</v>
       </c>
       <c r="B43" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4886,10 +4866,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>409684</v>
+        <v>409744</v>
       </c>
       <c r="R43" t="n">
-        <v>6782322</v>
+        <v>6782394</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4948,10 +4928,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129032407</v>
+        <v>129011394</v>
       </c>
       <c r="B44" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4983,10 +4963,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>409659</v>
+        <v>409543</v>
       </c>
       <c r="R44" t="n">
-        <v>6782436</v>
+        <v>6782361</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5016,9 +4996,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5033,22 +5023,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129032910</v>
+        <v>129011399</v>
       </c>
       <c r="B45" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5080,10 +5070,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>409744</v>
+        <v>409609</v>
       </c>
       <c r="R45" t="n">
-        <v>6782394</v>
+        <v>6782404</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5113,9 +5103,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5130,22 +5130,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129032883</v>
+        <v>129011408</v>
       </c>
       <c r="B46" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5177,10 +5177,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>409010</v>
+        <v>409801</v>
       </c>
       <c r="R46" t="n">
-        <v>6782399</v>
+        <v>6782315</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5210,9 +5210,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5227,22 +5237,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129032884</v>
+        <v>129032883</v>
       </c>
       <c r="B47" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5274,10 +5284,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>409039</v>
+        <v>409010</v>
       </c>
       <c r="R47" t="n">
-        <v>6782290</v>
+        <v>6782399</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5336,10 +5346,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129011408</v>
+        <v>129011380</v>
       </c>
       <c r="B48" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5371,10 +5381,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>409801</v>
+        <v>408984</v>
       </c>
       <c r="R48" t="n">
-        <v>6782315</v>
+        <v>6782385</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5406,7 +5416,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5416,7 +5426,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5443,10 +5453,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129011380</v>
+        <v>129032884</v>
       </c>
       <c r="B49" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5478,10 +5488,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>408984</v>
+        <v>409039</v>
       </c>
       <c r="R49" t="n">
-        <v>6782385</v>
+        <v>6782290</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5511,19 +5521,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>16:07</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>16:07</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5538,12 +5538,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -5553,7 +5553,7 @@
         <v>129032869</v>
       </c>
       <c r="B50" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5650,7 +5650,7 @@
         <v>129011401</v>
       </c>
       <c r="B51" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5754,10 +5754,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129011386</v>
+        <v>129032899</v>
       </c>
       <c r="B52" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5789,10 +5789,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>409210</v>
+        <v>409397</v>
       </c>
       <c r="R52" t="n">
-        <v>6782365</v>
+        <v>6782272</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5822,19 +5822,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>15:26</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>15:26</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5849,22 +5839,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129011409</v>
+        <v>129011386</v>
       </c>
       <c r="B53" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5896,10 +5886,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>409202</v>
+        <v>409210</v>
       </c>
       <c r="R53" t="n">
-        <v>6782367</v>
+        <v>6782365</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5950,7 +5940,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -5969,10 +5958,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129032899</v>
+        <v>129011409</v>
       </c>
       <c r="B54" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6004,10 +5993,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>409397</v>
+        <v>409202</v>
       </c>
       <c r="R54" t="n">
-        <v>6782272</v>
+        <v>6782367</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6037,29 +6026,40 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -6069,7 +6069,7 @@
         <v>129011396</v>
       </c>
       <c r="B55" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6176,7 +6176,7 @@
         <v>129032866</v>
       </c>
       <c r="B56" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6270,10 +6270,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129032889</v>
+        <v>129011373</v>
       </c>
       <c r="B57" t="n">
-        <v>79035</v>
+        <v>91553</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6281,34 +6281,41 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>409164</v>
+        <v>409435</v>
       </c>
       <c r="R57" t="n">
-        <v>6782308</v>
+        <v>6782383</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6338,39 +6345,55 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>4 st på samma tall</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129032403</v>
+        <v>129011372</v>
       </c>
       <c r="B58" t="n">
-        <v>79035</v>
+        <v>57725</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6378,34 +6401,42 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>409021</v>
+        <v>409796</v>
       </c>
       <c r="R58" t="n">
-        <v>6782365</v>
+        <v>6782327</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6435,9 +6466,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6452,22 +6493,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129011375</v>
+        <v>129032889</v>
       </c>
       <c r="B59" t="n">
-        <v>78792</v>
+        <v>79039</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6475,21 +6516,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6499,10 +6540,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>409335</v>
+        <v>409164</v>
       </c>
       <c r="R59" t="n">
-        <v>6782352</v>
+        <v>6782308</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6532,19 +6573,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>14:40</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>14:40</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6559,22 +6590,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129011373</v>
+        <v>129011375</v>
       </c>
       <c r="B60" t="n">
-        <v>91546</v>
+        <v>78796</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6582,41 +6613,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5442</v>
+        <v>6446</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>409435</v>
+        <v>409335</v>
       </c>
       <c r="R60" t="n">
-        <v>6782383</v>
+        <v>6782352</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6648,7 +6672,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6658,12 +6682,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:14</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>4 st på samma tall</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6672,7 +6691,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6691,10 +6709,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129011372</v>
+        <v>129032403</v>
       </c>
       <c r="B61" t="n">
-        <v>57723</v>
+        <v>79039</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6702,42 +6720,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>409796</v>
+        <v>409021</v>
       </c>
       <c r="R61" t="n">
-        <v>6782327</v>
+        <v>6782365</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6767,19 +6777,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>11:10</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6794,44 +6794,44 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129032400</v>
+        <v>129011387</v>
       </c>
       <c r="B62" t="n">
-        <v>91981</v>
+        <v>79039</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6841,10 +6841,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>409738</v>
+        <v>409232</v>
       </c>
       <c r="R62" t="n">
-        <v>6782382</v>
+        <v>6782353</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6874,9 +6874,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6891,22 +6901,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129032874</v>
+        <v>129032872</v>
       </c>
       <c r="B63" t="n">
-        <v>91544</v>
+        <v>78796</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6914,21 +6924,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5432</v>
+        <v>6446</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6938,10 +6948,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>409405</v>
+        <v>409594</v>
       </c>
       <c r="R63" t="n">
-        <v>6782366</v>
+        <v>6782294</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7003,7 +7013,7 @@
         <v>129032886</v>
       </c>
       <c r="B64" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7097,10 +7107,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129011379</v>
+        <v>129011384</v>
       </c>
       <c r="B65" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7132,10 +7142,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>408991</v>
+        <v>409068</v>
       </c>
       <c r="R65" t="n">
-        <v>6782360</v>
+        <v>6782377</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7167,7 +7177,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7177,7 +7187,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7204,10 +7214,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129032914</v>
+        <v>129011379</v>
       </c>
       <c r="B66" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7239,10 +7249,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>409759</v>
+        <v>408991</v>
       </c>
       <c r="R66" t="n">
-        <v>6782343</v>
+        <v>6782360</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7272,9 +7282,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7289,22 +7309,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129032396</v>
+        <v>129032914</v>
       </c>
       <c r="B67" t="n">
-        <v>57723</v>
+        <v>79039</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7312,42 +7332,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>409753</v>
+        <v>409759</v>
       </c>
       <c r="R67" t="n">
-        <v>6782323</v>
+        <v>6782343</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7394,12 +7406,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -7409,7 +7421,7 @@
         <v>129032867</v>
       </c>
       <c r="B68" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7503,10 +7515,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129011387</v>
+        <v>129032396</v>
       </c>
       <c r="B69" t="n">
-        <v>79035</v>
+        <v>57725</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7514,34 +7526,42 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>409232</v>
+        <v>409753</v>
       </c>
       <c r="R69" t="n">
-        <v>6782353</v>
+        <v>6782323</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7571,19 +7591,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>15:22</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>15:22</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7598,44 +7608,44 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129011384</v>
+        <v>129032400</v>
       </c>
       <c r="B70" t="n">
-        <v>79035</v>
+        <v>91988</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7645,10 +7655,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>409068</v>
+        <v>409738</v>
       </c>
       <c r="R70" t="n">
-        <v>6782377</v>
+        <v>6782382</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7678,19 +7688,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>15:43</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>15:43</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7705,22 +7705,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129032872</v>
+        <v>129032874</v>
       </c>
       <c r="B71" t="n">
-        <v>78792</v>
+        <v>91551</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7728,21 +7728,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6446</v>
+        <v>5432</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7752,10 +7752,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>409594</v>
+        <v>409405</v>
       </c>
       <c r="R71" t="n">
-        <v>6782294</v>
+        <v>6782366</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7817,7 +7817,7 @@
         <v>129032873</v>
       </c>
       <c r="B72" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7918,7 +7918,7 @@
         <v>129032896</v>
       </c>
       <c r="B73" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8015,7 +8015,7 @@
         <v>129032902</v>
       </c>
       <c r="B74" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8112,7 +8112,7 @@
         <v>129032917</v>
       </c>
       <c r="B75" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8209,7 +8209,7 @@
         <v>129032900</v>
       </c>
       <c r="B76" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8303,10 +8303,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129032402</v>
+        <v>129032893</v>
       </c>
       <c r="B77" t="n">
-        <v>91544</v>
+        <v>79039</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8314,21 +8314,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8338,10 +8338,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>409767</v>
+        <v>409280</v>
       </c>
       <c r="R77" t="n">
-        <v>6782352</v>
+        <v>6782382</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8388,22 +8388,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129032893</v>
+        <v>129011404</v>
       </c>
       <c r="B78" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8435,10 +8435,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>409280</v>
+        <v>409736</v>
       </c>
       <c r="R78" t="n">
-        <v>6782382</v>
+        <v>6782394</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8468,9 +8468,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8485,22 +8495,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129011404</v>
+        <v>129032901</v>
       </c>
       <c r="B79" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8532,10 +8542,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>409736</v>
+        <v>409528</v>
       </c>
       <c r="R79" t="n">
-        <v>6782394</v>
+        <v>6782292</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8565,19 +8575,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>11:59</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>11:59</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8592,22 +8592,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129032901</v>
+        <v>129032888</v>
       </c>
       <c r="B80" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8639,10 +8639,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>409528</v>
+        <v>409127</v>
       </c>
       <c r="R80" t="n">
-        <v>6782292</v>
+        <v>6782290</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8701,10 +8701,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129032888</v>
+        <v>129032402</v>
       </c>
       <c r="B81" t="n">
-        <v>79035</v>
+        <v>91551</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8712,21 +8712,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8736,10 +8736,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>409127</v>
+        <v>409767</v>
       </c>
       <c r="R81" t="n">
-        <v>6782290</v>
+        <v>6782352</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8786,12 +8786,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
@@ -8801,7 +8801,7 @@
         <v>129032908</v>
       </c>
       <c r="B82" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8898,7 +8898,7 @@
         <v>129032879</v>
       </c>
       <c r="B83" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8992,10 +8992,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129032916</v>
+        <v>129032409</v>
       </c>
       <c r="B84" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9027,10 +9027,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>409812</v>
+        <v>409782</v>
       </c>
       <c r="R84" t="n">
-        <v>6782309</v>
+        <v>6782339</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9077,22 +9077,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129032409</v>
+        <v>129032916</v>
       </c>
       <c r="B85" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9124,10 +9124,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>409782</v>
+        <v>409812</v>
       </c>
       <c r="R85" t="n">
-        <v>6782339</v>
+        <v>6782309</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9174,12 +9174,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
@@ -9189,7 +9189,7 @@
         <v>129032898</v>
       </c>
       <c r="B86" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9286,7 +9286,7 @@
         <v>129032918</v>
       </c>
       <c r="B87" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9380,10 +9380,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129032870</v>
+        <v>129011370</v>
       </c>
       <c r="B88" t="n">
-        <v>91546</v>
+        <v>57725</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9391,34 +9391,31 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
@@ -9426,10 +9423,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>409530</v>
+        <v>409759</v>
       </c>
       <c r="R88" t="n">
-        <v>6782289</v>
+        <v>6782330</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9459,40 +9456,49 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AD88" t="b">
         <v>0</v>
       </c>
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129011370</v>
+        <v>129032870</v>
       </c>
       <c r="B89" t="n">
-        <v>57723</v>
+        <v>91553</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9500,31 +9506,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
@@ -9532,10 +9541,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>409759</v>
+        <v>409530</v>
       </c>
       <c r="R89" t="n">
-        <v>6782330</v>
+        <v>6782289</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9565,49 +9574,40 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
       <c r="AD89" t="b">
         <v>0</v>
       </c>
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129032895</v>
+        <v>129011393</v>
       </c>
       <c r="B90" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9639,10 +9639,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>409310</v>
+        <v>409472</v>
       </c>
       <c r="R90" t="n">
-        <v>6782326</v>
+        <v>6782351</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9672,9 +9672,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9689,22 +9699,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129032903</v>
+        <v>129032895</v>
       </c>
       <c r="B91" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9736,10 +9746,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>409582</v>
+        <v>409310</v>
       </c>
       <c r="R91" t="n">
-        <v>6782297</v>
+        <v>6782326</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9798,10 +9808,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129032880</v>
+        <v>129032903</v>
       </c>
       <c r="B92" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9833,10 +9843,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>408901</v>
+        <v>409582</v>
       </c>
       <c r="R92" t="n">
-        <v>6782390</v>
+        <v>6782297</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9895,10 +9905,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129032405</v>
+        <v>129032880</v>
       </c>
       <c r="B93" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9930,10 +9940,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>409048</v>
+        <v>408901</v>
       </c>
       <c r="R93" t="n">
-        <v>6782365</v>
+        <v>6782390</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9980,22 +9990,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129011393</v>
+        <v>129032405</v>
       </c>
       <c r="B94" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10027,10 +10037,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>409472</v>
+        <v>409048</v>
       </c>
       <c r="R94" t="n">
-        <v>6782351</v>
+        <v>6782365</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10060,19 +10070,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z94" t="inlineStr">
-        <is>
-          <t>14:05</t>
-        </is>
-      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>14:05</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10087,12 +10087,12 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
@@ -10102,7 +10102,7 @@
         <v>129011388</v>
       </c>
       <c r="B95" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10206,10 +10206,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129032912</v>
+        <v>129011406</v>
       </c>
       <c r="B96" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10241,10 +10241,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>409762</v>
+        <v>409759</v>
       </c>
       <c r="R96" t="n">
-        <v>6782335</v>
+        <v>6782314</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10274,9 +10274,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10291,22 +10301,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129032890</v>
+        <v>129032408</v>
       </c>
       <c r="B97" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10338,10 +10348,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>409228</v>
+        <v>409749</v>
       </c>
       <c r="R97" t="n">
-        <v>6782298</v>
+        <v>6782325</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10388,22 +10398,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129032875</v>
+        <v>129032912</v>
       </c>
       <c r="B98" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10435,10 +10445,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>409034</v>
+        <v>409762</v>
       </c>
       <c r="R98" t="n">
-        <v>6782261</v>
+        <v>6782335</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10497,10 +10507,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129011390</v>
+        <v>129032890</v>
       </c>
       <c r="B99" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10532,10 +10542,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>409349</v>
+        <v>409228</v>
       </c>
       <c r="R99" t="n">
-        <v>6782376</v>
+        <v>6782298</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10565,19 +10575,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>14:34</t>
-        </is>
-      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>14:34</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10592,22 +10592,22 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129011406</v>
+        <v>129032875</v>
       </c>
       <c r="B100" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10639,10 +10639,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>409759</v>
+        <v>409034</v>
       </c>
       <c r="R100" t="n">
-        <v>6782314</v>
+        <v>6782261</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10672,19 +10672,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>11:41</t>
-        </is>
-      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>11:41</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10699,22 +10689,22 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129032408</v>
+        <v>129011390</v>
       </c>
       <c r="B101" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10746,10 +10736,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>409749</v>
+        <v>409349</v>
       </c>
       <c r="R101" t="n">
-        <v>6782325</v>
+        <v>6782376</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10779,9 +10769,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10796,12 +10796,12 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
@@ -10811,7 +10811,7 @@
         <v>129032401</v>
       </c>
       <c r="B102" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10908,7 +10908,7 @@
         <v>129011377</v>
       </c>
       <c r="B103" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11012,10 +11012,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129032877</v>
+        <v>129011402</v>
       </c>
       <c r="B104" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11047,10 +11047,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>408994</v>
+        <v>409671</v>
       </c>
       <c r="R104" t="n">
-        <v>6782293</v>
+        <v>6782390</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11080,9 +11080,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11097,22 +11107,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129032904</v>
+        <v>129011385</v>
       </c>
       <c r="B105" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11144,10 +11154,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>409568</v>
+        <v>409214</v>
       </c>
       <c r="R105" t="n">
-        <v>6782383</v>
+        <v>6782345</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11177,9 +11187,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11194,22 +11214,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129032915</v>
+        <v>129032877</v>
       </c>
       <c r="B106" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11241,10 +11261,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>409765</v>
+        <v>408994</v>
       </c>
       <c r="R106" t="n">
-        <v>6782330</v>
+        <v>6782293</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11303,10 +11323,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129011402</v>
+        <v>129032904</v>
       </c>
       <c r="B107" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11338,10 +11358,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>409671</v>
+        <v>409568</v>
       </c>
       <c r="R107" t="n">
-        <v>6782390</v>
+        <v>6782383</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11371,19 +11391,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z107" t="inlineStr">
-        <is>
-          <t>12:57</t>
-        </is>
-      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB107" t="inlineStr">
-        <is>
-          <t>12:57</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11398,22 +11408,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129011385</v>
+        <v>129032915</v>
       </c>
       <c r="B108" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11445,10 +11455,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>409214</v>
+        <v>409765</v>
       </c>
       <c r="R108" t="n">
-        <v>6782345</v>
+        <v>6782330</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11478,19 +11488,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z108" t="inlineStr">
-        <is>
-          <t>15:29</t>
-        </is>
-      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB108" t="inlineStr">
-        <is>
-          <t>15:29</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11505,12 +11505,12 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>

--- a/artfynd/A 47938-2025 artfynd.xlsx
+++ b/artfynd/A 47938-2025 artfynd.xlsx
@@ -1180,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129032907</v>
+        <v>129032394</v>
       </c>
       <c r="B7" t="n">
-        <v>79039</v>
+        <v>79629</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>409686</v>
+        <v>409553</v>
       </c>
       <c r="R7" t="n">
-        <v>6782351</v>
+        <v>6782378</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1265,19 +1265,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129011389</v>
+        <v>129032907</v>
       </c>
       <c r="B8" t="n">
         <v>79039</v>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>409278</v>
+        <v>409686</v>
       </c>
       <c r="R8" t="n">
-        <v>6782361</v>
+        <v>6782351</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1345,19 +1345,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>15:18</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>15:18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1372,19 +1362,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129032919</v>
+        <v>129011389</v>
       </c>
       <c r="B9" t="n">
         <v>79039</v>
@@ -1419,10 +1409,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>409358</v>
+        <v>409278</v>
       </c>
       <c r="R9" t="n">
-        <v>6782291</v>
+        <v>6782361</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1452,9 +1442,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1469,22 +1469,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129032394</v>
+        <v>129032919</v>
       </c>
       <c r="B10" t="n">
-        <v>79629</v>
+        <v>79039</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1492,21 +1492,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>409553</v>
+        <v>409358</v>
       </c>
       <c r="R10" t="n">
-        <v>6782378</v>
+        <v>6782291</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1566,12 +1566,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -2384,10 +2384,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129032885</v>
+        <v>129032868</v>
       </c>
       <c r="B19" t="n">
-        <v>79039</v>
+        <v>57725</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2395,21 +2395,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2419,10 +2419,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>409078</v>
+        <v>409688</v>
       </c>
       <c r="R19" t="n">
-        <v>6782312</v>
+        <v>6782303</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2481,7 +2481,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129011400</v>
+        <v>129032885</v>
       </c>
       <c r="B20" t="n">
         <v>79039</v>
@@ -2516,10 +2516,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>409643</v>
+        <v>409078</v>
       </c>
       <c r="R20" t="n">
-        <v>6782378</v>
+        <v>6782312</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2549,19 +2549,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>12:59</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>12:59</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2576,19 +2566,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129032892</v>
+        <v>129011400</v>
       </c>
       <c r="B21" t="n">
         <v>79039</v>
@@ -2623,10 +2613,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>409244</v>
+        <v>409643</v>
       </c>
       <c r="R21" t="n">
-        <v>6782381</v>
+        <v>6782378</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2656,9 +2646,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2673,22 +2673,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129032868</v>
+        <v>129032892</v>
       </c>
       <c r="B22" t="n">
-        <v>57725</v>
+        <v>79039</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2696,21 +2696,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2720,10 +2720,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>409688</v>
+        <v>409244</v>
       </c>
       <c r="R22" t="n">
-        <v>6782303</v>
+        <v>6782381</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2782,10 +2782,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129011383</v>
+        <v>129032399</v>
       </c>
       <c r="B23" t="n">
-        <v>79039</v>
+        <v>91553</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2793,21 +2793,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2817,10 +2817,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>409028</v>
+        <v>409492</v>
       </c>
       <c r="R23" t="n">
-        <v>6782350</v>
+        <v>6782346</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2850,19 +2850,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>16:04</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>16:04</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2877,22 +2867,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129011395</v>
+        <v>129011374</v>
       </c>
       <c r="B24" t="n">
-        <v>79039</v>
+        <v>91553</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2900,34 +2890,41 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>409555</v>
+        <v>409475</v>
       </c>
       <c r="R24" t="n">
-        <v>6782356</v>
+        <v>6782342</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2959,7 +2956,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -2969,7 +2966,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>hackspetthål under tickorna</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2978,6 +2980,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -2996,7 +2999,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129011407</v>
+        <v>129011383</v>
       </c>
       <c r="B25" t="n">
         <v>79039</v>
@@ -3031,10 +3034,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>409795</v>
+        <v>409028</v>
       </c>
       <c r="R25" t="n">
-        <v>6782327</v>
+        <v>6782350</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3066,7 +3069,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3076,7 +3079,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3103,10 +3106,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129032393</v>
+        <v>129011395</v>
       </c>
       <c r="B26" t="n">
-        <v>79629</v>
+        <v>79039</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3114,21 +3117,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3138,10 +3141,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>409554</v>
+        <v>409555</v>
       </c>
       <c r="R26" t="n">
-        <v>6782380</v>
+        <v>6782356</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3171,9 +3174,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3188,22 +3201,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129032399</v>
+        <v>129011407</v>
       </c>
       <c r="B27" t="n">
-        <v>91553</v>
+        <v>79039</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3211,21 +3224,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3235,10 +3248,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>409492</v>
+        <v>409795</v>
       </c>
       <c r="R27" t="n">
-        <v>6782346</v>
+        <v>6782327</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3268,9 +3281,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3285,22 +3308,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129011374</v>
+        <v>129032395</v>
       </c>
       <c r="B28" t="n">
-        <v>91553</v>
+        <v>57725</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3308,30 +3331,31 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3339,10 +3363,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>409475</v>
+        <v>409759</v>
       </c>
       <c r="R28" t="n">
-        <v>6782342</v>
+        <v>6782358</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3372,55 +3396,39 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>13:57</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>13:57</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>hackspetthål under tickorna</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129032395</v>
+        <v>129032393</v>
       </c>
       <c r="B29" t="n">
-        <v>57725</v>
+        <v>79629</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3428,42 +3436,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>409759</v>
+        <v>409554</v>
       </c>
       <c r="R29" t="n">
-        <v>6782358</v>
+        <v>6782380</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -7418,32 +7418,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129032867</v>
+        <v>129032400</v>
       </c>
       <c r="B68" t="n">
-        <v>57725</v>
+        <v>91988</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7453,10 +7453,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>409693</v>
+        <v>409738</v>
       </c>
       <c r="R68" t="n">
-        <v>6782357</v>
+        <v>6782382</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7503,22 +7503,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129032396</v>
+        <v>129032874</v>
       </c>
       <c r="B69" t="n">
-        <v>57725</v>
+        <v>91551</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7526,42 +7526,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>409753</v>
+        <v>409405</v>
       </c>
       <c r="R69" t="n">
-        <v>6782323</v>
+        <v>6782366</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7608,44 +7600,44 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129032400</v>
+        <v>129032867</v>
       </c>
       <c r="B70" t="n">
-        <v>91988</v>
+        <v>57725</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7655,10 +7647,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>409738</v>
+        <v>409693</v>
       </c>
       <c r="R70" t="n">
-        <v>6782382</v>
+        <v>6782357</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7705,22 +7697,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129032874</v>
+        <v>129032396</v>
       </c>
       <c r="B71" t="n">
-        <v>91551</v>
+        <v>57725</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7728,34 +7720,42 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>409405</v>
+        <v>409753</v>
       </c>
       <c r="R71" t="n">
-        <v>6782366</v>
+        <v>6782323</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7802,12 +7802,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>

--- a/artfynd/A 47938-2025 artfynd.xlsx
+++ b/artfynd/A 47938-2025 artfynd.xlsx
@@ -1180,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129032394</v>
+        <v>129032907</v>
       </c>
       <c r="B7" t="n">
-        <v>79629</v>
+        <v>79039</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>409553</v>
+        <v>409686</v>
       </c>
       <c r="R7" t="n">
-        <v>6782378</v>
+        <v>6782351</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1265,19 +1265,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129032907</v>
+        <v>129032919</v>
       </c>
       <c r="B8" t="n">
         <v>79039</v>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>409686</v>
+        <v>409358</v>
       </c>
       <c r="R8" t="n">
-        <v>6782351</v>
+        <v>6782291</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1374,10 +1374,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129011389</v>
+        <v>129032394</v>
       </c>
       <c r="B9" t="n">
-        <v>79039</v>
+        <v>79629</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1385,21 +1385,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1409,10 +1409,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>409278</v>
+        <v>409553</v>
       </c>
       <c r="R9" t="n">
-        <v>6782361</v>
+        <v>6782378</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1442,19 +1442,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>15:18</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>15:18</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1469,19 +1459,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129032919</v>
+        <v>129011389</v>
       </c>
       <c r="B10" t="n">
         <v>79039</v>
@@ -1516,10 +1506,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>409358</v>
+        <v>409278</v>
       </c>
       <c r="R10" t="n">
-        <v>6782291</v>
+        <v>6782361</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1549,9 +1539,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1566,12 +1566,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1581,7 +1581,7 @@
         <v>129032398</v>
       </c>
       <c r="B11" t="n">
-        <v>91553</v>
+        <v>91560</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129011398</v>
+        <v>129032894</v>
       </c>
       <c r="B12" t="n">
         <v>79039</v>
@@ -1710,10 +1710,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>409596</v>
+        <v>409292</v>
       </c>
       <c r="R12" t="n">
-        <v>6782395</v>
+        <v>6782306</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1743,19 +1743,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>13:08</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>13:08</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1770,19 +1760,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129032894</v>
+        <v>129011398</v>
       </c>
       <c r="B13" t="n">
         <v>79039</v>
@@ -1817,10 +1807,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>409292</v>
+        <v>409596</v>
       </c>
       <c r="R13" t="n">
-        <v>6782306</v>
+        <v>6782395</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1850,9 +1840,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1867,19 +1867,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129011378</v>
+        <v>129032897</v>
       </c>
       <c r="B14" t="n">
         <v>79039</v>
@@ -1914,10 +1914,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>408984</v>
+        <v>409469</v>
       </c>
       <c r="R14" t="n">
-        <v>6782347</v>
+        <v>6782371</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1947,19 +1947,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>16:10</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>16:10</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1974,22 +1964,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129032392</v>
+        <v>129032909</v>
       </c>
       <c r="B15" t="n">
-        <v>79658</v>
+        <v>79039</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1997,21 +1987,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2021,10 +2011,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>409554</v>
+        <v>409727</v>
       </c>
       <c r="R15" t="n">
-        <v>6782380</v>
+        <v>6782352</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2071,19 +2061,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129032897</v>
+        <v>129011378</v>
       </c>
       <c r="B16" t="n">
         <v>79039</v>
@@ -2118,10 +2108,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>409469</v>
+        <v>408984</v>
       </c>
       <c r="R16" t="n">
-        <v>6782371</v>
+        <v>6782347</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2151,9 +2141,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2168,22 +2168,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129032909</v>
+        <v>129032392</v>
       </c>
       <c r="B17" t="n">
-        <v>79039</v>
+        <v>79658</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2191,21 +2191,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>409727</v>
+        <v>409554</v>
       </c>
       <c r="R17" t="n">
-        <v>6782352</v>
+        <v>6782380</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2265,22 +2265,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129011376</v>
+        <v>129011400</v>
       </c>
       <c r="B18" t="n">
-        <v>91551</v>
+        <v>79039</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2288,21 +2288,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2312,10 +2312,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>409774</v>
+        <v>409643</v>
       </c>
       <c r="R18" t="n">
-        <v>6782323</v>
+        <v>6782378</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2357,7 +2357,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2481,10 +2481,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129032885</v>
+        <v>129011376</v>
       </c>
       <c r="B20" t="n">
-        <v>79039</v>
+        <v>91558</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2492,21 +2492,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2516,10 +2516,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>409078</v>
+        <v>409774</v>
       </c>
       <c r="R20" t="n">
-        <v>6782312</v>
+        <v>6782323</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2549,9 +2549,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2566,19 +2576,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129011400</v>
+        <v>129032885</v>
       </c>
       <c r="B21" t="n">
         <v>79039</v>
@@ -2613,10 +2623,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>409643</v>
+        <v>409078</v>
       </c>
       <c r="R21" t="n">
-        <v>6782378</v>
+        <v>6782312</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2646,19 +2656,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>12:59</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>12:59</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2673,12 +2673,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2785,7 +2785,7 @@
         <v>129032399</v>
       </c>
       <c r="B23" t="n">
-        <v>91553</v>
+        <v>91560</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>129011374</v>
       </c>
       <c r="B24" t="n">
-        <v>91553</v>
+        <v>91560</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129011395</v>
+        <v>129011407</v>
       </c>
       <c r="B26" t="n">
         <v>79039</v>
@@ -3141,10 +3141,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>409555</v>
+        <v>409795</v>
       </c>
       <c r="R26" t="n">
-        <v>6782356</v>
+        <v>6782327</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3176,7 +3176,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3213,7 +3213,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129011407</v>
+        <v>129011395</v>
       </c>
       <c r="B27" t="n">
         <v>79039</v>
@@ -3248,10 +3248,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>409795</v>
+        <v>409555</v>
       </c>
       <c r="R27" t="n">
-        <v>6782327</v>
+        <v>6782356</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3283,7 +3283,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3293,7 +3293,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4336,7 +4336,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129032891</v>
+        <v>129032407</v>
       </c>
       <c r="B38" t="n">
         <v>79039</v>
@@ -4371,10 +4371,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>409241</v>
+        <v>409659</v>
       </c>
       <c r="R38" t="n">
-        <v>6782372</v>
+        <v>6782436</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4421,19 +4421,19 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129011392</v>
+        <v>129011399</v>
       </c>
       <c r="B39" t="n">
         <v>79039</v>
@@ -4468,10 +4468,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>409361</v>
+        <v>409609</v>
       </c>
       <c r="R39" t="n">
-        <v>6782401</v>
+        <v>6782404</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4513,7 +4513,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4540,7 +4540,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129032911</v>
+        <v>129011394</v>
       </c>
       <c r="B40" t="n">
         <v>79039</v>
@@ -4575,10 +4575,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>409777</v>
+        <v>409543</v>
       </c>
       <c r="R40" t="n">
-        <v>6782445</v>
+        <v>6782361</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4608,9 +4608,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4625,19 +4635,19 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129032906</v>
+        <v>129011392</v>
       </c>
       <c r="B41" t="n">
         <v>79039</v>
@@ -4672,10 +4682,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>409684</v>
+        <v>409361</v>
       </c>
       <c r="R41" t="n">
-        <v>6782322</v>
+        <v>6782401</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4705,9 +4715,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4722,19 +4742,19 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129032407</v>
+        <v>129032891</v>
       </c>
       <c r="B42" t="n">
         <v>79039</v>
@@ -4769,10 +4789,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>409659</v>
+        <v>409241</v>
       </c>
       <c r="R42" t="n">
-        <v>6782436</v>
+        <v>6782372</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4819,19 +4839,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129032910</v>
+        <v>129032911</v>
       </c>
       <c r="B43" t="n">
         <v>79039</v>
@@ -4866,10 +4886,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>409744</v>
+        <v>409777</v>
       </c>
       <c r="R43" t="n">
-        <v>6782394</v>
+        <v>6782445</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4928,7 +4948,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129011394</v>
+        <v>129032906</v>
       </c>
       <c r="B44" t="n">
         <v>79039</v>
@@ -4963,10 +4983,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>409543</v>
+        <v>409684</v>
       </c>
       <c r="R44" t="n">
-        <v>6782361</v>
+        <v>6782322</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4996,19 +5016,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>13:27</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>13:27</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5023,19 +5033,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129011399</v>
+        <v>129032910</v>
       </c>
       <c r="B45" t="n">
         <v>79039</v>
@@ -5070,10 +5080,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>409609</v>
+        <v>409744</v>
       </c>
       <c r="R45" t="n">
-        <v>6782404</v>
+        <v>6782394</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5103,19 +5113,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>13:06</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>13:06</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5130,22 +5130,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129011408</v>
+        <v>129032869</v>
       </c>
       <c r="B46" t="n">
-        <v>79039</v>
+        <v>57725</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5153,21 +5153,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5177,10 +5177,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>409801</v>
+        <v>409754</v>
       </c>
       <c r="R46" t="n">
-        <v>6782315</v>
+        <v>6782356</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5210,19 +5210,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>11:08</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>11:08</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5237,12 +5227,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5550,10 +5540,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129032869</v>
+        <v>129011408</v>
       </c>
       <c r="B50" t="n">
-        <v>57725</v>
+        <v>79039</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5561,21 +5551,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5585,10 +5575,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>409754</v>
+        <v>409801</v>
       </c>
       <c r="R50" t="n">
-        <v>6782356</v>
+        <v>6782315</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5618,9 +5608,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5635,19 +5635,19 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129011401</v>
+        <v>129011386</v>
       </c>
       <c r="B51" t="n">
         <v>79039</v>
@@ -5682,10 +5682,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>409663</v>
+        <v>409210</v>
       </c>
       <c r="R51" t="n">
-        <v>6782385</v>
+        <v>6782365</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5717,7 +5717,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5727,7 +5727,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5754,7 +5754,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129032899</v>
+        <v>129011396</v>
       </c>
       <c r="B52" t="n">
         <v>79039</v>
@@ -5789,10 +5789,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>409397</v>
+        <v>409584</v>
       </c>
       <c r="R52" t="n">
-        <v>6782272</v>
+        <v>6782395</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5822,9 +5822,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5839,19 +5849,19 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129011386</v>
+        <v>129011409</v>
       </c>
       <c r="B53" t="n">
         <v>79039</v>
@@ -5886,10 +5896,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>409210</v>
+        <v>409202</v>
       </c>
       <c r="R53" t="n">
-        <v>6782365</v>
+        <v>6782367</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5940,6 +5950,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -5958,7 +5969,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129011409</v>
+        <v>129011401</v>
       </c>
       <c r="B54" t="n">
         <v>79039</v>
@@ -5993,10 +6004,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>409202</v>
+        <v>409663</v>
       </c>
       <c r="R54" t="n">
-        <v>6782367</v>
+        <v>6782385</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6028,7 +6039,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6038,7 +6049,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6047,7 +6058,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6066,10 +6076,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129011396</v>
+        <v>129032866</v>
       </c>
       <c r="B55" t="n">
-        <v>79039</v>
+        <v>57725</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6077,21 +6087,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6101,10 +6111,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>409584</v>
+        <v>409757</v>
       </c>
       <c r="R55" t="n">
-        <v>6782395</v>
+        <v>6782386</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6134,19 +6144,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>13:11</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>13:11</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6161,22 +6161,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129032866</v>
+        <v>129032899</v>
       </c>
       <c r="B56" t="n">
-        <v>57725</v>
+        <v>79039</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6184,21 +6184,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6208,10 +6208,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>409757</v>
+        <v>409397</v>
       </c>
       <c r="R56" t="n">
-        <v>6782386</v>
+        <v>6782272</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6270,10 +6270,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129011373</v>
+        <v>129032403</v>
       </c>
       <c r="B57" t="n">
-        <v>91553</v>
+        <v>79039</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6281,41 +6281,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>409435</v>
+        <v>409021</v>
       </c>
       <c r="R57" t="n">
-        <v>6782383</v>
+        <v>6782365</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6345,55 +6338,39 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>4 st på samma tall</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129011372</v>
+        <v>129011375</v>
       </c>
       <c r="B58" t="n">
-        <v>57725</v>
+        <v>78796</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6401,42 +6378,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>409796</v>
+        <v>409335</v>
       </c>
       <c r="R58" t="n">
-        <v>6782327</v>
+        <v>6782352</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6468,7 +6437,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6478,7 +6447,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6505,10 +6474,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129032889</v>
+        <v>129011372</v>
       </c>
       <c r="B59" t="n">
-        <v>79039</v>
+        <v>57725</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6516,34 +6485,42 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>409164</v>
+        <v>409796</v>
       </c>
       <c r="R59" t="n">
-        <v>6782308</v>
+        <v>6782327</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6573,9 +6550,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6590,22 +6577,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129011375</v>
+        <v>129011373</v>
       </c>
       <c r="B60" t="n">
-        <v>78796</v>
+        <v>91560</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6613,34 +6600,41 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6446</v>
+        <v>5442</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>409335</v>
+        <v>409435</v>
       </c>
       <c r="R60" t="n">
-        <v>6782352</v>
+        <v>6782383</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6672,7 +6666,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6682,7 +6676,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>4 st på samma tall</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6691,6 +6690,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6709,7 +6709,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129032403</v>
+        <v>129032889</v>
       </c>
       <c r="B61" t="n">
         <v>79039</v>
@@ -6744,10 +6744,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>409021</v>
+        <v>409164</v>
       </c>
       <c r="R61" t="n">
-        <v>6782365</v>
+        <v>6782308</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6794,44 +6794,44 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129011387</v>
+        <v>129032400</v>
       </c>
       <c r="B62" t="n">
-        <v>79039</v>
+        <v>91995</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6841,10 +6841,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>409232</v>
+        <v>409738</v>
       </c>
       <c r="R62" t="n">
-        <v>6782353</v>
+        <v>6782382</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6874,19 +6874,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>15:22</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>15:22</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6901,22 +6891,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129032872</v>
+        <v>129032874</v>
       </c>
       <c r="B63" t="n">
-        <v>78796</v>
+        <v>91558</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6924,21 +6914,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6446</v>
+        <v>5432</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6948,10 +6938,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>409594</v>
+        <v>409405</v>
       </c>
       <c r="R63" t="n">
-        <v>6782294</v>
+        <v>6782366</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7010,10 +7000,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129032886</v>
+        <v>129032396</v>
       </c>
       <c r="B64" t="n">
-        <v>79039</v>
+        <v>57725</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7021,34 +7011,42 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>409108</v>
+        <v>409753</v>
       </c>
       <c r="R64" t="n">
-        <v>6782395</v>
+        <v>6782323</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7095,22 +7093,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129011384</v>
+        <v>129032867</v>
       </c>
       <c r="B65" t="n">
-        <v>79039</v>
+        <v>57725</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7118,21 +7116,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7142,10 +7140,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>409068</v>
+        <v>409693</v>
       </c>
       <c r="R65" t="n">
-        <v>6782377</v>
+        <v>6782357</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7175,19 +7173,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>15:43</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>15:43</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7202,12 +7190,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -7321,7 +7309,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129032914</v>
+        <v>129032886</v>
       </c>
       <c r="B67" t="n">
         <v>79039</v>
@@ -7356,10 +7344,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>409759</v>
+        <v>409108</v>
       </c>
       <c r="R67" t="n">
-        <v>6782343</v>
+        <v>6782395</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7418,32 +7406,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129032400</v>
+        <v>129011384</v>
       </c>
       <c r="B68" t="n">
-        <v>91988</v>
+        <v>79039</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7453,10 +7441,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>409738</v>
+        <v>409068</v>
       </c>
       <c r="R68" t="n">
-        <v>6782382</v>
+        <v>6782377</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7486,9 +7474,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7503,22 +7501,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129032874</v>
+        <v>129032914</v>
       </c>
       <c r="B69" t="n">
-        <v>91551</v>
+        <v>79039</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7526,21 +7524,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7550,10 +7548,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>409405</v>
+        <v>409759</v>
       </c>
       <c r="R69" t="n">
-        <v>6782366</v>
+        <v>6782343</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7612,10 +7610,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129032867</v>
+        <v>129032872</v>
       </c>
       <c r="B70" t="n">
-        <v>57725</v>
+        <v>78796</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7623,21 +7621,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7647,10 +7645,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>409693</v>
+        <v>409594</v>
       </c>
       <c r="R70" t="n">
-        <v>6782357</v>
+        <v>6782294</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7709,10 +7707,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129032396</v>
+        <v>129011387</v>
       </c>
       <c r="B71" t="n">
-        <v>57725</v>
+        <v>79039</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7720,42 +7718,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>409753</v>
+        <v>409232</v>
       </c>
       <c r="R71" t="n">
-        <v>6782323</v>
+        <v>6782353</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7785,9 +7775,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7802,22 +7802,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129032873</v>
+        <v>129032896</v>
       </c>
       <c r="B72" t="n">
-        <v>91533</v>
+        <v>79039</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7825,37 +7825,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>409075</v>
+        <v>409331</v>
       </c>
       <c r="R72" t="n">
-        <v>6782317</v>
+        <v>6782342</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7896,7 +7893,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -7915,7 +7911,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129032896</v>
+        <v>129032902</v>
       </c>
       <c r="B73" t="n">
         <v>79039</v>
@@ -7950,10 +7946,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>409331</v>
+        <v>409549</v>
       </c>
       <c r="R73" t="n">
-        <v>6782342</v>
+        <v>6782286</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8012,7 +8008,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129032902</v>
+        <v>129032917</v>
       </c>
       <c r="B74" t="n">
         <v>79039</v>
@@ -8047,10 +8043,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>409549</v>
+        <v>409360</v>
       </c>
       <c r="R74" t="n">
-        <v>6782286</v>
+        <v>6782355</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8109,7 +8105,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129032917</v>
+        <v>129032900</v>
       </c>
       <c r="B75" t="n">
         <v>79039</v>
@@ -8144,10 +8140,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>409360</v>
+        <v>409449</v>
       </c>
       <c r="R75" t="n">
-        <v>6782355</v>
+        <v>6782286</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8206,10 +8202,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129032900</v>
+        <v>129032873</v>
       </c>
       <c r="B76" t="n">
-        <v>79039</v>
+        <v>91540</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8217,34 +8213,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>409449</v>
+        <v>409075</v>
       </c>
       <c r="R76" t="n">
-        <v>6782286</v>
+        <v>6782317</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8285,6 +8284,7 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8303,10 +8303,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129032893</v>
+        <v>129032402</v>
       </c>
       <c r="B77" t="n">
-        <v>79039</v>
+        <v>91558</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8314,21 +8314,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8338,10 +8338,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>409280</v>
+        <v>409767</v>
       </c>
       <c r="R77" t="n">
-        <v>6782382</v>
+        <v>6782352</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8388,19 +8388,19 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129011404</v>
+        <v>129032893</v>
       </c>
       <c r="B78" t="n">
         <v>79039</v>
@@ -8435,10 +8435,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>409736</v>
+        <v>409280</v>
       </c>
       <c r="R78" t="n">
-        <v>6782394</v>
+        <v>6782382</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8468,19 +8468,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>11:59</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>11:59</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8495,19 +8485,19 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129032901</v>
+        <v>129011404</v>
       </c>
       <c r="B79" t="n">
         <v>79039</v>
@@ -8542,10 +8532,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>409528</v>
+        <v>409736</v>
       </c>
       <c r="R79" t="n">
-        <v>6782292</v>
+        <v>6782394</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8575,9 +8565,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8592,19 +8592,19 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129032888</v>
+        <v>129032901</v>
       </c>
       <c r="B80" t="n">
         <v>79039</v>
@@ -8639,10 +8639,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>409127</v>
+        <v>409528</v>
       </c>
       <c r="R80" t="n">
-        <v>6782290</v>
+        <v>6782292</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8701,10 +8701,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129032402</v>
+        <v>129032888</v>
       </c>
       <c r="B81" t="n">
-        <v>91551</v>
+        <v>79039</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8712,21 +8712,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8736,10 +8736,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>409767</v>
+        <v>409127</v>
       </c>
       <c r="R81" t="n">
-        <v>6782352</v>
+        <v>6782290</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8786,12 +8786,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
@@ -9186,10 +9186,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129032898</v>
+        <v>129032870</v>
       </c>
       <c r="B86" t="n">
-        <v>79039</v>
+        <v>91560</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9197,31 +9197,42 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>409390</v>
+        <v>409530</v>
       </c>
       <c r="R86" t="n">
         <v>6782289</v>
@@ -9265,6 +9276,7 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9283,7 +9295,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129032918</v>
+        <v>129032898</v>
       </c>
       <c r="B87" t="n">
         <v>79039</v>
@@ -9318,10 +9330,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>409363</v>
+        <v>409390</v>
       </c>
       <c r="R87" t="n">
-        <v>6782377</v>
+        <v>6782289</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9380,10 +9392,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129011370</v>
+        <v>129032918</v>
       </c>
       <c r="B88" t="n">
-        <v>57725</v>
+        <v>79039</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9391,42 +9403,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>409759</v>
+        <v>409363</v>
       </c>
       <c r="R88" t="n">
-        <v>6782330</v>
+        <v>6782377</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9456,19 +9460,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>11:48</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9483,22 +9477,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129032870</v>
+        <v>129011370</v>
       </c>
       <c r="B89" t="n">
-        <v>91553</v>
+        <v>57725</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9506,34 +9500,31 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
@@ -9541,10 +9532,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>409530</v>
+        <v>409759</v>
       </c>
       <c r="R89" t="n">
-        <v>6782289</v>
+        <v>6782330</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9574,30 +9565,39 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AD89" t="b">
         <v>0</v>
       </c>
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
@@ -10811,7 +10811,7 @@
         <v>129032401</v>
       </c>
       <c r="B102" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10905,7 +10905,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129011377</v>
+        <v>129011402</v>
       </c>
       <c r="B103" t="n">
         <v>79039</v>
@@ -10940,10 +10940,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>408995</v>
+        <v>409671</v>
       </c>
       <c r="R103" t="n">
-        <v>6782299</v>
+        <v>6782390</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10975,7 +10975,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -10985,7 +10985,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11012,7 +11012,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129011402</v>
+        <v>129032877</v>
       </c>
       <c r="B104" t="n">
         <v>79039</v>
@@ -11047,10 +11047,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>409671</v>
+        <v>408994</v>
       </c>
       <c r="R104" t="n">
-        <v>6782390</v>
+        <v>6782293</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11080,19 +11080,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z104" t="inlineStr">
-        <is>
-          <t>12:57</t>
-        </is>
-      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB104" t="inlineStr">
-        <is>
-          <t>12:57</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11107,19 +11097,19 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129011385</v>
+        <v>129032904</v>
       </c>
       <c r="B105" t="n">
         <v>79039</v>
@@ -11154,10 +11144,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>409214</v>
+        <v>409568</v>
       </c>
       <c r="R105" t="n">
-        <v>6782345</v>
+        <v>6782383</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11187,19 +11177,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z105" t="inlineStr">
-        <is>
-          <t>15:29</t>
-        </is>
-      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB105" t="inlineStr">
-        <is>
-          <t>15:29</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11214,19 +11194,19 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129032877</v>
+        <v>129032915</v>
       </c>
       <c r="B106" t="n">
         <v>79039</v>
@@ -11261,10 +11241,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>408994</v>
+        <v>409765</v>
       </c>
       <c r="R106" t="n">
-        <v>6782293</v>
+        <v>6782330</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11323,7 +11303,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129032904</v>
+        <v>129011385</v>
       </c>
       <c r="B107" t="n">
         <v>79039</v>
@@ -11358,10 +11338,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>409568</v>
+        <v>409214</v>
       </c>
       <c r="R107" t="n">
-        <v>6782383</v>
+        <v>6782345</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11391,9 +11371,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11408,19 +11398,19 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129032915</v>
+        <v>129011377</v>
       </c>
       <c r="B108" t="n">
         <v>79039</v>
@@ -11455,10 +11445,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>409765</v>
+        <v>408995</v>
       </c>
       <c r="R108" t="n">
-        <v>6782330</v>
+        <v>6782299</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11488,9 +11478,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11505,12 +11505,12 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>

--- a/artfynd/A 47938-2025 artfynd.xlsx
+++ b/artfynd/A 47938-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129032920</v>
       </c>
       <c r="B2" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129011405</v>
       </c>
       <c r="B3" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>129032876</v>
       </c>
       <c r="B4" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>129011403</v>
       </c>
       <c r="B5" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>129032905</v>
       </c>
       <c r="B6" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1180,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129032907</v>
+        <v>129032394</v>
       </c>
       <c r="B7" t="n">
-        <v>79039</v>
+        <v>79631</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>409686</v>
+        <v>409553</v>
       </c>
       <c r="R7" t="n">
-        <v>6782351</v>
+        <v>6782378</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1265,22 +1265,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129032919</v>
+        <v>129032907</v>
       </c>
       <c r="B8" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>409358</v>
+        <v>409686</v>
       </c>
       <c r="R8" t="n">
-        <v>6782291</v>
+        <v>6782351</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1374,10 +1374,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129032394</v>
+        <v>129011389</v>
       </c>
       <c r="B9" t="n">
-        <v>79629</v>
+        <v>79041</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1385,21 +1385,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1409,10 +1409,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>409553</v>
+        <v>409278</v>
       </c>
       <c r="R9" t="n">
-        <v>6782378</v>
+        <v>6782361</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1442,9 +1442,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1459,22 +1469,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129011389</v>
+        <v>129032919</v>
       </c>
       <c r="B10" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1506,10 +1516,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>409278</v>
+        <v>409358</v>
       </c>
       <c r="R10" t="n">
-        <v>6782361</v>
+        <v>6782291</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1539,19 +1549,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>15:18</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>15:18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1566,22 +1566,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129032398</v>
+        <v>129011398</v>
       </c>
       <c r="B11" t="n">
-        <v>91560</v>
+        <v>79041</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1589,21 +1589,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1613,10 +1613,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>409482</v>
+        <v>409596</v>
       </c>
       <c r="R11" t="n">
-        <v>6782335</v>
+        <v>6782395</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1646,9 +1646,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1663,12 +1673,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1678,7 +1688,7 @@
         <v>129032894</v>
       </c>
       <c r="B12" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1772,10 +1782,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129011398</v>
+        <v>129032398</v>
       </c>
       <c r="B13" t="n">
-        <v>79039</v>
+        <v>91562</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1783,21 +1793,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1807,10 +1817,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>409596</v>
+        <v>409482</v>
       </c>
       <c r="R13" t="n">
-        <v>6782395</v>
+        <v>6782335</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1840,19 +1850,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>13:08</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>13:08</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1867,22 +1867,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129032897</v>
+        <v>129011378</v>
       </c>
       <c r="B14" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1914,10 +1914,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>409469</v>
+        <v>408984</v>
       </c>
       <c r="R14" t="n">
-        <v>6782371</v>
+        <v>6782347</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1947,9 +1947,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1964,22 +1974,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129032909</v>
+        <v>129032392</v>
       </c>
       <c r="B15" t="n">
-        <v>79039</v>
+        <v>79660</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1987,21 +1997,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2011,10 +2021,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>409727</v>
+        <v>409554</v>
       </c>
       <c r="R15" t="n">
-        <v>6782352</v>
+        <v>6782380</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2061,22 +2071,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129011378</v>
+        <v>129032897</v>
       </c>
       <c r="B16" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2108,10 +2118,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>408984</v>
+        <v>409469</v>
       </c>
       <c r="R16" t="n">
-        <v>6782347</v>
+        <v>6782371</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2141,19 +2151,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>16:10</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>16:10</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2168,22 +2168,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129032392</v>
+        <v>129032909</v>
       </c>
       <c r="B17" t="n">
-        <v>79658</v>
+        <v>79041</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2191,21 +2191,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>409554</v>
+        <v>409727</v>
       </c>
       <c r="R17" t="n">
-        <v>6782380</v>
+        <v>6782352</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2265,22 +2265,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129011400</v>
+        <v>129011376</v>
       </c>
       <c r="B18" t="n">
-        <v>79039</v>
+        <v>91560</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2288,21 +2288,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2312,10 +2312,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>409643</v>
+        <v>409774</v>
       </c>
       <c r="R18" t="n">
-        <v>6782378</v>
+        <v>6782323</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2357,7 +2357,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2384,10 +2384,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129032868</v>
+        <v>129032885</v>
       </c>
       <c r="B19" t="n">
-        <v>57725</v>
+        <v>79041</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2395,21 +2395,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2419,10 +2419,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>409688</v>
+        <v>409078</v>
       </c>
       <c r="R19" t="n">
-        <v>6782303</v>
+        <v>6782312</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2481,10 +2481,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129011376</v>
+        <v>129011400</v>
       </c>
       <c r="B20" t="n">
-        <v>91558</v>
+        <v>79041</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2492,21 +2492,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2516,10 +2516,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>409774</v>
+        <v>409643</v>
       </c>
       <c r="R20" t="n">
-        <v>6782323</v>
+        <v>6782378</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2551,7 +2551,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2588,10 +2588,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129032885</v>
+        <v>129032892</v>
       </c>
       <c r="B21" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2623,10 +2623,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>409078</v>
+        <v>409244</v>
       </c>
       <c r="R21" t="n">
-        <v>6782312</v>
+        <v>6782381</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2685,10 +2685,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129032892</v>
+        <v>129032868</v>
       </c>
       <c r="B22" t="n">
-        <v>79039</v>
+        <v>57727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2696,21 +2696,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2720,10 +2720,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>409244</v>
+        <v>409688</v>
       </c>
       <c r="R22" t="n">
-        <v>6782381</v>
+        <v>6782303</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2782,10 +2782,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129032399</v>
+        <v>129011383</v>
       </c>
       <c r="B23" t="n">
-        <v>91560</v>
+        <v>79041</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2793,21 +2793,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2817,10 +2817,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>409492</v>
+        <v>409028</v>
       </c>
       <c r="R23" t="n">
-        <v>6782346</v>
+        <v>6782350</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2850,9 +2850,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2867,22 +2877,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129011374</v>
+        <v>129011395</v>
       </c>
       <c r="B24" t="n">
-        <v>91560</v>
+        <v>79041</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2890,41 +2900,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>409475</v>
+        <v>409555</v>
       </c>
       <c r="R24" t="n">
-        <v>6782342</v>
+        <v>6782356</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2956,7 +2959,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -2966,12 +2969,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:57</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>hackspetthål under tickorna</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2980,7 +2978,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -2999,10 +2996,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129011383</v>
+        <v>129011407</v>
       </c>
       <c r="B25" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3034,10 +3031,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>409028</v>
+        <v>409795</v>
       </c>
       <c r="R25" t="n">
-        <v>6782350</v>
+        <v>6782327</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3069,7 +3066,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3079,7 +3076,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3106,10 +3103,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129011407</v>
+        <v>129032399</v>
       </c>
       <c r="B26" t="n">
-        <v>79039</v>
+        <v>91562</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3117,21 +3114,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3141,10 +3138,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>409795</v>
+        <v>409492</v>
       </c>
       <c r="R26" t="n">
-        <v>6782327</v>
+        <v>6782346</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3174,19 +3171,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>11:12</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>11:12</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3201,22 +3188,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129011395</v>
+        <v>129011374</v>
       </c>
       <c r="B27" t="n">
-        <v>79039</v>
+        <v>91562</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3224,34 +3211,41 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>409555</v>
+        <v>409475</v>
       </c>
       <c r="R27" t="n">
-        <v>6782356</v>
+        <v>6782342</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3283,7 +3277,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3293,7 +3287,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>hackspetthål under tickorna</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3302,6 +3301,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3323,7 +3323,7 @@
         <v>129032395</v>
       </c>
       <c r="B28" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
         <v>129032393</v>
       </c>
       <c r="B29" t="n">
-        <v>79629</v>
+        <v>79631</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
         <v>129032913</v>
       </c>
       <c r="B30" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3622,7 +3622,7 @@
         <v>129032406</v>
       </c>
       <c r="B31" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3719,7 +3719,7 @@
         <v>129032882</v>
       </c>
       <c r="B32" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3816,7 +3816,7 @@
         <v>129011391</v>
       </c>
       <c r="B33" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         <v>129032878</v>
       </c>
       <c r="B34" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4020,7 +4020,7 @@
         <v>129011369</v>
       </c>
       <c r="B35" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4135,7 +4135,7 @@
         <v>129032887</v>
       </c>
       <c r="B36" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4232,7 +4232,7 @@
         <v>129011381</v>
       </c>
       <c r="B37" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4336,10 +4336,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129032407</v>
+        <v>129032891</v>
       </c>
       <c r="B38" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4371,10 +4371,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>409659</v>
+        <v>409241</v>
       </c>
       <c r="R38" t="n">
-        <v>6782436</v>
+        <v>6782372</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4421,22 +4421,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129011399</v>
+        <v>129011392</v>
       </c>
       <c r="B39" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4468,10 +4468,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>409609</v>
+        <v>409361</v>
       </c>
       <c r="R39" t="n">
-        <v>6782404</v>
+        <v>6782401</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4513,7 +4513,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4540,10 +4540,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129011394</v>
+        <v>129032911</v>
       </c>
       <c r="B40" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4575,10 +4575,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>409543</v>
+        <v>409777</v>
       </c>
       <c r="R40" t="n">
-        <v>6782361</v>
+        <v>6782445</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4608,19 +4608,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>13:27</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>13:27</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4635,22 +4625,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129011392</v>
+        <v>129032906</v>
       </c>
       <c r="B41" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4682,10 +4672,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>409361</v>
+        <v>409684</v>
       </c>
       <c r="R41" t="n">
-        <v>6782401</v>
+        <v>6782322</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4715,19 +4705,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>14:31</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>14:31</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4742,22 +4722,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129032891</v>
+        <v>129032407</v>
       </c>
       <c r="B42" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4789,10 +4769,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>409241</v>
+        <v>409659</v>
       </c>
       <c r="R42" t="n">
-        <v>6782372</v>
+        <v>6782436</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4839,22 +4819,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129032911</v>
+        <v>129032910</v>
       </c>
       <c r="B43" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4886,10 +4866,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>409777</v>
+        <v>409744</v>
       </c>
       <c r="R43" t="n">
-        <v>6782445</v>
+        <v>6782394</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4948,10 +4928,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129032906</v>
+        <v>129011394</v>
       </c>
       <c r="B44" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4983,10 +4963,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>409684</v>
+        <v>409543</v>
       </c>
       <c r="R44" t="n">
-        <v>6782322</v>
+        <v>6782361</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5016,9 +4996,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5033,22 +5023,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129032910</v>
+        <v>129011399</v>
       </c>
       <c r="B45" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5080,10 +5070,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>409744</v>
+        <v>409609</v>
       </c>
       <c r="R45" t="n">
-        <v>6782394</v>
+        <v>6782404</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5113,9 +5103,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5130,12 +5130,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5145,7 +5145,7 @@
         <v>129032869</v>
       </c>
       <c r="B46" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5239,10 +5239,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129032883</v>
+        <v>129011408</v>
       </c>
       <c r="B47" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5274,10 +5274,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>409010</v>
+        <v>409801</v>
       </c>
       <c r="R47" t="n">
-        <v>6782399</v>
+        <v>6782315</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5307,9 +5307,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5324,22 +5334,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129011380</v>
+        <v>129032883</v>
       </c>
       <c r="B48" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5371,10 +5381,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>408984</v>
+        <v>409010</v>
       </c>
       <c r="R48" t="n">
-        <v>6782385</v>
+        <v>6782399</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5404,19 +5414,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>16:07</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>16:07</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5431,22 +5431,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129032884</v>
+        <v>129011380</v>
       </c>
       <c r="B49" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5478,10 +5478,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>409039</v>
+        <v>408984</v>
       </c>
       <c r="R49" t="n">
-        <v>6782290</v>
+        <v>6782385</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5511,9 +5511,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5528,22 +5538,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129011408</v>
+        <v>129032884</v>
       </c>
       <c r="B50" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5575,10 +5585,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>409801</v>
+        <v>409039</v>
       </c>
       <c r="R50" t="n">
-        <v>6782315</v>
+        <v>6782290</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5608,19 +5618,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>11:08</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>11:08</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5635,22 +5635,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129011386</v>
+        <v>129032866</v>
       </c>
       <c r="B51" t="n">
-        <v>79039</v>
+        <v>57727</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5658,21 +5658,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5682,10 +5682,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>409210</v>
+        <v>409757</v>
       </c>
       <c r="R51" t="n">
-        <v>6782365</v>
+        <v>6782386</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5715,19 +5715,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>15:26</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>15:26</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5742,22 +5732,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129011396</v>
+        <v>129011401</v>
       </c>
       <c r="B52" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5789,10 +5779,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>409584</v>
+        <v>409663</v>
       </c>
       <c r="R52" t="n">
-        <v>6782395</v>
+        <v>6782385</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5824,7 +5814,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -5834,7 +5824,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5861,10 +5851,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129011409</v>
+        <v>129032899</v>
       </c>
       <c r="B53" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5896,10 +5886,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>409202</v>
+        <v>409397</v>
       </c>
       <c r="R53" t="n">
-        <v>6782367</v>
+        <v>6782272</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5929,50 +5919,39 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>15:26</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>15:26</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129011401</v>
+        <v>129011386</v>
       </c>
       <c r="B54" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6004,10 +5983,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>409663</v>
+        <v>409210</v>
       </c>
       <c r="R54" t="n">
-        <v>6782385</v>
+        <v>6782365</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6039,7 +6018,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6049,7 +6028,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6076,10 +6055,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129032866</v>
+        <v>129011409</v>
       </c>
       <c r="B55" t="n">
-        <v>57725</v>
+        <v>79041</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6087,21 +6066,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6111,10 +6090,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>409757</v>
+        <v>409202</v>
       </c>
       <c r="R55" t="n">
-        <v>6782386</v>
+        <v>6782367</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6144,39 +6123,50 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129032899</v>
+        <v>129011396</v>
       </c>
       <c r="B56" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6208,10 +6198,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>409397</v>
+        <v>409584</v>
       </c>
       <c r="R56" t="n">
-        <v>6782272</v>
+        <v>6782395</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6241,9 +6231,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6258,22 +6258,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129032403</v>
+        <v>129032889</v>
       </c>
       <c r="B57" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6305,10 +6305,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>409021</v>
+        <v>409164</v>
       </c>
       <c r="R57" t="n">
-        <v>6782365</v>
+        <v>6782308</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6355,12 +6355,12 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -6370,7 +6370,7 @@
         <v>129011375</v>
       </c>
       <c r="B58" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6474,10 +6474,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129011372</v>
+        <v>129032403</v>
       </c>
       <c r="B59" t="n">
-        <v>57725</v>
+        <v>79041</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6485,42 +6485,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>409796</v>
+        <v>409021</v>
       </c>
       <c r="R59" t="n">
-        <v>6782327</v>
+        <v>6782365</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6550,19 +6542,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>11:10</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6577,12 +6559,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -6592,7 +6574,7 @@
         <v>129011373</v>
       </c>
       <c r="B60" t="n">
-        <v>91560</v>
+        <v>91562</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6709,10 +6691,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129032889</v>
+        <v>129011372</v>
       </c>
       <c r="B61" t="n">
-        <v>79039</v>
+        <v>57727</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6720,34 +6702,42 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>409164</v>
+        <v>409796</v>
       </c>
       <c r="R61" t="n">
-        <v>6782308</v>
+        <v>6782327</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6777,9 +6767,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6794,44 +6794,44 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129032400</v>
+        <v>129011387</v>
       </c>
       <c r="B62" t="n">
-        <v>91995</v>
+        <v>79041</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6841,10 +6841,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>409738</v>
+        <v>409232</v>
       </c>
       <c r="R62" t="n">
-        <v>6782382</v>
+        <v>6782353</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6874,9 +6874,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6891,22 +6901,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129032874</v>
+        <v>129032872</v>
       </c>
       <c r="B63" t="n">
-        <v>91558</v>
+        <v>78798</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6914,21 +6924,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5432</v>
+        <v>6446</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6938,10 +6948,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>409405</v>
+        <v>409594</v>
       </c>
       <c r="R63" t="n">
-        <v>6782366</v>
+        <v>6782294</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7000,10 +7010,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129032396</v>
+        <v>129032886</v>
       </c>
       <c r="B64" t="n">
-        <v>57725</v>
+        <v>79041</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7011,42 +7021,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>409753</v>
+        <v>409108</v>
       </c>
       <c r="R64" t="n">
-        <v>6782323</v>
+        <v>6782395</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7093,22 +7095,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129032867</v>
+        <v>129011384</v>
       </c>
       <c r="B65" t="n">
-        <v>57725</v>
+        <v>79041</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7116,21 +7118,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7140,10 +7142,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>409693</v>
+        <v>409068</v>
       </c>
       <c r="R65" t="n">
-        <v>6782357</v>
+        <v>6782377</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7173,9 +7175,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7190,12 +7202,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -7205,7 +7217,7 @@
         <v>129011379</v>
       </c>
       <c r="B66" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7309,10 +7321,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129032886</v>
+        <v>129032914</v>
       </c>
       <c r="B67" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7344,10 +7356,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>409108</v>
+        <v>409759</v>
       </c>
       <c r="R67" t="n">
-        <v>6782395</v>
+        <v>6782343</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7406,10 +7418,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129011384</v>
+        <v>129032874</v>
       </c>
       <c r="B68" t="n">
-        <v>79039</v>
+        <v>91560</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7417,21 +7429,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7441,10 +7453,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>409068</v>
+        <v>409405</v>
       </c>
       <c r="R68" t="n">
-        <v>6782377</v>
+        <v>6782366</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7474,19 +7486,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>15:43</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>15:43</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7501,44 +7503,44 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129032914</v>
+        <v>129032400</v>
       </c>
       <c r="B69" t="n">
-        <v>79039</v>
+        <v>91997</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7548,10 +7550,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>409759</v>
+        <v>409738</v>
       </c>
       <c r="R69" t="n">
-        <v>6782343</v>
+        <v>6782382</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7598,22 +7600,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129032872</v>
+        <v>129032396</v>
       </c>
       <c r="B70" t="n">
-        <v>78796</v>
+        <v>57727</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7621,34 +7623,42 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>409594</v>
+        <v>409753</v>
       </c>
       <c r="R70" t="n">
-        <v>6782294</v>
+        <v>6782323</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7695,22 +7705,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129011387</v>
+        <v>129032867</v>
       </c>
       <c r="B71" t="n">
-        <v>79039</v>
+        <v>57727</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7718,21 +7728,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7742,10 +7752,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>409232</v>
+        <v>409693</v>
       </c>
       <c r="R71" t="n">
-        <v>6782353</v>
+        <v>6782357</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7775,19 +7785,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>15:22</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>15:22</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7802,12 +7802,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -7817,7 +7817,7 @@
         <v>129032896</v>
       </c>
       <c r="B72" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7914,7 +7914,7 @@
         <v>129032902</v>
       </c>
       <c r="B73" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8011,7 +8011,7 @@
         <v>129032917</v>
       </c>
       <c r="B74" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8108,7 +8108,7 @@
         <v>129032900</v>
       </c>
       <c r="B75" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8205,7 +8205,7 @@
         <v>129032873</v>
       </c>
       <c r="B76" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8303,10 +8303,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129032402</v>
+        <v>129032893</v>
       </c>
       <c r="B77" t="n">
-        <v>91558</v>
+        <v>79041</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8314,21 +8314,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8338,10 +8338,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>409767</v>
+        <v>409280</v>
       </c>
       <c r="R77" t="n">
-        <v>6782352</v>
+        <v>6782382</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8388,22 +8388,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129032893</v>
+        <v>129011404</v>
       </c>
       <c r="B78" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8435,10 +8435,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>409280</v>
+        <v>409736</v>
       </c>
       <c r="R78" t="n">
-        <v>6782382</v>
+        <v>6782394</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8468,9 +8468,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8485,22 +8495,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129011404</v>
+        <v>129032901</v>
       </c>
       <c r="B79" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8532,10 +8542,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>409736</v>
+        <v>409528</v>
       </c>
       <c r="R79" t="n">
-        <v>6782394</v>
+        <v>6782292</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8565,19 +8575,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>11:59</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>11:59</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8592,22 +8592,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129032901</v>
+        <v>129032888</v>
       </c>
       <c r="B80" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8639,10 +8639,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>409528</v>
+        <v>409127</v>
       </c>
       <c r="R80" t="n">
-        <v>6782292</v>
+        <v>6782290</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8701,10 +8701,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129032888</v>
+        <v>129032402</v>
       </c>
       <c r="B81" t="n">
-        <v>79039</v>
+        <v>91560</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8712,21 +8712,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8736,10 +8736,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>409127</v>
+        <v>409767</v>
       </c>
       <c r="R81" t="n">
-        <v>6782290</v>
+        <v>6782352</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8786,12 +8786,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
@@ -8801,7 +8801,7 @@
         <v>129032908</v>
       </c>
       <c r="B82" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8898,7 +8898,7 @@
         <v>129032879</v>
       </c>
       <c r="B83" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8995,7 +8995,7 @@
         <v>129032409</v>
       </c>
       <c r="B84" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9092,7 +9092,7 @@
         <v>129032916</v>
       </c>
       <c r="B85" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9186,10 +9186,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129032870</v>
+        <v>129032898</v>
       </c>
       <c r="B86" t="n">
-        <v>91560</v>
+        <v>79041</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9197,42 +9197,31 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>409530</v>
+        <v>409390</v>
       </c>
       <c r="R86" t="n">
         <v>6782289</v>
@@ -9276,7 +9265,6 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9295,10 +9283,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129032898</v>
+        <v>129032918</v>
       </c>
       <c r="B87" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9330,10 +9318,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>409390</v>
+        <v>409363</v>
       </c>
       <c r="R87" t="n">
-        <v>6782289</v>
+        <v>6782377</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9392,10 +9380,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129032918</v>
+        <v>129032870</v>
       </c>
       <c r="B88" t="n">
-        <v>79039</v>
+        <v>91562</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9403,34 +9391,45 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>409363</v>
+        <v>409530</v>
       </c>
       <c r="R88" t="n">
-        <v>6782377</v>
+        <v>6782289</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9471,6 +9470,7 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -9492,7 +9492,7 @@
         <v>129011370</v>
       </c>
       <c r="B89" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9607,7 +9607,7 @@
         <v>129011393</v>
       </c>
       <c r="B90" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9714,7 +9714,7 @@
         <v>129032895</v>
       </c>
       <c r="B91" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9811,7 +9811,7 @@
         <v>129032903</v>
       </c>
       <c r="B92" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9908,7 +9908,7 @@
         <v>129032880</v>
       </c>
       <c r="B93" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10005,7 +10005,7 @@
         <v>129032405</v>
       </c>
       <c r="B94" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10102,7 +10102,7 @@
         <v>129011388</v>
       </c>
       <c r="B95" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10209,7 +10209,7 @@
         <v>129011406</v>
       </c>
       <c r="B96" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10316,7 +10316,7 @@
         <v>129032408</v>
       </c>
       <c r="B97" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10413,7 +10413,7 @@
         <v>129032912</v>
       </c>
       <c r="B98" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10510,7 +10510,7 @@
         <v>129032890</v>
       </c>
       <c r="B99" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10607,7 +10607,7 @@
         <v>129032875</v>
       </c>
       <c r="B100" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10704,7 +10704,7 @@
         <v>129011390</v>
       </c>
       <c r="B101" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10808,10 +10808,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129032401</v>
+        <v>129011377</v>
       </c>
       <c r="B102" t="n">
-        <v>91558</v>
+        <v>79041</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10819,21 +10819,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10843,10 +10843,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>409226</v>
+        <v>408995</v>
       </c>
       <c r="R102" t="n">
-        <v>6782376</v>
+        <v>6782299</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10876,9 +10876,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10893,12 +10903,12 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
@@ -10908,7 +10918,7 @@
         <v>129011402</v>
       </c>
       <c r="B103" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11012,10 +11022,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129032877</v>
+        <v>129011385</v>
       </c>
       <c r="B104" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11047,10 +11057,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>408994</v>
+        <v>409214</v>
       </c>
       <c r="R104" t="n">
-        <v>6782293</v>
+        <v>6782345</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11080,9 +11090,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11097,22 +11117,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129032904</v>
+        <v>129032877</v>
       </c>
       <c r="B105" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11144,10 +11164,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>409568</v>
+        <v>408994</v>
       </c>
       <c r="R105" t="n">
-        <v>6782383</v>
+        <v>6782293</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11206,10 +11226,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129032915</v>
+        <v>129032904</v>
       </c>
       <c r="B106" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11241,10 +11261,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>409765</v>
+        <v>409568</v>
       </c>
       <c r="R106" t="n">
-        <v>6782330</v>
+        <v>6782383</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11303,10 +11323,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129011385</v>
+        <v>129032915</v>
       </c>
       <c r="B107" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11338,10 +11358,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>409214</v>
+        <v>409765</v>
       </c>
       <c r="R107" t="n">
-        <v>6782345</v>
+        <v>6782330</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11371,19 +11391,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z107" t="inlineStr">
-        <is>
-          <t>15:29</t>
-        </is>
-      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB107" t="inlineStr">
-        <is>
-          <t>15:29</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11398,22 +11408,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129011377</v>
+        <v>129032401</v>
       </c>
       <c r="B108" t="n">
-        <v>79039</v>
+        <v>91560</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11421,21 +11431,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11445,10 +11455,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>408995</v>
+        <v>409226</v>
       </c>
       <c r="R108" t="n">
-        <v>6782299</v>
+        <v>6782376</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11478,19 +11488,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z108" t="inlineStr">
-        <is>
-          <t>16:13</t>
-        </is>
-      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB108" t="inlineStr">
-        <is>
-          <t>16:13</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11505,12 +11505,12 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>

--- a/artfynd/A 47938-2025 artfynd.xlsx
+++ b/artfynd/A 47938-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129032920</v>
+        <v>129032876</v>
       </c>
       <c r="B2" t="n">
         <v>79041</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>409793</v>
+        <v>408997</v>
       </c>
       <c r="R2" t="n">
-        <v>6782448</v>
+        <v>6782283</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129011405</v>
+        <v>129011403</v>
       </c>
       <c r="B3" t="n">
         <v>79041</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>409747</v>
+        <v>409706</v>
       </c>
       <c r="R3" t="n">
-        <v>6782328</v>
+        <v>6782359</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -842,7 +842,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -852,7 +852,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129032876</v>
+        <v>129032905</v>
       </c>
       <c r="B4" t="n">
         <v>79041</v>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>408997</v>
+        <v>409624</v>
       </c>
       <c r="R4" t="n">
-        <v>6782283</v>
+        <v>6782292</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,7 +976,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129011403</v>
+        <v>129032920</v>
       </c>
       <c r="B5" t="n">
         <v>79041</v>
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>409706</v>
+        <v>409793</v>
       </c>
       <c r="R5" t="n">
-        <v>6782359</v>
+        <v>6782448</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1044,19 +1044,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>12:06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,19 +1061,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129032905</v>
+        <v>129011405</v>
       </c>
       <c r="B6" t="n">
         <v>79041</v>
@@ -1118,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>409624</v>
+        <v>409747</v>
       </c>
       <c r="R6" t="n">
-        <v>6782292</v>
+        <v>6782328</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1151,9 +1141,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1168,22 +1168,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129032394</v>
+        <v>129011389</v>
       </c>
       <c r="B7" t="n">
-        <v>79631</v>
+        <v>79041</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>409553</v>
+        <v>409278</v>
       </c>
       <c r="R7" t="n">
-        <v>6782378</v>
+        <v>6782361</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1248,9 +1248,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1265,19 +1275,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129032907</v>
+        <v>129032919</v>
       </c>
       <c r="B8" t="n">
         <v>79041</v>
@@ -1312,10 +1322,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>409686</v>
+        <v>409358</v>
       </c>
       <c r="R8" t="n">
-        <v>6782351</v>
+        <v>6782291</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1374,7 +1384,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129011389</v>
+        <v>129032907</v>
       </c>
       <c r="B9" t="n">
         <v>79041</v>
@@ -1409,10 +1419,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>409278</v>
+        <v>409686</v>
       </c>
       <c r="R9" t="n">
-        <v>6782361</v>
+        <v>6782351</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1442,19 +1452,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>15:18</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>15:18</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1469,22 +1469,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129032919</v>
+        <v>129032394</v>
       </c>
       <c r="B10" t="n">
-        <v>79041</v>
+        <v>79631</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1492,21 +1492,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>409358</v>
+        <v>409553</v>
       </c>
       <c r="R10" t="n">
-        <v>6782291</v>
+        <v>6782378</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1566,19 +1566,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129011398</v>
+        <v>129032894</v>
       </c>
       <c r="B11" t="n">
         <v>79041</v>
@@ -1613,10 +1613,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>409596</v>
+        <v>409292</v>
       </c>
       <c r="R11" t="n">
-        <v>6782395</v>
+        <v>6782306</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1646,19 +1646,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>13:08</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>13:08</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1673,19 +1663,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129032894</v>
+        <v>129011398</v>
       </c>
       <c r="B12" t="n">
         <v>79041</v>
@@ -1720,10 +1710,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>409292</v>
+        <v>409596</v>
       </c>
       <c r="R12" t="n">
-        <v>6782306</v>
+        <v>6782395</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1753,9 +1743,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1770,12 +1770,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2083,7 +2083,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129032897</v>
+        <v>129032909</v>
       </c>
       <c r="B16" t="n">
         <v>79041</v>
@@ -2118,10 +2118,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>409469</v>
+        <v>409727</v>
       </c>
       <c r="R16" t="n">
-        <v>6782371</v>
+        <v>6782352</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2180,7 +2180,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129032909</v>
+        <v>129032897</v>
       </c>
       <c r="B17" t="n">
         <v>79041</v>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>409727</v>
+        <v>409469</v>
       </c>
       <c r="R17" t="n">
-        <v>6782352</v>
+        <v>6782371</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2277,10 +2277,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129011376</v>
+        <v>129032885</v>
       </c>
       <c r="B18" t="n">
-        <v>91560</v>
+        <v>79041</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2288,21 +2288,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2312,10 +2312,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>409774</v>
+        <v>409078</v>
       </c>
       <c r="R18" t="n">
-        <v>6782323</v>
+        <v>6782312</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2345,19 +2345,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>11:31</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>11:31</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2372,19 +2362,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129032885</v>
+        <v>129032892</v>
       </c>
       <c r="B19" t="n">
         <v>79041</v>
@@ -2419,10 +2409,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>409078</v>
+        <v>409244</v>
       </c>
       <c r="R19" t="n">
-        <v>6782312</v>
+        <v>6782381</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2588,10 +2578,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129032892</v>
+        <v>129011376</v>
       </c>
       <c r="B21" t="n">
-        <v>79041</v>
+        <v>91560</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2599,21 +2589,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2623,10 +2613,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>409244</v>
+        <v>409774</v>
       </c>
       <c r="R21" t="n">
-        <v>6782381</v>
+        <v>6782323</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2656,9 +2646,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2673,12 +2673,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2782,7 +2782,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129011383</v>
+        <v>129011407</v>
       </c>
       <c r="B23" t="n">
         <v>79041</v>
@@ -2817,10 +2817,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>409028</v>
+        <v>409795</v>
       </c>
       <c r="R23" t="n">
-        <v>6782350</v>
+        <v>6782327</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2852,7 +2852,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2996,7 +2996,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129011407</v>
+        <v>129011383</v>
       </c>
       <c r="B25" t="n">
         <v>79041</v>
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>409795</v>
+        <v>409028</v>
       </c>
       <c r="R25" t="n">
-        <v>6782327</v>
+        <v>6782350</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3066,7 +3066,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3522,10 +3522,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129032913</v>
+        <v>129011369</v>
       </c>
       <c r="B30" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3533,34 +3533,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>409757</v>
+        <v>409683</v>
       </c>
       <c r="R30" t="n">
-        <v>6782355</v>
+        <v>6782391</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3590,9 +3598,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3607,19 +3625,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129032406</v>
+        <v>129011391</v>
       </c>
       <c r="B31" t="n">
         <v>79041</v>
@@ -3654,10 +3672,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>409253</v>
+        <v>409349</v>
       </c>
       <c r="R31" t="n">
-        <v>6782372</v>
+        <v>6782383</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3687,9 +3705,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3704,19 +3732,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129032882</v>
+        <v>129032878</v>
       </c>
       <c r="B32" t="n">
         <v>79041</v>
@@ -3751,10 +3779,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>408992</v>
+        <v>408966</v>
       </c>
       <c r="R32" t="n">
-        <v>6782394</v>
+        <v>6782283</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3813,7 +3841,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129011391</v>
+        <v>129032913</v>
       </c>
       <c r="B33" t="n">
         <v>79041</v>
@@ -3848,10 +3876,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>409349</v>
+        <v>409757</v>
       </c>
       <c r="R33" t="n">
-        <v>6782383</v>
+        <v>6782355</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3881,19 +3909,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>14:34</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>14:34</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3908,19 +3926,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129032878</v>
+        <v>129032406</v>
       </c>
       <c r="B34" t="n">
         <v>79041</v>
@@ -3955,10 +3973,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>408966</v>
+        <v>409253</v>
       </c>
       <c r="R34" t="n">
-        <v>6782283</v>
+        <v>6782372</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4005,22 +4023,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129011369</v>
+        <v>129032882</v>
       </c>
       <c r="B35" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4028,42 +4046,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>409683</v>
+        <v>408992</v>
       </c>
       <c r="R35" t="n">
-        <v>6782391</v>
+        <v>6782394</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4093,19 +4103,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>12:56</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>12:56</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4120,19 +4120,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129032887</v>
+        <v>129011381</v>
       </c>
       <c r="B36" t="n">
         <v>79041</v>
@@ -4167,10 +4167,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>409176</v>
+        <v>409010</v>
       </c>
       <c r="R36" t="n">
-        <v>6782420</v>
+        <v>6782383</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4200,9 +4200,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4217,19 +4227,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129011381</v>
+        <v>129032887</v>
       </c>
       <c r="B37" t="n">
         <v>79041</v>
@@ -4264,10 +4274,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>409010</v>
+        <v>409176</v>
       </c>
       <c r="R37" t="n">
-        <v>6782383</v>
+        <v>6782420</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4297,19 +4307,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>16:06</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>16:06</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4324,19 +4324,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129032891</v>
+        <v>129011399</v>
       </c>
       <c r="B38" t="n">
         <v>79041</v>
@@ -4371,10 +4371,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>409241</v>
+        <v>409609</v>
       </c>
       <c r="R38" t="n">
-        <v>6782372</v>
+        <v>6782404</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4404,9 +4404,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4421,19 +4431,19 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129011392</v>
+        <v>129032911</v>
       </c>
       <c r="B39" t="n">
         <v>79041</v>
@@ -4468,10 +4478,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>409361</v>
+        <v>409777</v>
       </c>
       <c r="R39" t="n">
-        <v>6782401</v>
+        <v>6782445</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4501,19 +4511,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>14:31</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>14:31</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4528,19 +4528,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129032911</v>
+        <v>129032407</v>
       </c>
       <c r="B40" t="n">
         <v>79041</v>
@@ -4575,10 +4575,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>409777</v>
+        <v>409659</v>
       </c>
       <c r="R40" t="n">
-        <v>6782445</v>
+        <v>6782436</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4625,12 +4625,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -4734,7 +4734,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129032407</v>
+        <v>129011394</v>
       </c>
       <c r="B42" t="n">
         <v>79041</v>
@@ -4769,10 +4769,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>409659</v>
+        <v>409543</v>
       </c>
       <c r="R42" t="n">
-        <v>6782436</v>
+        <v>6782361</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4802,9 +4802,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4819,12 +4829,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -4928,7 +4938,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129011394</v>
+        <v>129032891</v>
       </c>
       <c r="B44" t="n">
         <v>79041</v>
@@ -4963,10 +4973,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>409543</v>
+        <v>409241</v>
       </c>
       <c r="R44" t="n">
-        <v>6782361</v>
+        <v>6782372</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4996,19 +5006,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>13:27</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>13:27</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5023,19 +5023,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129011399</v>
+        <v>129011392</v>
       </c>
       <c r="B45" t="n">
         <v>79041</v>
@@ -5070,10 +5070,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>409609</v>
+        <v>409361</v>
       </c>
       <c r="R45" t="n">
-        <v>6782404</v>
+        <v>6782401</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5105,7 +5105,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5115,7 +5115,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5239,7 +5239,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129011408</v>
+        <v>129032884</v>
       </c>
       <c r="B47" t="n">
         <v>79041</v>
@@ -5274,10 +5274,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>409801</v>
+        <v>409039</v>
       </c>
       <c r="R47" t="n">
-        <v>6782315</v>
+        <v>6782290</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5307,19 +5307,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>11:08</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>11:08</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5334,12 +5324,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -5443,7 +5433,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129011380</v>
+        <v>129011408</v>
       </c>
       <c r="B49" t="n">
         <v>79041</v>
@@ -5478,10 +5468,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>408984</v>
+        <v>409801</v>
       </c>
       <c r="R49" t="n">
-        <v>6782385</v>
+        <v>6782315</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5513,7 +5503,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5523,7 +5513,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5550,7 +5540,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129032884</v>
+        <v>129011380</v>
       </c>
       <c r="B50" t="n">
         <v>79041</v>
@@ -5585,10 +5575,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>409039</v>
+        <v>408984</v>
       </c>
       <c r="R50" t="n">
-        <v>6782290</v>
+        <v>6782385</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5618,9 +5608,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5635,22 +5635,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129032866</v>
+        <v>129032899</v>
       </c>
       <c r="B51" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5658,21 +5658,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5682,10 +5682,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>409757</v>
+        <v>409397</v>
       </c>
       <c r="R51" t="n">
-        <v>6782386</v>
+        <v>6782272</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5744,7 +5744,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129011401</v>
+        <v>129011386</v>
       </c>
       <c r="B52" t="n">
         <v>79041</v>
@@ -5779,10 +5779,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>409663</v>
+        <v>409210</v>
       </c>
       <c r="R52" t="n">
-        <v>6782385</v>
+        <v>6782365</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5814,7 +5814,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5851,7 +5851,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129032899</v>
+        <v>129011396</v>
       </c>
       <c r="B53" t="n">
         <v>79041</v>
@@ -5886,10 +5886,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>409397</v>
+        <v>409584</v>
       </c>
       <c r="R53" t="n">
-        <v>6782272</v>
+        <v>6782395</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5919,9 +5919,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5936,19 +5946,19 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129011386</v>
+        <v>129011409</v>
       </c>
       <c r="B54" t="n">
         <v>79041</v>
@@ -5983,10 +5993,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>409210</v>
+        <v>409202</v>
       </c>
       <c r="R54" t="n">
-        <v>6782365</v>
+        <v>6782367</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6037,6 +6047,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6055,7 +6066,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129011409</v>
+        <v>129011401</v>
       </c>
       <c r="B55" t="n">
         <v>79041</v>
@@ -6090,10 +6101,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>409202</v>
+        <v>409663</v>
       </c>
       <c r="R55" t="n">
-        <v>6782367</v>
+        <v>6782385</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6125,7 +6136,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6135,7 +6146,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6144,7 +6155,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6163,10 +6173,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129011396</v>
+        <v>129032866</v>
       </c>
       <c r="B56" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6174,21 +6184,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6198,10 +6208,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>409584</v>
+        <v>409757</v>
       </c>
       <c r="R56" t="n">
-        <v>6782395</v>
+        <v>6782386</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6231,19 +6241,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>13:11</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>13:11</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6258,12 +6258,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -6367,10 +6367,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129011375</v>
+        <v>129032403</v>
       </c>
       <c r="B58" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6378,21 +6378,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6402,10 +6402,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>409335</v>
+        <v>409021</v>
       </c>
       <c r="R58" t="n">
-        <v>6782352</v>
+        <v>6782365</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6435,19 +6435,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>14:40</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>14:40</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6462,22 +6452,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129032403</v>
+        <v>129011375</v>
       </c>
       <c r="B59" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6485,21 +6475,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6509,10 +6499,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>409021</v>
+        <v>409335</v>
       </c>
       <c r="R59" t="n">
-        <v>6782365</v>
+        <v>6782352</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6542,9 +6532,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6559,12 +6559,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -6806,32 +6806,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129011387</v>
+        <v>129032400</v>
       </c>
       <c r="B62" t="n">
-        <v>79041</v>
+        <v>91997</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6841,10 +6841,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>409232</v>
+        <v>409738</v>
       </c>
       <c r="R62" t="n">
-        <v>6782353</v>
+        <v>6782382</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6874,19 +6874,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>15:22</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>15:22</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6901,22 +6891,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129032872</v>
+        <v>129032914</v>
       </c>
       <c r="B63" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6924,21 +6914,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6948,10 +6938,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>409594</v>
+        <v>409759</v>
       </c>
       <c r="R63" t="n">
-        <v>6782294</v>
+        <v>6782343</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7010,10 +7000,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129032886</v>
+        <v>129032872</v>
       </c>
       <c r="B64" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7021,21 +7011,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7045,10 +7035,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>409108</v>
+        <v>409594</v>
       </c>
       <c r="R64" t="n">
-        <v>6782395</v>
+        <v>6782294</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7107,7 +7097,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129011384</v>
+        <v>129011379</v>
       </c>
       <c r="B65" t="n">
         <v>79041</v>
@@ -7142,10 +7132,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>409068</v>
+        <v>408991</v>
       </c>
       <c r="R65" t="n">
-        <v>6782377</v>
+        <v>6782360</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7177,7 +7167,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7187,7 +7177,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7214,7 +7204,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129011379</v>
+        <v>129011387</v>
       </c>
       <c r="B66" t="n">
         <v>79041</v>
@@ -7249,10 +7239,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>408991</v>
+        <v>409232</v>
       </c>
       <c r="R66" t="n">
-        <v>6782360</v>
+        <v>6782353</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7284,7 +7274,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7294,7 +7284,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7321,7 +7311,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129032914</v>
+        <v>129032886</v>
       </c>
       <c r="B67" t="n">
         <v>79041</v>
@@ -7356,10 +7346,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>409759</v>
+        <v>409108</v>
       </c>
       <c r="R67" t="n">
-        <v>6782343</v>
+        <v>6782395</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7418,10 +7408,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129032874</v>
+        <v>129011384</v>
       </c>
       <c r="B68" t="n">
-        <v>91560</v>
+        <v>79041</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7429,21 +7419,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7453,10 +7443,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>409405</v>
+        <v>409068</v>
       </c>
       <c r="R68" t="n">
-        <v>6782366</v>
+        <v>6782377</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7486,9 +7476,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7503,44 +7503,44 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129032400</v>
+        <v>129032874</v>
       </c>
       <c r="B69" t="n">
-        <v>91997</v>
+        <v>91560</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1209</v>
+        <v>5432</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7550,10 +7550,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>409738</v>
+        <v>409405</v>
       </c>
       <c r="R69" t="n">
-        <v>6782382</v>
+        <v>6782366</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7600,12 +7600,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
@@ -7814,10 +7814,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129032896</v>
+        <v>129032873</v>
       </c>
       <c r="B72" t="n">
-        <v>79041</v>
+        <v>91542</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7825,34 +7825,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>409331</v>
+        <v>409075</v>
       </c>
       <c r="R72" t="n">
-        <v>6782342</v>
+        <v>6782317</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7893,6 +7896,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -7911,7 +7915,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129032902</v>
+        <v>129032900</v>
       </c>
       <c r="B73" t="n">
         <v>79041</v>
@@ -7946,7 +7950,7 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>409549</v>
+        <v>409449</v>
       </c>
       <c r="R73" t="n">
         <v>6782286</v>
@@ -8105,7 +8109,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129032900</v>
+        <v>129032902</v>
       </c>
       <c r="B75" t="n">
         <v>79041</v>
@@ -8140,7 +8144,7 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>409449</v>
+        <v>409549</v>
       </c>
       <c r="R75" t="n">
         <v>6782286</v>
@@ -8202,10 +8206,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129032873</v>
+        <v>129032896</v>
       </c>
       <c r="B76" t="n">
-        <v>91542</v>
+        <v>79041</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8213,37 +8217,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>409075</v>
+        <v>409331</v>
       </c>
       <c r="R76" t="n">
-        <v>6782317</v>
+        <v>6782342</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8284,7 +8285,6 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8303,7 +8303,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129032893</v>
+        <v>129011404</v>
       </c>
       <c r="B77" t="n">
         <v>79041</v>
@@ -8338,10 +8338,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>409280</v>
+        <v>409736</v>
       </c>
       <c r="R77" t="n">
-        <v>6782382</v>
+        <v>6782394</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8371,9 +8371,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8388,19 +8398,19 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129011404</v>
+        <v>129032901</v>
       </c>
       <c r="B78" t="n">
         <v>79041</v>
@@ -8435,10 +8445,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>409736</v>
+        <v>409528</v>
       </c>
       <c r="R78" t="n">
-        <v>6782394</v>
+        <v>6782292</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8468,19 +8478,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>11:59</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>11:59</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8495,19 +8495,19 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129032901</v>
+        <v>129032888</v>
       </c>
       <c r="B79" t="n">
         <v>79041</v>
@@ -8542,10 +8542,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>409528</v>
+        <v>409127</v>
       </c>
       <c r="R79" t="n">
-        <v>6782292</v>
+        <v>6782290</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8604,7 +8604,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129032888</v>
+        <v>129032893</v>
       </c>
       <c r="B80" t="n">
         <v>79041</v>
@@ -8639,10 +8639,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>409127</v>
+        <v>409280</v>
       </c>
       <c r="R80" t="n">
-        <v>6782290</v>
+        <v>6782382</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8992,7 +8992,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129032409</v>
+        <v>129032916</v>
       </c>
       <c r="B84" t="n">
         <v>79041</v>
@@ -9027,10 +9027,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>409782</v>
+        <v>409812</v>
       </c>
       <c r="R84" t="n">
-        <v>6782339</v>
+        <v>6782309</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9077,19 +9077,19 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129032916</v>
+        <v>129032409</v>
       </c>
       <c r="B85" t="n">
         <v>79041</v>
@@ -9124,10 +9124,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>409812</v>
+        <v>409782</v>
       </c>
       <c r="R85" t="n">
-        <v>6782309</v>
+        <v>6782339</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9174,19 +9174,19 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129032898</v>
+        <v>129032918</v>
       </c>
       <c r="B86" t="n">
         <v>79041</v>
@@ -9221,10 +9221,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>409390</v>
+        <v>409363</v>
       </c>
       <c r="R86" t="n">
-        <v>6782289</v>
+        <v>6782377</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9283,7 +9283,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129032918</v>
+        <v>129032898</v>
       </c>
       <c r="B87" t="n">
         <v>79041</v>
@@ -9318,10 +9318,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>409363</v>
+        <v>409390</v>
       </c>
       <c r="R87" t="n">
-        <v>6782377</v>
+        <v>6782289</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9604,7 +9604,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129011393</v>
+        <v>129032895</v>
       </c>
       <c r="B90" t="n">
         <v>79041</v>
@@ -9639,10 +9639,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>409472</v>
+        <v>409310</v>
       </c>
       <c r="R90" t="n">
-        <v>6782351</v>
+        <v>6782326</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9672,19 +9672,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>14:05</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>14:05</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9699,19 +9689,19 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129032895</v>
+        <v>129032405</v>
       </c>
       <c r="B91" t="n">
         <v>79041</v>
@@ -9746,10 +9736,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>409310</v>
+        <v>409048</v>
       </c>
       <c r="R91" t="n">
-        <v>6782326</v>
+        <v>6782365</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9796,19 +9786,19 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129032903</v>
+        <v>129032880</v>
       </c>
       <c r="B92" t="n">
         <v>79041</v>
@@ -9843,10 +9833,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>409582</v>
+        <v>408901</v>
       </c>
       <c r="R92" t="n">
-        <v>6782297</v>
+        <v>6782390</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9905,7 +9895,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129032880</v>
+        <v>129011393</v>
       </c>
       <c r="B93" t="n">
         <v>79041</v>
@@ -9940,10 +9930,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>408901</v>
+        <v>409472</v>
       </c>
       <c r="R93" t="n">
-        <v>6782390</v>
+        <v>6782351</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9973,9 +9963,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -9990,19 +9990,19 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129032405</v>
+        <v>129032903</v>
       </c>
       <c r="B94" t="n">
         <v>79041</v>
@@ -10037,10 +10037,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>409048</v>
+        <v>409582</v>
       </c>
       <c r="R94" t="n">
-        <v>6782365</v>
+        <v>6782297</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10087,19 +10087,19 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129011388</v>
+        <v>129032408</v>
       </c>
       <c r="B95" t="n">
         <v>79041</v>
@@ -10134,10 +10134,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>409250</v>
+        <v>409749</v>
       </c>
       <c r="R95" t="n">
-        <v>6782354</v>
+        <v>6782325</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10167,19 +10167,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z95" t="inlineStr">
-        <is>
-          <t>15:19</t>
-        </is>
-      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB95" t="inlineStr">
-        <is>
-          <t>15:19</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10194,19 +10184,19 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129011406</v>
+        <v>129032890</v>
       </c>
       <c r="B96" t="n">
         <v>79041</v>
@@ -10241,10 +10231,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>409759</v>
+        <v>409228</v>
       </c>
       <c r="R96" t="n">
-        <v>6782314</v>
+        <v>6782298</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10274,19 +10264,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z96" t="inlineStr">
-        <is>
-          <t>11:41</t>
-        </is>
-      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB96" t="inlineStr">
-        <is>
-          <t>11:41</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10301,19 +10281,19 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129032408</v>
+        <v>129032875</v>
       </c>
       <c r="B97" t="n">
         <v>79041</v>
@@ -10348,10 +10328,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>409749</v>
+        <v>409034</v>
       </c>
       <c r="R97" t="n">
-        <v>6782325</v>
+        <v>6782261</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10398,12 +10378,12 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
@@ -10507,7 +10487,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129032890</v>
+        <v>129011406</v>
       </c>
       <c r="B99" t="n">
         <v>79041</v>
@@ -10542,10 +10522,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>409228</v>
+        <v>409759</v>
       </c>
       <c r="R99" t="n">
-        <v>6782298</v>
+        <v>6782314</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10575,9 +10555,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10592,19 +10582,19 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129032875</v>
+        <v>129011388</v>
       </c>
       <c r="B100" t="n">
         <v>79041</v>
@@ -10639,10 +10629,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>409034</v>
+        <v>409250</v>
       </c>
       <c r="R100" t="n">
-        <v>6782261</v>
+        <v>6782354</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10672,9 +10662,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10689,12 +10689,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
@@ -10808,7 +10808,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129011377</v>
+        <v>129011385</v>
       </c>
       <c r="B102" t="n">
         <v>79041</v>
@@ -10843,10 +10843,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>408995</v>
+        <v>409214</v>
       </c>
       <c r="R102" t="n">
-        <v>6782299</v>
+        <v>6782345</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10878,7 +10878,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -10888,7 +10888,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10915,7 +10915,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129011402</v>
+        <v>129011377</v>
       </c>
       <c r="B103" t="n">
         <v>79041</v>
@@ -10950,10 +10950,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>409671</v>
+        <v>408995</v>
       </c>
       <c r="R103" t="n">
-        <v>6782390</v>
+        <v>6782299</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10985,7 +10985,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -10995,7 +10995,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11022,7 +11022,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129011385</v>
+        <v>129032915</v>
       </c>
       <c r="B104" t="n">
         <v>79041</v>
@@ -11057,10 +11057,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>409214</v>
+        <v>409765</v>
       </c>
       <c r="R104" t="n">
-        <v>6782345</v>
+        <v>6782330</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11090,19 +11090,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z104" t="inlineStr">
-        <is>
-          <t>15:29</t>
-        </is>
-      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB104" t="inlineStr">
-        <is>
-          <t>15:29</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11117,19 +11107,19 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129032877</v>
+        <v>129032904</v>
       </c>
       <c r="B105" t="n">
         <v>79041</v>
@@ -11164,10 +11154,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>408994</v>
+        <v>409568</v>
       </c>
       <c r="R105" t="n">
-        <v>6782293</v>
+        <v>6782383</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11226,7 +11216,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129032904</v>
+        <v>129011402</v>
       </c>
       <c r="B106" t="n">
         <v>79041</v>
@@ -11261,10 +11251,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>409568</v>
+        <v>409671</v>
       </c>
       <c r="R106" t="n">
-        <v>6782383</v>
+        <v>6782390</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11294,9 +11284,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11311,19 +11311,19 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129032915</v>
+        <v>129032877</v>
       </c>
       <c r="B107" t="n">
         <v>79041</v>
@@ -11358,10 +11358,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>409765</v>
+        <v>408994</v>
       </c>
       <c r="R107" t="n">
-        <v>6782330</v>
+        <v>6782293</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>

--- a/artfynd/A 47938-2025 artfynd.xlsx
+++ b/artfynd/A 47938-2025 artfynd.xlsx
@@ -2782,10 +2782,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129011407</v>
+        <v>129032393</v>
       </c>
       <c r="B23" t="n">
-        <v>79041</v>
+        <v>79631</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2793,21 +2793,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2817,10 +2817,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>409795</v>
+        <v>409554</v>
       </c>
       <c r="R23" t="n">
-        <v>6782327</v>
+        <v>6782380</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2850,19 +2850,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>11:12</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>11:12</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2877,19 +2867,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129011395</v>
+        <v>129011407</v>
       </c>
       <c r="B24" t="n">
         <v>79041</v>
@@ -2924,10 +2914,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>409555</v>
+        <v>409795</v>
       </c>
       <c r="R24" t="n">
-        <v>6782356</v>
+        <v>6782327</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2959,7 +2949,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -2969,7 +2959,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2996,7 +2986,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129011383</v>
+        <v>129011395</v>
       </c>
       <c r="B25" t="n">
         <v>79041</v>
@@ -3031,10 +3021,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>409028</v>
+        <v>409555</v>
       </c>
       <c r="R25" t="n">
-        <v>6782350</v>
+        <v>6782356</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3066,7 +3056,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3076,7 +3066,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3103,10 +3093,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129032399</v>
+        <v>129011383</v>
       </c>
       <c r="B26" t="n">
-        <v>91562</v>
+        <v>79041</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3114,21 +3104,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3138,10 +3128,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>409492</v>
+        <v>409028</v>
       </c>
       <c r="R26" t="n">
-        <v>6782346</v>
+        <v>6782350</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3171,9 +3161,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3188,19 +3188,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129011374</v>
+        <v>129032399</v>
       </c>
       <c r="B27" t="n">
         <v>91562</v>
@@ -3228,24 +3228,17 @@
           <t>(Brot.) Murrill</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>409475</v>
+        <v>409492</v>
       </c>
       <c r="R27" t="n">
-        <v>6782342</v>
+        <v>6782346</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3275,55 +3268,39 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>13:57</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>13:57</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>hackspetthål under tickorna</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129032395</v>
+        <v>129011374</v>
       </c>
       <c r="B28" t="n">
-        <v>57727</v>
+        <v>91562</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3331,31 +3308,30 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3363,10 +3339,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>409759</v>
+        <v>409475</v>
       </c>
       <c r="R28" t="n">
-        <v>6782358</v>
+        <v>6782342</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3396,39 +3372,55 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>hackspetthål under tickorna</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129032393</v>
+        <v>129032395</v>
       </c>
       <c r="B29" t="n">
-        <v>79631</v>
+        <v>57727</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3436,34 +3428,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>409554</v>
+        <v>409759</v>
       </c>
       <c r="R29" t="n">
-        <v>6782380</v>
+        <v>6782358</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4336,7 +4336,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129011399</v>
+        <v>129011394</v>
       </c>
       <c r="B38" t="n">
         <v>79041</v>
@@ -4371,10 +4371,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>409609</v>
+        <v>409543</v>
       </c>
       <c r="R38" t="n">
-        <v>6782404</v>
+        <v>6782361</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4406,7 +4406,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4443,7 +4443,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129032911</v>
+        <v>129032910</v>
       </c>
       <c r="B39" t="n">
         <v>79041</v>
@@ -4478,10 +4478,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>409777</v>
+        <v>409744</v>
       </c>
       <c r="R39" t="n">
-        <v>6782445</v>
+        <v>6782394</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4540,7 +4540,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129032407</v>
+        <v>129032891</v>
       </c>
       <c r="B40" t="n">
         <v>79041</v>
@@ -4575,10 +4575,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>409659</v>
+        <v>409241</v>
       </c>
       <c r="R40" t="n">
-        <v>6782436</v>
+        <v>6782372</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4625,19 +4625,19 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129032906</v>
+        <v>129011399</v>
       </c>
       <c r="B41" t="n">
         <v>79041</v>
@@ -4672,10 +4672,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>409684</v>
+        <v>409609</v>
       </c>
       <c r="R41" t="n">
-        <v>6782322</v>
+        <v>6782404</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4705,9 +4705,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4722,19 +4732,19 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129011394</v>
+        <v>129032911</v>
       </c>
       <c r="B42" t="n">
         <v>79041</v>
@@ -4769,10 +4779,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>409543</v>
+        <v>409777</v>
       </c>
       <c r="R42" t="n">
-        <v>6782361</v>
+        <v>6782445</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4802,19 +4812,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>13:27</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>13:27</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4829,19 +4829,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129032910</v>
+        <v>129032407</v>
       </c>
       <c r="B43" t="n">
         <v>79041</v>
@@ -4876,10 +4876,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>409744</v>
+        <v>409659</v>
       </c>
       <c r="R43" t="n">
-        <v>6782394</v>
+        <v>6782436</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4926,19 +4926,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129032891</v>
+        <v>129011392</v>
       </c>
       <c r="B44" t="n">
         <v>79041</v>
@@ -4973,10 +4973,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>409241</v>
+        <v>409361</v>
       </c>
       <c r="R44" t="n">
-        <v>6782372</v>
+        <v>6782401</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5006,9 +5006,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5023,19 +5033,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129011392</v>
+        <v>129032906</v>
       </c>
       <c r="B45" t="n">
         <v>79041</v>
@@ -5070,10 +5080,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>409361</v>
+        <v>409684</v>
       </c>
       <c r="R45" t="n">
-        <v>6782401</v>
+        <v>6782322</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5103,19 +5113,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>14:31</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>14:31</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5130,22 +5130,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129032869</v>
+        <v>129032884</v>
       </c>
       <c r="B46" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5153,21 +5153,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5177,10 +5177,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>409754</v>
+        <v>409039</v>
       </c>
       <c r="R46" t="n">
-        <v>6782356</v>
+        <v>6782290</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5239,7 +5239,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129032884</v>
+        <v>129032883</v>
       </c>
       <c r="B47" t="n">
         <v>79041</v>
@@ -5274,10 +5274,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>409039</v>
+        <v>409010</v>
       </c>
       <c r="R47" t="n">
-        <v>6782290</v>
+        <v>6782399</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5336,7 +5336,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129032883</v>
+        <v>129011408</v>
       </c>
       <c r="B48" t="n">
         <v>79041</v>
@@ -5371,10 +5371,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>409010</v>
+        <v>409801</v>
       </c>
       <c r="R48" t="n">
-        <v>6782399</v>
+        <v>6782315</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5404,9 +5404,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5421,19 +5431,19 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129011408</v>
+        <v>129011380</v>
       </c>
       <c r="B49" t="n">
         <v>79041</v>
@@ -5468,10 +5478,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>409801</v>
+        <v>408984</v>
       </c>
       <c r="R49" t="n">
-        <v>6782315</v>
+        <v>6782385</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5503,7 +5513,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5513,7 +5523,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5540,10 +5550,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129011380</v>
+        <v>129032869</v>
       </c>
       <c r="B50" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5551,21 +5561,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5575,10 +5585,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>408984</v>
+        <v>409754</v>
       </c>
       <c r="R50" t="n">
-        <v>6782385</v>
+        <v>6782356</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5608,19 +5618,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>16:07</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>16:07</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5635,12 +5635,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -6806,32 +6806,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129032400</v>
+        <v>129032914</v>
       </c>
       <c r="B62" t="n">
-        <v>91997</v>
+        <v>79041</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6841,10 +6841,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>409738</v>
+        <v>409759</v>
       </c>
       <c r="R62" t="n">
-        <v>6782382</v>
+        <v>6782343</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6891,22 +6891,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129032914</v>
+        <v>129032872</v>
       </c>
       <c r="B63" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6914,21 +6914,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6938,10 +6938,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>409759</v>
+        <v>409594</v>
       </c>
       <c r="R63" t="n">
-        <v>6782343</v>
+        <v>6782294</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7000,10 +7000,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129032872</v>
+        <v>129011379</v>
       </c>
       <c r="B64" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7011,21 +7011,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7035,10 +7035,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>409594</v>
+        <v>408991</v>
       </c>
       <c r="R64" t="n">
-        <v>6782294</v>
+        <v>6782360</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7068,9 +7068,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7085,19 +7095,19 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129011379</v>
+        <v>129011387</v>
       </c>
       <c r="B65" t="n">
         <v>79041</v>
@@ -7132,10 +7142,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>408991</v>
+        <v>409232</v>
       </c>
       <c r="R65" t="n">
-        <v>6782360</v>
+        <v>6782353</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7167,7 +7177,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7177,7 +7187,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7204,7 +7214,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129011387</v>
+        <v>129032886</v>
       </c>
       <c r="B66" t="n">
         <v>79041</v>
@@ -7239,10 +7249,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>409232</v>
+        <v>409108</v>
       </c>
       <c r="R66" t="n">
-        <v>6782353</v>
+        <v>6782395</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7272,19 +7282,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>15:22</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>15:22</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7299,19 +7299,19 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129032886</v>
+        <v>129011384</v>
       </c>
       <c r="B67" t="n">
         <v>79041</v>
@@ -7346,10 +7346,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>409108</v>
+        <v>409068</v>
       </c>
       <c r="R67" t="n">
-        <v>6782395</v>
+        <v>6782377</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7379,9 +7379,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7396,44 +7406,44 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129011384</v>
+        <v>129032400</v>
       </c>
       <c r="B68" t="n">
-        <v>79041</v>
+        <v>91997</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7443,10 +7453,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>409068</v>
+        <v>409738</v>
       </c>
       <c r="R68" t="n">
-        <v>6782377</v>
+        <v>6782382</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7476,19 +7486,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>15:43</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>15:43</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7503,12 +7503,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>

--- a/artfynd/A 47938-2025 artfynd.xlsx
+++ b/artfynd/A 47938-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129032876</v>
+        <v>129032920</v>
       </c>
       <c r="B2" t="n">
         <v>79041</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>408997</v>
+        <v>409793</v>
       </c>
       <c r="R2" t="n">
-        <v>6782283</v>
+        <v>6782448</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129011403</v>
+        <v>129011405</v>
       </c>
       <c r="B3" t="n">
         <v>79041</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>409706</v>
+        <v>409747</v>
       </c>
       <c r="R3" t="n">
-        <v>6782359</v>
+        <v>6782328</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -842,7 +842,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -852,7 +852,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129032905</v>
+        <v>129032876</v>
       </c>
       <c r="B4" t="n">
         <v>79041</v>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>409624</v>
+        <v>408997</v>
       </c>
       <c r="R4" t="n">
-        <v>6782292</v>
+        <v>6782283</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,7 +976,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129032920</v>
+        <v>129011403</v>
       </c>
       <c r="B5" t="n">
         <v>79041</v>
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>409793</v>
+        <v>409706</v>
       </c>
       <c r="R5" t="n">
-        <v>6782448</v>
+        <v>6782359</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1044,9 +1044,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1061,19 +1071,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129011405</v>
+        <v>129032905</v>
       </c>
       <c r="B6" t="n">
         <v>79041</v>
@@ -1108,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>409747</v>
+        <v>409624</v>
       </c>
       <c r="R6" t="n">
-        <v>6782328</v>
+        <v>6782292</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1141,19 +1151,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>11:47</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>11:47</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1168,19 +1168,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129011389</v>
+        <v>129032907</v>
       </c>
       <c r="B7" t="n">
         <v>79041</v>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>409278</v>
+        <v>409686</v>
       </c>
       <c r="R7" t="n">
-        <v>6782361</v>
+        <v>6782351</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1248,19 +1248,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>15:18</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>15:18</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1275,22 +1265,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129032919</v>
+        <v>129032394</v>
       </c>
       <c r="B8" t="n">
-        <v>79041</v>
+        <v>79631</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1298,21 +1288,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1322,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>409358</v>
+        <v>409553</v>
       </c>
       <c r="R8" t="n">
-        <v>6782291</v>
+        <v>6782378</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1372,19 +1362,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129032907</v>
+        <v>129011389</v>
       </c>
       <c r="B9" t="n">
         <v>79041</v>
@@ -1419,10 +1409,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>409686</v>
+        <v>409278</v>
       </c>
       <c r="R9" t="n">
-        <v>6782351</v>
+        <v>6782361</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1452,9 +1442,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1469,22 +1469,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129032394</v>
+        <v>129032919</v>
       </c>
       <c r="B10" t="n">
-        <v>79631</v>
+        <v>79041</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1492,21 +1492,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>409553</v>
+        <v>409358</v>
       </c>
       <c r="R10" t="n">
-        <v>6782378</v>
+        <v>6782291</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1566,22 +1566,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129032894</v>
+        <v>129032398</v>
       </c>
       <c r="B11" t="n">
-        <v>79041</v>
+        <v>91560</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1589,21 +1589,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1613,10 +1613,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>409292</v>
+        <v>409482</v>
       </c>
       <c r="R11" t="n">
-        <v>6782306</v>
+        <v>6782335</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1663,12 +1663,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1782,10 +1782,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129032398</v>
+        <v>129032894</v>
       </c>
       <c r="B13" t="n">
-        <v>91562</v>
+        <v>79041</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1793,21 +1793,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1817,10 +1817,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>409482</v>
+        <v>409292</v>
       </c>
       <c r="R13" t="n">
-        <v>6782335</v>
+        <v>6782306</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1867,12 +1867,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2083,7 +2083,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129032909</v>
+        <v>129032897</v>
       </c>
       <c r="B16" t="n">
         <v>79041</v>
@@ -2118,10 +2118,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>409727</v>
+        <v>409469</v>
       </c>
       <c r="R16" t="n">
-        <v>6782352</v>
+        <v>6782371</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2180,7 +2180,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129032897</v>
+        <v>129032909</v>
       </c>
       <c r="B17" t="n">
         <v>79041</v>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>409469</v>
+        <v>409727</v>
       </c>
       <c r="R17" t="n">
-        <v>6782371</v>
+        <v>6782352</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2277,7 +2277,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129032885</v>
+        <v>129011400</v>
       </c>
       <c r="B18" t="n">
         <v>79041</v>
@@ -2312,10 +2312,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>409078</v>
+        <v>409643</v>
       </c>
       <c r="R18" t="n">
-        <v>6782312</v>
+        <v>6782378</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2345,9 +2345,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2362,22 +2372,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129032892</v>
+        <v>129032868</v>
       </c>
       <c r="B19" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2385,21 +2395,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2409,10 +2419,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>409244</v>
+        <v>409688</v>
       </c>
       <c r="R19" t="n">
-        <v>6782381</v>
+        <v>6782303</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2471,10 +2481,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129011400</v>
+        <v>129011376</v>
       </c>
       <c r="B20" t="n">
-        <v>79041</v>
+        <v>91558</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2482,21 +2492,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2506,10 +2516,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>409643</v>
+        <v>409774</v>
       </c>
       <c r="R20" t="n">
-        <v>6782378</v>
+        <v>6782323</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2541,7 +2551,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2551,7 +2561,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2578,10 +2588,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129011376</v>
+        <v>129032885</v>
       </c>
       <c r="B21" t="n">
-        <v>91560</v>
+        <v>79041</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2589,21 +2599,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2613,10 +2623,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>409774</v>
+        <v>409078</v>
       </c>
       <c r="R21" t="n">
-        <v>6782323</v>
+        <v>6782312</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2646,19 +2656,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>11:31</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>11:31</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2673,22 +2673,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129032868</v>
+        <v>129032892</v>
       </c>
       <c r="B22" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2696,21 +2696,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2720,10 +2720,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>409688</v>
+        <v>409244</v>
       </c>
       <c r="R22" t="n">
-        <v>6782303</v>
+        <v>6782381</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2782,10 +2782,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129032393</v>
+        <v>129011383</v>
       </c>
       <c r="B23" t="n">
-        <v>79631</v>
+        <v>79041</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2793,21 +2793,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2817,10 +2817,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>409554</v>
+        <v>409028</v>
       </c>
       <c r="R23" t="n">
-        <v>6782380</v>
+        <v>6782350</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2850,9 +2850,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2867,19 +2877,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129011407</v>
+        <v>129011395</v>
       </c>
       <c r="B24" t="n">
         <v>79041</v>
@@ -2914,10 +2924,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>409795</v>
+        <v>409555</v>
       </c>
       <c r="R24" t="n">
-        <v>6782327</v>
+        <v>6782356</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2949,7 +2959,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -2959,7 +2969,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2986,7 +2996,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129011395</v>
+        <v>129011407</v>
       </c>
       <c r="B25" t="n">
         <v>79041</v>
@@ -3021,10 +3031,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>409555</v>
+        <v>409795</v>
       </c>
       <c r="R25" t="n">
-        <v>6782356</v>
+        <v>6782327</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3056,7 +3066,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3066,7 +3076,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3093,10 +3103,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129011383</v>
+        <v>129032393</v>
       </c>
       <c r="B26" t="n">
-        <v>79041</v>
+        <v>79631</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3104,21 +3114,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3128,10 +3138,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>409028</v>
+        <v>409554</v>
       </c>
       <c r="R26" t="n">
-        <v>6782350</v>
+        <v>6782380</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3161,19 +3171,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>16:04</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>16:04</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3188,12 +3188,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3203,7 +3203,7 @@
         <v>129032399</v>
       </c>
       <c r="B27" t="n">
-        <v>91562</v>
+        <v>91560</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3300,7 +3300,7 @@
         <v>129011374</v>
       </c>
       <c r="B28" t="n">
-        <v>91562</v>
+        <v>91560</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3522,10 +3522,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129011369</v>
+        <v>129032913</v>
       </c>
       <c r="B30" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3533,42 +3533,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>409683</v>
+        <v>409757</v>
       </c>
       <c r="R30" t="n">
-        <v>6782391</v>
+        <v>6782355</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3598,19 +3590,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>12:56</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>12:56</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3625,12 +3607,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -3841,7 +3823,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129032913</v>
+        <v>129032406</v>
       </c>
       <c r="B33" t="n">
         <v>79041</v>
@@ -3876,10 +3858,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>409757</v>
+        <v>409253</v>
       </c>
       <c r="R33" t="n">
-        <v>6782355</v>
+        <v>6782372</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3926,19 +3908,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129032406</v>
+        <v>129032882</v>
       </c>
       <c r="B34" t="n">
         <v>79041</v>
@@ -3973,10 +3955,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>409253</v>
+        <v>408992</v>
       </c>
       <c r="R34" t="n">
-        <v>6782372</v>
+        <v>6782394</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4023,22 +4005,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129032882</v>
+        <v>129011369</v>
       </c>
       <c r="B35" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4046,34 +4028,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>408992</v>
+        <v>409683</v>
       </c>
       <c r="R35" t="n">
-        <v>6782394</v>
+        <v>6782391</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4103,9 +4093,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4120,19 +4120,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129011381</v>
+        <v>129032887</v>
       </c>
       <c r="B36" t="n">
         <v>79041</v>
@@ -4167,10 +4167,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>409010</v>
+        <v>409176</v>
       </c>
       <c r="R36" t="n">
-        <v>6782383</v>
+        <v>6782420</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4200,19 +4200,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>16:06</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>16:06</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4227,19 +4217,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129032887</v>
+        <v>129011381</v>
       </c>
       <c r="B37" t="n">
         <v>79041</v>
@@ -4274,10 +4264,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>409176</v>
+        <v>409010</v>
       </c>
       <c r="R37" t="n">
-        <v>6782420</v>
+        <v>6782383</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4307,9 +4297,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4324,19 +4324,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129011394</v>
+        <v>129032891</v>
       </c>
       <c r="B38" t="n">
         <v>79041</v>
@@ -4371,10 +4371,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>409543</v>
+        <v>409241</v>
       </c>
       <c r="R38" t="n">
-        <v>6782361</v>
+        <v>6782372</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4404,19 +4404,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>13:27</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>13:27</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4431,19 +4421,19 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129032910</v>
+        <v>129011392</v>
       </c>
       <c r="B39" t="n">
         <v>79041</v>
@@ -4478,10 +4468,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>409744</v>
+        <v>409361</v>
       </c>
       <c r="R39" t="n">
-        <v>6782394</v>
+        <v>6782401</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4511,9 +4501,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4528,19 +4528,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129032891</v>
+        <v>129032911</v>
       </c>
       <c r="B40" t="n">
         <v>79041</v>
@@ -4575,10 +4575,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>409241</v>
+        <v>409777</v>
       </c>
       <c r="R40" t="n">
-        <v>6782372</v>
+        <v>6782445</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4637,7 +4637,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129011399</v>
+        <v>129032906</v>
       </c>
       <c r="B41" t="n">
         <v>79041</v>
@@ -4672,10 +4672,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>409609</v>
+        <v>409684</v>
       </c>
       <c r="R41" t="n">
-        <v>6782404</v>
+        <v>6782322</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4705,19 +4705,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>13:06</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>13:06</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4732,19 +4722,19 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129032911</v>
+        <v>129032910</v>
       </c>
       <c r="B42" t="n">
         <v>79041</v>
@@ -4779,10 +4769,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>409777</v>
+        <v>409744</v>
       </c>
       <c r="R42" t="n">
-        <v>6782445</v>
+        <v>6782394</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4841,7 +4831,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129032407</v>
+        <v>129011394</v>
       </c>
       <c r="B43" t="n">
         <v>79041</v>
@@ -4876,10 +4866,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>409659</v>
+        <v>409543</v>
       </c>
       <c r="R43" t="n">
-        <v>6782436</v>
+        <v>6782361</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4909,9 +4899,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4926,19 +4926,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129011392</v>
+        <v>129011399</v>
       </c>
       <c r="B44" t="n">
         <v>79041</v>
@@ -4973,10 +4973,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>409361</v>
+        <v>409609</v>
       </c>
       <c r="R44" t="n">
-        <v>6782401</v>
+        <v>6782404</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5008,7 +5008,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5045,7 +5045,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129032906</v>
+        <v>129032407</v>
       </c>
       <c r="B45" t="n">
         <v>79041</v>
@@ -5080,10 +5080,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>409684</v>
+        <v>409659</v>
       </c>
       <c r="R45" t="n">
-        <v>6782322</v>
+        <v>6782436</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5130,19 +5130,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129032884</v>
+        <v>129011408</v>
       </c>
       <c r="B46" t="n">
         <v>79041</v>
@@ -5177,10 +5177,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>409039</v>
+        <v>409801</v>
       </c>
       <c r="R46" t="n">
-        <v>6782290</v>
+        <v>6782315</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5210,9 +5210,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5227,12 +5237,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5336,7 +5346,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129011408</v>
+        <v>129011380</v>
       </c>
       <c r="B48" t="n">
         <v>79041</v>
@@ -5371,10 +5381,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>409801</v>
+        <v>408984</v>
       </c>
       <c r="R48" t="n">
-        <v>6782315</v>
+        <v>6782385</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5406,7 +5416,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5416,7 +5426,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:08</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5443,10 +5453,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129011380</v>
+        <v>129032869</v>
       </c>
       <c r="B49" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5454,21 +5464,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5478,10 +5488,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>408984</v>
+        <v>409754</v>
       </c>
       <c r="R49" t="n">
-        <v>6782385</v>
+        <v>6782356</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5511,19 +5521,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>16:07</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>16:07</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5538,22 +5538,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129032869</v>
+        <v>129032884</v>
       </c>
       <c r="B50" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5561,21 +5561,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5585,10 +5585,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>409754</v>
+        <v>409039</v>
       </c>
       <c r="R50" t="n">
-        <v>6782356</v>
+        <v>6782290</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5647,7 +5647,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129032899</v>
+        <v>129011401</v>
       </c>
       <c r="B51" t="n">
         <v>79041</v>
@@ -5682,10 +5682,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>409397</v>
+        <v>409663</v>
       </c>
       <c r="R51" t="n">
-        <v>6782272</v>
+        <v>6782385</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5715,9 +5715,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5732,19 +5742,19 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129011386</v>
+        <v>129032899</v>
       </c>
       <c r="B52" t="n">
         <v>79041</v>
@@ -5779,10 +5789,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>409210</v>
+        <v>409397</v>
       </c>
       <c r="R52" t="n">
-        <v>6782365</v>
+        <v>6782272</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5812,19 +5822,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>15:26</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>15:26</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5839,19 +5839,19 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129011396</v>
+        <v>129011386</v>
       </c>
       <c r="B53" t="n">
         <v>79041</v>
@@ -5886,10 +5886,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>409584</v>
+        <v>409210</v>
       </c>
       <c r="R53" t="n">
-        <v>6782395</v>
+        <v>6782365</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6066,7 +6066,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129011401</v>
+        <v>129011396</v>
       </c>
       <c r="B55" t="n">
         <v>79041</v>
@@ -6101,10 +6101,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>409663</v>
+        <v>409584</v>
       </c>
       <c r="R55" t="n">
-        <v>6782385</v>
+        <v>6782395</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6136,7 +6136,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6146,7 +6146,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6367,10 +6367,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129032403</v>
+        <v>129011372</v>
       </c>
       <c r="B58" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6378,34 +6378,42 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>409021</v>
+        <v>409796</v>
       </c>
       <c r="R58" t="n">
-        <v>6782365</v>
+        <v>6782327</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6435,9 +6443,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6452,22 +6470,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129011375</v>
+        <v>129011373</v>
       </c>
       <c r="B59" t="n">
-        <v>78798</v>
+        <v>91560</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6475,34 +6493,41 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6446</v>
+        <v>5442</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>409335</v>
+        <v>409435</v>
       </c>
       <c r="R59" t="n">
-        <v>6782352</v>
+        <v>6782383</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6534,7 +6559,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6544,7 +6569,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>4 st på samma tall</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6553,6 +6583,7 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6571,10 +6602,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129011373</v>
+        <v>129011375</v>
       </c>
       <c r="B60" t="n">
-        <v>91562</v>
+        <v>78798</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6582,41 +6613,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5442</v>
+        <v>6446</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>409435</v>
+        <v>409335</v>
       </c>
       <c r="R60" t="n">
-        <v>6782383</v>
+        <v>6782352</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6648,7 +6672,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6658,12 +6682,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:14</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>4 st på samma tall</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6672,7 +6691,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6691,10 +6709,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129011372</v>
+        <v>129032403</v>
       </c>
       <c r="B61" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6702,42 +6720,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>409796</v>
+        <v>409021</v>
       </c>
       <c r="R61" t="n">
-        <v>6782327</v>
+        <v>6782365</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6767,19 +6777,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>11:10</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6794,44 +6794,44 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129032914</v>
+        <v>129032400</v>
       </c>
       <c r="B62" t="n">
-        <v>79041</v>
+        <v>91992</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6841,10 +6841,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>409759</v>
+        <v>409738</v>
       </c>
       <c r="R62" t="n">
-        <v>6782343</v>
+        <v>6782382</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6891,22 +6891,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129032872</v>
+        <v>129032874</v>
       </c>
       <c r="B63" t="n">
-        <v>78798</v>
+        <v>91558</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6914,21 +6914,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6446</v>
+        <v>5432</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6938,10 +6938,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>409594</v>
+        <v>409405</v>
       </c>
       <c r="R63" t="n">
-        <v>6782294</v>
+        <v>6782366</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7000,10 +7000,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129011379</v>
+        <v>129032396</v>
       </c>
       <c r="B64" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7011,34 +7011,42 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>408991</v>
+        <v>409753</v>
       </c>
       <c r="R64" t="n">
-        <v>6782360</v>
+        <v>6782323</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7068,19 +7076,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>16:09</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>16:09</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7095,22 +7093,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129011387</v>
+        <v>129032867</v>
       </c>
       <c r="B65" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7118,21 +7116,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7142,10 +7140,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>409232</v>
+        <v>409693</v>
       </c>
       <c r="R65" t="n">
-        <v>6782353</v>
+        <v>6782357</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7175,19 +7173,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>15:22</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>15:22</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7202,19 +7190,19 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129032886</v>
+        <v>129011387</v>
       </c>
       <c r="B66" t="n">
         <v>79041</v>
@@ -7249,10 +7237,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>409108</v>
+        <v>409232</v>
       </c>
       <c r="R66" t="n">
-        <v>6782395</v>
+        <v>6782353</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7282,9 +7270,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7299,19 +7297,19 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129011384</v>
+        <v>129032886</v>
       </c>
       <c r="B67" t="n">
         <v>79041</v>
@@ -7346,10 +7344,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>409068</v>
+        <v>409108</v>
       </c>
       <c r="R67" t="n">
-        <v>6782377</v>
+        <v>6782395</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7379,19 +7377,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>15:43</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>15:43</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7406,44 +7394,44 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129032400</v>
+        <v>129011379</v>
       </c>
       <c r="B68" t="n">
-        <v>91997</v>
+        <v>79041</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7453,10 +7441,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>409738</v>
+        <v>408991</v>
       </c>
       <c r="R68" t="n">
-        <v>6782382</v>
+        <v>6782360</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7486,9 +7474,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7503,22 +7501,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129032874</v>
+        <v>129032914</v>
       </c>
       <c r="B69" t="n">
-        <v>91560</v>
+        <v>79041</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7526,21 +7524,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7550,10 +7548,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>409405</v>
+        <v>409759</v>
       </c>
       <c r="R69" t="n">
-        <v>6782366</v>
+        <v>6782343</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7612,10 +7610,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129032396</v>
+        <v>129032872</v>
       </c>
       <c r="B70" t="n">
-        <v>57727</v>
+        <v>78798</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7623,42 +7621,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>409753</v>
+        <v>409594</v>
       </c>
       <c r="R70" t="n">
-        <v>6782323</v>
+        <v>6782294</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7705,22 +7695,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129032867</v>
+        <v>129011384</v>
       </c>
       <c r="B71" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7728,21 +7718,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7752,10 +7742,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>409693</v>
+        <v>409068</v>
       </c>
       <c r="R71" t="n">
-        <v>6782357</v>
+        <v>6782377</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7785,9 +7775,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7802,12 +7802,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -7817,7 +7817,7 @@
         <v>129032873</v>
       </c>
       <c r="B72" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7915,7 +7915,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129032900</v>
+        <v>129032896</v>
       </c>
       <c r="B73" t="n">
         <v>79041</v>
@@ -7950,10 +7950,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>409449</v>
+        <v>409331</v>
       </c>
       <c r="R73" t="n">
-        <v>6782286</v>
+        <v>6782342</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8012,7 +8012,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129032917</v>
+        <v>129032902</v>
       </c>
       <c r="B74" t="n">
         <v>79041</v>
@@ -8047,10 +8047,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>409360</v>
+        <v>409549</v>
       </c>
       <c r="R74" t="n">
-        <v>6782355</v>
+        <v>6782286</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8109,7 +8109,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129032902</v>
+        <v>129032917</v>
       </c>
       <c r="B75" t="n">
         <v>79041</v>
@@ -8144,10 +8144,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>409549</v>
+        <v>409360</v>
       </c>
       <c r="R75" t="n">
-        <v>6782286</v>
+        <v>6782355</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8206,7 +8206,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129032896</v>
+        <v>129032900</v>
       </c>
       <c r="B76" t="n">
         <v>79041</v>
@@ -8241,10 +8241,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>409331</v>
+        <v>409449</v>
       </c>
       <c r="R76" t="n">
-        <v>6782342</v>
+        <v>6782286</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8604,10 +8604,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129032893</v>
+        <v>129032402</v>
       </c>
       <c r="B80" t="n">
-        <v>79041</v>
+        <v>91558</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8615,21 +8615,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8639,10 +8639,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>409280</v>
+        <v>409767</v>
       </c>
       <c r="R80" t="n">
-        <v>6782382</v>
+        <v>6782352</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8689,22 +8689,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129032402</v>
+        <v>129032893</v>
       </c>
       <c r="B81" t="n">
-        <v>91560</v>
+        <v>79041</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8712,21 +8712,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8736,10 +8736,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>409767</v>
+        <v>409280</v>
       </c>
       <c r="R81" t="n">
-        <v>6782352</v>
+        <v>6782382</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8786,19 +8786,19 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129032908</v>
+        <v>129032879</v>
       </c>
       <c r="B82" t="n">
         <v>79041</v>
@@ -8833,10 +8833,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>409715</v>
+        <v>408909</v>
       </c>
       <c r="R82" t="n">
-        <v>6782363</v>
+        <v>6782332</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8895,7 +8895,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129032879</v>
+        <v>129032409</v>
       </c>
       <c r="B83" t="n">
         <v>79041</v>
@@ -8930,10 +8930,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>408909</v>
+        <v>409782</v>
       </c>
       <c r="R83" t="n">
-        <v>6782332</v>
+        <v>6782339</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8980,12 +8980,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
@@ -9089,7 +9089,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129032409</v>
+        <v>129032908</v>
       </c>
       <c r="B85" t="n">
         <v>79041</v>
@@ -9124,10 +9124,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>409782</v>
+        <v>409715</v>
       </c>
       <c r="R85" t="n">
-        <v>6782339</v>
+        <v>6782363</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9174,22 +9174,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129032918</v>
+        <v>129032870</v>
       </c>
       <c r="B86" t="n">
-        <v>79041</v>
+        <v>91560</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9197,34 +9197,45 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>409363</v>
+        <v>409530</v>
       </c>
       <c r="R86" t="n">
-        <v>6782377</v>
+        <v>6782289</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9265,6 +9276,7 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9380,10 +9392,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129032870</v>
+        <v>129032918</v>
       </c>
       <c r="B88" t="n">
-        <v>91562</v>
+        <v>79041</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9391,45 +9403,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>409530</v>
+        <v>409363</v>
       </c>
       <c r="R88" t="n">
-        <v>6782289</v>
+        <v>6782377</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9470,7 +9471,6 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -9604,7 +9604,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129032895</v>
+        <v>129011393</v>
       </c>
       <c r="B90" t="n">
         <v>79041</v>
@@ -9639,10 +9639,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>409310</v>
+        <v>409472</v>
       </c>
       <c r="R90" t="n">
-        <v>6782326</v>
+        <v>6782351</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9672,9 +9672,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9689,19 +9699,19 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129032405</v>
+        <v>129032903</v>
       </c>
       <c r="B91" t="n">
         <v>79041</v>
@@ -9736,10 +9746,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>409048</v>
+        <v>409582</v>
       </c>
       <c r="R91" t="n">
-        <v>6782365</v>
+        <v>6782297</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9786,12 +9796,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
@@ -9895,7 +9905,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129011393</v>
+        <v>129032895</v>
       </c>
       <c r="B93" t="n">
         <v>79041</v>
@@ -9930,10 +9940,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>409472</v>
+        <v>409310</v>
       </c>
       <c r="R93" t="n">
-        <v>6782351</v>
+        <v>6782326</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9963,19 +9973,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>14:05</t>
-        </is>
-      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>14:05</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -9990,19 +9990,19 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129032903</v>
+        <v>129032405</v>
       </c>
       <c r="B94" t="n">
         <v>79041</v>
@@ -10037,10 +10037,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>409582</v>
+        <v>409048</v>
       </c>
       <c r="R94" t="n">
-        <v>6782297</v>
+        <v>6782365</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10087,19 +10087,19 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129032408</v>
+        <v>129011388</v>
       </c>
       <c r="B95" t="n">
         <v>79041</v>
@@ -10134,10 +10134,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>409749</v>
+        <v>409250</v>
       </c>
       <c r="R95" t="n">
-        <v>6782325</v>
+        <v>6782354</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10167,9 +10167,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10184,19 +10194,19 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129032890</v>
+        <v>129032408</v>
       </c>
       <c r="B96" t="n">
         <v>79041</v>
@@ -10231,10 +10241,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>409228</v>
+        <v>409749</v>
       </c>
       <c r="R96" t="n">
-        <v>6782298</v>
+        <v>6782325</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10281,19 +10291,19 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129032875</v>
+        <v>129032912</v>
       </c>
       <c r="B97" t="n">
         <v>79041</v>
@@ -10328,10 +10338,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>409034</v>
+        <v>409762</v>
       </c>
       <c r="R97" t="n">
-        <v>6782261</v>
+        <v>6782335</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10390,7 +10400,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129032912</v>
+        <v>129032890</v>
       </c>
       <c r="B98" t="n">
         <v>79041</v>
@@ -10425,10 +10435,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>409762</v>
+        <v>409228</v>
       </c>
       <c r="R98" t="n">
-        <v>6782335</v>
+        <v>6782298</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10594,7 +10604,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129011388</v>
+        <v>129032875</v>
       </c>
       <c r="B100" t="n">
         <v>79041</v>
@@ -10629,10 +10639,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>409250</v>
+        <v>409034</v>
       </c>
       <c r="R100" t="n">
-        <v>6782354</v>
+        <v>6782261</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10662,19 +10672,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>15:19</t>
-        </is>
-      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>15:19</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10689,12 +10689,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
@@ -10808,10 +10808,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129011385</v>
+        <v>129032401</v>
       </c>
       <c r="B102" t="n">
-        <v>79041</v>
+        <v>91558</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10819,21 +10819,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10843,10 +10843,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>409214</v>
+        <v>409226</v>
       </c>
       <c r="R102" t="n">
-        <v>6782345</v>
+        <v>6782376</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10876,19 +10876,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z102" t="inlineStr">
-        <is>
-          <t>15:29</t>
-        </is>
-      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB102" t="inlineStr">
-        <is>
-          <t>15:29</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10903,19 +10893,19 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129011377</v>
+        <v>129032915</v>
       </c>
       <c r="B103" t="n">
         <v>79041</v>
@@ -10950,10 +10940,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>408995</v>
+        <v>409765</v>
       </c>
       <c r="R103" t="n">
-        <v>6782299</v>
+        <v>6782330</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10983,19 +10973,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z103" t="inlineStr">
-        <is>
-          <t>16:13</t>
-        </is>
-      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB103" t="inlineStr">
-        <is>
-          <t>16:13</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11010,19 +10990,19 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129032915</v>
+        <v>129011377</v>
       </c>
       <c r="B104" t="n">
         <v>79041</v>
@@ -11057,10 +11037,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>409765</v>
+        <v>408995</v>
       </c>
       <c r="R104" t="n">
-        <v>6782330</v>
+        <v>6782299</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11090,9 +11070,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11107,19 +11097,19 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129032904</v>
+        <v>129011402</v>
       </c>
       <c r="B105" t="n">
         <v>79041</v>
@@ -11154,10 +11144,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>409568</v>
+        <v>409671</v>
       </c>
       <c r="R105" t="n">
-        <v>6782383</v>
+        <v>6782390</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11187,9 +11177,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11204,19 +11204,19 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129011402</v>
+        <v>129011385</v>
       </c>
       <c r="B106" t="n">
         <v>79041</v>
@@ -11251,10 +11251,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>409671</v>
+        <v>409214</v>
       </c>
       <c r="R106" t="n">
-        <v>6782390</v>
+        <v>6782345</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11286,7 +11286,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11296,7 +11296,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11420,10 +11420,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129032401</v>
+        <v>129032904</v>
       </c>
       <c r="B108" t="n">
-        <v>91560</v>
+        <v>79041</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11431,21 +11431,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11455,10 +11455,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>409226</v>
+        <v>409568</v>
       </c>
       <c r="R108" t="n">
-        <v>6782376</v>
+        <v>6782383</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11505,12 +11505,12 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>

--- a/artfynd/A 47938-2025 artfynd.xlsx
+++ b/artfynd/A 47938-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129032920</v>
+        <v>129011405</v>
       </c>
       <c r="B2" t="n">
         <v>79041</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>409793</v>
+        <v>409747</v>
       </c>
       <c r="R2" t="n">
-        <v>6782448</v>
+        <v>6782328</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -743,9 +743,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -760,19 +770,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129011405</v>
+        <v>129011403</v>
       </c>
       <c r="B3" t="n">
         <v>79041</v>
@@ -807,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>409747</v>
+        <v>409706</v>
       </c>
       <c r="R3" t="n">
-        <v>6782328</v>
+        <v>6782359</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -842,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -852,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129032876</v>
+        <v>129032920</v>
       </c>
       <c r="B4" t="n">
         <v>79041</v>
@@ -914,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>408997</v>
+        <v>409793</v>
       </c>
       <c r="R4" t="n">
-        <v>6782283</v>
+        <v>6782448</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,7 +986,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129011403</v>
+        <v>129032876</v>
       </c>
       <c r="B5" t="n">
         <v>79041</v>
@@ -1011,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>409706</v>
+        <v>408997</v>
       </c>
       <c r="R5" t="n">
-        <v>6782359</v>
+        <v>6782283</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1044,19 +1054,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>12:06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,12 +1071,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1277,10 +1277,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129032394</v>
+        <v>129032919</v>
       </c>
       <c r="B8" t="n">
-        <v>79631</v>
+        <v>79041</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1288,21 +1288,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>409553</v>
+        <v>409358</v>
       </c>
       <c r="R8" t="n">
-        <v>6782378</v>
+        <v>6782291</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1362,22 +1362,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129011389</v>
+        <v>129032394</v>
       </c>
       <c r="B9" t="n">
-        <v>79041</v>
+        <v>79631</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1385,21 +1385,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1409,10 +1409,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>409278</v>
+        <v>409553</v>
       </c>
       <c r="R9" t="n">
-        <v>6782361</v>
+        <v>6782378</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1442,19 +1442,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>15:18</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>15:18</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1469,19 +1459,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129032919</v>
+        <v>129011389</v>
       </c>
       <c r="B10" t="n">
         <v>79041</v>
@@ -1516,10 +1506,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>409358</v>
+        <v>409278</v>
       </c>
       <c r="R10" t="n">
-        <v>6782291</v>
+        <v>6782361</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1549,9 +1539,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1566,22 +1566,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129032398</v>
+        <v>129011398</v>
       </c>
       <c r="B11" t="n">
-        <v>91560</v>
+        <v>79041</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1589,21 +1589,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1613,10 +1613,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>409482</v>
+        <v>409596</v>
       </c>
       <c r="R11" t="n">
-        <v>6782335</v>
+        <v>6782395</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1646,9 +1646,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1663,19 +1673,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129011398</v>
+        <v>129032894</v>
       </c>
       <c r="B12" t="n">
         <v>79041</v>
@@ -1710,10 +1720,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>409596</v>
+        <v>409292</v>
       </c>
       <c r="R12" t="n">
-        <v>6782395</v>
+        <v>6782306</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1743,19 +1753,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>13:08</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>13:08</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1770,22 +1770,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129032894</v>
+        <v>129032398</v>
       </c>
       <c r="B13" t="n">
-        <v>79041</v>
+        <v>91561</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1793,21 +1793,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1817,10 +1817,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>409292</v>
+        <v>409482</v>
       </c>
       <c r="R13" t="n">
-        <v>6782306</v>
+        <v>6782335</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1867,12 +1867,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -1986,10 +1986,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129032392</v>
+        <v>129032897</v>
       </c>
       <c r="B15" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1997,21 +1997,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2021,10 +2021,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>409554</v>
+        <v>409469</v>
       </c>
       <c r="R15" t="n">
-        <v>6782380</v>
+        <v>6782371</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2071,19 +2071,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129032897</v>
+        <v>129032909</v>
       </c>
       <c r="B16" t="n">
         <v>79041</v>
@@ -2118,10 +2118,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>409469</v>
+        <v>409727</v>
       </c>
       <c r="R16" t="n">
-        <v>6782371</v>
+        <v>6782352</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2180,10 +2180,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129032909</v>
+        <v>129032392</v>
       </c>
       <c r="B17" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2191,21 +2191,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>409727</v>
+        <v>409554</v>
       </c>
       <c r="R17" t="n">
-        <v>6782352</v>
+        <v>6782380</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2265,19 +2265,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129011400</v>
+        <v>129032885</v>
       </c>
       <c r="B18" t="n">
         <v>79041</v>
@@ -2312,10 +2312,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>409643</v>
+        <v>409078</v>
       </c>
       <c r="R18" t="n">
-        <v>6782378</v>
+        <v>6782312</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2345,19 +2345,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>12:59</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>12:59</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2372,12 +2362,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2481,10 +2471,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129011376</v>
+        <v>129032892</v>
       </c>
       <c r="B20" t="n">
-        <v>91558</v>
+        <v>79041</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2492,21 +2482,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2516,10 +2506,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>409774</v>
+        <v>409244</v>
       </c>
       <c r="R20" t="n">
-        <v>6782323</v>
+        <v>6782381</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2549,19 +2539,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>11:31</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>11:31</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2576,19 +2556,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129032885</v>
+        <v>129011400</v>
       </c>
       <c r="B21" t="n">
         <v>79041</v>
@@ -2623,10 +2603,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>409078</v>
+        <v>409643</v>
       </c>
       <c r="R21" t="n">
-        <v>6782312</v>
+        <v>6782378</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2656,9 +2636,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2673,22 +2663,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129032892</v>
+        <v>129011376</v>
       </c>
       <c r="B22" t="n">
-        <v>79041</v>
+        <v>91560</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2696,23 +2686,19 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2720,10 +2706,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>409244</v>
+        <v>409774</v>
       </c>
       <c r="R22" t="n">
-        <v>6782381</v>
+        <v>6782323</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2753,9 +2739,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2770,12 +2766,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -2889,10 +2885,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129011395</v>
+        <v>129032395</v>
       </c>
       <c r="B24" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2900,34 +2896,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>409555</v>
+        <v>409759</v>
       </c>
       <c r="R24" t="n">
-        <v>6782356</v>
+        <v>6782358</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2957,19 +2961,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>13:17</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>13:17</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2984,22 +2978,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129011407</v>
+        <v>129032399</v>
       </c>
       <c r="B25" t="n">
-        <v>79041</v>
+        <v>91561</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3007,21 +3001,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3031,10 +3025,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>409795</v>
+        <v>409492</v>
       </c>
       <c r="R25" t="n">
-        <v>6782327</v>
+        <v>6782346</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3064,19 +3058,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>11:12</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>11:12</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3091,22 +3075,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129032393</v>
+        <v>129011374</v>
       </c>
       <c r="B26" t="n">
-        <v>79631</v>
+        <v>91561</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3114,34 +3098,41 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229821</v>
+        <v>5442</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>409554</v>
+        <v>409475</v>
       </c>
       <c r="R26" t="n">
-        <v>6782380</v>
+        <v>6782342</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3171,39 +3162,55 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>hackspetthål under tickorna</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129032399</v>
+        <v>129011395</v>
       </c>
       <c r="B27" t="n">
-        <v>91560</v>
+        <v>79041</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3211,21 +3218,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3235,10 +3242,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>409492</v>
+        <v>409555</v>
       </c>
       <c r="R27" t="n">
-        <v>6782346</v>
+        <v>6782356</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3268,9 +3275,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3285,22 +3302,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129011374</v>
+        <v>129011407</v>
       </c>
       <c r="B28" t="n">
-        <v>91560</v>
+        <v>79041</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3308,41 +3325,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>409475</v>
+        <v>409795</v>
       </c>
       <c r="R28" t="n">
-        <v>6782342</v>
+        <v>6782327</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3374,7 +3384,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3384,12 +3394,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:57</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>hackspetthål under tickorna</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3398,7 +3403,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3417,10 +3421,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129032395</v>
+        <v>129032393</v>
       </c>
       <c r="B29" t="n">
-        <v>57727</v>
+        <v>79631</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3428,42 +3432,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>409759</v>
+        <v>409554</v>
       </c>
       <c r="R29" t="n">
-        <v>6782358</v>
+        <v>6782380</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3522,7 +3518,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129032913</v>
+        <v>129011391</v>
       </c>
       <c r="B30" t="n">
         <v>79041</v>
@@ -3557,10 +3553,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>409757</v>
+        <v>409349</v>
       </c>
       <c r="R30" t="n">
-        <v>6782355</v>
+        <v>6782383</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3590,9 +3586,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3607,19 +3613,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129011391</v>
+        <v>129032913</v>
       </c>
       <c r="B31" t="n">
         <v>79041</v>
@@ -3654,10 +3660,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>409349</v>
+        <v>409757</v>
       </c>
       <c r="R31" t="n">
-        <v>6782383</v>
+        <v>6782355</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3687,19 +3693,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>14:34</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>14:34</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3714,19 +3710,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129032878</v>
+        <v>129032406</v>
       </c>
       <c r="B32" t="n">
         <v>79041</v>
@@ -3761,10 +3757,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>408966</v>
+        <v>409253</v>
       </c>
       <c r="R32" t="n">
-        <v>6782283</v>
+        <v>6782372</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3811,19 +3807,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129032406</v>
+        <v>129032882</v>
       </c>
       <c r="B33" t="n">
         <v>79041</v>
@@ -3858,10 +3854,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>409253</v>
+        <v>408992</v>
       </c>
       <c r="R33" t="n">
-        <v>6782372</v>
+        <v>6782394</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3908,19 +3904,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129032882</v>
+        <v>129032878</v>
       </c>
       <c r="B34" t="n">
         <v>79041</v>
@@ -3955,10 +3951,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>408992</v>
+        <v>408966</v>
       </c>
       <c r="R34" t="n">
-        <v>6782394</v>
+        <v>6782283</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4132,7 +4128,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129032887</v>
+        <v>129011381</v>
       </c>
       <c r="B36" t="n">
         <v>79041</v>
@@ -4167,10 +4163,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>409176</v>
+        <v>409010</v>
       </c>
       <c r="R36" t="n">
-        <v>6782420</v>
+        <v>6782383</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4200,9 +4196,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4217,19 +4223,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129011381</v>
+        <v>129032887</v>
       </c>
       <c r="B37" t="n">
         <v>79041</v>
@@ -4264,10 +4270,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>409010</v>
+        <v>409176</v>
       </c>
       <c r="R37" t="n">
-        <v>6782383</v>
+        <v>6782420</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4297,19 +4303,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>16:06</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>16:06</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4324,19 +4320,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129032891</v>
+        <v>129011392</v>
       </c>
       <c r="B38" t="n">
         <v>79041</v>
@@ -4371,10 +4367,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>409241</v>
+        <v>409361</v>
       </c>
       <c r="R38" t="n">
-        <v>6782372</v>
+        <v>6782401</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4404,9 +4400,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4421,19 +4427,19 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129011392</v>
+        <v>129011394</v>
       </c>
       <c r="B39" t="n">
         <v>79041</v>
@@ -4468,10 +4474,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>409361</v>
+        <v>409543</v>
       </c>
       <c r="R39" t="n">
-        <v>6782401</v>
+        <v>6782361</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4503,7 +4509,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4513,7 +4519,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4540,7 +4546,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129032911</v>
+        <v>129011399</v>
       </c>
       <c r="B40" t="n">
         <v>79041</v>
@@ -4575,10 +4581,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>409777</v>
+        <v>409609</v>
       </c>
       <c r="R40" t="n">
-        <v>6782445</v>
+        <v>6782404</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4608,9 +4614,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4625,19 +4641,19 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129032906</v>
+        <v>129032891</v>
       </c>
       <c r="B41" t="n">
         <v>79041</v>
@@ -4672,10 +4688,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>409684</v>
+        <v>409241</v>
       </c>
       <c r="R41" t="n">
-        <v>6782322</v>
+        <v>6782372</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4734,7 +4750,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129032910</v>
+        <v>129032911</v>
       </c>
       <c r="B42" t="n">
         <v>79041</v>
@@ -4769,10 +4785,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>409744</v>
+        <v>409777</v>
       </c>
       <c r="R42" t="n">
-        <v>6782394</v>
+        <v>6782445</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4831,7 +4847,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129011394</v>
+        <v>129032906</v>
       </c>
       <c r="B43" t="n">
         <v>79041</v>
@@ -4866,10 +4882,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>409543</v>
+        <v>409684</v>
       </c>
       <c r="R43" t="n">
-        <v>6782361</v>
+        <v>6782322</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4899,19 +4915,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>13:27</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>13:27</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4926,19 +4932,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129011399</v>
+        <v>129032407</v>
       </c>
       <c r="B44" t="n">
         <v>79041</v>
@@ -4973,10 +4979,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>409609</v>
+        <v>409659</v>
       </c>
       <c r="R44" t="n">
-        <v>6782404</v>
+        <v>6782436</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5006,19 +5012,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>13:06</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>13:06</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5033,19 +5029,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129032407</v>
+        <v>129032910</v>
       </c>
       <c r="B45" t="n">
         <v>79041</v>
@@ -5080,10 +5076,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>409659</v>
+        <v>409744</v>
       </c>
       <c r="R45" t="n">
-        <v>6782436</v>
+        <v>6782394</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5130,19 +5126,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129011408</v>
+        <v>129032883</v>
       </c>
       <c r="B46" t="n">
         <v>79041</v>
@@ -5177,10 +5173,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>409801</v>
+        <v>409010</v>
       </c>
       <c r="R46" t="n">
-        <v>6782315</v>
+        <v>6782399</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5210,19 +5206,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>11:08</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>11:08</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5237,19 +5223,19 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129032883</v>
+        <v>129011408</v>
       </c>
       <c r="B47" t="n">
         <v>79041</v>
@@ -5284,10 +5270,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>409010</v>
+        <v>409801</v>
       </c>
       <c r="R47" t="n">
-        <v>6782399</v>
+        <v>6782315</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5317,9 +5303,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5334,22 +5330,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129011380</v>
+        <v>129032869</v>
       </c>
       <c r="B48" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5357,21 +5353,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5381,10 +5377,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>408984</v>
+        <v>409754</v>
       </c>
       <c r="R48" t="n">
-        <v>6782385</v>
+        <v>6782356</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5414,19 +5410,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>16:07</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>16:07</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5441,22 +5427,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129032869</v>
+        <v>129011380</v>
       </c>
       <c r="B49" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5464,21 +5450,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5488,10 +5474,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>409754</v>
+        <v>408984</v>
       </c>
       <c r="R49" t="n">
-        <v>6782356</v>
+        <v>6782385</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5521,9 +5507,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5538,12 +5534,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -5754,7 +5750,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129032899</v>
+        <v>129011409</v>
       </c>
       <c r="B52" t="n">
         <v>79041</v>
@@ -5789,10 +5785,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>409397</v>
+        <v>409202</v>
       </c>
       <c r="R52" t="n">
-        <v>6782272</v>
+        <v>6782367</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5822,29 +5818,40 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -5958,7 +5965,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129011409</v>
+        <v>129011396</v>
       </c>
       <c r="B54" t="n">
         <v>79041</v>
@@ -5993,10 +6000,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>409202</v>
+        <v>409584</v>
       </c>
       <c r="R54" t="n">
-        <v>6782367</v>
+        <v>6782395</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6028,7 +6035,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6038,7 +6045,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6047,7 +6054,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6066,7 +6072,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129011396</v>
+        <v>129032899</v>
       </c>
       <c r="B55" t="n">
         <v>79041</v>
@@ -6101,10 +6107,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>409584</v>
+        <v>409397</v>
       </c>
       <c r="R55" t="n">
-        <v>6782395</v>
+        <v>6782272</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6134,19 +6140,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>13:11</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>13:11</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6161,12 +6157,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6367,10 +6363,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129011372</v>
+        <v>129032403</v>
       </c>
       <c r="B58" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6378,42 +6374,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>409796</v>
+        <v>409021</v>
       </c>
       <c r="R58" t="n">
-        <v>6782327</v>
+        <v>6782365</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6443,19 +6431,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>11:10</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6470,12 +6448,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -6485,7 +6463,7 @@
         <v>129011373</v>
       </c>
       <c r="B59" t="n">
-        <v>91560</v>
+        <v>91561</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6709,10 +6687,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129032403</v>
+        <v>129011372</v>
       </c>
       <c r="B61" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6720,34 +6698,42 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>409021</v>
+        <v>409796</v>
       </c>
       <c r="R61" t="n">
-        <v>6782365</v>
+        <v>6782327</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6777,9 +6763,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6794,12 +6790,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -6809,7 +6805,7 @@
         <v>129032400</v>
       </c>
       <c r="B62" t="n">
-        <v>91992</v>
+        <v>91993</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6903,10 +6899,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129032874</v>
+        <v>129011387</v>
       </c>
       <c r="B63" t="n">
-        <v>91558</v>
+        <v>79041</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6914,21 +6910,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6938,10 +6934,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>409405</v>
+        <v>409232</v>
       </c>
       <c r="R63" t="n">
-        <v>6782366</v>
+        <v>6782353</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6971,9 +6967,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6988,22 +6994,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129032396</v>
+        <v>129032872</v>
       </c>
       <c r="B64" t="n">
-        <v>57727</v>
+        <v>78798</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7011,42 +7017,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>409753</v>
+        <v>409594</v>
       </c>
       <c r="R64" t="n">
-        <v>6782323</v>
+        <v>6782294</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7093,12 +7091,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
@@ -7202,7 +7200,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129011387</v>
+        <v>129011379</v>
       </c>
       <c r="B66" t="n">
         <v>79041</v>
@@ -7237,10 +7235,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>409232</v>
+        <v>408991</v>
       </c>
       <c r="R66" t="n">
-        <v>6782353</v>
+        <v>6782360</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7272,7 +7270,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7282,7 +7280,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7406,7 +7404,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129011379</v>
+        <v>129011384</v>
       </c>
       <c r="B68" t="n">
         <v>79041</v>
@@ -7441,10 +7439,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>408991</v>
+        <v>409068</v>
       </c>
       <c r="R68" t="n">
-        <v>6782360</v>
+        <v>6782377</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7476,7 +7474,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7486,7 +7484,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7610,10 +7608,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129032872</v>
+        <v>129032874</v>
       </c>
       <c r="B70" t="n">
-        <v>78798</v>
+        <v>91560</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7621,23 +7619,19 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6446</v>
+        <v>5432</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -7645,10 +7639,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>409594</v>
+        <v>409405</v>
       </c>
       <c r="R70" t="n">
-        <v>6782294</v>
+        <v>6782366</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7707,10 +7701,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129011384</v>
+        <v>129032396</v>
       </c>
       <c r="B71" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7718,34 +7712,42 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>409068</v>
+        <v>409753</v>
       </c>
       <c r="R71" t="n">
-        <v>6782377</v>
+        <v>6782323</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7775,19 +7777,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>15:43</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>15:43</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7802,12 +7794,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -8303,10 +8295,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129011404</v>
+        <v>129032402</v>
       </c>
       <c r="B77" t="n">
-        <v>79041</v>
+        <v>91560</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8314,23 +8306,19 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
@@ -8338,10 +8326,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>409736</v>
+        <v>409767</v>
       </c>
       <c r="R77" t="n">
-        <v>6782394</v>
+        <v>6782352</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8371,19 +8359,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>11:59</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>11:59</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8398,19 +8376,19 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129032901</v>
+        <v>129032893</v>
       </c>
       <c r="B78" t="n">
         <v>79041</v>
@@ -8445,10 +8423,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>409528</v>
+        <v>409280</v>
       </c>
       <c r="R78" t="n">
-        <v>6782292</v>
+        <v>6782382</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8507,7 +8485,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129032888</v>
+        <v>129011404</v>
       </c>
       <c r="B79" t="n">
         <v>79041</v>
@@ -8542,10 +8520,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>409127</v>
+        <v>409736</v>
       </c>
       <c r="R79" t="n">
-        <v>6782290</v>
+        <v>6782394</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8575,9 +8553,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8592,22 +8580,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129032402</v>
+        <v>129032901</v>
       </c>
       <c r="B80" t="n">
-        <v>91558</v>
+        <v>79041</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8615,21 +8603,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8639,10 +8627,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>409767</v>
+        <v>409528</v>
       </c>
       <c r="R80" t="n">
-        <v>6782352</v>
+        <v>6782292</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8689,19 +8677,19 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129032893</v>
+        <v>129032888</v>
       </c>
       <c r="B81" t="n">
         <v>79041</v>
@@ -8736,10 +8724,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>409280</v>
+        <v>409127</v>
       </c>
       <c r="R81" t="n">
-        <v>6782382</v>
+        <v>6782290</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8798,7 +8786,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129032879</v>
+        <v>129032908</v>
       </c>
       <c r="B82" t="n">
         <v>79041</v>
@@ -8833,10 +8821,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>408909</v>
+        <v>409715</v>
       </c>
       <c r="R82" t="n">
-        <v>6782332</v>
+        <v>6782363</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8895,7 +8883,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129032409</v>
+        <v>129032879</v>
       </c>
       <c r="B83" t="n">
         <v>79041</v>
@@ -8930,10 +8918,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>409782</v>
+        <v>408909</v>
       </c>
       <c r="R83" t="n">
-        <v>6782339</v>
+        <v>6782332</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8980,19 +8968,19 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129032916</v>
+        <v>129032409</v>
       </c>
       <c r="B84" t="n">
         <v>79041</v>
@@ -9027,10 +9015,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>409812</v>
+        <v>409782</v>
       </c>
       <c r="R84" t="n">
-        <v>6782309</v>
+        <v>6782339</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9077,19 +9065,19 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129032908</v>
+        <v>129032916</v>
       </c>
       <c r="B85" t="n">
         <v>79041</v>
@@ -9124,10 +9112,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>409715</v>
+        <v>409812</v>
       </c>
       <c r="R85" t="n">
-        <v>6782363</v>
+        <v>6782309</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9189,7 +9177,7 @@
         <v>129032870</v>
       </c>
       <c r="B86" t="n">
-        <v>91560</v>
+        <v>91561</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9711,7 +9699,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129032903</v>
+        <v>129032895</v>
       </c>
       <c r="B91" t="n">
         <v>79041</v>
@@ -9746,10 +9734,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>409582</v>
+        <v>409310</v>
       </c>
       <c r="R91" t="n">
-        <v>6782297</v>
+        <v>6782326</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9808,7 +9796,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129032880</v>
+        <v>129032903</v>
       </c>
       <c r="B92" t="n">
         <v>79041</v>
@@ -9843,10 +9831,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>408901</v>
+        <v>409582</v>
       </c>
       <c r="R92" t="n">
-        <v>6782390</v>
+        <v>6782297</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9905,7 +9893,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129032895</v>
+        <v>129032880</v>
       </c>
       <c r="B93" t="n">
         <v>79041</v>
@@ -9940,10 +9928,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>409310</v>
+        <v>408901</v>
       </c>
       <c r="R93" t="n">
-        <v>6782326</v>
+        <v>6782390</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10099,7 +10087,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129011388</v>
+        <v>129011390</v>
       </c>
       <c r="B95" t="n">
         <v>79041</v>
@@ -10134,10 +10122,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>409250</v>
+        <v>409349</v>
       </c>
       <c r="R95" t="n">
-        <v>6782354</v>
+        <v>6782376</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10169,7 +10157,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10179,7 +10167,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10206,7 +10194,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129032408</v>
+        <v>129011388</v>
       </c>
       <c r="B96" t="n">
         <v>79041</v>
@@ -10241,10 +10229,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>409749</v>
+        <v>409250</v>
       </c>
       <c r="R96" t="n">
-        <v>6782325</v>
+        <v>6782354</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10274,9 +10262,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10291,19 +10289,19 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129032912</v>
+        <v>129011406</v>
       </c>
       <c r="B97" t="n">
         <v>79041</v>
@@ -10338,10 +10336,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>409762</v>
+        <v>409759</v>
       </c>
       <c r="R97" t="n">
-        <v>6782335</v>
+        <v>6782314</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10371,9 +10369,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10388,19 +10396,19 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129032890</v>
+        <v>129032408</v>
       </c>
       <c r="B98" t="n">
         <v>79041</v>
@@ -10435,10 +10443,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>409228</v>
+        <v>409749</v>
       </c>
       <c r="R98" t="n">
-        <v>6782298</v>
+        <v>6782325</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10485,19 +10493,19 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129011406</v>
+        <v>129032912</v>
       </c>
       <c r="B99" t="n">
         <v>79041</v>
@@ -10532,10 +10540,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>409759</v>
+        <v>409762</v>
       </c>
       <c r="R99" t="n">
-        <v>6782314</v>
+        <v>6782335</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10565,19 +10573,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>11:41</t>
-        </is>
-      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>11:41</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10592,19 +10590,19 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129032875</v>
+        <v>129032890</v>
       </c>
       <c r="B100" t="n">
         <v>79041</v>
@@ -10639,10 +10637,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>409034</v>
+        <v>409228</v>
       </c>
       <c r="R100" t="n">
-        <v>6782261</v>
+        <v>6782298</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10701,7 +10699,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129011390</v>
+        <v>129032875</v>
       </c>
       <c r="B101" t="n">
         <v>79041</v>
@@ -10736,10 +10734,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>409349</v>
+        <v>409034</v>
       </c>
       <c r="R101" t="n">
-        <v>6782376</v>
+        <v>6782261</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10769,19 +10767,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z101" t="inlineStr">
-        <is>
-          <t>14:34</t>
-        </is>
-      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB101" t="inlineStr">
-        <is>
-          <t>14:34</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10796,22 +10784,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129032401</v>
+        <v>129011377</v>
       </c>
       <c r="B102" t="n">
-        <v>91558</v>
+        <v>79041</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10819,21 +10807,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10843,10 +10831,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>409226</v>
+        <v>408995</v>
       </c>
       <c r="R102" t="n">
-        <v>6782376</v>
+        <v>6782299</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10876,9 +10864,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10893,19 +10891,19 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129032915</v>
+        <v>129011385</v>
       </c>
       <c r="B103" t="n">
         <v>79041</v>
@@ -10940,10 +10938,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>409765</v>
+        <v>409214</v>
       </c>
       <c r="R103" t="n">
-        <v>6782330</v>
+        <v>6782345</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10973,9 +10971,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10990,22 +10998,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129011377</v>
+        <v>129032401</v>
       </c>
       <c r="B104" t="n">
-        <v>79041</v>
+        <v>91560</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11013,23 +11021,19 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
@@ -11037,10 +11041,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>408995</v>
+        <v>409226</v>
       </c>
       <c r="R104" t="n">
-        <v>6782299</v>
+        <v>6782376</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11070,19 +11074,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z104" t="inlineStr">
-        <is>
-          <t>16:13</t>
-        </is>
-      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB104" t="inlineStr">
-        <is>
-          <t>16:13</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11097,19 +11091,19 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129011402</v>
+        <v>129032877</v>
       </c>
       <c r="B105" t="n">
         <v>79041</v>
@@ -11144,10 +11138,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>409671</v>
+        <v>408994</v>
       </c>
       <c r="R105" t="n">
-        <v>6782390</v>
+        <v>6782293</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11177,19 +11171,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z105" t="inlineStr">
-        <is>
-          <t>12:57</t>
-        </is>
-      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB105" t="inlineStr">
-        <is>
-          <t>12:57</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11204,19 +11188,19 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129011385</v>
+        <v>129032904</v>
       </c>
       <c r="B106" t="n">
         <v>79041</v>
@@ -11251,10 +11235,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>409214</v>
+        <v>409568</v>
       </c>
       <c r="R106" t="n">
-        <v>6782345</v>
+        <v>6782383</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11284,19 +11268,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z106" t="inlineStr">
-        <is>
-          <t>15:29</t>
-        </is>
-      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB106" t="inlineStr">
-        <is>
-          <t>15:29</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11311,19 +11285,19 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129032877</v>
+        <v>129032915</v>
       </c>
       <c r="B107" t="n">
         <v>79041</v>
@@ -11358,10 +11332,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>408994</v>
+        <v>409765</v>
       </c>
       <c r="R107" t="n">
-        <v>6782293</v>
+        <v>6782330</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11420,7 +11394,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129032904</v>
+        <v>129011402</v>
       </c>
       <c r="B108" t="n">
         <v>79041</v>
@@ -11455,10 +11429,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>409568</v>
+        <v>409671</v>
       </c>
       <c r="R108" t="n">
-        <v>6782383</v>
+        <v>6782390</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11488,9 +11462,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11505,12 +11489,12 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>

--- a/artfynd/A 47938-2025 artfynd.xlsx
+++ b/artfynd/A 47938-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129011405</v>
+        <v>129032920</v>
       </c>
       <c r="B2" t="n">
         <v>79041</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>409747</v>
+        <v>409793</v>
       </c>
       <c r="R2" t="n">
-        <v>6782328</v>
+        <v>6782448</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -743,19 +743,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>11:47</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>11:47</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,19 +760,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129011403</v>
+        <v>129011405</v>
       </c>
       <c r="B3" t="n">
         <v>79041</v>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>409706</v>
+        <v>409747</v>
       </c>
       <c r="R3" t="n">
-        <v>6782359</v>
+        <v>6782328</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +842,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +852,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129032920</v>
+        <v>129032876</v>
       </c>
       <c r="B4" t="n">
         <v>79041</v>
@@ -924,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>409793</v>
+        <v>408997</v>
       </c>
       <c r="R4" t="n">
-        <v>6782448</v>
+        <v>6782283</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,7 +976,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129032876</v>
+        <v>129011403</v>
       </c>
       <c r="B5" t="n">
         <v>79041</v>
@@ -1021,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>408997</v>
+        <v>409706</v>
       </c>
       <c r="R5" t="n">
-        <v>6782283</v>
+        <v>6782359</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1054,9 +1044,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,12 +1071,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1277,7 +1277,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129032919</v>
+        <v>129011389</v>
       </c>
       <c r="B8" t="n">
         <v>79041</v>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>409358</v>
+        <v>409278</v>
       </c>
       <c r="R8" t="n">
-        <v>6782291</v>
+        <v>6782361</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1345,9 +1345,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1362,22 +1372,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129032394</v>
+        <v>129032919</v>
       </c>
       <c r="B9" t="n">
-        <v>79631</v>
+        <v>79041</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1385,21 +1395,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1409,10 +1419,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>409553</v>
+        <v>409358</v>
       </c>
       <c r="R9" t="n">
-        <v>6782378</v>
+        <v>6782291</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1459,22 +1469,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129011389</v>
+        <v>129032394</v>
       </c>
       <c r="B10" t="n">
-        <v>79041</v>
+        <v>79631</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1482,21 +1492,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1506,10 +1516,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>409278</v>
+        <v>409553</v>
       </c>
       <c r="R10" t="n">
-        <v>6782361</v>
+        <v>6782378</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1539,19 +1549,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>15:18</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>15:18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1566,12 +1566,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1986,10 +1986,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129032897</v>
+        <v>129032392</v>
       </c>
       <c r="B15" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1997,21 +1997,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2021,10 +2021,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>409469</v>
+        <v>409554</v>
       </c>
       <c r="R15" t="n">
-        <v>6782371</v>
+        <v>6782380</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2071,19 +2071,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129032909</v>
+        <v>129032897</v>
       </c>
       <c r="B16" t="n">
         <v>79041</v>
@@ -2118,10 +2118,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>409727</v>
+        <v>409469</v>
       </c>
       <c r="R16" t="n">
-        <v>6782352</v>
+        <v>6782371</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2180,10 +2180,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129032392</v>
+        <v>129032909</v>
       </c>
       <c r="B17" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2191,21 +2191,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>409554</v>
+        <v>409727</v>
       </c>
       <c r="R17" t="n">
-        <v>6782380</v>
+        <v>6782352</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2265,22 +2265,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129032885</v>
+        <v>129011376</v>
       </c>
       <c r="B18" t="n">
-        <v>79041</v>
+        <v>91560</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2288,23 +2288,19 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2312,10 +2308,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>409078</v>
+        <v>409774</v>
       </c>
       <c r="R18" t="n">
-        <v>6782312</v>
+        <v>6782323</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2345,9 +2341,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2362,22 +2368,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129032868</v>
+        <v>129032885</v>
       </c>
       <c r="B19" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2385,21 +2391,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2409,10 +2415,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>409688</v>
+        <v>409078</v>
       </c>
       <c r="R19" t="n">
-        <v>6782303</v>
+        <v>6782312</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2471,7 +2477,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129032892</v>
+        <v>129011400</v>
       </c>
       <c r="B20" t="n">
         <v>79041</v>
@@ -2506,10 +2512,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>409244</v>
+        <v>409643</v>
       </c>
       <c r="R20" t="n">
-        <v>6782381</v>
+        <v>6782378</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2539,9 +2545,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2556,19 +2572,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129011400</v>
+        <v>129032892</v>
       </c>
       <c r="B21" t="n">
         <v>79041</v>
@@ -2603,10 +2619,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>409643</v>
+        <v>409244</v>
       </c>
       <c r="R21" t="n">
-        <v>6782378</v>
+        <v>6782381</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2636,19 +2652,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>12:59</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>12:59</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2663,22 +2669,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129011376</v>
+        <v>129032868</v>
       </c>
       <c r="B22" t="n">
-        <v>91560</v>
+        <v>57727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2686,19 +2692,23 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2706,10 +2716,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>409774</v>
+        <v>409688</v>
       </c>
       <c r="R22" t="n">
-        <v>6782323</v>
+        <v>6782303</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2739,19 +2749,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>11:31</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>11:31</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2766,22 +2766,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129011383</v>
+        <v>129032399</v>
       </c>
       <c r="B23" t="n">
-        <v>79041</v>
+        <v>91561</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2789,21 +2789,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2813,10 +2813,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>409028</v>
+        <v>409492</v>
       </c>
       <c r="R23" t="n">
-        <v>6782350</v>
+        <v>6782346</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2846,19 +2846,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>16:04</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>16:04</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2873,22 +2863,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129032395</v>
+        <v>129011374</v>
       </c>
       <c r="B24" t="n">
-        <v>57727</v>
+        <v>91561</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2896,31 +2886,30 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -2928,10 +2917,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>409759</v>
+        <v>409475</v>
       </c>
       <c r="R24" t="n">
-        <v>6782358</v>
+        <v>6782342</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2961,39 +2950,55 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>hackspetthål under tickorna</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129032399</v>
+        <v>129011383</v>
       </c>
       <c r="B25" t="n">
-        <v>91561</v>
+        <v>79041</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3001,21 +3006,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3025,10 +3030,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>409492</v>
+        <v>409028</v>
       </c>
       <c r="R25" t="n">
-        <v>6782346</v>
+        <v>6782350</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3058,9 +3063,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3075,22 +3090,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129011374</v>
+        <v>129011395</v>
       </c>
       <c r="B26" t="n">
-        <v>91561</v>
+        <v>79041</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3098,41 +3113,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>409475</v>
+        <v>409555</v>
       </c>
       <c r="R26" t="n">
-        <v>6782342</v>
+        <v>6782356</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3164,7 +3172,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3174,12 +3182,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:57</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>hackspetthål under tickorna</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3188,7 +3191,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3207,7 +3209,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129011395</v>
+        <v>129011407</v>
       </c>
       <c r="B27" t="n">
         <v>79041</v>
@@ -3242,10 +3244,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>409555</v>
+        <v>409795</v>
       </c>
       <c r="R27" t="n">
-        <v>6782356</v>
+        <v>6782327</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3277,7 +3279,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3287,7 +3289,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3314,10 +3316,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129011407</v>
+        <v>129032395</v>
       </c>
       <c r="B28" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3325,34 +3327,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>409795</v>
+        <v>409759</v>
       </c>
       <c r="R28" t="n">
-        <v>6782327</v>
+        <v>6782358</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3382,19 +3392,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>11:12</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>11:12</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3409,12 +3409,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3518,7 +3518,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129011391</v>
+        <v>129032913</v>
       </c>
       <c r="B30" t="n">
         <v>79041</v>
@@ -3553,10 +3553,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>409349</v>
+        <v>409757</v>
       </c>
       <c r="R30" t="n">
-        <v>6782383</v>
+        <v>6782355</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3586,19 +3586,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>14:34</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>14:34</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3613,19 +3603,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129032913</v>
+        <v>129032406</v>
       </c>
       <c r="B31" t="n">
         <v>79041</v>
@@ -3660,10 +3650,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>409757</v>
+        <v>409253</v>
       </c>
       <c r="R31" t="n">
-        <v>6782355</v>
+        <v>6782372</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3710,19 +3700,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129032406</v>
+        <v>129032882</v>
       </c>
       <c r="B32" t="n">
         <v>79041</v>
@@ -3757,10 +3747,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>409253</v>
+        <v>408992</v>
       </c>
       <c r="R32" t="n">
-        <v>6782372</v>
+        <v>6782394</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3807,19 +3797,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129032882</v>
+        <v>129011391</v>
       </c>
       <c r="B33" t="n">
         <v>79041</v>
@@ -3854,10 +3844,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>408992</v>
+        <v>409349</v>
       </c>
       <c r="R33" t="n">
-        <v>6782394</v>
+        <v>6782383</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3887,9 +3877,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3904,12 +3904,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4128,7 +4128,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129011381</v>
+        <v>129032887</v>
       </c>
       <c r="B36" t="n">
         <v>79041</v>
@@ -4163,10 +4163,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>409010</v>
+        <v>409176</v>
       </c>
       <c r="R36" t="n">
-        <v>6782383</v>
+        <v>6782420</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4196,19 +4196,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>16:06</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>16:06</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4223,19 +4213,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129032887</v>
+        <v>129011381</v>
       </c>
       <c r="B37" t="n">
         <v>79041</v>
@@ -4270,10 +4260,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>409176</v>
+        <v>409010</v>
       </c>
       <c r="R37" t="n">
-        <v>6782420</v>
+        <v>6782383</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4303,9 +4293,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4320,19 +4320,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129011392</v>
+        <v>129032891</v>
       </c>
       <c r="B38" t="n">
         <v>79041</v>
@@ -4367,10 +4367,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>409361</v>
+        <v>409241</v>
       </c>
       <c r="R38" t="n">
-        <v>6782401</v>
+        <v>6782372</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4400,19 +4400,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>14:31</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>14:31</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4427,19 +4417,19 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129011394</v>
+        <v>129011392</v>
       </c>
       <c r="B39" t="n">
         <v>79041</v>
@@ -4474,10 +4464,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>409543</v>
+        <v>409361</v>
       </c>
       <c r="R39" t="n">
-        <v>6782361</v>
+        <v>6782401</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4509,7 +4499,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4519,7 +4509,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4546,7 +4536,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129011399</v>
+        <v>129032911</v>
       </c>
       <c r="B40" t="n">
         <v>79041</v>
@@ -4581,10 +4571,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>409609</v>
+        <v>409777</v>
       </c>
       <c r="R40" t="n">
-        <v>6782404</v>
+        <v>6782445</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4614,19 +4604,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>13:06</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>13:06</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4641,19 +4621,19 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129032891</v>
+        <v>129032906</v>
       </c>
       <c r="B41" t="n">
         <v>79041</v>
@@ -4688,10 +4668,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>409241</v>
+        <v>409684</v>
       </c>
       <c r="R41" t="n">
-        <v>6782372</v>
+        <v>6782322</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4750,7 +4730,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129032911</v>
+        <v>129032407</v>
       </c>
       <c r="B42" t="n">
         <v>79041</v>
@@ -4785,10 +4765,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>409777</v>
+        <v>409659</v>
       </c>
       <c r="R42" t="n">
-        <v>6782445</v>
+        <v>6782436</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4835,19 +4815,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129032906</v>
+        <v>129032910</v>
       </c>
       <c r="B43" t="n">
         <v>79041</v>
@@ -4882,10 +4862,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>409684</v>
+        <v>409744</v>
       </c>
       <c r="R43" t="n">
-        <v>6782322</v>
+        <v>6782394</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4944,7 +4924,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129032407</v>
+        <v>129011394</v>
       </c>
       <c r="B44" t="n">
         <v>79041</v>
@@ -4979,10 +4959,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>409659</v>
+        <v>409543</v>
       </c>
       <c r="R44" t="n">
-        <v>6782436</v>
+        <v>6782361</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5012,9 +4992,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5029,19 +5019,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129032910</v>
+        <v>129011399</v>
       </c>
       <c r="B45" t="n">
         <v>79041</v>
@@ -5076,10 +5066,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>409744</v>
+        <v>409609</v>
       </c>
       <c r="R45" t="n">
-        <v>6782394</v>
+        <v>6782404</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5109,9 +5099,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5126,19 +5126,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129032883</v>
+        <v>129011408</v>
       </c>
       <c r="B46" t="n">
         <v>79041</v>
@@ -5173,10 +5173,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>409010</v>
+        <v>409801</v>
       </c>
       <c r="R46" t="n">
-        <v>6782399</v>
+        <v>6782315</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5206,9 +5206,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5223,19 +5233,19 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129011408</v>
+        <v>129032883</v>
       </c>
       <c r="B47" t="n">
         <v>79041</v>
@@ -5270,10 +5280,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>409801</v>
+        <v>409010</v>
       </c>
       <c r="R47" t="n">
-        <v>6782315</v>
+        <v>6782399</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5303,19 +5313,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>11:08</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>11:08</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5330,22 +5330,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129032869</v>
+        <v>129011380</v>
       </c>
       <c r="B48" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5353,21 +5353,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5377,10 +5377,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>409754</v>
+        <v>408984</v>
       </c>
       <c r="R48" t="n">
-        <v>6782356</v>
+        <v>6782385</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5410,9 +5410,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5427,19 +5437,19 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129011380</v>
+        <v>129032884</v>
       </c>
       <c r="B49" t="n">
         <v>79041</v>
@@ -5474,10 +5484,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>408984</v>
+        <v>409039</v>
       </c>
       <c r="R49" t="n">
-        <v>6782385</v>
+        <v>6782290</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5507,19 +5517,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>16:07</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>16:07</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5534,22 +5534,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129032884</v>
+        <v>129032869</v>
       </c>
       <c r="B50" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5557,21 +5557,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5581,10 +5581,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>409039</v>
+        <v>409754</v>
       </c>
       <c r="R50" t="n">
-        <v>6782290</v>
+        <v>6782356</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5643,10 +5643,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129011401</v>
+        <v>129032866</v>
       </c>
       <c r="B51" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5654,21 +5654,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5678,10 +5678,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>409663</v>
+        <v>409757</v>
       </c>
       <c r="R51" t="n">
-        <v>6782385</v>
+        <v>6782386</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5711,19 +5711,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>12:58</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>12:58</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5738,19 +5728,19 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129011409</v>
+        <v>129011401</v>
       </c>
       <c r="B52" t="n">
         <v>79041</v>
@@ -5785,10 +5775,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>409202</v>
+        <v>409663</v>
       </c>
       <c r="R52" t="n">
-        <v>6782367</v>
+        <v>6782385</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5820,7 +5810,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -5830,7 +5820,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5839,7 +5829,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5858,7 +5847,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129011386</v>
+        <v>129032899</v>
       </c>
       <c r="B53" t="n">
         <v>79041</v>
@@ -5893,10 +5882,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>409210</v>
+        <v>409397</v>
       </c>
       <c r="R53" t="n">
-        <v>6782365</v>
+        <v>6782272</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5926,19 +5915,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>15:26</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>15:26</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5953,19 +5932,19 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129011396</v>
+        <v>129011386</v>
       </c>
       <c r="B54" t="n">
         <v>79041</v>
@@ -6000,10 +5979,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>409584</v>
+        <v>409210</v>
       </c>
       <c r="R54" t="n">
-        <v>6782395</v>
+        <v>6782365</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6035,7 +6014,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6045,7 +6024,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6072,7 +6051,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129032899</v>
+        <v>129011409</v>
       </c>
       <c r="B55" t="n">
         <v>79041</v>
@@ -6107,10 +6086,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>409397</v>
+        <v>409202</v>
       </c>
       <c r="R55" t="n">
-        <v>6782272</v>
+        <v>6782367</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6140,39 +6119,50 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129032866</v>
+        <v>129011396</v>
       </c>
       <c r="B56" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6180,21 +6170,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6204,10 +6194,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>409757</v>
+        <v>409584</v>
       </c>
       <c r="R56" t="n">
-        <v>6782386</v>
+        <v>6782395</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6237,9 +6227,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6254,22 +6254,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129032889</v>
+        <v>129011372</v>
       </c>
       <c r="B57" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6277,34 +6277,42 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>409164</v>
+        <v>409796</v>
       </c>
       <c r="R57" t="n">
-        <v>6782308</v>
+        <v>6782327</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6334,9 +6342,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6351,22 +6369,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129032403</v>
+        <v>129011373</v>
       </c>
       <c r="B58" t="n">
-        <v>79041</v>
+        <v>91561</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6374,34 +6392,41 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>409021</v>
+        <v>409435</v>
       </c>
       <c r="R58" t="n">
-        <v>6782365</v>
+        <v>6782383</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6431,39 +6456,55 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>4 st på samma tall</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129011373</v>
+        <v>129032889</v>
       </c>
       <c r="B59" t="n">
-        <v>91561</v>
+        <v>79041</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6471,41 +6512,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>409435</v>
+        <v>409164</v>
       </c>
       <c r="R59" t="n">
-        <v>6782383</v>
+        <v>6782308</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6535,45 +6569,29 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>4 st på samma tall</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -6687,10 +6705,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129011372</v>
+        <v>129032403</v>
       </c>
       <c r="B61" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6698,42 +6716,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>409796</v>
+        <v>409021</v>
       </c>
       <c r="R61" t="n">
-        <v>6782327</v>
+        <v>6782365</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6763,19 +6773,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>11:10</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6790,12 +6790,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -7103,10 +7103,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129032867</v>
+        <v>129032886</v>
       </c>
       <c r="B65" t="n">
-        <v>57727</v>
+        <v>79041</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7114,21 +7114,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7138,10 +7138,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>409693</v>
+        <v>409108</v>
       </c>
       <c r="R65" t="n">
-        <v>6782357</v>
+        <v>6782395</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7200,7 +7200,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129011379</v>
+        <v>129011384</v>
       </c>
       <c r="B66" t="n">
         <v>79041</v>
@@ -7235,10 +7235,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>408991</v>
+        <v>409068</v>
       </c>
       <c r="R66" t="n">
-        <v>6782360</v>
+        <v>6782377</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7270,7 +7270,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7280,7 +7280,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7307,7 +7307,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129032886</v>
+        <v>129011379</v>
       </c>
       <c r="B67" t="n">
         <v>79041</v>
@@ -7342,10 +7342,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>409108</v>
+        <v>408991</v>
       </c>
       <c r="R67" t="n">
-        <v>6782395</v>
+        <v>6782360</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7375,9 +7375,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7392,19 +7402,19 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129011384</v>
+        <v>129032914</v>
       </c>
       <c r="B68" t="n">
         <v>79041</v>
@@ -7439,10 +7449,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>409068</v>
+        <v>409759</v>
       </c>
       <c r="R68" t="n">
-        <v>6782377</v>
+        <v>6782343</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7472,19 +7482,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>15:43</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>15:43</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7499,22 +7499,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129032914</v>
+        <v>129032867</v>
       </c>
       <c r="B69" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7522,21 +7522,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7546,10 +7546,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>409759</v>
+        <v>409693</v>
       </c>
       <c r="R69" t="n">
-        <v>6782343</v>
+        <v>6782357</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7608,10 +7608,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129032874</v>
+        <v>129032396</v>
       </c>
       <c r="B70" t="n">
-        <v>91560</v>
+        <v>57727</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7619,30 +7619,42 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>409405</v>
+        <v>409753</v>
       </c>
       <c r="R70" t="n">
-        <v>6782366</v>
+        <v>6782323</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7689,22 +7701,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129032396</v>
+        <v>129032874</v>
       </c>
       <c r="B71" t="n">
-        <v>57727</v>
+        <v>91560</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7712,42 +7724,30 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>409753</v>
+        <v>409405</v>
       </c>
       <c r="R71" t="n">
-        <v>6782323</v>
+        <v>6782366</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7794,22 +7794,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129032873</v>
+        <v>129032896</v>
       </c>
       <c r="B72" t="n">
-        <v>91540</v>
+        <v>79041</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7817,37 +7817,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>409075</v>
+        <v>409331</v>
       </c>
       <c r="R72" t="n">
-        <v>6782317</v>
+        <v>6782342</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7888,7 +7885,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -7907,7 +7903,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129032896</v>
+        <v>129032902</v>
       </c>
       <c r="B73" t="n">
         <v>79041</v>
@@ -7942,10 +7938,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>409331</v>
+        <v>409549</v>
       </c>
       <c r="R73" t="n">
-        <v>6782342</v>
+        <v>6782286</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8004,7 +8000,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129032902</v>
+        <v>129032917</v>
       </c>
       <c r="B74" t="n">
         <v>79041</v>
@@ -8039,10 +8035,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>409549</v>
+        <v>409360</v>
       </c>
       <c r="R74" t="n">
-        <v>6782286</v>
+        <v>6782355</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8101,7 +8097,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129032917</v>
+        <v>129032900</v>
       </c>
       <c r="B75" t="n">
         <v>79041</v>
@@ -8136,10 +8132,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>409360</v>
+        <v>409449</v>
       </c>
       <c r="R75" t="n">
-        <v>6782355</v>
+        <v>6782286</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8198,10 +8194,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129032900</v>
+        <v>129032873</v>
       </c>
       <c r="B76" t="n">
-        <v>79041</v>
+        <v>91540</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8209,34 +8205,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>409449</v>
+        <v>409075</v>
       </c>
       <c r="R76" t="n">
-        <v>6782286</v>
+        <v>6782317</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8277,6 +8276,7 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8295,10 +8295,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129032402</v>
+        <v>129032893</v>
       </c>
       <c r="B77" t="n">
-        <v>91560</v>
+        <v>79041</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8306,19 +8306,23 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
@@ -8326,10 +8330,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>409767</v>
+        <v>409280</v>
       </c>
       <c r="R77" t="n">
-        <v>6782352</v>
+        <v>6782382</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8376,19 +8380,19 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129032893</v>
+        <v>129011404</v>
       </c>
       <c r="B78" t="n">
         <v>79041</v>
@@ -8423,10 +8427,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>409280</v>
+        <v>409736</v>
       </c>
       <c r="R78" t="n">
-        <v>6782382</v>
+        <v>6782394</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8456,9 +8460,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8473,19 +8487,19 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129011404</v>
+        <v>129032901</v>
       </c>
       <c r="B79" t="n">
         <v>79041</v>
@@ -8520,10 +8534,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>409736</v>
+        <v>409528</v>
       </c>
       <c r="R79" t="n">
-        <v>6782394</v>
+        <v>6782292</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8553,19 +8567,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>11:59</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>11:59</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8580,19 +8584,19 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129032901</v>
+        <v>129032888</v>
       </c>
       <c r="B80" t="n">
         <v>79041</v>
@@ -8627,10 +8631,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>409528</v>
+        <v>409127</v>
       </c>
       <c r="R80" t="n">
-        <v>6782292</v>
+        <v>6782290</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8689,10 +8693,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129032888</v>
+        <v>129032402</v>
       </c>
       <c r="B81" t="n">
-        <v>79041</v>
+        <v>91560</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8700,23 +8704,19 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
@@ -8724,10 +8724,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>409127</v>
+        <v>409767</v>
       </c>
       <c r="R81" t="n">
-        <v>6782290</v>
+        <v>6782352</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8774,12 +8774,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
@@ -9174,10 +9174,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129032870</v>
+        <v>129011370</v>
       </c>
       <c r="B86" t="n">
-        <v>91561</v>
+        <v>57727</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9185,34 +9185,31 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
@@ -9220,10 +9217,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>409530</v>
+        <v>409759</v>
       </c>
       <c r="R86" t="n">
-        <v>6782289</v>
+        <v>6782330</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9253,30 +9250,39 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
@@ -9477,10 +9483,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129011370</v>
+        <v>129032870</v>
       </c>
       <c r="B89" t="n">
-        <v>57727</v>
+        <v>91561</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9488,31 +9494,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
@@ -9520,10 +9529,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>409759</v>
+        <v>409530</v>
       </c>
       <c r="R89" t="n">
-        <v>6782330</v>
+        <v>6782289</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9553,39 +9562,30 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
       <c r="AD89" t="b">
         <v>0</v>
       </c>
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
@@ -10087,7 +10087,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129011390</v>
+        <v>129011388</v>
       </c>
       <c r="B95" t="n">
         <v>79041</v>
@@ -10122,10 +10122,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>409349</v>
+        <v>409250</v>
       </c>
       <c r="R95" t="n">
-        <v>6782376</v>
+        <v>6782354</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10157,7 +10157,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10167,7 +10167,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10194,7 +10194,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129011388</v>
+        <v>129011406</v>
       </c>
       <c r="B96" t="n">
         <v>79041</v>
@@ -10229,10 +10229,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>409250</v>
+        <v>409759</v>
       </c>
       <c r="R96" t="n">
-        <v>6782354</v>
+        <v>6782314</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10264,7 +10264,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10274,7 +10274,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10301,7 +10301,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129011406</v>
+        <v>129032408</v>
       </c>
       <c r="B97" t="n">
         <v>79041</v>
@@ -10336,10 +10336,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>409759</v>
+        <v>409749</v>
       </c>
       <c r="R97" t="n">
-        <v>6782314</v>
+        <v>6782325</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10369,19 +10369,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z97" t="inlineStr">
-        <is>
-          <t>11:41</t>
-        </is>
-      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>11:41</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10396,19 +10386,19 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129032408</v>
+        <v>129032912</v>
       </c>
       <c r="B98" t="n">
         <v>79041</v>
@@ -10443,10 +10433,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>409749</v>
+        <v>409762</v>
       </c>
       <c r="R98" t="n">
-        <v>6782325</v>
+        <v>6782335</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10493,19 +10483,19 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129032912</v>
+        <v>129032890</v>
       </c>
       <c r="B99" t="n">
         <v>79041</v>
@@ -10540,10 +10530,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>409762</v>
+        <v>409228</v>
       </c>
       <c r="R99" t="n">
-        <v>6782335</v>
+        <v>6782298</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10602,7 +10592,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129032890</v>
+        <v>129032875</v>
       </c>
       <c r="B100" t="n">
         <v>79041</v>
@@ -10637,10 +10627,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>409228</v>
+        <v>409034</v>
       </c>
       <c r="R100" t="n">
-        <v>6782298</v>
+        <v>6782261</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10699,7 +10689,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129032875</v>
+        <v>129011390</v>
       </c>
       <c r="B101" t="n">
         <v>79041</v>
@@ -10734,10 +10724,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>409034</v>
+        <v>409349</v>
       </c>
       <c r="R101" t="n">
-        <v>6782261</v>
+        <v>6782376</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10767,9 +10757,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10784,12 +10784,12 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
@@ -10903,7 +10903,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129011385</v>
+        <v>129011402</v>
       </c>
       <c r="B103" t="n">
         <v>79041</v>
@@ -10938,10 +10938,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>409214</v>
+        <v>409671</v>
       </c>
       <c r="R103" t="n">
-        <v>6782345</v>
+        <v>6782390</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10973,7 +10973,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -10983,7 +10983,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11010,10 +11010,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129032401</v>
+        <v>129011385</v>
       </c>
       <c r="B104" t="n">
-        <v>91560</v>
+        <v>79041</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11021,19 +11021,23 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
@@ -11041,10 +11045,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>409226</v>
+        <v>409214</v>
       </c>
       <c r="R104" t="n">
-        <v>6782376</v>
+        <v>6782345</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11074,9 +11078,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11091,12 +11105,12 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
@@ -11394,10 +11408,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129011402</v>
+        <v>129032401</v>
       </c>
       <c r="B108" t="n">
-        <v>79041</v>
+        <v>91560</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11405,23 +11419,19 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr"/>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
@@ -11429,10 +11439,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>409671</v>
+        <v>409226</v>
       </c>
       <c r="R108" t="n">
-        <v>6782390</v>
+        <v>6782376</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11462,19 +11472,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z108" t="inlineStr">
-        <is>
-          <t>12:57</t>
-        </is>
-      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB108" t="inlineStr">
-        <is>
-          <t>12:57</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11489,12 +11489,12 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>

--- a/artfynd/A 47938-2025 artfynd.xlsx
+++ b/artfynd/A 47938-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129032920</v>
+        <v>129011405</v>
       </c>
       <c r="B2" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>409793</v>
+        <v>409747</v>
       </c>
       <c r="R2" t="n">
-        <v>6782448</v>
+        <v>6782328</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -743,9 +743,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -760,22 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129011405</v>
+        <v>129032876</v>
       </c>
       <c r="B3" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>409747</v>
+        <v>408997</v>
       </c>
       <c r="R3" t="n">
-        <v>6782328</v>
+        <v>6782283</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -840,19 +850,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>11:47</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:47</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,22 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129032876</v>
+        <v>129032905</v>
       </c>
       <c r="B4" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>408997</v>
+        <v>409624</v>
       </c>
       <c r="R4" t="n">
-        <v>6782283</v>
+        <v>6782292</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,10 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129011403</v>
+        <v>129032920</v>
       </c>
       <c r="B5" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>409706</v>
+        <v>409793</v>
       </c>
       <c r="R5" t="n">
-        <v>6782359</v>
+        <v>6782448</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1044,19 +1044,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>12:06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,22 +1061,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129032905</v>
+        <v>129011403</v>
       </c>
       <c r="B6" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1118,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>409624</v>
+        <v>409706</v>
       </c>
       <c r="R6" t="n">
-        <v>6782292</v>
+        <v>6782359</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1151,9 +1141,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1168,12 +1168,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1183,7 +1183,7 @@
         <v>129032907</v>
       </c>
       <c r="B7" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>129011389</v>
       </c>
       <c r="B8" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>129032919</v>
       </c>
       <c r="B9" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>129032394</v>
       </c>
       <c r="B10" t="n">
-        <v>79631</v>
+        <v>79633</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>129011398</v>
       </c>
       <c r="B11" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>129032894</v>
       </c>
       <c r="B12" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>129032398</v>
       </c>
       <c r="B13" t="n">
-        <v>91561</v>
+        <v>91564</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>129011378</v>
       </c>
       <c r="B14" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1986,10 +1986,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129032392</v>
+        <v>129032897</v>
       </c>
       <c r="B15" t="n">
-        <v>79660</v>
+        <v>79043</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1997,21 +1997,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2021,10 +2021,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>409554</v>
+        <v>409469</v>
       </c>
       <c r="R15" t="n">
-        <v>6782380</v>
+        <v>6782371</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2071,22 +2071,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129032897</v>
+        <v>129032909</v>
       </c>
       <c r="B16" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2118,10 +2118,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>409469</v>
+        <v>409727</v>
       </c>
       <c r="R16" t="n">
-        <v>6782371</v>
+        <v>6782352</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2180,10 +2180,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129032909</v>
+        <v>129032392</v>
       </c>
       <c r="B17" t="n">
-        <v>79041</v>
+        <v>79662</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2191,21 +2191,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>409727</v>
+        <v>409554</v>
       </c>
       <c r="R17" t="n">
-        <v>6782352</v>
+        <v>6782380</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2265,12 +2265,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2280,7 +2280,7 @@
         <v>129011376</v>
       </c>
       <c r="B18" t="n">
-        <v>91560</v>
+        <v>91563</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>129032885</v>
       </c>
       <c r="B19" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2477,10 +2477,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129011400</v>
+        <v>129032868</v>
       </c>
       <c r="B20" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2488,21 +2488,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2512,10 +2512,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>409643</v>
+        <v>409688</v>
       </c>
       <c r="R20" t="n">
-        <v>6782378</v>
+        <v>6782303</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2545,19 +2545,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>12:59</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>12:59</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2572,22 +2562,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129032892</v>
+        <v>129011400</v>
       </c>
       <c r="B21" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2619,10 +2609,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>409244</v>
+        <v>409643</v>
       </c>
       <c r="R21" t="n">
-        <v>6782381</v>
+        <v>6782378</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2652,9 +2642,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2669,22 +2669,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129032868</v>
+        <v>129032892</v>
       </c>
       <c r="B22" t="n">
-        <v>57727</v>
+        <v>79043</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2692,21 +2692,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2716,10 +2716,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>409688</v>
+        <v>409244</v>
       </c>
       <c r="R22" t="n">
-        <v>6782303</v>
+        <v>6782381</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2778,10 +2778,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129032399</v>
+        <v>129011383</v>
       </c>
       <c r="B23" t="n">
-        <v>91561</v>
+        <v>79043</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2789,21 +2789,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2813,10 +2813,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>409492</v>
+        <v>409028</v>
       </c>
       <c r="R23" t="n">
-        <v>6782346</v>
+        <v>6782350</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2846,9 +2846,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2863,22 +2873,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129011374</v>
+        <v>129011395</v>
       </c>
       <c r="B24" t="n">
-        <v>91561</v>
+        <v>79043</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2886,41 +2896,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>409475</v>
+        <v>409555</v>
       </c>
       <c r="R24" t="n">
-        <v>6782342</v>
+        <v>6782356</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2952,7 +2955,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -2962,12 +2965,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:57</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>hackspetthål under tickorna</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2976,7 +2974,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -2995,10 +2992,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129011383</v>
+        <v>129011407</v>
       </c>
       <c r="B25" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3030,10 +3027,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>409028</v>
+        <v>409795</v>
       </c>
       <c r="R25" t="n">
-        <v>6782350</v>
+        <v>6782327</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3065,7 +3062,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3075,7 +3072,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3102,10 +3099,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129011395</v>
+        <v>129032399</v>
       </c>
       <c r="B26" t="n">
-        <v>79041</v>
+        <v>91564</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3113,21 +3110,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3137,10 +3134,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>409555</v>
+        <v>409492</v>
       </c>
       <c r="R26" t="n">
-        <v>6782356</v>
+        <v>6782346</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3170,19 +3167,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>13:17</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>13:17</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3197,22 +3184,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129011407</v>
+        <v>129011374</v>
       </c>
       <c r="B27" t="n">
-        <v>79041</v>
+        <v>91564</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3220,34 +3207,41 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>409795</v>
+        <v>409475</v>
       </c>
       <c r="R27" t="n">
-        <v>6782327</v>
+        <v>6782342</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3279,7 +3273,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3289,7 +3283,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>hackspetthål under tickorna</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3298,6 +3297,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3424,7 +3424,7 @@
         <v>129032393</v>
       </c>
       <c r="B29" t="n">
-        <v>79631</v>
+        <v>79633</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3518,10 +3518,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129032913</v>
+        <v>129032406</v>
       </c>
       <c r="B30" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3553,10 +3553,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>409757</v>
+        <v>409253</v>
       </c>
       <c r="R30" t="n">
-        <v>6782355</v>
+        <v>6782372</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3603,22 +3603,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129032406</v>
+        <v>129032882</v>
       </c>
       <c r="B31" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3650,10 +3650,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>409253</v>
+        <v>408992</v>
       </c>
       <c r="R31" t="n">
-        <v>6782372</v>
+        <v>6782394</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3700,22 +3700,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129032882</v>
+        <v>129032878</v>
       </c>
       <c r="B32" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3747,10 +3747,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>408992</v>
+        <v>408966</v>
       </c>
       <c r="R32" t="n">
-        <v>6782394</v>
+        <v>6782283</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3809,10 +3809,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129011391</v>
+        <v>129011369</v>
       </c>
       <c r="B33" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3820,34 +3820,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>409349</v>
+        <v>409683</v>
       </c>
       <c r="R33" t="n">
-        <v>6782383</v>
+        <v>6782391</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3879,7 +3887,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -3889,7 +3897,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3916,10 +3924,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129032878</v>
+        <v>129032913</v>
       </c>
       <c r="B34" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3951,10 +3959,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>408966</v>
+        <v>409757</v>
       </c>
       <c r="R34" t="n">
-        <v>6782283</v>
+        <v>6782355</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4013,10 +4021,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129011369</v>
+        <v>129011391</v>
       </c>
       <c r="B35" t="n">
-        <v>57727</v>
+        <v>79043</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4024,42 +4032,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>409683</v>
+        <v>409349</v>
       </c>
       <c r="R35" t="n">
-        <v>6782391</v>
+        <v>6782383</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4091,7 +4091,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4128,10 +4128,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129032887</v>
+        <v>129011381</v>
       </c>
       <c r="B36" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4163,10 +4163,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>409176</v>
+        <v>409010</v>
       </c>
       <c r="R36" t="n">
-        <v>6782420</v>
+        <v>6782383</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4196,9 +4196,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4213,22 +4223,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129011381</v>
+        <v>129032887</v>
       </c>
       <c r="B37" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4260,10 +4270,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>409010</v>
+        <v>409176</v>
       </c>
       <c r="R37" t="n">
-        <v>6782383</v>
+        <v>6782420</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4293,19 +4303,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>16:06</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>16:06</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4320,22 +4320,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129032891</v>
+        <v>129011392</v>
       </c>
       <c r="B38" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4367,10 +4367,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>409241</v>
+        <v>409361</v>
       </c>
       <c r="R38" t="n">
-        <v>6782372</v>
+        <v>6782401</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4400,9 +4400,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4417,22 +4427,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129011392</v>
+        <v>129032911</v>
       </c>
       <c r="B39" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4464,10 +4474,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>409361</v>
+        <v>409777</v>
       </c>
       <c r="R39" t="n">
-        <v>6782401</v>
+        <v>6782445</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4497,19 +4507,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>14:31</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>14:31</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4524,22 +4524,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129032911</v>
+        <v>129032407</v>
       </c>
       <c r="B40" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4571,10 +4571,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>409777</v>
+        <v>409659</v>
       </c>
       <c r="R40" t="n">
-        <v>6782445</v>
+        <v>6782436</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4621,22 +4621,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129032906</v>
+        <v>129011394</v>
       </c>
       <c r="B41" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4668,10 +4668,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>409684</v>
+        <v>409543</v>
       </c>
       <c r="R41" t="n">
-        <v>6782322</v>
+        <v>6782361</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4701,9 +4701,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4718,22 +4728,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129032407</v>
+        <v>129011399</v>
       </c>
       <c r="B42" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4765,10 +4775,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>409659</v>
+        <v>409609</v>
       </c>
       <c r="R42" t="n">
-        <v>6782436</v>
+        <v>6782404</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4798,9 +4808,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4815,22 +4835,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129032910</v>
+        <v>129032891</v>
       </c>
       <c r="B43" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4862,10 +4882,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>409744</v>
+        <v>409241</v>
       </c>
       <c r="R43" t="n">
-        <v>6782394</v>
+        <v>6782372</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4924,10 +4944,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129011394</v>
+        <v>129032906</v>
       </c>
       <c r="B44" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4959,10 +4979,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>409543</v>
+        <v>409684</v>
       </c>
       <c r="R44" t="n">
-        <v>6782361</v>
+        <v>6782322</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4992,19 +5012,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>13:27</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>13:27</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5019,22 +5029,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129011399</v>
+        <v>129032910</v>
       </c>
       <c r="B45" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5066,10 +5076,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>409609</v>
+        <v>409744</v>
       </c>
       <c r="R45" t="n">
-        <v>6782404</v>
+        <v>6782394</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5099,19 +5109,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>13:06</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>13:06</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5126,12 +5126,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5141,7 +5141,7 @@
         <v>129011408</v>
       </c>
       <c r="B46" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5248,7 +5248,7 @@
         <v>129032883</v>
       </c>
       <c r="B47" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5345,7 +5345,7 @@
         <v>129011380</v>
       </c>
       <c r="B48" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5452,7 +5452,7 @@
         <v>129032884</v>
       </c>
       <c r="B49" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5643,10 +5643,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129032866</v>
+        <v>129032899</v>
       </c>
       <c r="B51" t="n">
-        <v>57727</v>
+        <v>79043</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5654,21 +5654,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5678,10 +5678,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>409757</v>
+        <v>409397</v>
       </c>
       <c r="R51" t="n">
-        <v>6782386</v>
+        <v>6782272</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5740,10 +5740,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129011401</v>
+        <v>129011409</v>
       </c>
       <c r="B52" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5775,10 +5775,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>409663</v>
+        <v>409202</v>
       </c>
       <c r="R52" t="n">
-        <v>6782385</v>
+        <v>6782367</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5810,7 +5810,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5829,6 +5829,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5847,10 +5848,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129032899</v>
+        <v>129011401</v>
       </c>
       <c r="B53" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5882,10 +5883,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>409397</v>
+        <v>409663</v>
       </c>
       <c r="R53" t="n">
-        <v>6782272</v>
+        <v>6782385</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5915,9 +5916,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5932,12 +5943,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -5947,7 +5958,7 @@
         <v>129011386</v>
       </c>
       <c r="B54" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6051,10 +6062,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129011409</v>
+        <v>129011396</v>
       </c>
       <c r="B55" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6086,10 +6097,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>409202</v>
+        <v>409584</v>
       </c>
       <c r="R55" t="n">
-        <v>6782367</v>
+        <v>6782395</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6121,7 +6132,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6131,7 +6142,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6140,7 +6151,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6159,10 +6169,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129011396</v>
+        <v>129032866</v>
       </c>
       <c r="B56" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6170,21 +6180,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6194,10 +6204,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>409584</v>
+        <v>409757</v>
       </c>
       <c r="R56" t="n">
-        <v>6782395</v>
+        <v>6782386</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6227,19 +6237,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>13:11</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>13:11</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6254,22 +6254,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129011372</v>
+        <v>129032403</v>
       </c>
       <c r="B57" t="n">
-        <v>57727</v>
+        <v>79043</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6277,42 +6277,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>409796</v>
+        <v>409021</v>
       </c>
       <c r="R57" t="n">
-        <v>6782327</v>
+        <v>6782365</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6342,19 +6334,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>11:10</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6369,22 +6351,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129011373</v>
+        <v>129011372</v>
       </c>
       <c r="B58" t="n">
-        <v>91561</v>
+        <v>57727</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6392,30 +6374,31 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6423,10 +6406,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>409435</v>
+        <v>409796</v>
       </c>
       <c r="R58" t="n">
-        <v>6782383</v>
+        <v>6782327</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6458,7 +6441,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6468,12 +6451,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:14</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>4 st på samma tall</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6482,7 +6460,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6501,10 +6478,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129032889</v>
+        <v>129011373</v>
       </c>
       <c r="B59" t="n">
-        <v>79041</v>
+        <v>91564</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6512,34 +6489,41 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>409164</v>
+        <v>409435</v>
       </c>
       <c r="R59" t="n">
-        <v>6782308</v>
+        <v>6782383</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6569,39 +6553,55 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>4 st på samma tall</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129011375</v>
+        <v>129032889</v>
       </c>
       <c r="B60" t="n">
-        <v>78798</v>
+        <v>79043</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6609,21 +6609,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6633,10 +6633,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>409335</v>
+        <v>409164</v>
       </c>
       <c r="R60" t="n">
-        <v>6782352</v>
+        <v>6782308</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6666,19 +6666,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>14:40</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>14:40</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6693,22 +6683,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129032403</v>
+        <v>129011375</v>
       </c>
       <c r="B61" t="n">
-        <v>79041</v>
+        <v>78800</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6716,21 +6706,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6740,10 +6730,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>409021</v>
+        <v>409335</v>
       </c>
       <c r="R61" t="n">
-        <v>6782365</v>
+        <v>6782352</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6773,9 +6763,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6790,44 +6790,44 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129032400</v>
+        <v>129011387</v>
       </c>
       <c r="B62" t="n">
-        <v>91993</v>
+        <v>79043</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>409738</v>
+        <v>409232</v>
       </c>
       <c r="R62" t="n">
-        <v>6782382</v>
+        <v>6782353</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6870,9 +6870,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6887,22 +6897,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129011387</v>
+        <v>129011384</v>
       </c>
       <c r="B63" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6934,10 +6944,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>409232</v>
+        <v>409068</v>
       </c>
       <c r="R63" t="n">
-        <v>6782353</v>
+        <v>6782377</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6969,7 +6979,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -6979,7 +6989,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7006,10 +7016,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129032872</v>
+        <v>129011379</v>
       </c>
       <c r="B64" t="n">
-        <v>78798</v>
+        <v>79043</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7017,21 +7027,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7041,10 +7051,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>409594</v>
+        <v>408991</v>
       </c>
       <c r="R64" t="n">
-        <v>6782294</v>
+        <v>6782360</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7074,9 +7084,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7091,44 +7111,44 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129032886</v>
+        <v>129032400</v>
       </c>
       <c r="B65" t="n">
-        <v>79041</v>
+        <v>91996</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7138,10 +7158,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>409108</v>
+        <v>409738</v>
       </c>
       <c r="R65" t="n">
-        <v>6782395</v>
+        <v>6782382</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7188,22 +7208,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129011384</v>
+        <v>129032874</v>
       </c>
       <c r="B66" t="n">
-        <v>79041</v>
+        <v>91563</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7211,23 +7231,19 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7235,10 +7251,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>409068</v>
+        <v>409405</v>
       </c>
       <c r="R66" t="n">
-        <v>6782377</v>
+        <v>6782366</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7268,19 +7284,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>15:43</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>15:43</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7295,22 +7301,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129011379</v>
+        <v>129032872</v>
       </c>
       <c r="B67" t="n">
-        <v>79041</v>
+        <v>78800</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7318,21 +7324,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7342,10 +7348,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>408991</v>
+        <v>409594</v>
       </c>
       <c r="R67" t="n">
-        <v>6782360</v>
+        <v>6782294</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7375,19 +7381,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>16:09</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>16:09</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7402,22 +7398,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129032914</v>
+        <v>129032886</v>
       </c>
       <c r="B68" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7449,10 +7445,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>409759</v>
+        <v>409108</v>
       </c>
       <c r="R68" t="n">
-        <v>6782343</v>
+        <v>6782395</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7511,10 +7507,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129032867</v>
+        <v>129032914</v>
       </c>
       <c r="B69" t="n">
-        <v>57727</v>
+        <v>79043</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7522,21 +7518,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7546,10 +7542,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>409693</v>
+        <v>409759</v>
       </c>
       <c r="R69" t="n">
-        <v>6782357</v>
+        <v>6782343</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7713,10 +7709,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129032874</v>
+        <v>129032867</v>
       </c>
       <c r="B71" t="n">
-        <v>91560</v>
+        <v>57727</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7724,19 +7720,23 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -7744,10 +7744,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>409405</v>
+        <v>409693</v>
       </c>
       <c r="R71" t="n">
-        <v>6782366</v>
+        <v>6782357</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7806,10 +7806,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129032896</v>
+        <v>129032900</v>
       </c>
       <c r="B72" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7841,10 +7841,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>409331</v>
+        <v>409449</v>
       </c>
       <c r="R72" t="n">
-        <v>6782342</v>
+        <v>6782286</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7903,10 +7903,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129032902</v>
+        <v>129032873</v>
       </c>
       <c r="B73" t="n">
-        <v>79041</v>
+        <v>91543</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7914,34 +7914,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>409549</v>
+        <v>409075</v>
       </c>
       <c r="R73" t="n">
-        <v>6782286</v>
+        <v>6782317</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7982,6 +7985,7 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -8000,10 +8004,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129032917</v>
+        <v>129032896</v>
       </c>
       <c r="B74" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8035,10 +8039,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>409360</v>
+        <v>409331</v>
       </c>
       <c r="R74" t="n">
-        <v>6782355</v>
+        <v>6782342</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8097,10 +8101,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129032900</v>
+        <v>129032902</v>
       </c>
       <c r="B75" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8132,7 +8136,7 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>409449</v>
+        <v>409549</v>
       </c>
       <c r="R75" t="n">
         <v>6782286</v>
@@ -8194,10 +8198,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129032873</v>
+        <v>129032917</v>
       </c>
       <c r="B76" t="n">
-        <v>91540</v>
+        <v>79043</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8205,37 +8209,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>409075</v>
+        <v>409360</v>
       </c>
       <c r="R76" t="n">
-        <v>6782317</v>
+        <v>6782355</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8276,7 +8277,6 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8295,10 +8295,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129032893</v>
+        <v>129011404</v>
       </c>
       <c r="B77" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8330,10 +8330,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>409280</v>
+        <v>409736</v>
       </c>
       <c r="R77" t="n">
-        <v>6782382</v>
+        <v>6782394</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8363,9 +8363,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8380,22 +8390,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129011404</v>
+        <v>129032893</v>
       </c>
       <c r="B78" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8427,10 +8437,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>409736</v>
+        <v>409280</v>
       </c>
       <c r="R78" t="n">
-        <v>6782394</v>
+        <v>6782382</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8460,19 +8470,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>11:59</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>11:59</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8487,22 +8487,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129032901</v>
+        <v>129032402</v>
       </c>
       <c r="B79" t="n">
-        <v>79041</v>
+        <v>91563</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8510,23 +8510,19 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
@@ -8534,10 +8530,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>409528</v>
+        <v>409767</v>
       </c>
       <c r="R79" t="n">
-        <v>6782292</v>
+        <v>6782352</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8584,22 +8580,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129032888</v>
+        <v>129032901</v>
       </c>
       <c r="B80" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8631,10 +8627,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>409127</v>
+        <v>409528</v>
       </c>
       <c r="R80" t="n">
-        <v>6782290</v>
+        <v>6782292</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8693,10 +8689,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129032402</v>
+        <v>129032888</v>
       </c>
       <c r="B81" t="n">
-        <v>91560</v>
+        <v>79043</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8704,19 +8700,23 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
@@ -8724,10 +8724,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>409767</v>
+        <v>409127</v>
       </c>
       <c r="R81" t="n">
-        <v>6782352</v>
+        <v>6782290</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8774,22 +8774,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129032908</v>
+        <v>129032916</v>
       </c>
       <c r="B82" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8821,10 +8821,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>409715</v>
+        <v>409812</v>
       </c>
       <c r="R82" t="n">
-        <v>6782363</v>
+        <v>6782309</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8886,7 +8886,7 @@
         <v>129032879</v>
       </c>
       <c r="B83" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8983,7 +8983,7 @@
         <v>129032409</v>
       </c>
       <c r="B84" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9077,10 +9077,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129032916</v>
+        <v>129032908</v>
       </c>
       <c r="B85" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9112,10 +9112,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>409812</v>
+        <v>409715</v>
       </c>
       <c r="R85" t="n">
-        <v>6782309</v>
+        <v>6782363</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9174,10 +9174,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129011370</v>
+        <v>129032870</v>
       </c>
       <c r="B86" t="n">
-        <v>57727</v>
+        <v>91564</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9185,31 +9185,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
@@ -9217,10 +9220,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>409759</v>
+        <v>409530</v>
       </c>
       <c r="R86" t="n">
-        <v>6782330</v>
+        <v>6782289</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9250,39 +9253,30 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
@@ -9292,7 +9286,7 @@
         <v>129032898</v>
       </c>
       <c r="B87" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9389,7 +9383,7 @@
         <v>129032918</v>
       </c>
       <c r="B88" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9483,10 +9477,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129032870</v>
+        <v>129011370</v>
       </c>
       <c r="B89" t="n">
-        <v>91561</v>
+        <v>57727</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9494,34 +9488,31 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
@@ -9529,10 +9520,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>409530</v>
+        <v>409759</v>
       </c>
       <c r="R89" t="n">
-        <v>6782289</v>
+        <v>6782330</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9562,30 +9553,39 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AD89" t="b">
         <v>0</v>
       </c>
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
@@ -9595,7 +9595,7 @@
         <v>129011393</v>
       </c>
       <c r="B90" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9699,10 +9699,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129032895</v>
+        <v>129032405</v>
       </c>
       <c r="B91" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9734,10 +9734,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>409310</v>
+        <v>409048</v>
       </c>
       <c r="R91" t="n">
-        <v>6782326</v>
+        <v>6782365</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9784,22 +9784,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129032903</v>
+        <v>129032895</v>
       </c>
       <c r="B92" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9831,10 +9831,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>409582</v>
+        <v>409310</v>
       </c>
       <c r="R92" t="n">
-        <v>6782297</v>
+        <v>6782326</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9893,10 +9893,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129032880</v>
+        <v>129032903</v>
       </c>
       <c r="B93" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9928,10 +9928,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>408901</v>
+        <v>409582</v>
       </c>
       <c r="R93" t="n">
-        <v>6782390</v>
+        <v>6782297</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9990,10 +9990,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129032405</v>
+        <v>129032880</v>
       </c>
       <c r="B94" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10025,10 +10025,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>409048</v>
+        <v>408901</v>
       </c>
       <c r="R94" t="n">
-        <v>6782365</v>
+        <v>6782390</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10075,22 +10075,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129011388</v>
+        <v>129011406</v>
       </c>
       <c r="B95" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10122,10 +10122,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>409250</v>
+        <v>409759</v>
       </c>
       <c r="R95" t="n">
-        <v>6782354</v>
+        <v>6782314</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10157,7 +10157,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10167,7 +10167,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10194,10 +10194,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129011406</v>
+        <v>129011388</v>
       </c>
       <c r="B96" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10229,10 +10229,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>409759</v>
+        <v>409250</v>
       </c>
       <c r="R96" t="n">
-        <v>6782314</v>
+        <v>6782354</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10264,7 +10264,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10274,7 +10274,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10304,7 +10304,7 @@
         <v>129032408</v>
       </c>
       <c r="B97" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10398,10 +10398,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129032912</v>
+        <v>129032875</v>
       </c>
       <c r="B98" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10433,10 +10433,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>409762</v>
+        <v>409034</v>
       </c>
       <c r="R98" t="n">
-        <v>6782335</v>
+        <v>6782261</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10495,10 +10495,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129032890</v>
+        <v>129011390</v>
       </c>
       <c r="B99" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10530,10 +10530,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>409228</v>
+        <v>409349</v>
       </c>
       <c r="R99" t="n">
-        <v>6782298</v>
+        <v>6782376</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10563,9 +10563,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10580,22 +10590,22 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129032875</v>
+        <v>129032912</v>
       </c>
       <c r="B100" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10627,10 +10637,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>409034</v>
+        <v>409762</v>
       </c>
       <c r="R100" t="n">
-        <v>6782261</v>
+        <v>6782335</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10689,10 +10699,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129011390</v>
+        <v>129032890</v>
       </c>
       <c r="B101" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10724,10 +10734,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>409349</v>
+        <v>409228</v>
       </c>
       <c r="R101" t="n">
-        <v>6782376</v>
+        <v>6782298</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10757,19 +10767,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z101" t="inlineStr">
-        <is>
-          <t>14:34</t>
-        </is>
-      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB101" t="inlineStr">
-        <is>
-          <t>14:34</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10784,22 +10784,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129011377</v>
+        <v>129032401</v>
       </c>
       <c r="B102" t="n">
-        <v>79041</v>
+        <v>91563</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10807,23 +10807,19 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
@@ -10831,10 +10827,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>408995</v>
+        <v>409226</v>
       </c>
       <c r="R102" t="n">
-        <v>6782299</v>
+        <v>6782376</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10864,19 +10860,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z102" t="inlineStr">
-        <is>
-          <t>16:13</t>
-        </is>
-      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB102" t="inlineStr">
-        <is>
-          <t>16:13</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10891,22 +10877,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129011402</v>
+        <v>129032904</v>
       </c>
       <c r="B103" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10938,10 +10924,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>409671</v>
+        <v>409568</v>
       </c>
       <c r="R103" t="n">
-        <v>6782390</v>
+        <v>6782383</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10971,19 +10957,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z103" t="inlineStr">
-        <is>
-          <t>12:57</t>
-        </is>
-      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB103" t="inlineStr">
-        <is>
-          <t>12:57</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10998,22 +10974,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129011385</v>
+        <v>129011377</v>
       </c>
       <c r="B104" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11045,10 +11021,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>409214</v>
+        <v>408995</v>
       </c>
       <c r="R104" t="n">
-        <v>6782345</v>
+        <v>6782299</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11080,7 +11056,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11090,7 +11066,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11117,10 +11093,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129032877</v>
+        <v>129011402</v>
       </c>
       <c r="B105" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11152,10 +11128,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>408994</v>
+        <v>409671</v>
       </c>
       <c r="R105" t="n">
-        <v>6782293</v>
+        <v>6782390</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11185,9 +11161,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11202,22 +11188,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129032904</v>
+        <v>129011385</v>
       </c>
       <c r="B106" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11249,10 +11235,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>409568</v>
+        <v>409214</v>
       </c>
       <c r="R106" t="n">
-        <v>6782383</v>
+        <v>6782345</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11282,9 +11268,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11299,22 +11295,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129032915</v>
+        <v>129032877</v>
       </c>
       <c r="B107" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11346,10 +11342,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>409765</v>
+        <v>408994</v>
       </c>
       <c r="R107" t="n">
-        <v>6782330</v>
+        <v>6782293</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11408,10 +11404,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129032401</v>
+        <v>129032915</v>
       </c>
       <c r="B108" t="n">
-        <v>91560</v>
+        <v>79043</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11419,19 +11415,23 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
@@ -11439,10 +11439,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>409226</v>
+        <v>409765</v>
       </c>
       <c r="R108" t="n">
-        <v>6782376</v>
+        <v>6782330</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11489,12 +11489,12 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>

--- a/artfynd/A 47938-2025 artfynd.xlsx
+++ b/artfynd/A 47938-2025 artfynd.xlsx
@@ -1578,10 +1578,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129011398</v>
+        <v>129032398</v>
       </c>
       <c r="B11" t="n">
-        <v>79043</v>
+        <v>91564</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1589,21 +1589,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1613,10 +1613,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>409596</v>
+        <v>409482</v>
       </c>
       <c r="R11" t="n">
-        <v>6782395</v>
+        <v>6782335</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1646,19 +1646,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>13:08</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>13:08</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1673,19 +1663,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129032894</v>
+        <v>129011398</v>
       </c>
       <c r="B12" t="n">
         <v>79043</v>
@@ -1720,10 +1710,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>409292</v>
+        <v>409596</v>
       </c>
       <c r="R12" t="n">
-        <v>6782306</v>
+        <v>6782395</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1753,9 +1743,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1770,22 +1770,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129032398</v>
+        <v>129032894</v>
       </c>
       <c r="B13" t="n">
-        <v>91564</v>
+        <v>79043</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1793,21 +1793,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1817,10 +1817,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>409482</v>
+        <v>409292</v>
       </c>
       <c r="R13" t="n">
-        <v>6782335</v>
+        <v>6782306</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1867,19 +1867,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129011378</v>
+        <v>129032897</v>
       </c>
       <c r="B14" t="n">
         <v>79043</v>
@@ -1914,10 +1914,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>408984</v>
+        <v>409469</v>
       </c>
       <c r="R14" t="n">
-        <v>6782347</v>
+        <v>6782371</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1947,19 +1947,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>16:10</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>16:10</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1974,19 +1964,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129032897</v>
+        <v>129032909</v>
       </c>
       <c r="B15" t="n">
         <v>79043</v>
@@ -2021,10 +2011,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>409469</v>
+        <v>409727</v>
       </c>
       <c r="R15" t="n">
-        <v>6782371</v>
+        <v>6782352</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2083,7 +2073,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129032909</v>
+        <v>129011378</v>
       </c>
       <c r="B16" t="n">
         <v>79043</v>
@@ -2118,10 +2108,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>409727</v>
+        <v>408984</v>
       </c>
       <c r="R16" t="n">
-        <v>6782352</v>
+        <v>6782347</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2151,9 +2141,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2168,12 +2168,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -4847,7 +4847,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129032891</v>
+        <v>129032910</v>
       </c>
       <c r="B43" t="n">
         <v>79043</v>
@@ -4882,10 +4882,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>409241</v>
+        <v>409744</v>
       </c>
       <c r="R43" t="n">
-        <v>6782372</v>
+        <v>6782394</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4944,7 +4944,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129032906</v>
+        <v>129032891</v>
       </c>
       <c r="B44" t="n">
         <v>79043</v>
@@ -4979,10 +4979,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>409684</v>
+        <v>409241</v>
       </c>
       <c r="R44" t="n">
-        <v>6782322</v>
+        <v>6782372</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5041,7 +5041,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129032910</v>
+        <v>129032906</v>
       </c>
       <c r="B45" t="n">
         <v>79043</v>
@@ -5076,10 +5076,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>409744</v>
+        <v>409684</v>
       </c>
       <c r="R45" t="n">
-        <v>6782394</v>
+        <v>6782322</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5643,7 +5643,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129032899</v>
+        <v>129011401</v>
       </c>
       <c r="B51" t="n">
         <v>79043</v>
@@ -5678,10 +5678,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>409397</v>
+        <v>409663</v>
       </c>
       <c r="R51" t="n">
-        <v>6782272</v>
+        <v>6782385</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5711,9 +5711,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5728,19 +5738,19 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129011409</v>
+        <v>129011386</v>
       </c>
       <c r="B52" t="n">
         <v>79043</v>
@@ -5775,10 +5785,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>409202</v>
+        <v>409210</v>
       </c>
       <c r="R52" t="n">
-        <v>6782367</v>
+        <v>6782365</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5829,7 +5839,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5848,7 +5857,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129011401</v>
+        <v>129011396</v>
       </c>
       <c r="B53" t="n">
         <v>79043</v>
@@ -5883,10 +5892,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>409663</v>
+        <v>409584</v>
       </c>
       <c r="R53" t="n">
-        <v>6782385</v>
+        <v>6782395</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5918,7 +5927,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -5928,7 +5937,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5955,7 +5964,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129011386</v>
+        <v>129032899</v>
       </c>
       <c r="B54" t="n">
         <v>79043</v>
@@ -5990,10 +5999,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>409210</v>
+        <v>409397</v>
       </c>
       <c r="R54" t="n">
-        <v>6782365</v>
+        <v>6782272</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6023,19 +6032,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>15:26</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>15:26</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6050,19 +6049,19 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129011396</v>
+        <v>129011409</v>
       </c>
       <c r="B55" t="n">
         <v>79043</v>
@@ -6097,10 +6096,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>409584</v>
+        <v>409202</v>
       </c>
       <c r="R55" t="n">
-        <v>6782395</v>
+        <v>6782367</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6132,7 +6131,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6142,7 +6141,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6151,6 +6150,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -7123,34 +7123,30 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129032400</v>
+        <v>129032874</v>
       </c>
       <c r="B65" t="n">
-        <v>91996</v>
+        <v>91563</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1209</v>
+        <v>5432</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7158,10 +7154,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>409738</v>
+        <v>409405</v>
       </c>
       <c r="R65" t="n">
-        <v>6782382</v>
+        <v>6782366</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7208,42 +7204,46 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129032874</v>
+        <v>129032400</v>
       </c>
       <c r="B66" t="n">
-        <v>91563</v>
+        <v>91996</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr"/>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7251,10 +7251,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>409405</v>
+        <v>409738</v>
       </c>
       <c r="R66" t="n">
-        <v>6782366</v>
+        <v>6782382</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7301,12 +7301,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -8295,10 +8295,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129011404</v>
+        <v>129032402</v>
       </c>
       <c r="B77" t="n">
-        <v>79043</v>
+        <v>91563</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8306,23 +8306,19 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
@@ -8330,10 +8326,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>409736</v>
+        <v>409767</v>
       </c>
       <c r="R77" t="n">
-        <v>6782394</v>
+        <v>6782352</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8363,19 +8359,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>11:59</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>11:59</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8390,19 +8376,19 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129032893</v>
+        <v>129032901</v>
       </c>
       <c r="B78" t="n">
         <v>79043</v>
@@ -8437,10 +8423,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>409280</v>
+        <v>409528</v>
       </c>
       <c r="R78" t="n">
-        <v>6782382</v>
+        <v>6782292</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8499,10 +8485,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129032402</v>
+        <v>129032888</v>
       </c>
       <c r="B79" t="n">
-        <v>91563</v>
+        <v>79043</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8510,19 +8496,23 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
@@ -8530,10 +8520,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>409767</v>
+        <v>409127</v>
       </c>
       <c r="R79" t="n">
-        <v>6782352</v>
+        <v>6782290</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8580,19 +8570,19 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129032901</v>
+        <v>129011404</v>
       </c>
       <c r="B80" t="n">
         <v>79043</v>
@@ -8627,10 +8617,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>409528</v>
+        <v>409736</v>
       </c>
       <c r="R80" t="n">
-        <v>6782292</v>
+        <v>6782394</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8660,9 +8650,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8677,19 +8677,19 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129032888</v>
+        <v>129032893</v>
       </c>
       <c r="B81" t="n">
         <v>79043</v>
@@ -8724,10 +8724,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>409127</v>
+        <v>409280</v>
       </c>
       <c r="R81" t="n">
-        <v>6782290</v>
+        <v>6782382</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8786,7 +8786,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129032916</v>
+        <v>129032879</v>
       </c>
       <c r="B82" t="n">
         <v>79043</v>
@@ -8821,10 +8821,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>409812</v>
+        <v>408909</v>
       </c>
       <c r="R82" t="n">
-        <v>6782309</v>
+        <v>6782332</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8883,7 +8883,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129032879</v>
+        <v>129032409</v>
       </c>
       <c r="B83" t="n">
         <v>79043</v>
@@ -8918,10 +8918,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>408909</v>
+        <v>409782</v>
       </c>
       <c r="R83" t="n">
-        <v>6782332</v>
+        <v>6782339</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8968,19 +8968,19 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129032409</v>
+        <v>129032908</v>
       </c>
       <c r="B84" t="n">
         <v>79043</v>
@@ -9015,10 +9015,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>409782</v>
+        <v>409715</v>
       </c>
       <c r="R84" t="n">
-        <v>6782339</v>
+        <v>6782363</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9065,19 +9065,19 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129032908</v>
+        <v>129032916</v>
       </c>
       <c r="B85" t="n">
         <v>79043</v>
@@ -9112,10 +9112,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>409715</v>
+        <v>409812</v>
       </c>
       <c r="R85" t="n">
-        <v>6782363</v>
+        <v>6782309</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>

--- a/artfynd/A 47938-2025 artfynd.xlsx
+++ b/artfynd/A 47938-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129011405</v>
+        <v>129032920</v>
       </c>
       <c r="B2" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>409747</v>
+        <v>409793</v>
       </c>
       <c r="R2" t="n">
-        <v>6782328</v>
+        <v>6782448</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -743,19 +743,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>11:47</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>11:47</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129032876</v>
+        <v>129011405</v>
       </c>
       <c r="B3" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>408997</v>
+        <v>409747</v>
       </c>
       <c r="R3" t="n">
-        <v>6782283</v>
+        <v>6782328</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -850,9 +840,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,22 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129032905</v>
+        <v>129032876</v>
       </c>
       <c r="B4" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>409624</v>
+        <v>408997</v>
       </c>
       <c r="R4" t="n">
-        <v>6782292</v>
+        <v>6782283</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,10 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129032920</v>
+        <v>129011403</v>
       </c>
       <c r="B5" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>409793</v>
+        <v>409706</v>
       </c>
       <c r="R5" t="n">
-        <v>6782448</v>
+        <v>6782359</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1044,9 +1044,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1061,22 +1071,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129011403</v>
+        <v>129032905</v>
       </c>
       <c r="B6" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1108,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>409706</v>
+        <v>409624</v>
       </c>
       <c r="R6" t="n">
-        <v>6782359</v>
+        <v>6782292</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1141,19 +1151,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>12:06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1168,12 +1168,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1183,7 +1183,7 @@
         <v>129032907</v>
       </c>
       <c r="B7" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>129011389</v>
       </c>
       <c r="B8" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,7 +1387,7 @@
         <v>129032919</v>
       </c>
       <c r="B9" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>129032394</v>
       </c>
       <c r="B10" t="n">
-        <v>79633</v>
+        <v>79634</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1578,10 +1578,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129032398</v>
+        <v>129011398</v>
       </c>
       <c r="B11" t="n">
-        <v>91564</v>
+        <v>79044</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1589,21 +1589,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1613,10 +1613,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>409482</v>
+        <v>409596</v>
       </c>
       <c r="R11" t="n">
-        <v>6782335</v>
+        <v>6782395</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1646,9 +1646,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1663,22 +1673,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129011398</v>
+        <v>129032894</v>
       </c>
       <c r="B12" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1710,10 +1720,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>409596</v>
+        <v>409292</v>
       </c>
       <c r="R12" t="n">
-        <v>6782395</v>
+        <v>6782306</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1743,19 +1753,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>13:08</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>13:08</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1770,22 +1770,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129032894</v>
+        <v>129032398</v>
       </c>
       <c r="B13" t="n">
-        <v>79043</v>
+        <v>91566</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1793,21 +1793,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1817,10 +1817,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>409292</v>
+        <v>409482</v>
       </c>
       <c r="R13" t="n">
-        <v>6782306</v>
+        <v>6782335</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1867,12 +1867,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -1882,7 +1882,7 @@
         <v>129032897</v>
       </c>
       <c r="B14" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>129032909</v>
       </c>
       <c r="B15" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2073,10 +2073,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129011378</v>
+        <v>129032392</v>
       </c>
       <c r="B16" t="n">
-        <v>79043</v>
+        <v>79663</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2084,21 +2084,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2108,10 +2108,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>408984</v>
+        <v>409554</v>
       </c>
       <c r="R16" t="n">
-        <v>6782347</v>
+        <v>6782380</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2141,19 +2141,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>16:10</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>16:10</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2168,22 +2158,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129032392</v>
+        <v>129011378</v>
       </c>
       <c r="B17" t="n">
-        <v>79662</v>
+        <v>79044</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2191,21 +2181,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2215,10 +2205,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>409554</v>
+        <v>408984</v>
       </c>
       <c r="R17" t="n">
-        <v>6782380</v>
+        <v>6782347</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2248,9 +2238,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2265,22 +2265,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129011376</v>
+        <v>129032892</v>
       </c>
       <c r="B18" t="n">
-        <v>91563</v>
+        <v>79044</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2288,19 +2288,23 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2308,10 +2312,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>409774</v>
+        <v>409244</v>
       </c>
       <c r="R18" t="n">
-        <v>6782323</v>
+        <v>6782381</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2341,19 +2345,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>11:31</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>11:31</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2368,22 +2362,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129032885</v>
+        <v>129032868</v>
       </c>
       <c r="B19" t="n">
-        <v>79043</v>
+        <v>57727</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2391,21 +2385,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2415,10 +2409,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>409078</v>
+        <v>409688</v>
       </c>
       <c r="R19" t="n">
-        <v>6782312</v>
+        <v>6782303</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2477,10 +2471,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129032868</v>
+        <v>129011376</v>
       </c>
       <c r="B20" t="n">
-        <v>57727</v>
+        <v>91565</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2488,23 +2482,19 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2512,10 +2502,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>409688</v>
+        <v>409774</v>
       </c>
       <c r="R20" t="n">
-        <v>6782303</v>
+        <v>6782323</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2545,9 +2535,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2562,22 +2562,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129011400</v>
+        <v>129032885</v>
       </c>
       <c r="B21" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2609,10 +2609,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>409643</v>
+        <v>409078</v>
       </c>
       <c r="R21" t="n">
-        <v>6782378</v>
+        <v>6782312</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2642,19 +2642,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>12:59</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>12:59</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2669,22 +2659,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129032892</v>
+        <v>129011400</v>
       </c>
       <c r="B22" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2716,10 +2706,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>409244</v>
+        <v>409643</v>
       </c>
       <c r="R22" t="n">
-        <v>6782381</v>
+        <v>6782378</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2749,9 +2739,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2766,12 +2766,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -2781,7 +2781,7 @@
         <v>129011383</v>
       </c>
       <c r="B23" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2888,7 +2888,7 @@
         <v>129011395</v>
       </c>
       <c r="B24" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2995,7 +2995,7 @@
         <v>129011407</v>
       </c>
       <c r="B25" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3099,10 +3099,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129032399</v>
+        <v>129032395</v>
       </c>
       <c r="B26" t="n">
-        <v>91564</v>
+        <v>57727</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3110,34 +3110,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>409492</v>
+        <v>409759</v>
       </c>
       <c r="R26" t="n">
-        <v>6782346</v>
+        <v>6782358</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3196,10 +3204,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129011374</v>
+        <v>129032399</v>
       </c>
       <c r="B27" t="n">
-        <v>91564</v>
+        <v>91566</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3224,24 +3232,17 @@
           <t>(Brot.) Murrill</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>409475</v>
+        <v>409492</v>
       </c>
       <c r="R27" t="n">
-        <v>6782342</v>
+        <v>6782346</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3271,55 +3272,39 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>13:57</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>13:57</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>hackspetthål under tickorna</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129032395</v>
+        <v>129011374</v>
       </c>
       <c r="B28" t="n">
-        <v>57727</v>
+        <v>91566</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3327,31 +3312,30 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3359,10 +3343,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>409759</v>
+        <v>409475</v>
       </c>
       <c r="R28" t="n">
-        <v>6782358</v>
+        <v>6782342</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3392,29 +3376,45 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>hackspetthål under tickorna</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3424,7 +3424,7 @@
         <v>129032393</v>
       </c>
       <c r="B29" t="n">
-        <v>79633</v>
+        <v>79634</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3518,10 +3518,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129032406</v>
+        <v>129032913</v>
       </c>
       <c r="B30" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3553,10 +3553,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>409253</v>
+        <v>409757</v>
       </c>
       <c r="R30" t="n">
-        <v>6782372</v>
+        <v>6782355</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3603,22 +3603,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129032882</v>
+        <v>129032406</v>
       </c>
       <c r="B31" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3650,10 +3650,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>408992</v>
+        <v>409253</v>
       </c>
       <c r="R31" t="n">
-        <v>6782394</v>
+        <v>6782372</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3700,22 +3700,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129032878</v>
+        <v>129032882</v>
       </c>
       <c r="B32" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3747,10 +3747,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>408966</v>
+        <v>408992</v>
       </c>
       <c r="R32" t="n">
-        <v>6782283</v>
+        <v>6782394</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3809,10 +3809,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129011369</v>
+        <v>129032878</v>
       </c>
       <c r="B33" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3820,42 +3820,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>409683</v>
+        <v>408966</v>
       </c>
       <c r="R33" t="n">
-        <v>6782391</v>
+        <v>6782283</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3885,19 +3877,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>12:56</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>12:56</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3912,22 +3894,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129032913</v>
+        <v>129011369</v>
       </c>
       <c r="B34" t="n">
-        <v>79043</v>
+        <v>57727</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3935,34 +3917,42 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>409757</v>
+        <v>409683</v>
       </c>
       <c r="R34" t="n">
-        <v>6782355</v>
+        <v>6782391</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3992,9 +3982,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4009,12 +4009,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4024,7 +4024,7 @@
         <v>129011391</v>
       </c>
       <c r="B35" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129011381</v>
+        <v>129032887</v>
       </c>
       <c r="B36" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4163,10 +4163,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>409010</v>
+        <v>409176</v>
       </c>
       <c r="R36" t="n">
-        <v>6782383</v>
+        <v>6782420</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4196,19 +4196,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>16:06</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>16:06</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4223,22 +4213,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129032887</v>
+        <v>129011381</v>
       </c>
       <c r="B37" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4270,10 +4260,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>409176</v>
+        <v>409010</v>
       </c>
       <c r="R37" t="n">
-        <v>6782420</v>
+        <v>6782383</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4303,9 +4293,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4320,22 +4320,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129011392</v>
+        <v>129032891</v>
       </c>
       <c r="B38" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4367,10 +4367,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>409361</v>
+        <v>409241</v>
       </c>
       <c r="R38" t="n">
-        <v>6782401</v>
+        <v>6782372</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4400,19 +4400,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>14:31</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>14:31</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4427,22 +4417,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129032911</v>
+        <v>129011392</v>
       </c>
       <c r="B39" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4474,10 +4464,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>409777</v>
+        <v>409361</v>
       </c>
       <c r="R39" t="n">
-        <v>6782445</v>
+        <v>6782401</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4507,9 +4497,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4524,22 +4524,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129032407</v>
+        <v>129032911</v>
       </c>
       <c r="B40" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4571,10 +4571,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>409659</v>
+        <v>409777</v>
       </c>
       <c r="R40" t="n">
-        <v>6782436</v>
+        <v>6782445</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4621,22 +4621,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129011394</v>
+        <v>129032906</v>
       </c>
       <c r="B41" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4668,10 +4668,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>409543</v>
+        <v>409684</v>
       </c>
       <c r="R41" t="n">
-        <v>6782361</v>
+        <v>6782322</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4701,19 +4701,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>13:27</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>13:27</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4728,22 +4718,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129011399</v>
+        <v>129032407</v>
       </c>
       <c r="B42" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4775,10 +4765,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>409609</v>
+        <v>409659</v>
       </c>
       <c r="R42" t="n">
-        <v>6782404</v>
+        <v>6782436</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4808,19 +4798,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>13:06</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>13:06</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4835,12 +4815,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -4850,7 +4830,7 @@
         <v>129032910</v>
       </c>
       <c r="B43" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4944,10 +4924,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129032891</v>
+        <v>129011394</v>
       </c>
       <c r="B44" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4979,10 +4959,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>409241</v>
+        <v>409543</v>
       </c>
       <c r="R44" t="n">
-        <v>6782372</v>
+        <v>6782361</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5012,9 +4992,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5029,22 +5019,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129032906</v>
+        <v>129011399</v>
       </c>
       <c r="B45" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5076,10 +5066,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>409684</v>
+        <v>409609</v>
       </c>
       <c r="R45" t="n">
-        <v>6782322</v>
+        <v>6782404</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5109,9 +5099,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5126,22 +5126,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129011408</v>
+        <v>129032884</v>
       </c>
       <c r="B46" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5173,10 +5173,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>409801</v>
+        <v>409039</v>
       </c>
       <c r="R46" t="n">
-        <v>6782315</v>
+        <v>6782290</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5206,19 +5206,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>11:08</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>11:08</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5233,22 +5223,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129032883</v>
+        <v>129011408</v>
       </c>
       <c r="B47" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5280,10 +5270,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>409010</v>
+        <v>409801</v>
       </c>
       <c r="R47" t="n">
-        <v>6782399</v>
+        <v>6782315</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5313,9 +5303,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5330,22 +5330,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129011380</v>
+        <v>129032883</v>
       </c>
       <c r="B48" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5377,10 +5377,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>408984</v>
+        <v>409010</v>
       </c>
       <c r="R48" t="n">
-        <v>6782385</v>
+        <v>6782399</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5410,19 +5410,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>16:07</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>16:07</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5437,22 +5427,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129032884</v>
+        <v>129011380</v>
       </c>
       <c r="B49" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5484,10 +5474,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>409039</v>
+        <v>408984</v>
       </c>
       <c r="R49" t="n">
-        <v>6782290</v>
+        <v>6782385</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5517,9 +5507,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5534,12 +5534,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -5643,10 +5643,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129011401</v>
+        <v>129032866</v>
       </c>
       <c r="B51" t="n">
-        <v>79043</v>
+        <v>57727</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5654,21 +5654,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5678,10 +5678,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>409663</v>
+        <v>409757</v>
       </c>
       <c r="R51" t="n">
-        <v>6782385</v>
+        <v>6782386</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5711,19 +5711,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>12:58</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>12:58</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5738,22 +5728,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129011386</v>
+        <v>129011401</v>
       </c>
       <c r="B52" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5785,10 +5775,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>409210</v>
+        <v>409663</v>
       </c>
       <c r="R52" t="n">
-        <v>6782365</v>
+        <v>6782385</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5820,7 +5810,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -5830,7 +5820,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5857,10 +5847,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129011396</v>
+        <v>129032899</v>
       </c>
       <c r="B53" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5892,10 +5882,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>409584</v>
+        <v>409397</v>
       </c>
       <c r="R53" t="n">
-        <v>6782395</v>
+        <v>6782272</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5925,19 +5915,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>13:11</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>13:11</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5952,22 +5932,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129032899</v>
+        <v>129011386</v>
       </c>
       <c r="B54" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5999,10 +5979,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>409397</v>
+        <v>409210</v>
       </c>
       <c r="R54" t="n">
-        <v>6782272</v>
+        <v>6782365</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6032,9 +6012,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6049,12 +6039,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -6064,7 +6054,7 @@
         <v>129011409</v>
       </c>
       <c r="B55" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6169,10 +6159,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129032866</v>
+        <v>129011396</v>
       </c>
       <c r="B56" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6180,21 +6170,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6204,10 +6194,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>409757</v>
+        <v>409584</v>
       </c>
       <c r="R56" t="n">
-        <v>6782386</v>
+        <v>6782395</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6237,9 +6227,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6254,22 +6254,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129032403</v>
+        <v>129011373</v>
       </c>
       <c r="B57" t="n">
-        <v>79043</v>
+        <v>91566</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6277,34 +6277,41 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>409021</v>
+        <v>409435</v>
       </c>
       <c r="R57" t="n">
-        <v>6782365</v>
+        <v>6782383</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6334,29 +6341,45 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>4 st på samma tall</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -6478,10 +6501,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129011373</v>
+        <v>129032889</v>
       </c>
       <c r="B59" t="n">
-        <v>91564</v>
+        <v>79044</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6489,41 +6512,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>409435</v>
+        <v>409164</v>
       </c>
       <c r="R59" t="n">
-        <v>6782383</v>
+        <v>6782308</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6553,55 +6569,39 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>4 st på samma tall</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129032889</v>
+        <v>129032403</v>
       </c>
       <c r="B60" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6633,10 +6633,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>409164</v>
+        <v>409021</v>
       </c>
       <c r="R60" t="n">
-        <v>6782308</v>
+        <v>6782365</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6683,12 +6683,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -6698,7 +6698,7 @@
         <v>129011375</v>
       </c>
       <c r="B61" t="n">
-        <v>78800</v>
+        <v>78801</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6802,10 +6802,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129011387</v>
+        <v>129032874</v>
       </c>
       <c r="B62" t="n">
-        <v>79043</v>
+        <v>91565</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6813,23 +6813,19 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -6837,10 +6833,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>409232</v>
+        <v>409405</v>
       </c>
       <c r="R62" t="n">
-        <v>6782353</v>
+        <v>6782366</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6870,19 +6866,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>15:22</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>15:22</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6897,44 +6883,44 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129011384</v>
+        <v>129032400</v>
       </c>
       <c r="B63" t="n">
-        <v>79043</v>
+        <v>91998</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6944,10 +6930,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>409068</v>
+        <v>409738</v>
       </c>
       <c r="R63" t="n">
-        <v>6782377</v>
+        <v>6782382</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6977,19 +6963,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>15:43</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>15:43</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7004,22 +6980,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129011379</v>
+        <v>129011387</v>
       </c>
       <c r="B64" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7051,10 +7027,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>408991</v>
+        <v>409232</v>
       </c>
       <c r="R64" t="n">
-        <v>6782360</v>
+        <v>6782353</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7086,7 +7062,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7096,7 +7072,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7123,10 +7099,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129032874</v>
+        <v>129032886</v>
       </c>
       <c r="B65" t="n">
-        <v>91563</v>
+        <v>79044</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7134,19 +7110,23 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7154,10 +7134,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>409405</v>
+        <v>409108</v>
       </c>
       <c r="R65" t="n">
-        <v>6782366</v>
+        <v>6782395</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7216,32 +7196,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129032400</v>
+        <v>129011384</v>
       </c>
       <c r="B66" t="n">
-        <v>91996</v>
+        <v>79044</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7251,10 +7231,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>409738</v>
+        <v>409068</v>
       </c>
       <c r="R66" t="n">
-        <v>6782382</v>
+        <v>6782377</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7284,9 +7264,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7301,22 +7291,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129032872</v>
+        <v>129011379</v>
       </c>
       <c r="B67" t="n">
-        <v>78800</v>
+        <v>79044</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7324,21 +7314,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7348,10 +7338,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>409594</v>
+        <v>408991</v>
       </c>
       <c r="R67" t="n">
-        <v>6782294</v>
+        <v>6782360</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7381,9 +7371,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7398,22 +7398,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129032886</v>
+        <v>129032914</v>
       </c>
       <c r="B68" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7445,10 +7445,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>409108</v>
+        <v>409759</v>
       </c>
       <c r="R68" t="n">
-        <v>6782395</v>
+        <v>6782343</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7507,10 +7507,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129032914</v>
+        <v>129032872</v>
       </c>
       <c r="B69" t="n">
-        <v>79043</v>
+        <v>78801</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7518,21 +7518,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7542,10 +7542,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>409759</v>
+        <v>409594</v>
       </c>
       <c r="R69" t="n">
-        <v>6782343</v>
+        <v>6782294</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7806,10 +7806,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129032900</v>
+        <v>129032873</v>
       </c>
       <c r="B72" t="n">
-        <v>79043</v>
+        <v>91545</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7817,34 +7817,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>409449</v>
+        <v>409075</v>
       </c>
       <c r="R72" t="n">
-        <v>6782286</v>
+        <v>6782317</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7885,6 +7888,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -7903,10 +7907,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129032873</v>
+        <v>129032902</v>
       </c>
       <c r="B73" t="n">
-        <v>91543</v>
+        <v>79044</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7914,37 +7918,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>409075</v>
+        <v>409549</v>
       </c>
       <c r="R73" t="n">
-        <v>6782317</v>
+        <v>6782286</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7985,7 +7986,6 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -8004,10 +8004,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129032896</v>
+        <v>129032917</v>
       </c>
       <c r="B74" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8039,10 +8039,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>409331</v>
+        <v>409360</v>
       </c>
       <c r="R74" t="n">
-        <v>6782342</v>
+        <v>6782355</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8101,10 +8101,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129032902</v>
+        <v>129032900</v>
       </c>
       <c r="B75" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8136,7 +8136,7 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>409549</v>
+        <v>409449</v>
       </c>
       <c r="R75" t="n">
         <v>6782286</v>
@@ -8198,10 +8198,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129032917</v>
+        <v>129032896</v>
       </c>
       <c r="B76" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8233,10 +8233,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>409360</v>
+        <v>409331</v>
       </c>
       <c r="R76" t="n">
-        <v>6782355</v>
+        <v>6782342</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8295,10 +8295,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129032402</v>
+        <v>129032893</v>
       </c>
       <c r="B77" t="n">
-        <v>91563</v>
+        <v>79044</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8306,19 +8306,23 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
@@ -8326,10 +8330,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>409767</v>
+        <v>409280</v>
       </c>
       <c r="R77" t="n">
-        <v>6782352</v>
+        <v>6782382</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8376,22 +8380,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129032901</v>
+        <v>129011404</v>
       </c>
       <c r="B78" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8423,10 +8427,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>409528</v>
+        <v>409736</v>
       </c>
       <c r="R78" t="n">
-        <v>6782292</v>
+        <v>6782394</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8456,9 +8460,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8473,22 +8487,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129032888</v>
+        <v>129032901</v>
       </c>
       <c r="B79" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8520,10 +8534,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>409127</v>
+        <v>409528</v>
       </c>
       <c r="R79" t="n">
-        <v>6782290</v>
+        <v>6782292</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8582,10 +8596,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129011404</v>
+        <v>129032888</v>
       </c>
       <c r="B80" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8617,10 +8631,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>409736</v>
+        <v>409127</v>
       </c>
       <c r="R80" t="n">
-        <v>6782394</v>
+        <v>6782290</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8650,19 +8664,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>11:59</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>11:59</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8677,22 +8681,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129032893</v>
+        <v>129032402</v>
       </c>
       <c r="B81" t="n">
-        <v>79043</v>
+        <v>91565</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8700,23 +8704,19 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
@@ -8724,10 +8724,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>409280</v>
+        <v>409767</v>
       </c>
       <c r="R81" t="n">
-        <v>6782382</v>
+        <v>6782352</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8774,22 +8774,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129032879</v>
+        <v>129032908</v>
       </c>
       <c r="B82" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8821,10 +8821,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>408909</v>
+        <v>409715</v>
       </c>
       <c r="R82" t="n">
-        <v>6782332</v>
+        <v>6782363</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8883,10 +8883,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129032409</v>
+        <v>129032879</v>
       </c>
       <c r="B83" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8918,10 +8918,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>409782</v>
+        <v>408909</v>
       </c>
       <c r="R83" t="n">
-        <v>6782339</v>
+        <v>6782332</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8968,22 +8968,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129032908</v>
+        <v>129032409</v>
       </c>
       <c r="B84" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9015,10 +9015,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>409715</v>
+        <v>409782</v>
       </c>
       <c r="R84" t="n">
-        <v>6782363</v>
+        <v>6782339</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9065,12 +9065,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
@@ -9080,7 +9080,7 @@
         <v>129032916</v>
       </c>
       <c r="B85" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9174,10 +9174,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129032870</v>
+        <v>129032898</v>
       </c>
       <c r="B86" t="n">
-        <v>91564</v>
+        <v>79044</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9185,42 +9185,31 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>409530</v>
+        <v>409390</v>
       </c>
       <c r="R86" t="n">
         <v>6782289</v>
@@ -9264,7 +9253,6 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9283,10 +9271,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129032898</v>
+        <v>129032918</v>
       </c>
       <c r="B87" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9318,10 +9306,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>409390</v>
+        <v>409363</v>
       </c>
       <c r="R87" t="n">
-        <v>6782289</v>
+        <v>6782377</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9380,10 +9368,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129032918</v>
+        <v>129011370</v>
       </c>
       <c r="B88" t="n">
-        <v>79043</v>
+        <v>57727</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9391,34 +9379,42 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>409363</v>
+        <v>409759</v>
       </c>
       <c r="R88" t="n">
-        <v>6782377</v>
+        <v>6782330</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9448,9 +9444,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9465,22 +9471,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129011370</v>
+        <v>129032870</v>
       </c>
       <c r="B89" t="n">
-        <v>57727</v>
+        <v>91566</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9488,31 +9494,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
@@ -9520,10 +9529,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>409759</v>
+        <v>409530</v>
       </c>
       <c r="R89" t="n">
-        <v>6782330</v>
+        <v>6782289</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9553,49 +9562,40 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
       <c r="AD89" t="b">
         <v>0</v>
       </c>
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129011393</v>
+        <v>129032895</v>
       </c>
       <c r="B90" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9627,10 +9627,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>409472</v>
+        <v>409310</v>
       </c>
       <c r="R90" t="n">
-        <v>6782351</v>
+        <v>6782326</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9660,19 +9660,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>14:05</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>14:05</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9687,22 +9677,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129032405</v>
+        <v>129011393</v>
       </c>
       <c r="B91" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9734,10 +9724,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>409048</v>
+        <v>409472</v>
       </c>
       <c r="R91" t="n">
-        <v>6782365</v>
+        <v>6782351</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9767,9 +9757,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9784,22 +9784,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129032895</v>
+        <v>129032903</v>
       </c>
       <c r="B92" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9831,10 +9831,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>409310</v>
+        <v>409582</v>
       </c>
       <c r="R92" t="n">
-        <v>6782326</v>
+        <v>6782297</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9893,10 +9893,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129032903</v>
+        <v>129032880</v>
       </c>
       <c r="B93" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9928,10 +9928,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>409582</v>
+        <v>408901</v>
       </c>
       <c r="R93" t="n">
-        <v>6782297</v>
+        <v>6782390</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9990,10 +9990,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129032880</v>
+        <v>129032405</v>
       </c>
       <c r="B94" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10025,10 +10025,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>408901</v>
+        <v>409048</v>
       </c>
       <c r="R94" t="n">
-        <v>6782390</v>
+        <v>6782365</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10075,22 +10075,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129011406</v>
+        <v>129032408</v>
       </c>
       <c r="B95" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10122,10 +10122,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>409759</v>
+        <v>409749</v>
       </c>
       <c r="R95" t="n">
-        <v>6782314</v>
+        <v>6782325</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10155,19 +10155,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z95" t="inlineStr">
-        <is>
-          <t>11:41</t>
-        </is>
-      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB95" t="inlineStr">
-        <is>
-          <t>11:41</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10182,12 +10172,12 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
@@ -10197,7 +10187,7 @@
         <v>129011388</v>
       </c>
       <c r="B96" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10301,10 +10291,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129032408</v>
+        <v>129011406</v>
       </c>
       <c r="B97" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10336,10 +10326,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>409749</v>
+        <v>409759</v>
       </c>
       <c r="R97" t="n">
-        <v>6782325</v>
+        <v>6782314</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10369,9 +10359,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10386,22 +10386,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129032875</v>
+        <v>129032912</v>
       </c>
       <c r="B98" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10433,10 +10433,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>409034</v>
+        <v>409762</v>
       </c>
       <c r="R98" t="n">
-        <v>6782261</v>
+        <v>6782335</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10495,10 +10495,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129011390</v>
+        <v>129032890</v>
       </c>
       <c r="B99" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10530,10 +10530,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>409349</v>
+        <v>409228</v>
       </c>
       <c r="R99" t="n">
-        <v>6782376</v>
+        <v>6782298</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10563,19 +10563,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>14:34</t>
-        </is>
-      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>14:34</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10590,22 +10580,22 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129032912</v>
+        <v>129032875</v>
       </c>
       <c r="B100" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10637,10 +10627,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>409762</v>
+        <v>409034</v>
       </c>
       <c r="R100" t="n">
-        <v>6782335</v>
+        <v>6782261</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10699,10 +10689,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129032890</v>
+        <v>129011390</v>
       </c>
       <c r="B101" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10734,10 +10724,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>409228</v>
+        <v>409349</v>
       </c>
       <c r="R101" t="n">
-        <v>6782298</v>
+        <v>6782376</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10767,9 +10757,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10784,12 +10784,12 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
@@ -10799,7 +10799,7 @@
         <v>129032401</v>
       </c>
       <c r="B102" t="n">
-        <v>91563</v>
+        <v>91565</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10889,10 +10889,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129032904</v>
+        <v>129011377</v>
       </c>
       <c r="B103" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10924,10 +10924,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>409568</v>
+        <v>408995</v>
       </c>
       <c r="R103" t="n">
-        <v>6782383</v>
+        <v>6782299</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10957,9 +10957,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10974,22 +10984,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129011377</v>
+        <v>129032904</v>
       </c>
       <c r="B104" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11021,10 +11031,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>408995</v>
+        <v>409568</v>
       </c>
       <c r="R104" t="n">
-        <v>6782299</v>
+        <v>6782383</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11054,19 +11064,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z104" t="inlineStr">
-        <is>
-          <t>16:13</t>
-        </is>
-      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB104" t="inlineStr">
-        <is>
-          <t>16:13</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11081,22 +11081,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129011402</v>
+        <v>129032915</v>
       </c>
       <c r="B105" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11128,10 +11128,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>409671</v>
+        <v>409765</v>
       </c>
       <c r="R105" t="n">
-        <v>6782390</v>
+        <v>6782330</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11161,19 +11161,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z105" t="inlineStr">
-        <is>
-          <t>12:57</t>
-        </is>
-      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB105" t="inlineStr">
-        <is>
-          <t>12:57</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11188,22 +11178,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129011385</v>
+        <v>129011402</v>
       </c>
       <c r="B106" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11235,10 +11225,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>409214</v>
+        <v>409671</v>
       </c>
       <c r="R106" t="n">
-        <v>6782345</v>
+        <v>6782390</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11270,7 +11260,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11280,7 +11270,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11307,10 +11297,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129032877</v>
+        <v>129011385</v>
       </c>
       <c r="B107" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11342,10 +11332,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>408994</v>
+        <v>409214</v>
       </c>
       <c r="R107" t="n">
-        <v>6782293</v>
+        <v>6782345</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11375,9 +11365,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11392,22 +11392,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129032915</v>
+        <v>129032877</v>
       </c>
       <c r="B108" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11439,10 +11439,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>409765</v>
+        <v>408994</v>
       </c>
       <c r="R108" t="n">
-        <v>6782330</v>
+        <v>6782293</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>

--- a/artfynd/A 47938-2025 artfynd.xlsx
+++ b/artfynd/A 47938-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129032920</v>
+        <v>129011403</v>
       </c>
       <c r="B2" t="n">
         <v>79044</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>409793</v>
+        <v>409706</v>
       </c>
       <c r="R2" t="n">
-        <v>6782448</v>
+        <v>6782359</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -743,9 +743,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -760,19 +770,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129011405</v>
+        <v>129032905</v>
       </c>
       <c r="B3" t="n">
         <v>79044</v>
@@ -807,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>409747</v>
+        <v>409624</v>
       </c>
       <c r="R3" t="n">
-        <v>6782328</v>
+        <v>6782292</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -840,19 +850,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>11:47</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:47</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,19 +867,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129032876</v>
+        <v>129032920</v>
       </c>
       <c r="B4" t="n">
         <v>79044</v>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>408997</v>
+        <v>409793</v>
       </c>
       <c r="R4" t="n">
-        <v>6782283</v>
+        <v>6782448</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,7 +976,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129011403</v>
+        <v>129011405</v>
       </c>
       <c r="B5" t="n">
         <v>79044</v>
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>409706</v>
+        <v>409747</v>
       </c>
       <c r="R5" t="n">
-        <v>6782359</v>
+        <v>6782328</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129032905</v>
+        <v>129032876</v>
       </c>
       <c r="B6" t="n">
         <v>79044</v>
@@ -1118,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>409624</v>
+        <v>408997</v>
       </c>
       <c r="R6" t="n">
-        <v>6782292</v>
+        <v>6782283</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,7 +1180,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129032907</v>
+        <v>129032919</v>
       </c>
       <c r="B7" t="n">
         <v>79044</v>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>409686</v>
+        <v>409358</v>
       </c>
       <c r="R7" t="n">
-        <v>6782351</v>
+        <v>6782291</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1277,10 +1277,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129011389</v>
+        <v>129032394</v>
       </c>
       <c r="B8" t="n">
-        <v>79044</v>
+        <v>79634</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1288,21 +1288,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>409278</v>
+        <v>409553</v>
       </c>
       <c r="R8" t="n">
-        <v>6782361</v>
+        <v>6782378</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1345,19 +1345,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>15:18</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>15:18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1372,19 +1362,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129032919</v>
+        <v>129032907</v>
       </c>
       <c r="B9" t="n">
         <v>79044</v>
@@ -1419,10 +1409,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>409358</v>
+        <v>409686</v>
       </c>
       <c r="R9" t="n">
-        <v>6782291</v>
+        <v>6782351</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1481,10 +1471,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129032394</v>
+        <v>129011389</v>
       </c>
       <c r="B10" t="n">
-        <v>79634</v>
+        <v>79044</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1492,21 +1482,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1516,10 +1506,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>409553</v>
+        <v>409278</v>
       </c>
       <c r="R10" t="n">
-        <v>6782378</v>
+        <v>6782361</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1549,9 +1539,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1566,22 +1566,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129011398</v>
+        <v>129032398</v>
       </c>
       <c r="B11" t="n">
-        <v>79044</v>
+        <v>91570</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1589,21 +1589,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1613,10 +1613,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>409596</v>
+        <v>409482</v>
       </c>
       <c r="R11" t="n">
-        <v>6782395</v>
+        <v>6782335</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1646,19 +1646,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>13:08</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>13:08</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1673,19 +1663,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129032894</v>
+        <v>129011398</v>
       </c>
       <c r="B12" t="n">
         <v>79044</v>
@@ -1720,10 +1710,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>409292</v>
+        <v>409596</v>
       </c>
       <c r="R12" t="n">
-        <v>6782306</v>
+        <v>6782395</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1753,9 +1743,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1770,22 +1770,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129032398</v>
+        <v>129032894</v>
       </c>
       <c r="B13" t="n">
-        <v>91566</v>
+        <v>79044</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1793,21 +1793,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1817,10 +1817,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>409482</v>
+        <v>409292</v>
       </c>
       <c r="R13" t="n">
-        <v>6782335</v>
+        <v>6782306</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1867,19 +1867,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129032897</v>
+        <v>129011378</v>
       </c>
       <c r="B14" t="n">
         <v>79044</v>
@@ -1914,10 +1914,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>409469</v>
+        <v>408984</v>
       </c>
       <c r="R14" t="n">
-        <v>6782371</v>
+        <v>6782347</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1947,9 +1947,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1964,19 +1974,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129032909</v>
+        <v>129032897</v>
       </c>
       <c r="B15" t="n">
         <v>79044</v>
@@ -2011,10 +2021,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>409727</v>
+        <v>409469</v>
       </c>
       <c r="R15" t="n">
-        <v>6782352</v>
+        <v>6782371</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2073,10 +2083,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129032392</v>
+        <v>129032909</v>
       </c>
       <c r="B16" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2084,21 +2094,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2108,10 +2118,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>409554</v>
+        <v>409727</v>
       </c>
       <c r="R16" t="n">
-        <v>6782380</v>
+        <v>6782352</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2158,22 +2168,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129011378</v>
+        <v>129032392</v>
       </c>
       <c r="B17" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2181,21 +2191,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2205,10 +2215,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>408984</v>
+        <v>409554</v>
       </c>
       <c r="R17" t="n">
-        <v>6782347</v>
+        <v>6782380</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2238,19 +2248,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>16:10</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>16:10</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2265,22 +2265,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129032892</v>
+        <v>129011376</v>
       </c>
       <c r="B18" t="n">
-        <v>79044</v>
+        <v>91569</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2288,23 +2288,19 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2312,10 +2308,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>409244</v>
+        <v>409774</v>
       </c>
       <c r="R18" t="n">
-        <v>6782381</v>
+        <v>6782323</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2345,9 +2341,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2362,22 +2368,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129032868</v>
+        <v>129032885</v>
       </c>
       <c r="B19" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2385,21 +2391,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2409,10 +2415,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>409688</v>
+        <v>409078</v>
       </c>
       <c r="R19" t="n">
-        <v>6782303</v>
+        <v>6782312</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2471,10 +2477,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129011376</v>
+        <v>129011400</v>
       </c>
       <c r="B20" t="n">
-        <v>91565</v>
+        <v>79044</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2482,19 +2488,23 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2502,10 +2512,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>409774</v>
+        <v>409643</v>
       </c>
       <c r="R20" t="n">
-        <v>6782323</v>
+        <v>6782378</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2537,7 +2547,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2547,7 +2557,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2574,7 +2584,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129032885</v>
+        <v>129032892</v>
       </c>
       <c r="B21" t="n">
         <v>79044</v>
@@ -2609,10 +2619,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>409078</v>
+        <v>409244</v>
       </c>
       <c r="R21" t="n">
-        <v>6782312</v>
+        <v>6782381</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2671,10 +2681,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129011400</v>
+        <v>129032868</v>
       </c>
       <c r="B22" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2682,21 +2692,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2706,10 +2716,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>409643</v>
+        <v>409688</v>
       </c>
       <c r="R22" t="n">
-        <v>6782378</v>
+        <v>6782303</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2739,19 +2749,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>12:59</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>12:59</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2766,22 +2766,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129011383</v>
+        <v>129032399</v>
       </c>
       <c r="B23" t="n">
-        <v>79044</v>
+        <v>91570</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2789,21 +2789,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2813,10 +2813,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>409028</v>
+        <v>409492</v>
       </c>
       <c r="R23" t="n">
-        <v>6782350</v>
+        <v>6782346</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2846,19 +2846,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>16:04</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>16:04</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2873,22 +2863,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129011395</v>
+        <v>129011374</v>
       </c>
       <c r="B24" t="n">
-        <v>79044</v>
+        <v>91570</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2896,34 +2886,41 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>409555</v>
+        <v>409475</v>
       </c>
       <c r="R24" t="n">
-        <v>6782356</v>
+        <v>6782341</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2955,7 +2952,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -2965,7 +2962,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>hackspetthål under tickorna</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2974,6 +2976,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -2992,7 +2995,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129011407</v>
+        <v>129011383</v>
       </c>
       <c r="B25" t="n">
         <v>79044</v>
@@ -3027,10 +3030,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>409795</v>
+        <v>409028</v>
       </c>
       <c r="R25" t="n">
-        <v>6782327</v>
+        <v>6782350</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3062,7 +3065,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3072,7 +3075,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3099,10 +3102,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129032395</v>
+        <v>129011395</v>
       </c>
       <c r="B26" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3110,42 +3113,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>409759</v>
+        <v>409555</v>
       </c>
       <c r="R26" t="n">
-        <v>6782358</v>
+        <v>6782356</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3175,9 +3170,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3192,22 +3197,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129032399</v>
+        <v>129011407</v>
       </c>
       <c r="B27" t="n">
-        <v>91566</v>
+        <v>79044</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3215,21 +3220,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3239,10 +3244,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>409492</v>
+        <v>409795</v>
       </c>
       <c r="R27" t="n">
-        <v>6782346</v>
+        <v>6782327</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3272,9 +3277,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3289,22 +3304,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129011374</v>
+        <v>129032395</v>
       </c>
       <c r="B28" t="n">
-        <v>91566</v>
+        <v>57727</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3312,30 +3327,31 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3343,10 +3359,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>409475</v>
+        <v>409759</v>
       </c>
       <c r="R28" t="n">
-        <v>6782342</v>
+        <v>6782358</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3376,45 +3392,29 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>13:57</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>13:57</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>hackspetthål under tickorna</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3809,7 +3809,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129032878</v>
+        <v>129011391</v>
       </c>
       <c r="B33" t="n">
         <v>79044</v>
@@ -3844,10 +3844,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>408966</v>
+        <v>409349</v>
       </c>
       <c r="R33" t="n">
-        <v>6782283</v>
+        <v>6782383</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3877,9 +3877,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3894,22 +3904,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129011369</v>
+        <v>129032878</v>
       </c>
       <c r="B34" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3917,42 +3927,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>409683</v>
+        <v>408966</v>
       </c>
       <c r="R34" t="n">
-        <v>6782391</v>
+        <v>6782283</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3982,19 +3984,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>12:56</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>12:56</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4009,22 +4001,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129011391</v>
+        <v>129011369</v>
       </c>
       <c r="B35" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4032,34 +4024,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>409349</v>
+        <v>409683</v>
       </c>
       <c r="R35" t="n">
-        <v>6782383</v>
+        <v>6782391</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4091,7 +4091,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -6269,7 +6269,7 @@
         <v>129011373</v>
       </c>
       <c r="B57" t="n">
-        <v>91566</v>
+        <v>91570</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6386,10 +6386,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129011372</v>
+        <v>129032889</v>
       </c>
       <c r="B58" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6397,42 +6397,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>409796</v>
+        <v>409164</v>
       </c>
       <c r="R58" t="n">
-        <v>6782327</v>
+        <v>6782308</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6462,19 +6454,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>11:10</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6489,22 +6471,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129032889</v>
+        <v>129011375</v>
       </c>
       <c r="B59" t="n">
-        <v>79044</v>
+        <v>78801</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6512,21 +6494,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6536,10 +6518,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>409164</v>
+        <v>409335</v>
       </c>
       <c r="R59" t="n">
-        <v>6782308</v>
+        <v>6782352</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6569,9 +6551,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6586,12 +6578,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -6695,10 +6687,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129011375</v>
+        <v>129011372</v>
       </c>
       <c r="B61" t="n">
-        <v>78801</v>
+        <v>57727</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6706,34 +6698,42 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>409335</v>
+        <v>409796</v>
       </c>
       <c r="R61" t="n">
-        <v>6782352</v>
+        <v>6782327</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6765,7 +6765,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -6775,7 +6775,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6802,30 +6802,34 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129032874</v>
+        <v>129032400</v>
       </c>
       <c r="B62" t="n">
-        <v>91565</v>
+        <v>92002</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr"/>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -6833,10 +6837,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>409405</v>
+        <v>409738</v>
       </c>
       <c r="R62" t="n">
-        <v>6782366</v>
+        <v>6782382</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6883,44 +6887,44 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129032400</v>
+        <v>129011387</v>
       </c>
       <c r="B63" t="n">
-        <v>91998</v>
+        <v>79044</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6930,10 +6934,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>409738</v>
+        <v>409232</v>
       </c>
       <c r="R63" t="n">
-        <v>6782382</v>
+        <v>6782353</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6963,9 +6967,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6980,22 +6994,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129011387</v>
+        <v>129032872</v>
       </c>
       <c r="B64" t="n">
-        <v>79044</v>
+        <v>78801</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7003,21 +7017,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7027,10 +7041,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>409232</v>
+        <v>409594</v>
       </c>
       <c r="R64" t="n">
-        <v>6782353</v>
+        <v>6782294</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7060,19 +7074,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>15:22</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>15:22</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7087,12 +7091,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
@@ -7507,10 +7511,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129032872</v>
+        <v>129032874</v>
       </c>
       <c r="B69" t="n">
-        <v>78801</v>
+        <v>91569</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7518,23 +7522,19 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6446</v>
+        <v>5432</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -7542,10 +7542,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>409594</v>
+        <v>409405</v>
       </c>
       <c r="R69" t="n">
-        <v>6782294</v>
+        <v>6782366</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7806,10 +7806,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129032873</v>
+        <v>129032902</v>
       </c>
       <c r="B72" t="n">
-        <v>91545</v>
+        <v>79044</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7817,37 +7817,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>409075</v>
+        <v>409549</v>
       </c>
       <c r="R72" t="n">
-        <v>6782317</v>
+        <v>6782286</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7888,7 +7885,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -7907,10 +7903,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129032902</v>
+        <v>129032873</v>
       </c>
       <c r="B73" t="n">
-        <v>79044</v>
+        <v>91549</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7918,34 +7914,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>409549</v>
+        <v>409075</v>
       </c>
       <c r="R73" t="n">
-        <v>6782286</v>
+        <v>6782317</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7986,6 +7985,7 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -8004,7 +8004,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129032917</v>
+        <v>129032896</v>
       </c>
       <c r="B74" t="n">
         <v>79044</v>
@@ -8039,10 +8039,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>409360</v>
+        <v>409331</v>
       </c>
       <c r="R74" t="n">
-        <v>6782355</v>
+        <v>6782342</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8101,7 +8101,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129032900</v>
+        <v>129032917</v>
       </c>
       <c r="B75" t="n">
         <v>79044</v>
@@ -8136,10 +8136,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>409449</v>
+        <v>409360</v>
       </c>
       <c r="R75" t="n">
-        <v>6782286</v>
+        <v>6782355</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8198,7 +8198,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129032896</v>
+        <v>129032900</v>
       </c>
       <c r="B76" t="n">
         <v>79044</v>
@@ -8233,10 +8233,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>409331</v>
+        <v>409449</v>
       </c>
       <c r="R76" t="n">
-        <v>6782342</v>
+        <v>6782286</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8295,10 +8295,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129032893</v>
+        <v>129032402</v>
       </c>
       <c r="B77" t="n">
-        <v>79044</v>
+        <v>91569</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8306,23 +8306,19 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
@@ -8330,10 +8326,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>409280</v>
+        <v>409767</v>
       </c>
       <c r="R77" t="n">
-        <v>6782382</v>
+        <v>6782352</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8380,19 +8376,19 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129011404</v>
+        <v>129032888</v>
       </c>
       <c r="B78" t="n">
         <v>79044</v>
@@ -8427,10 +8423,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>409736</v>
+        <v>409127</v>
       </c>
       <c r="R78" t="n">
-        <v>6782394</v>
+        <v>6782290</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8460,19 +8456,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>11:59</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>11:59</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8487,19 +8473,19 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129032901</v>
+        <v>129032893</v>
       </c>
       <c r="B79" t="n">
         <v>79044</v>
@@ -8534,10 +8520,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>409528</v>
+        <v>409280</v>
       </c>
       <c r="R79" t="n">
-        <v>6782292</v>
+        <v>6782382</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8596,7 +8582,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129032888</v>
+        <v>129011404</v>
       </c>
       <c r="B80" t="n">
         <v>79044</v>
@@ -8631,10 +8617,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>409127</v>
+        <v>409736</v>
       </c>
       <c r="R80" t="n">
-        <v>6782290</v>
+        <v>6782394</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8664,9 +8650,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8681,22 +8677,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129032402</v>
+        <v>129032901</v>
       </c>
       <c r="B81" t="n">
-        <v>91565</v>
+        <v>79044</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8704,19 +8700,23 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
@@ -8724,10 +8724,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>409767</v>
+        <v>409528</v>
       </c>
       <c r="R81" t="n">
-        <v>6782352</v>
+        <v>6782292</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8774,12 +8774,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
@@ -9174,10 +9174,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129032898</v>
+        <v>129032870</v>
       </c>
       <c r="B86" t="n">
-        <v>79044</v>
+        <v>91570</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9185,31 +9185,42 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>409390</v>
+        <v>409530</v>
       </c>
       <c r="R86" t="n">
         <v>6782289</v>
@@ -9253,6 +9264,7 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9483,10 +9495,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129032870</v>
+        <v>129032898</v>
       </c>
       <c r="B89" t="n">
-        <v>91566</v>
+        <v>79044</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9494,42 +9506,31 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>409530</v>
+        <v>409390</v>
       </c>
       <c r="R89" t="n">
         <v>6782289</v>
@@ -9573,7 +9574,6 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -9592,7 +9592,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129032895</v>
+        <v>129011393</v>
       </c>
       <c r="B90" t="n">
         <v>79044</v>
@@ -9627,10 +9627,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>409310</v>
+        <v>409472</v>
       </c>
       <c r="R90" t="n">
-        <v>6782326</v>
+        <v>6782351</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9660,9 +9660,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9677,19 +9687,19 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129011393</v>
+        <v>129032895</v>
       </c>
       <c r="B91" t="n">
         <v>79044</v>
@@ -9724,10 +9734,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>409472</v>
+        <v>409310</v>
       </c>
       <c r="R91" t="n">
-        <v>6782351</v>
+        <v>6782326</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9757,19 +9767,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>14:05</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>14:05</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9784,12 +9784,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
@@ -10087,7 +10087,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129032408</v>
+        <v>129011388</v>
       </c>
       <c r="B95" t="n">
         <v>79044</v>
@@ -10122,10 +10122,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>409749</v>
+        <v>409250</v>
       </c>
       <c r="R95" t="n">
-        <v>6782325</v>
+        <v>6782354</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10155,9 +10155,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10172,19 +10182,19 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129011388</v>
+        <v>129011406</v>
       </c>
       <c r="B96" t="n">
         <v>79044</v>
@@ -10219,10 +10229,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>409250</v>
+        <v>409759</v>
       </c>
       <c r="R96" t="n">
-        <v>6782354</v>
+        <v>6782314</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10254,7 +10264,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10264,7 +10274,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10291,7 +10301,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129011406</v>
+        <v>129032408</v>
       </c>
       <c r="B97" t="n">
         <v>79044</v>
@@ -10326,10 +10336,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>409759</v>
+        <v>409749</v>
       </c>
       <c r="R97" t="n">
-        <v>6782314</v>
+        <v>6782325</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10359,19 +10369,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z97" t="inlineStr">
-        <is>
-          <t>11:41</t>
-        </is>
-      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>11:41</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10386,12 +10386,12 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
@@ -10799,7 +10799,7 @@
         <v>129032401</v>
       </c>
       <c r="B102" t="n">
-        <v>91565</v>
+        <v>91569</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10996,7 +10996,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129032904</v>
+        <v>129011402</v>
       </c>
       <c r="B104" t="n">
         <v>79044</v>
@@ -11031,10 +11031,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>409568</v>
+        <v>409671</v>
       </c>
       <c r="R104" t="n">
-        <v>6782383</v>
+        <v>6782390</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11064,9 +11064,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11081,19 +11091,19 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129032915</v>
+        <v>129011385</v>
       </c>
       <c r="B105" t="n">
         <v>79044</v>
@@ -11128,10 +11138,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>409765</v>
+        <v>409214</v>
       </c>
       <c r="R105" t="n">
-        <v>6782330</v>
+        <v>6782345</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11161,9 +11171,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11178,19 +11198,19 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129011402</v>
+        <v>129032877</v>
       </c>
       <c r="B106" t="n">
         <v>79044</v>
@@ -11225,10 +11245,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>409671</v>
+        <v>408994</v>
       </c>
       <c r="R106" t="n">
-        <v>6782390</v>
+        <v>6782293</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11258,19 +11278,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z106" t="inlineStr">
-        <is>
-          <t>12:57</t>
-        </is>
-      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB106" t="inlineStr">
-        <is>
-          <t>12:57</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11285,19 +11295,19 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129011385</v>
+        <v>129032904</v>
       </c>
       <c r="B107" t="n">
         <v>79044</v>
@@ -11332,10 +11342,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>409214</v>
+        <v>409568</v>
       </c>
       <c r="R107" t="n">
-        <v>6782345</v>
+        <v>6782383</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11365,19 +11375,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z107" t="inlineStr">
-        <is>
-          <t>15:29</t>
-        </is>
-      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB107" t="inlineStr">
-        <is>
-          <t>15:29</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11392,19 +11392,19 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129032877</v>
+        <v>129032915</v>
       </c>
       <c r="B108" t="n">
         <v>79044</v>
@@ -11439,10 +11439,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>408994</v>
+        <v>409765</v>
       </c>
       <c r="R108" t="n">
-        <v>6782293</v>
+        <v>6782330</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>

--- a/artfynd/A 47938-2025 artfynd.xlsx
+++ b/artfynd/A 47938-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129011403</v>
+        <v>129032920</v>
       </c>
       <c r="B2" t="n">
         <v>79044</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>409706</v>
+        <v>409793</v>
       </c>
       <c r="R2" t="n">
-        <v>6782359</v>
+        <v>6782448</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -743,19 +743,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>12:06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,19 +760,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129032905</v>
+        <v>129011405</v>
       </c>
       <c r="B3" t="n">
         <v>79044</v>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>409624</v>
+        <v>409747</v>
       </c>
       <c r="R3" t="n">
-        <v>6782292</v>
+        <v>6782328</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -850,9 +840,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,19 +867,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129032920</v>
+        <v>129032876</v>
       </c>
       <c r="B4" t="n">
         <v>79044</v>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>409793</v>
+        <v>408997</v>
       </c>
       <c r="R4" t="n">
-        <v>6782448</v>
+        <v>6782283</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,7 +976,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129011405</v>
+        <v>129011403</v>
       </c>
       <c r="B5" t="n">
         <v>79044</v>
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>409747</v>
+        <v>409706</v>
       </c>
       <c r="R5" t="n">
-        <v>6782328</v>
+        <v>6782359</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129032876</v>
+        <v>129032905</v>
       </c>
       <c r="B6" t="n">
         <v>79044</v>
@@ -1118,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>408997</v>
+        <v>409624</v>
       </c>
       <c r="R6" t="n">
-        <v>6782283</v>
+        <v>6782292</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,7 +1180,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129032919</v>
+        <v>129032907</v>
       </c>
       <c r="B7" t="n">
         <v>79044</v>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>409358</v>
+        <v>409686</v>
       </c>
       <c r="R7" t="n">
-        <v>6782291</v>
+        <v>6782351</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1277,10 +1277,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129032394</v>
+        <v>129011389</v>
       </c>
       <c r="B8" t="n">
-        <v>79634</v>
+        <v>79044</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1288,21 +1288,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>409553</v>
+        <v>409278</v>
       </c>
       <c r="R8" t="n">
-        <v>6782378</v>
+        <v>6782361</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1345,9 +1345,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1362,19 +1372,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129032907</v>
+        <v>129032919</v>
       </c>
       <c r="B9" t="n">
         <v>79044</v>
@@ -1409,10 +1419,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>409686</v>
+        <v>409358</v>
       </c>
       <c r="R9" t="n">
-        <v>6782351</v>
+        <v>6782291</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1471,10 +1481,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129011389</v>
+        <v>129032394</v>
       </c>
       <c r="B10" t="n">
-        <v>79044</v>
+        <v>79634</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1482,21 +1492,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1506,10 +1516,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>409278</v>
+        <v>409553</v>
       </c>
       <c r="R10" t="n">
-        <v>6782361</v>
+        <v>6782378</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1539,19 +1549,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>15:18</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>15:18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1566,22 +1566,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129032398</v>
+        <v>129011398</v>
       </c>
       <c r="B11" t="n">
-        <v>91570</v>
+        <v>79044</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1589,21 +1589,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1613,10 +1613,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>409482</v>
+        <v>409596</v>
       </c>
       <c r="R11" t="n">
-        <v>6782335</v>
+        <v>6782395</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1646,9 +1646,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1663,19 +1673,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129011398</v>
+        <v>129032894</v>
       </c>
       <c r="B12" t="n">
         <v>79044</v>
@@ -1710,10 +1720,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>409596</v>
+        <v>409292</v>
       </c>
       <c r="R12" t="n">
-        <v>6782395</v>
+        <v>6782306</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1743,19 +1753,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>13:08</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>13:08</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1770,22 +1770,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129032894</v>
+        <v>129032398</v>
       </c>
       <c r="B13" t="n">
-        <v>79044</v>
+        <v>91571</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1793,21 +1793,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1817,10 +1817,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>409292</v>
+        <v>409482</v>
       </c>
       <c r="R13" t="n">
-        <v>6782306</v>
+        <v>6782335</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1867,22 +1867,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129011378</v>
+        <v>129032392</v>
       </c>
       <c r="B14" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1890,21 +1890,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1914,10 +1914,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>408984</v>
+        <v>409554</v>
       </c>
       <c r="R14" t="n">
-        <v>6782347</v>
+        <v>6782380</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1947,19 +1947,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>16:10</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>16:10</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1974,19 +1964,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129032897</v>
+        <v>129011378</v>
       </c>
       <c r="B15" t="n">
         <v>79044</v>
@@ -2021,10 +2011,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>409469</v>
+        <v>408984</v>
       </c>
       <c r="R15" t="n">
-        <v>6782371</v>
+        <v>6782347</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2054,9 +2044,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2071,19 +2071,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129032909</v>
+        <v>129032897</v>
       </c>
       <c r="B16" t="n">
         <v>79044</v>
@@ -2118,10 +2118,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>409727</v>
+        <v>409469</v>
       </c>
       <c r="R16" t="n">
-        <v>6782352</v>
+        <v>6782371</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2180,10 +2180,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129032392</v>
+        <v>129032909</v>
       </c>
       <c r="B17" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2191,21 +2191,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>409554</v>
+        <v>409727</v>
       </c>
       <c r="R17" t="n">
-        <v>6782380</v>
+        <v>6782352</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2265,22 +2265,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129011376</v>
+        <v>129032885</v>
       </c>
       <c r="B18" t="n">
-        <v>91569</v>
+        <v>79044</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2288,19 +2288,23 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2308,10 +2312,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>409774</v>
+        <v>409078</v>
       </c>
       <c r="R18" t="n">
-        <v>6782323</v>
+        <v>6782312</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2341,19 +2345,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>11:31</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>11:31</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2368,19 +2362,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129032885</v>
+        <v>129011400</v>
       </c>
       <c r="B19" t="n">
         <v>79044</v>
@@ -2415,10 +2409,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>409078</v>
+        <v>409643</v>
       </c>
       <c r="R19" t="n">
-        <v>6782312</v>
+        <v>6782378</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2448,9 +2442,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2465,19 +2469,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129011400</v>
+        <v>129032892</v>
       </c>
       <c r="B20" t="n">
         <v>79044</v>
@@ -2512,10 +2516,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>409643</v>
+        <v>409244</v>
       </c>
       <c r="R20" t="n">
-        <v>6782378</v>
+        <v>6782381</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2545,19 +2549,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>12:59</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>12:59</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2572,22 +2566,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129032892</v>
+        <v>129011376</v>
       </c>
       <c r="B21" t="n">
-        <v>79044</v>
+        <v>91570</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2595,23 +2589,19 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2619,10 +2609,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>409244</v>
+        <v>409774</v>
       </c>
       <c r="R21" t="n">
-        <v>6782381</v>
+        <v>6782323</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2652,9 +2642,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2669,12 +2669,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2781,7 +2781,7 @@
         <v>129032399</v>
       </c>
       <c r="B23" t="n">
-        <v>91570</v>
+        <v>91571</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2878,7 +2878,7 @@
         <v>129011374</v>
       </c>
       <c r="B24" t="n">
-        <v>91570</v>
+        <v>91571</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -5138,7 +5138,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129032884</v>
+        <v>129011408</v>
       </c>
       <c r="B46" t="n">
         <v>79044</v>
@@ -5173,10 +5173,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>409039</v>
+        <v>409801</v>
       </c>
       <c r="R46" t="n">
-        <v>6782290</v>
+        <v>6782315</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5206,9 +5206,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5223,19 +5233,19 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129011408</v>
+        <v>129032883</v>
       </c>
       <c r="B47" t="n">
         <v>79044</v>
@@ -5270,10 +5280,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>409801</v>
+        <v>409010</v>
       </c>
       <c r="R47" t="n">
-        <v>6782315</v>
+        <v>6782399</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5303,19 +5313,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>11:08</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>11:08</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5330,19 +5330,19 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129032883</v>
+        <v>129011380</v>
       </c>
       <c r="B48" t="n">
         <v>79044</v>
@@ -5377,10 +5377,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>409010</v>
+        <v>408984</v>
       </c>
       <c r="R48" t="n">
-        <v>6782399</v>
+        <v>6782385</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5410,9 +5410,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5427,19 +5437,19 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129011380</v>
+        <v>129032884</v>
       </c>
       <c r="B49" t="n">
         <v>79044</v>
@@ -5474,10 +5484,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>408984</v>
+        <v>409039</v>
       </c>
       <c r="R49" t="n">
-        <v>6782385</v>
+        <v>6782290</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5507,19 +5517,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>16:07</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>16:07</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5534,12 +5534,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -6266,10 +6266,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129011373</v>
+        <v>129032889</v>
       </c>
       <c r="B57" t="n">
-        <v>91570</v>
+        <v>79044</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6277,41 +6277,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>409435</v>
+        <v>409164</v>
       </c>
       <c r="R57" t="n">
-        <v>6782383</v>
+        <v>6782308</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6341,52 +6334,36 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>4 st på samma tall</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129032889</v>
+        <v>129032403</v>
       </c>
       <c r="B58" t="n">
         <v>79044</v>
@@ -6421,10 +6398,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>409164</v>
+        <v>409021</v>
       </c>
       <c r="R58" t="n">
-        <v>6782308</v>
+        <v>6782365</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6471,22 +6448,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129011375</v>
+        <v>129011372</v>
       </c>
       <c r="B59" t="n">
-        <v>78801</v>
+        <v>57727</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6494,34 +6471,42 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>409335</v>
+        <v>409796</v>
       </c>
       <c r="R59" t="n">
-        <v>6782352</v>
+        <v>6782327</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6553,7 +6538,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6563,7 +6548,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6590,10 +6575,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129032403</v>
+        <v>129011373</v>
       </c>
       <c r="B60" t="n">
-        <v>79044</v>
+        <v>91571</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6601,34 +6586,41 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>409021</v>
+        <v>409435</v>
       </c>
       <c r="R60" t="n">
-        <v>6782365</v>
+        <v>6782383</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6658,39 +6650,55 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>4 st på samma tall</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129011372</v>
+        <v>129011375</v>
       </c>
       <c r="B61" t="n">
-        <v>57727</v>
+        <v>78801</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6698,42 +6706,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>409796</v>
+        <v>409335</v>
       </c>
       <c r="R61" t="n">
-        <v>6782327</v>
+        <v>6782352</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6765,7 +6765,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -6775,7 +6775,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6805,7 +6805,7 @@
         <v>129032400</v>
       </c>
       <c r="B62" t="n">
-        <v>92002</v>
+        <v>92003</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129011387</v>
+        <v>129032874</v>
       </c>
       <c r="B63" t="n">
-        <v>79044</v>
+        <v>91570</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6910,23 +6910,19 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -6934,10 +6930,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>409232</v>
+        <v>409405</v>
       </c>
       <c r="R63" t="n">
-        <v>6782353</v>
+        <v>6782366</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6967,19 +6963,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>15:22</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>15:22</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6994,22 +6980,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129032872</v>
+        <v>129011387</v>
       </c>
       <c r="B64" t="n">
-        <v>78801</v>
+        <v>79044</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7017,21 +7003,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7041,10 +7027,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>409594</v>
+        <v>409232</v>
       </c>
       <c r="R64" t="n">
-        <v>6782294</v>
+        <v>6782353</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7074,9 +7060,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7091,12 +7087,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
@@ -7511,10 +7507,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129032874</v>
+        <v>129032872</v>
       </c>
       <c r="B69" t="n">
-        <v>91569</v>
+        <v>78801</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7522,19 +7518,23 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5432</v>
+        <v>6446</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr"/>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -7542,10 +7542,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>409405</v>
+        <v>409594</v>
       </c>
       <c r="R69" t="n">
-        <v>6782366</v>
+        <v>6782294</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7806,10 +7806,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129032902</v>
+        <v>129032873</v>
       </c>
       <c r="B72" t="n">
-        <v>79044</v>
+        <v>91550</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7817,34 +7817,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>409549</v>
+        <v>409075</v>
       </c>
       <c r="R72" t="n">
-        <v>6782286</v>
+        <v>6782317</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7885,6 +7888,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -7903,10 +7907,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129032873</v>
+        <v>129032896</v>
       </c>
       <c r="B73" t="n">
-        <v>91549</v>
+        <v>79044</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7914,37 +7918,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>409075</v>
+        <v>409331</v>
       </c>
       <c r="R73" t="n">
-        <v>6782317</v>
+        <v>6782342</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7985,7 +7986,6 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -8004,7 +8004,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129032896</v>
+        <v>129032902</v>
       </c>
       <c r="B74" t="n">
         <v>79044</v>
@@ -8039,10 +8039,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>409331</v>
+        <v>409549</v>
       </c>
       <c r="R74" t="n">
-        <v>6782342</v>
+        <v>6782286</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8298,7 +8298,7 @@
         <v>129032402</v>
       </c>
       <c r="B77" t="n">
-        <v>91569</v>
+        <v>91570</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8388,7 +8388,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129032888</v>
+        <v>129032893</v>
       </c>
       <c r="B78" t="n">
         <v>79044</v>
@@ -8423,10 +8423,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>409127</v>
+        <v>409280</v>
       </c>
       <c r="R78" t="n">
-        <v>6782290</v>
+        <v>6782382</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8485,7 +8485,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129032893</v>
+        <v>129011404</v>
       </c>
       <c r="B79" t="n">
         <v>79044</v>
@@ -8520,10 +8520,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>409280</v>
+        <v>409736</v>
       </c>
       <c r="R79" t="n">
-        <v>6782382</v>
+        <v>6782394</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8553,9 +8553,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8570,19 +8580,19 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129011404</v>
+        <v>129032901</v>
       </c>
       <c r="B80" t="n">
         <v>79044</v>
@@ -8617,10 +8627,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>409736</v>
+        <v>409528</v>
       </c>
       <c r="R80" t="n">
-        <v>6782394</v>
+        <v>6782292</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8650,19 +8660,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>11:59</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>11:59</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8677,19 +8677,19 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129032901</v>
+        <v>129032888</v>
       </c>
       <c r="B81" t="n">
         <v>79044</v>
@@ -8724,10 +8724,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>409528</v>
+        <v>409127</v>
       </c>
       <c r="R81" t="n">
-        <v>6782292</v>
+        <v>6782290</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9177,7 +9177,7 @@
         <v>129032870</v>
       </c>
       <c r="B86" t="n">
-        <v>91570</v>
+        <v>91571</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9283,10 +9283,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129032918</v>
+        <v>129011370</v>
       </c>
       <c r="B87" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9294,34 +9294,42 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>409363</v>
+        <v>409759</v>
       </c>
       <c r="R87" t="n">
-        <v>6782377</v>
+        <v>6782330</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9351,9 +9359,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9368,22 +9386,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129011370</v>
+        <v>129032898</v>
       </c>
       <c r="B88" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9391,42 +9409,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>409759</v>
+        <v>409390</v>
       </c>
       <c r="R88" t="n">
-        <v>6782330</v>
+        <v>6782289</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9456,19 +9466,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>11:48</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9483,19 +9483,19 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129032898</v>
+        <v>129032918</v>
       </c>
       <c r="B89" t="n">
         <v>79044</v>
@@ -9530,10 +9530,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>409390</v>
+        <v>409363</v>
       </c>
       <c r="R89" t="n">
-        <v>6782289</v>
+        <v>6782377</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10796,10 +10796,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129032401</v>
+        <v>129011377</v>
       </c>
       <c r="B102" t="n">
-        <v>91569</v>
+        <v>79044</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10807,19 +10807,23 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
@@ -10827,10 +10831,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>409226</v>
+        <v>408995</v>
       </c>
       <c r="R102" t="n">
-        <v>6782376</v>
+        <v>6782299</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10860,9 +10864,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10877,19 +10891,19 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129011377</v>
+        <v>129011402</v>
       </c>
       <c r="B103" t="n">
         <v>79044</v>
@@ -10924,10 +10938,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>408995</v>
+        <v>409671</v>
       </c>
       <c r="R103" t="n">
-        <v>6782299</v>
+        <v>6782390</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10959,7 +10973,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -10969,7 +10983,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10996,7 +11010,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129011402</v>
+        <v>129011385</v>
       </c>
       <c r="B104" t="n">
         <v>79044</v>
@@ -11031,10 +11045,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>409671</v>
+        <v>409214</v>
       </c>
       <c r="R104" t="n">
-        <v>6782390</v>
+        <v>6782345</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11066,7 +11080,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11076,7 +11090,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11103,7 +11117,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129011385</v>
+        <v>129032877</v>
       </c>
       <c r="B105" t="n">
         <v>79044</v>
@@ -11138,10 +11152,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>409214</v>
+        <v>408994</v>
       </c>
       <c r="R105" t="n">
-        <v>6782345</v>
+        <v>6782293</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11171,19 +11185,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z105" t="inlineStr">
-        <is>
-          <t>15:29</t>
-        </is>
-      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB105" t="inlineStr">
-        <is>
-          <t>15:29</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11198,19 +11202,19 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129032877</v>
+        <v>129032904</v>
       </c>
       <c r="B106" t="n">
         <v>79044</v>
@@ -11245,10 +11249,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>408994</v>
+        <v>409568</v>
       </c>
       <c r="R106" t="n">
-        <v>6782293</v>
+        <v>6782383</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11307,7 +11311,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129032904</v>
+        <v>129032915</v>
       </c>
       <c r="B107" t="n">
         <v>79044</v>
@@ -11342,10 +11346,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>409568</v>
+        <v>409765</v>
       </c>
       <c r="R107" t="n">
-        <v>6782383</v>
+        <v>6782330</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11404,10 +11408,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129032915</v>
+        <v>129032401</v>
       </c>
       <c r="B108" t="n">
-        <v>79044</v>
+        <v>91570</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11415,23 +11419,19 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr"/>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
@@ -11439,10 +11439,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>409765</v>
+        <v>409226</v>
       </c>
       <c r="R108" t="n">
-        <v>6782330</v>
+        <v>6782376</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11489,12 +11489,12 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>

--- a/artfynd/A 47938-2025 artfynd.xlsx
+++ b/artfynd/A 47938-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129032920</v>
+        <v>129032876</v>
       </c>
       <c r="B2" t="n">
         <v>79044</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>409793</v>
+        <v>408997</v>
       </c>
       <c r="R2" t="n">
-        <v>6782448</v>
+        <v>6782283</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129011405</v>
+        <v>129011403</v>
       </c>
       <c r="B3" t="n">
         <v>79044</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>409747</v>
+        <v>409706</v>
       </c>
       <c r="R3" t="n">
-        <v>6782328</v>
+        <v>6782359</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -842,7 +842,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -852,7 +852,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129032876</v>
+        <v>129032905</v>
       </c>
       <c r="B4" t="n">
         <v>79044</v>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>408997</v>
+        <v>409624</v>
       </c>
       <c r="R4" t="n">
-        <v>6782283</v>
+        <v>6782292</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,7 +976,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129011403</v>
+        <v>129032920</v>
       </c>
       <c r="B5" t="n">
         <v>79044</v>
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>409706</v>
+        <v>409793</v>
       </c>
       <c r="R5" t="n">
-        <v>6782359</v>
+        <v>6782448</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1044,19 +1044,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>12:06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,19 +1061,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129032905</v>
+        <v>129011405</v>
       </c>
       <c r="B6" t="n">
         <v>79044</v>
@@ -1118,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>409624</v>
+        <v>409747</v>
       </c>
       <c r="R6" t="n">
-        <v>6782292</v>
+        <v>6782328</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1151,9 +1141,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1168,22 +1168,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129032907</v>
+        <v>129032394</v>
       </c>
       <c r="B7" t="n">
-        <v>79044</v>
+        <v>79634</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>409686</v>
+        <v>409553</v>
       </c>
       <c r="R7" t="n">
-        <v>6782351</v>
+        <v>6782378</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1265,12 +1265,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1481,10 +1481,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129032394</v>
+        <v>129032907</v>
       </c>
       <c r="B10" t="n">
-        <v>79634</v>
+        <v>79044</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1492,21 +1492,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>409553</v>
+        <v>409686</v>
       </c>
       <c r="R10" t="n">
-        <v>6782378</v>
+        <v>6782351</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1566,22 +1566,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129011398</v>
+        <v>129032398</v>
       </c>
       <c r="B11" t="n">
-        <v>79044</v>
+        <v>91571</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1589,21 +1589,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1613,10 +1613,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>409596</v>
+        <v>409482</v>
       </c>
       <c r="R11" t="n">
-        <v>6782395</v>
+        <v>6782335</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1646,19 +1646,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>13:08</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>13:08</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1673,12 +1663,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1782,10 +1772,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129032398</v>
+        <v>129011398</v>
       </c>
       <c r="B13" t="n">
-        <v>91571</v>
+        <v>79044</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1793,21 +1783,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1817,10 +1807,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>409482</v>
+        <v>409596</v>
       </c>
       <c r="R13" t="n">
-        <v>6782335</v>
+        <v>6782395</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1850,9 +1840,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1867,22 +1867,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129032392</v>
+        <v>129011378</v>
       </c>
       <c r="B14" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1890,21 +1890,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1914,10 +1914,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>409554</v>
+        <v>408984</v>
       </c>
       <c r="R14" t="n">
-        <v>6782380</v>
+        <v>6782347</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1947,9 +1947,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1964,22 +1974,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129011378</v>
+        <v>129032392</v>
       </c>
       <c r="B15" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1987,21 +1997,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2011,10 +2021,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>408984</v>
+        <v>409554</v>
       </c>
       <c r="R15" t="n">
-        <v>6782347</v>
+        <v>6782380</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2044,19 +2054,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>16:10</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>16:10</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2071,19 +2071,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129032897</v>
+        <v>129032909</v>
       </c>
       <c r="B16" t="n">
         <v>79044</v>
@@ -2118,10 +2118,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>409469</v>
+        <v>409727</v>
       </c>
       <c r="R16" t="n">
-        <v>6782371</v>
+        <v>6782352</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2180,7 +2180,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129032909</v>
+        <v>129032897</v>
       </c>
       <c r="B17" t="n">
         <v>79044</v>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>409727</v>
+        <v>409469</v>
       </c>
       <c r="R17" t="n">
-        <v>6782352</v>
+        <v>6782371</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2277,10 +2277,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129032885</v>
+        <v>129011376</v>
       </c>
       <c r="B18" t="n">
-        <v>79044</v>
+        <v>91570</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2288,23 +2288,19 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2312,10 +2308,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>409078</v>
+        <v>409774</v>
       </c>
       <c r="R18" t="n">
-        <v>6782312</v>
+        <v>6782323</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2345,9 +2341,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2362,22 +2368,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129011400</v>
+        <v>129032868</v>
       </c>
       <c r="B19" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2385,21 +2391,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2409,10 +2415,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>409643</v>
+        <v>409688</v>
       </c>
       <c r="R19" t="n">
-        <v>6782378</v>
+        <v>6782303</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2442,19 +2448,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>12:59</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>12:59</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2469,19 +2465,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129032892</v>
+        <v>129032885</v>
       </c>
       <c r="B20" t="n">
         <v>79044</v>
@@ -2516,10 +2512,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>409244</v>
+        <v>409078</v>
       </c>
       <c r="R20" t="n">
-        <v>6782381</v>
+        <v>6782312</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2578,10 +2574,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129011376</v>
+        <v>129032892</v>
       </c>
       <c r="B21" t="n">
-        <v>91570</v>
+        <v>79044</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2589,19 +2585,23 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2609,10 +2609,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>409774</v>
+        <v>409244</v>
       </c>
       <c r="R21" t="n">
-        <v>6782323</v>
+        <v>6782381</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2642,19 +2642,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>11:31</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>11:31</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2669,22 +2659,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129032868</v>
+        <v>129011400</v>
       </c>
       <c r="B22" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2692,21 +2682,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2716,10 +2706,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>409688</v>
+        <v>409643</v>
       </c>
       <c r="R22" t="n">
-        <v>6782303</v>
+        <v>6782378</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2749,9 +2739,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2766,22 +2766,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129032399</v>
+        <v>129032395</v>
       </c>
       <c r="B23" t="n">
-        <v>91571</v>
+        <v>57727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2789,34 +2789,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>409492</v>
+        <v>409759</v>
       </c>
       <c r="R23" t="n">
-        <v>6782346</v>
+        <v>6782358</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2875,7 +2883,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129011374</v>
+        <v>129032399</v>
       </c>
       <c r="B24" t="n">
         <v>91571</v>
@@ -2903,24 +2911,17 @@
           <t>(Brot.) Murrill</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>409475</v>
+        <v>409492</v>
       </c>
       <c r="R24" t="n">
-        <v>6782341</v>
+        <v>6782346</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2950,55 +2951,39 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>13:57</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>13:57</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>hackspetthål under tickorna</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129011383</v>
+        <v>129011374</v>
       </c>
       <c r="B25" t="n">
-        <v>79044</v>
+        <v>91571</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3006,34 +2991,41 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>409028</v>
+        <v>409475</v>
       </c>
       <c r="R25" t="n">
-        <v>6782350</v>
+        <v>6782342</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3065,7 +3057,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3075,7 +3067,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>hackspetthål under tickorna</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3084,6 +3081,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3102,7 +3100,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129011395</v>
+        <v>129011407</v>
       </c>
       <c r="B26" t="n">
         <v>79044</v>
@@ -3137,10 +3135,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>409555</v>
+        <v>409795</v>
       </c>
       <c r="R26" t="n">
-        <v>6782356</v>
+        <v>6782327</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3172,7 +3170,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3182,7 +3180,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3209,7 +3207,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129011407</v>
+        <v>129011395</v>
       </c>
       <c r="B27" t="n">
         <v>79044</v>
@@ -3244,10 +3242,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>409795</v>
+        <v>409555</v>
       </c>
       <c r="R27" t="n">
-        <v>6782327</v>
+        <v>6782356</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3279,7 +3277,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3289,7 +3287,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3316,10 +3314,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129032395</v>
+        <v>129011383</v>
       </c>
       <c r="B28" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3327,42 +3325,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>409759</v>
+        <v>409028</v>
       </c>
       <c r="R28" t="n">
-        <v>6782358</v>
+        <v>6782350</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3392,9 +3382,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3409,12 +3409,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3518,10 +3518,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129032913</v>
+        <v>129011369</v>
       </c>
       <c r="B30" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3529,34 +3529,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>409757</v>
+        <v>409683</v>
       </c>
       <c r="R30" t="n">
-        <v>6782355</v>
+        <v>6782391</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3586,9 +3594,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3603,19 +3621,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129032406</v>
+        <v>129011391</v>
       </c>
       <c r="B31" t="n">
         <v>79044</v>
@@ -3650,10 +3668,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>409253</v>
+        <v>409349</v>
       </c>
       <c r="R31" t="n">
-        <v>6782372</v>
+        <v>6782383</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3683,9 +3701,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3700,19 +3728,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129032882</v>
+        <v>129032878</v>
       </c>
       <c r="B32" t="n">
         <v>79044</v>
@@ -3747,10 +3775,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>408992</v>
+        <v>408966</v>
       </c>
       <c r="R32" t="n">
-        <v>6782394</v>
+        <v>6782283</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3809,7 +3837,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129011391</v>
+        <v>129032913</v>
       </c>
       <c r="B33" t="n">
         <v>79044</v>
@@ -3844,10 +3872,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>409349</v>
+        <v>409757</v>
       </c>
       <c r="R33" t="n">
-        <v>6782383</v>
+        <v>6782355</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3877,19 +3905,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>14:34</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>14:34</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3904,19 +3922,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129032878</v>
+        <v>129032406</v>
       </c>
       <c r="B34" t="n">
         <v>79044</v>
@@ -3951,10 +3969,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>408966</v>
+        <v>409253</v>
       </c>
       <c r="R34" t="n">
-        <v>6782283</v>
+        <v>6782372</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4001,22 +4019,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129011369</v>
+        <v>129032882</v>
       </c>
       <c r="B35" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4024,42 +4042,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>409683</v>
+        <v>408992</v>
       </c>
       <c r="R35" t="n">
-        <v>6782391</v>
+        <v>6782394</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4089,19 +4099,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>12:56</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>12:56</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4116,19 +4116,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129032887</v>
+        <v>129011381</v>
       </c>
       <c r="B36" t="n">
         <v>79044</v>
@@ -4163,10 +4163,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>409176</v>
+        <v>409010</v>
       </c>
       <c r="R36" t="n">
-        <v>6782420</v>
+        <v>6782383</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4196,9 +4196,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4213,19 +4223,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129011381</v>
+        <v>129032887</v>
       </c>
       <c r="B37" t="n">
         <v>79044</v>
@@ -4260,10 +4270,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>409010</v>
+        <v>409176</v>
       </c>
       <c r="R37" t="n">
-        <v>6782383</v>
+        <v>6782420</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4293,19 +4303,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>16:06</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>16:06</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4320,19 +4320,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129032891</v>
+        <v>129011394</v>
       </c>
       <c r="B38" t="n">
         <v>79044</v>
@@ -4367,10 +4367,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>409241</v>
+        <v>409543</v>
       </c>
       <c r="R38" t="n">
-        <v>6782372</v>
+        <v>6782361</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4400,9 +4400,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4417,19 +4427,19 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129011392</v>
+        <v>129032910</v>
       </c>
       <c r="B39" t="n">
         <v>79044</v>
@@ -4464,10 +4474,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>409361</v>
+        <v>409744</v>
       </c>
       <c r="R39" t="n">
-        <v>6782401</v>
+        <v>6782394</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4497,19 +4507,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>14:31</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>14:31</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4524,19 +4524,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129032911</v>
+        <v>129032891</v>
       </c>
       <c r="B40" t="n">
         <v>79044</v>
@@ -4571,10 +4571,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>409777</v>
+        <v>409241</v>
       </c>
       <c r="R40" t="n">
-        <v>6782445</v>
+        <v>6782372</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4633,7 +4633,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129032906</v>
+        <v>129011399</v>
       </c>
       <c r="B41" t="n">
         <v>79044</v>
@@ -4668,10 +4668,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>409684</v>
+        <v>409609</v>
       </c>
       <c r="R41" t="n">
-        <v>6782322</v>
+        <v>6782404</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4701,9 +4701,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4718,19 +4728,19 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129032407</v>
+        <v>129032911</v>
       </c>
       <c r="B42" t="n">
         <v>79044</v>
@@ -4765,10 +4775,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>409659</v>
+        <v>409777</v>
       </c>
       <c r="R42" t="n">
-        <v>6782436</v>
+        <v>6782445</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4815,19 +4825,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129032910</v>
+        <v>129032407</v>
       </c>
       <c r="B43" t="n">
         <v>79044</v>
@@ -4862,10 +4872,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>409744</v>
+        <v>409659</v>
       </c>
       <c r="R43" t="n">
-        <v>6782394</v>
+        <v>6782436</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4912,19 +4922,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129011394</v>
+        <v>129011392</v>
       </c>
       <c r="B44" t="n">
         <v>79044</v>
@@ -4959,10 +4969,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>409543</v>
+        <v>409361</v>
       </c>
       <c r="R44" t="n">
-        <v>6782361</v>
+        <v>6782401</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4994,7 +5004,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5004,7 +5014,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5031,7 +5041,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129011399</v>
+        <v>129032906</v>
       </c>
       <c r="B45" t="n">
         <v>79044</v>
@@ -5066,10 +5076,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>409609</v>
+        <v>409684</v>
       </c>
       <c r="R45" t="n">
-        <v>6782404</v>
+        <v>6782322</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5099,19 +5109,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>13:06</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>13:06</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5126,22 +5126,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129011408</v>
+        <v>129032869</v>
       </c>
       <c r="B46" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5149,21 +5149,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5173,10 +5173,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>409801</v>
+        <v>409754</v>
       </c>
       <c r="R46" t="n">
-        <v>6782315</v>
+        <v>6782356</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5206,19 +5206,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>11:08</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>11:08</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5233,19 +5223,19 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129032883</v>
+        <v>129032884</v>
       </c>
       <c r="B47" t="n">
         <v>79044</v>
@@ -5280,10 +5270,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>409010</v>
+        <v>409039</v>
       </c>
       <c r="R47" t="n">
-        <v>6782399</v>
+        <v>6782290</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5342,7 +5332,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129011380</v>
+        <v>129032883</v>
       </c>
       <c r="B48" t="n">
         <v>79044</v>
@@ -5377,10 +5367,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>408984</v>
+        <v>409010</v>
       </c>
       <c r="R48" t="n">
-        <v>6782385</v>
+        <v>6782399</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5410,19 +5400,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>16:07</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>16:07</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5437,19 +5417,19 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129032884</v>
+        <v>129011408</v>
       </c>
       <c r="B49" t="n">
         <v>79044</v>
@@ -5484,10 +5464,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>409039</v>
+        <v>409801</v>
       </c>
       <c r="R49" t="n">
-        <v>6782290</v>
+        <v>6782315</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5517,9 +5497,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5534,22 +5524,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129032869</v>
+        <v>129011380</v>
       </c>
       <c r="B50" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5557,21 +5547,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5581,10 +5571,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>409754</v>
+        <v>408984</v>
       </c>
       <c r="R50" t="n">
-        <v>6782356</v>
+        <v>6782385</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5614,9 +5604,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5631,22 +5631,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129032866</v>
+        <v>129032899</v>
       </c>
       <c r="B51" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5654,21 +5654,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5678,10 +5678,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>409757</v>
+        <v>409397</v>
       </c>
       <c r="R51" t="n">
-        <v>6782386</v>
+        <v>6782272</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5740,7 +5740,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129011401</v>
+        <v>129011386</v>
       </c>
       <c r="B52" t="n">
         <v>79044</v>
@@ -5775,10 +5775,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>409663</v>
+        <v>409210</v>
       </c>
       <c r="R52" t="n">
-        <v>6782385</v>
+        <v>6782365</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5810,7 +5810,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5847,7 +5847,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129032899</v>
+        <v>129011396</v>
       </c>
       <c r="B53" t="n">
         <v>79044</v>
@@ -5882,10 +5882,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>409397</v>
+        <v>409584</v>
       </c>
       <c r="R53" t="n">
-        <v>6782272</v>
+        <v>6782395</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5915,9 +5915,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5932,19 +5942,19 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129011386</v>
+        <v>129011409</v>
       </c>
       <c r="B54" t="n">
         <v>79044</v>
@@ -5979,10 +5989,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>409210</v>
+        <v>409202</v>
       </c>
       <c r="R54" t="n">
-        <v>6782365</v>
+        <v>6782367</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6033,6 +6043,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6051,7 +6062,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129011409</v>
+        <v>129011401</v>
       </c>
       <c r="B55" t="n">
         <v>79044</v>
@@ -6086,10 +6097,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>409202</v>
+        <v>409663</v>
       </c>
       <c r="R55" t="n">
-        <v>6782367</v>
+        <v>6782385</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6121,7 +6132,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6131,7 +6142,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6140,7 +6151,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6159,10 +6169,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129011396</v>
+        <v>129032866</v>
       </c>
       <c r="B56" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6170,21 +6180,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6194,10 +6204,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>409584</v>
+        <v>409757</v>
       </c>
       <c r="R56" t="n">
-        <v>6782395</v>
+        <v>6782386</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6227,19 +6237,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>13:11</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>13:11</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6254,22 +6254,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129032889</v>
+        <v>129011373</v>
       </c>
       <c r="B57" t="n">
-        <v>79044</v>
+        <v>91571</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6277,34 +6277,41 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>409164</v>
+        <v>409435</v>
       </c>
       <c r="R57" t="n">
-        <v>6782308</v>
+        <v>6782383</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6334,39 +6341,55 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>4 st på samma tall</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129032403</v>
+        <v>129011372</v>
       </c>
       <c r="B58" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6374,34 +6397,42 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>409021</v>
+        <v>409796</v>
       </c>
       <c r="R58" t="n">
-        <v>6782365</v>
+        <v>6782327</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6431,9 +6462,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6448,22 +6489,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129011372</v>
+        <v>129032889</v>
       </c>
       <c r="B59" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6471,42 +6512,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>409796</v>
+        <v>409164</v>
       </c>
       <c r="R59" t="n">
-        <v>6782327</v>
+        <v>6782308</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6536,19 +6569,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>11:10</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6563,22 +6586,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129011373</v>
+        <v>129032403</v>
       </c>
       <c r="B60" t="n">
-        <v>91571</v>
+        <v>79044</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6586,41 +6609,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>409435</v>
+        <v>409021</v>
       </c>
       <c r="R60" t="n">
-        <v>6782383</v>
+        <v>6782365</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6650,45 +6666,29 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>4 st på samma tall</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -6992,10 +6992,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129011387</v>
+        <v>129032396</v>
       </c>
       <c r="B64" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7003,34 +7003,42 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>409232</v>
+        <v>409753</v>
       </c>
       <c r="R64" t="n">
-        <v>6782353</v>
+        <v>6782323</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7060,19 +7068,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>15:22</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>15:22</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7087,22 +7085,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129032886</v>
+        <v>129032867</v>
       </c>
       <c r="B65" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7110,21 +7108,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7134,10 +7132,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>409108</v>
+        <v>409693</v>
       </c>
       <c r="R65" t="n">
-        <v>6782395</v>
+        <v>6782357</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7196,7 +7194,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129011384</v>
+        <v>129032914</v>
       </c>
       <c r="B66" t="n">
         <v>79044</v>
@@ -7231,10 +7229,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>409068</v>
+        <v>409759</v>
       </c>
       <c r="R66" t="n">
-        <v>6782377</v>
+        <v>6782343</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7264,19 +7262,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>15:43</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>15:43</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7291,22 +7279,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129011379</v>
+        <v>129032872</v>
       </c>
       <c r="B67" t="n">
-        <v>79044</v>
+        <v>78801</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7314,21 +7302,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7338,10 +7326,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>408991</v>
+        <v>409594</v>
       </c>
       <c r="R67" t="n">
-        <v>6782360</v>
+        <v>6782294</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7371,19 +7359,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>16:09</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>16:09</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7398,19 +7376,19 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129032914</v>
+        <v>129011379</v>
       </c>
       <c r="B68" t="n">
         <v>79044</v>
@@ -7445,10 +7423,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>409759</v>
+        <v>408991</v>
       </c>
       <c r="R68" t="n">
-        <v>6782343</v>
+        <v>6782360</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7478,9 +7456,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7495,22 +7483,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129032872</v>
+        <v>129011387</v>
       </c>
       <c r="B69" t="n">
-        <v>78801</v>
+        <v>79044</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7518,21 +7506,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7542,10 +7530,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>409594</v>
+        <v>409232</v>
       </c>
       <c r="R69" t="n">
-        <v>6782294</v>
+        <v>6782353</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7575,9 +7563,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7592,22 +7590,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129032396</v>
+        <v>129032886</v>
       </c>
       <c r="B70" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7615,42 +7613,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>409753</v>
+        <v>409108</v>
       </c>
       <c r="R70" t="n">
-        <v>6782323</v>
+        <v>6782395</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7697,22 +7687,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129032867</v>
+        <v>129011384</v>
       </c>
       <c r="B71" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7720,21 +7710,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7744,10 +7734,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>409693</v>
+        <v>409068</v>
       </c>
       <c r="R71" t="n">
-        <v>6782357</v>
+        <v>6782377</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7777,9 +7767,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7794,22 +7794,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129032873</v>
+        <v>129032900</v>
       </c>
       <c r="B72" t="n">
-        <v>91550</v>
+        <v>79044</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7817,37 +7817,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>409075</v>
+        <v>409449</v>
       </c>
       <c r="R72" t="n">
-        <v>6782317</v>
+        <v>6782286</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7888,7 +7885,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -7907,7 +7903,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129032896</v>
+        <v>129032917</v>
       </c>
       <c r="B73" t="n">
         <v>79044</v>
@@ -7942,10 +7938,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>409331</v>
+        <v>409360</v>
       </c>
       <c r="R73" t="n">
-        <v>6782342</v>
+        <v>6782355</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8101,7 +8097,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129032917</v>
+        <v>129032896</v>
       </c>
       <c r="B75" t="n">
         <v>79044</v>
@@ -8136,10 +8132,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>409360</v>
+        <v>409331</v>
       </c>
       <c r="R75" t="n">
-        <v>6782355</v>
+        <v>6782342</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8198,10 +8194,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129032900</v>
+        <v>129032873</v>
       </c>
       <c r="B76" t="n">
-        <v>79044</v>
+        <v>91550</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8209,34 +8205,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>409449</v>
+        <v>409075</v>
       </c>
       <c r="R76" t="n">
-        <v>6782286</v>
+        <v>6782317</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8277,6 +8276,7 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8388,7 +8388,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129032893</v>
+        <v>129011404</v>
       </c>
       <c r="B78" t="n">
         <v>79044</v>
@@ -8423,10 +8423,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>409280</v>
+        <v>409736</v>
       </c>
       <c r="R78" t="n">
-        <v>6782382</v>
+        <v>6782394</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8456,9 +8456,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8473,19 +8483,19 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129011404</v>
+        <v>129032901</v>
       </c>
       <c r="B79" t="n">
         <v>79044</v>
@@ -8520,10 +8530,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>409736</v>
+        <v>409528</v>
       </c>
       <c r="R79" t="n">
-        <v>6782394</v>
+        <v>6782292</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8553,19 +8563,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>11:59</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>11:59</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8580,19 +8580,19 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129032901</v>
+        <v>129032888</v>
       </c>
       <c r="B80" t="n">
         <v>79044</v>
@@ -8627,10 +8627,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>409528</v>
+        <v>409127</v>
       </c>
       <c r="R80" t="n">
-        <v>6782292</v>
+        <v>6782290</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8689,7 +8689,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129032888</v>
+        <v>129032893</v>
       </c>
       <c r="B81" t="n">
         <v>79044</v>
@@ -8724,10 +8724,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>409127</v>
+        <v>409280</v>
       </c>
       <c r="R81" t="n">
-        <v>6782290</v>
+        <v>6782382</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8980,7 +8980,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129032409</v>
+        <v>129032916</v>
       </c>
       <c r="B84" t="n">
         <v>79044</v>
@@ -9015,10 +9015,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>409782</v>
+        <v>409812</v>
       </c>
       <c r="R84" t="n">
-        <v>6782339</v>
+        <v>6782309</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9065,19 +9065,19 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129032916</v>
+        <v>129032409</v>
       </c>
       <c r="B85" t="n">
         <v>79044</v>
@@ -9112,10 +9112,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>409812</v>
+        <v>409782</v>
       </c>
       <c r="R85" t="n">
-        <v>6782309</v>
+        <v>6782339</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9162,22 +9162,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129032870</v>
+        <v>129011370</v>
       </c>
       <c r="B86" t="n">
-        <v>91571</v>
+        <v>57727</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9185,34 +9185,31 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
@@ -9220,10 +9217,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>409530</v>
+        <v>409759</v>
       </c>
       <c r="R86" t="n">
-        <v>6782289</v>
+        <v>6782330</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9253,40 +9250,49 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129011370</v>
+        <v>129032918</v>
       </c>
       <c r="B87" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9294,42 +9300,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>409759</v>
+        <v>409363</v>
       </c>
       <c r="R87" t="n">
-        <v>6782330</v>
+        <v>6782377</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9359,19 +9357,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>11:48</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9386,12 +9374,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
@@ -9495,10 +9483,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129032918</v>
+        <v>129032870</v>
       </c>
       <c r="B89" t="n">
-        <v>79044</v>
+        <v>91571</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9506,34 +9494,45 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>409363</v>
+        <v>409530</v>
       </c>
       <c r="R89" t="n">
-        <v>6782377</v>
+        <v>6782289</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9574,6 +9573,7 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -9592,7 +9592,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129011393</v>
+        <v>129032895</v>
       </c>
       <c r="B90" t="n">
         <v>79044</v>
@@ -9627,10 +9627,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>409472</v>
+        <v>409310</v>
       </c>
       <c r="R90" t="n">
-        <v>6782351</v>
+        <v>6782326</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9660,19 +9660,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>14:05</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>14:05</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9687,19 +9677,19 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129032895</v>
+        <v>129032405</v>
       </c>
       <c r="B91" t="n">
         <v>79044</v>
@@ -9734,10 +9724,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>409310</v>
+        <v>409048</v>
       </c>
       <c r="R91" t="n">
-        <v>6782326</v>
+        <v>6782365</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9784,19 +9774,19 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129032903</v>
+        <v>129032880</v>
       </c>
       <c r="B92" t="n">
         <v>79044</v>
@@ -9831,10 +9821,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>409582</v>
+        <v>408901</v>
       </c>
       <c r="R92" t="n">
-        <v>6782297</v>
+        <v>6782390</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9893,7 +9883,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129032880</v>
+        <v>129011393</v>
       </c>
       <c r="B93" t="n">
         <v>79044</v>
@@ -9928,10 +9918,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>408901</v>
+        <v>409472</v>
       </c>
       <c r="R93" t="n">
-        <v>6782390</v>
+        <v>6782351</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9961,9 +9951,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -9978,19 +9978,19 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129032405</v>
+        <v>129032903</v>
       </c>
       <c r="B94" t="n">
         <v>79044</v>
@@ -10025,10 +10025,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>409048</v>
+        <v>409582</v>
       </c>
       <c r="R94" t="n">
-        <v>6782365</v>
+        <v>6782297</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10075,19 +10075,19 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129011388</v>
+        <v>129032408</v>
       </c>
       <c r="B95" t="n">
         <v>79044</v>
@@ -10122,10 +10122,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>409250</v>
+        <v>409749</v>
       </c>
       <c r="R95" t="n">
-        <v>6782354</v>
+        <v>6782325</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10155,19 +10155,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z95" t="inlineStr">
-        <is>
-          <t>15:19</t>
-        </is>
-      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB95" t="inlineStr">
-        <is>
-          <t>15:19</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10182,19 +10172,19 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129011406</v>
+        <v>129032890</v>
       </c>
       <c r="B96" t="n">
         <v>79044</v>
@@ -10229,10 +10219,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>409759</v>
+        <v>409228</v>
       </c>
       <c r="R96" t="n">
-        <v>6782314</v>
+        <v>6782298</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10262,19 +10252,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z96" t="inlineStr">
-        <is>
-          <t>11:41</t>
-        </is>
-      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB96" t="inlineStr">
-        <is>
-          <t>11:41</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10289,19 +10269,19 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129032408</v>
+        <v>129032875</v>
       </c>
       <c r="B97" t="n">
         <v>79044</v>
@@ -10336,10 +10316,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>409749</v>
+        <v>409034</v>
       </c>
       <c r="R97" t="n">
-        <v>6782325</v>
+        <v>6782261</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10386,12 +10366,12 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
@@ -10495,7 +10475,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129032890</v>
+        <v>129011406</v>
       </c>
       <c r="B99" t="n">
         <v>79044</v>
@@ -10530,10 +10510,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>409228</v>
+        <v>409759</v>
       </c>
       <c r="R99" t="n">
-        <v>6782298</v>
+        <v>6782314</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10563,9 +10543,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10580,19 +10570,19 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129032875</v>
+        <v>129011388</v>
       </c>
       <c r="B100" t="n">
         <v>79044</v>
@@ -10627,10 +10617,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>409034</v>
+        <v>409250</v>
       </c>
       <c r="R100" t="n">
-        <v>6782261</v>
+        <v>6782354</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10660,9 +10650,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10677,12 +10677,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
@@ -10796,7 +10796,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129011377</v>
+        <v>129011385</v>
       </c>
       <c r="B102" t="n">
         <v>79044</v>
@@ -10831,10 +10831,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>408995</v>
+        <v>409214</v>
       </c>
       <c r="R102" t="n">
-        <v>6782299</v>
+        <v>6782345</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10866,7 +10866,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -10876,7 +10876,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10903,7 +10903,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129011402</v>
+        <v>129011377</v>
       </c>
       <c r="B103" t="n">
         <v>79044</v>
@@ -10938,10 +10938,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>409671</v>
+        <v>408995</v>
       </c>
       <c r="R103" t="n">
-        <v>6782390</v>
+        <v>6782299</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10973,7 +10973,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -10983,7 +10983,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11010,7 +11010,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129011385</v>
+        <v>129032915</v>
       </c>
       <c r="B104" t="n">
         <v>79044</v>
@@ -11045,10 +11045,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>409214</v>
+        <v>409765</v>
       </c>
       <c r="R104" t="n">
-        <v>6782345</v>
+        <v>6782330</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11078,19 +11078,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z104" t="inlineStr">
-        <is>
-          <t>15:29</t>
-        </is>
-      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB104" t="inlineStr">
-        <is>
-          <t>15:29</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11105,19 +11095,19 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129032877</v>
+        <v>129032904</v>
       </c>
       <c r="B105" t="n">
         <v>79044</v>
@@ -11152,10 +11142,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>408994</v>
+        <v>409568</v>
       </c>
       <c r="R105" t="n">
-        <v>6782293</v>
+        <v>6782383</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11214,7 +11204,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129032904</v>
+        <v>129011402</v>
       </c>
       <c r="B106" t="n">
         <v>79044</v>
@@ -11249,10 +11239,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>409568</v>
+        <v>409671</v>
       </c>
       <c r="R106" t="n">
-        <v>6782383</v>
+        <v>6782390</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11282,9 +11272,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11299,19 +11299,19 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129032915</v>
+        <v>129032877</v>
       </c>
       <c r="B107" t="n">
         <v>79044</v>
@@ -11346,10 +11346,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>409765</v>
+        <v>408994</v>
       </c>
       <c r="R107" t="n">
-        <v>6782330</v>
+        <v>6782293</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>

--- a/artfynd/A 47938-2025 artfynd.xlsx
+++ b/artfynd/A 47938-2025 artfynd.xlsx
@@ -2277,10 +2277,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129011376</v>
+        <v>129032868</v>
       </c>
       <c r="B18" t="n">
-        <v>91570</v>
+        <v>57727</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2288,19 +2288,23 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2308,10 +2312,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>409774</v>
+        <v>409688</v>
       </c>
       <c r="R18" t="n">
-        <v>6782323</v>
+        <v>6782303</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2341,19 +2345,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>11:31</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>11:31</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2368,22 +2362,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129032868</v>
+        <v>129032885</v>
       </c>
       <c r="B19" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2391,21 +2385,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2415,10 +2409,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>409688</v>
+        <v>409078</v>
       </c>
       <c r="R19" t="n">
-        <v>6782303</v>
+        <v>6782312</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2477,7 +2471,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129032885</v>
+        <v>129032892</v>
       </c>
       <c r="B20" t="n">
         <v>79044</v>
@@ -2512,10 +2506,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>409078</v>
+        <v>409244</v>
       </c>
       <c r="R20" t="n">
-        <v>6782312</v>
+        <v>6782381</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2574,7 +2568,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129032892</v>
+        <v>129011400</v>
       </c>
       <c r="B21" t="n">
         <v>79044</v>
@@ -2609,10 +2603,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>409244</v>
+        <v>409643</v>
       </c>
       <c r="R21" t="n">
-        <v>6782381</v>
+        <v>6782378</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2642,9 +2636,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2659,22 +2663,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129011400</v>
+        <v>129011376</v>
       </c>
       <c r="B22" t="n">
-        <v>79044</v>
+        <v>91570</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2682,23 +2686,19 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2706,10 +2706,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>409643</v>
+        <v>409774</v>
       </c>
       <c r="R22" t="n">
-        <v>6782378</v>
+        <v>6782323</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2741,7 +2741,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2751,7 +2751,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -6802,45 +6802,53 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129032400</v>
+        <v>129032396</v>
       </c>
       <c r="B62" t="n">
-        <v>92003</v>
+        <v>57727</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>409738</v>
+        <v>409753</v>
       </c>
       <c r="R62" t="n">
-        <v>6782382</v>
+        <v>6782323</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6899,10 +6907,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129032874</v>
+        <v>129032867</v>
       </c>
       <c r="B63" t="n">
-        <v>91570</v>
+        <v>57727</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6910,19 +6918,23 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -6930,10 +6942,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>409405</v>
+        <v>409693</v>
       </c>
       <c r="R63" t="n">
-        <v>6782366</v>
+        <v>6782357</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6992,10 +7004,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129032396</v>
+        <v>129032914</v>
       </c>
       <c r="B64" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7003,42 +7015,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>409753</v>
+        <v>409759</v>
       </c>
       <c r="R64" t="n">
-        <v>6782323</v>
+        <v>6782343</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7085,22 +7089,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129032867</v>
+        <v>129032872</v>
       </c>
       <c r="B65" t="n">
-        <v>57727</v>
+        <v>78801</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7108,21 +7112,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7132,10 +7136,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>409693</v>
+        <v>409594</v>
       </c>
       <c r="R65" t="n">
-        <v>6782357</v>
+        <v>6782294</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7194,7 +7198,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129032914</v>
+        <v>129011379</v>
       </c>
       <c r="B66" t="n">
         <v>79044</v>
@@ -7229,10 +7233,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>409759</v>
+        <v>408991</v>
       </c>
       <c r="R66" t="n">
-        <v>6782343</v>
+        <v>6782360</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7262,9 +7266,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7279,22 +7293,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129032872</v>
+        <v>129011387</v>
       </c>
       <c r="B67" t="n">
-        <v>78801</v>
+        <v>79044</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7302,21 +7316,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7326,10 +7340,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>409594</v>
+        <v>409232</v>
       </c>
       <c r="R67" t="n">
-        <v>6782294</v>
+        <v>6782353</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7359,9 +7373,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7376,19 +7400,19 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129011379</v>
+        <v>129032886</v>
       </c>
       <c r="B68" t="n">
         <v>79044</v>
@@ -7423,10 +7447,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>408991</v>
+        <v>409108</v>
       </c>
       <c r="R68" t="n">
-        <v>6782360</v>
+        <v>6782395</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7456,19 +7480,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>16:09</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>16:09</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7483,19 +7497,19 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129011387</v>
+        <v>129011384</v>
       </c>
       <c r="B69" t="n">
         <v>79044</v>
@@ -7530,10 +7544,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>409232</v>
+        <v>409068</v>
       </c>
       <c r="R69" t="n">
-        <v>6782353</v>
+        <v>6782377</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7565,7 +7579,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7575,7 +7589,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7602,32 +7616,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129032886</v>
+        <v>129032400</v>
       </c>
       <c r="B70" t="n">
-        <v>79044</v>
+        <v>92003</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7637,10 +7651,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>409108</v>
+        <v>409738</v>
       </c>
       <c r="R70" t="n">
-        <v>6782395</v>
+        <v>6782382</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7687,22 +7701,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129011384</v>
+        <v>129032874</v>
       </c>
       <c r="B71" t="n">
-        <v>79044</v>
+        <v>91570</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7710,23 +7724,19 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -7734,10 +7744,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>409068</v>
+        <v>409405</v>
       </c>
       <c r="R71" t="n">
-        <v>6782377</v>
+        <v>6782366</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7767,19 +7777,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>15:43</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>15:43</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7794,12 +7794,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -9174,10 +9174,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129011370</v>
+        <v>129032870</v>
       </c>
       <c r="B86" t="n">
-        <v>57727</v>
+        <v>91571</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9185,31 +9185,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
@@ -9217,10 +9220,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>409759</v>
+        <v>409530</v>
       </c>
       <c r="R86" t="n">
-        <v>6782330</v>
+        <v>6782289</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9250,49 +9253,40 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129032918</v>
+        <v>129011370</v>
       </c>
       <c r="B87" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9300,34 +9294,42 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>409363</v>
+        <v>409759</v>
       </c>
       <c r="R87" t="n">
-        <v>6782377</v>
+        <v>6782330</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9357,9 +9359,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9374,19 +9386,19 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129032898</v>
+        <v>129032918</v>
       </c>
       <c r="B88" t="n">
         <v>79044</v>
@@ -9421,10 +9433,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>409390</v>
+        <v>409363</v>
       </c>
       <c r="R88" t="n">
-        <v>6782289</v>
+        <v>6782377</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9483,10 +9495,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129032870</v>
+        <v>129032898</v>
       </c>
       <c r="B89" t="n">
-        <v>91571</v>
+        <v>79044</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9494,42 +9506,31 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>409530</v>
+        <v>409390</v>
       </c>
       <c r="R89" t="n">
         <v>6782289</v>
@@ -9573,7 +9574,6 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 47938-2025 artfynd.xlsx
+++ b/artfynd/A 47938-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129032876</v>
+        <v>129032920</v>
       </c>
       <c r="B2" t="n">
         <v>79044</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>408997</v>
+        <v>409793</v>
       </c>
       <c r="R2" t="n">
-        <v>6782283</v>
+        <v>6782448</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129011403</v>
+        <v>129032905</v>
       </c>
       <c r="B3" t="n">
         <v>79044</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>409706</v>
+        <v>409624</v>
       </c>
       <c r="R3" t="n">
-        <v>6782359</v>
+        <v>6782292</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -840,19 +840,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,19 +857,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129032905</v>
+        <v>129011405</v>
       </c>
       <c r="B4" t="n">
         <v>79044</v>
@@ -914,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>409624</v>
+        <v>409747</v>
       </c>
       <c r="R4" t="n">
-        <v>6782292</v>
+        <v>6782328</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -947,9 +937,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -964,19 +964,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129032920</v>
+        <v>129032876</v>
       </c>
       <c r="B5" t="n">
         <v>79044</v>
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>409793</v>
+        <v>408997</v>
       </c>
       <c r="R5" t="n">
-        <v>6782448</v>
+        <v>6782283</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1073,7 +1073,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129011405</v>
+        <v>129011403</v>
       </c>
       <c r="B6" t="n">
         <v>79044</v>
@@ -1108,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>409747</v>
+        <v>409706</v>
       </c>
       <c r="R6" t="n">
-        <v>6782328</v>
+        <v>6782359</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1180,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129032394</v>
+        <v>129032919</v>
       </c>
       <c r="B7" t="n">
-        <v>79634</v>
+        <v>79044</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,21 +1191,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>409553</v>
+        <v>409358</v>
       </c>
       <c r="R7" t="n">
-        <v>6782378</v>
+        <v>6782291</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1265,19 +1265,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129011389</v>
+        <v>129032907</v>
       </c>
       <c r="B8" t="n">
         <v>79044</v>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>409278</v>
+        <v>409686</v>
       </c>
       <c r="R8" t="n">
-        <v>6782361</v>
+        <v>6782351</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1345,19 +1345,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>15:18</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>15:18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1372,19 +1362,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129032919</v>
+        <v>129011389</v>
       </c>
       <c r="B9" t="n">
         <v>79044</v>
@@ -1419,10 +1409,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>409358</v>
+        <v>409278</v>
       </c>
       <c r="R9" t="n">
-        <v>6782291</v>
+        <v>6782361</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1452,9 +1442,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1469,22 +1469,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129032907</v>
+        <v>129032394</v>
       </c>
       <c r="B10" t="n">
-        <v>79044</v>
+        <v>79634</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1492,21 +1492,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>409686</v>
+        <v>409553</v>
       </c>
       <c r="R10" t="n">
-        <v>6782351</v>
+        <v>6782378</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1566,12 +1566,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1581,7 +1581,7 @@
         <v>129032398</v>
       </c>
       <c r="B11" t="n">
-        <v>91571</v>
+        <v>91574</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129032894</v>
+        <v>129011398</v>
       </c>
       <c r="B12" t="n">
         <v>79044</v>
@@ -1710,10 +1710,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>409292</v>
+        <v>409596</v>
       </c>
       <c r="R12" t="n">
-        <v>6782306</v>
+        <v>6782395</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1743,9 +1743,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1760,19 +1770,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129011398</v>
+        <v>129032894</v>
       </c>
       <c r="B13" t="n">
         <v>79044</v>
@@ -1807,10 +1817,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>409596</v>
+        <v>409292</v>
       </c>
       <c r="R13" t="n">
-        <v>6782395</v>
+        <v>6782306</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1840,19 +1850,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>13:08</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>13:08</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1867,19 +1867,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129011378</v>
+        <v>129032909</v>
       </c>
       <c r="B14" t="n">
         <v>79044</v>
@@ -1914,10 +1914,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>408984</v>
+        <v>409727</v>
       </c>
       <c r="R14" t="n">
-        <v>6782347</v>
+        <v>6782352</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1947,19 +1947,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>16:10</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>16:10</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1974,12 +1964,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2083,7 +2073,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129032909</v>
+        <v>129011378</v>
       </c>
       <c r="B16" t="n">
         <v>79044</v>
@@ -2118,10 +2108,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>409727</v>
+        <v>408984</v>
       </c>
       <c r="R16" t="n">
-        <v>6782352</v>
+        <v>6782347</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2151,9 +2141,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2168,12 +2168,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2277,10 +2277,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129032868</v>
+        <v>129011376</v>
       </c>
       <c r="B18" t="n">
-        <v>57727</v>
+        <v>91573</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2288,23 +2288,19 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2312,10 +2308,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>409688</v>
+        <v>409774</v>
       </c>
       <c r="R18" t="n">
-        <v>6782303</v>
+        <v>6782323</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2345,9 +2341,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2362,12 +2368,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2471,7 +2477,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129032892</v>
+        <v>129011400</v>
       </c>
       <c r="B20" t="n">
         <v>79044</v>
@@ -2506,10 +2512,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>409244</v>
+        <v>409643</v>
       </c>
       <c r="R20" t="n">
-        <v>6782381</v>
+        <v>6782378</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2539,9 +2545,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2556,19 +2572,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129011400</v>
+        <v>129032892</v>
       </c>
       <c r="B21" t="n">
         <v>79044</v>
@@ -2603,10 +2619,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>409643</v>
+        <v>409244</v>
       </c>
       <c r="R21" t="n">
-        <v>6782378</v>
+        <v>6782381</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2636,19 +2652,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>12:59</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>12:59</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2663,22 +2669,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129011376</v>
+        <v>129032868</v>
       </c>
       <c r="B22" t="n">
-        <v>91570</v>
+        <v>57727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2686,19 +2692,23 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2706,10 +2716,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>409774</v>
+        <v>409688</v>
       </c>
       <c r="R22" t="n">
-        <v>6782323</v>
+        <v>6782303</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2739,19 +2749,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>11:31</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>11:31</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2766,22 +2766,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129032395</v>
+        <v>129032399</v>
       </c>
       <c r="B23" t="n">
-        <v>57727</v>
+        <v>91574</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2789,42 +2789,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>409759</v>
+        <v>409492</v>
       </c>
       <c r="R23" t="n">
-        <v>6782358</v>
+        <v>6782346</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2883,10 +2875,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129032399</v>
+        <v>129011374</v>
       </c>
       <c r="B24" t="n">
-        <v>91571</v>
+        <v>91574</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2911,17 +2903,24 @@
           <t>(Brot.) Murrill</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>409492</v>
+        <v>409475</v>
       </c>
       <c r="R24" t="n">
-        <v>6782346</v>
+        <v>6782342</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2951,39 +2950,55 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>hackspetthål under tickorna</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129011374</v>
+        <v>129011383</v>
       </c>
       <c r="B25" t="n">
-        <v>91571</v>
+        <v>79044</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2991,41 +3006,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>409475</v>
+        <v>409028</v>
       </c>
       <c r="R25" t="n">
-        <v>6782342</v>
+        <v>6782350</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3057,7 +3065,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3067,12 +3075,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:57</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>hackspetthål under tickorna</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3081,7 +3084,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3100,7 +3102,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129011407</v>
+        <v>129011395</v>
       </c>
       <c r="B26" t="n">
         <v>79044</v>
@@ -3135,10 +3137,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>409795</v>
+        <v>409555</v>
       </c>
       <c r="R26" t="n">
-        <v>6782327</v>
+        <v>6782356</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3170,7 +3172,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3180,7 +3182,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3207,7 +3209,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129011395</v>
+        <v>129011407</v>
       </c>
       <c r="B27" t="n">
         <v>79044</v>
@@ -3242,10 +3244,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>409555</v>
+        <v>409795</v>
       </c>
       <c r="R27" t="n">
-        <v>6782356</v>
+        <v>6782327</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3277,7 +3279,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3287,7 +3289,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3314,10 +3316,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129011383</v>
+        <v>129032393</v>
       </c>
       <c r="B28" t="n">
-        <v>79044</v>
+        <v>79634</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3325,21 +3327,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3349,10 +3351,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>409028</v>
+        <v>409554</v>
       </c>
       <c r="R28" t="n">
-        <v>6782350</v>
+        <v>6782380</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3382,19 +3384,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>16:04</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>16:04</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3409,22 +3401,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129032393</v>
+        <v>129032395</v>
       </c>
       <c r="B29" t="n">
-        <v>79634</v>
+        <v>57727</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3432,34 +3424,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>409554</v>
+        <v>409759</v>
       </c>
       <c r="R29" t="n">
-        <v>6782380</v>
+        <v>6782358</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3518,10 +3518,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129011369</v>
+        <v>129032913</v>
       </c>
       <c r="B30" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3529,42 +3529,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>409683</v>
+        <v>409757</v>
       </c>
       <c r="R30" t="n">
-        <v>6782391</v>
+        <v>6782355</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3594,19 +3586,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>12:56</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>12:56</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3621,19 +3603,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129011391</v>
+        <v>129032406</v>
       </c>
       <c r="B31" t="n">
         <v>79044</v>
@@ -3668,10 +3650,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>409349</v>
+        <v>409253</v>
       </c>
       <c r="R31" t="n">
-        <v>6782383</v>
+        <v>6782372</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3701,19 +3683,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>14:34</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>14:34</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3728,19 +3700,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129032878</v>
+        <v>129011391</v>
       </c>
       <c r="B32" t="n">
         <v>79044</v>
@@ -3775,10 +3747,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>408966</v>
+        <v>409349</v>
       </c>
       <c r="R32" t="n">
-        <v>6782283</v>
+        <v>6782383</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3808,9 +3780,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3825,22 +3807,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129032913</v>
+        <v>129011369</v>
       </c>
       <c r="B33" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3848,34 +3830,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>409757</v>
+        <v>409683</v>
       </c>
       <c r="R33" t="n">
-        <v>6782355</v>
+        <v>6782391</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3905,9 +3895,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3922,19 +3922,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129032406</v>
+        <v>129032882</v>
       </c>
       <c r="B34" t="n">
         <v>79044</v>
@@ -3969,10 +3969,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>409253</v>
+        <v>408992</v>
       </c>
       <c r="R34" t="n">
-        <v>6782372</v>
+        <v>6782394</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4019,19 +4019,19 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129032882</v>
+        <v>129032878</v>
       </c>
       <c r="B35" t="n">
         <v>79044</v>
@@ -4066,10 +4066,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>408992</v>
+        <v>408966</v>
       </c>
       <c r="R35" t="n">
-        <v>6782394</v>
+        <v>6782283</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4332,7 +4332,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129011394</v>
+        <v>129011392</v>
       </c>
       <c r="B38" t="n">
         <v>79044</v>
@@ -4367,10 +4367,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>409543</v>
+        <v>409361</v>
       </c>
       <c r="R38" t="n">
-        <v>6782361</v>
+        <v>6782401</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4402,7 +4402,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4439,7 +4439,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129032910</v>
+        <v>129032906</v>
       </c>
       <c r="B39" t="n">
         <v>79044</v>
@@ -4474,10 +4474,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>409744</v>
+        <v>409684</v>
       </c>
       <c r="R39" t="n">
-        <v>6782394</v>
+        <v>6782322</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4536,7 +4536,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129032891</v>
+        <v>129032407</v>
       </c>
       <c r="B40" t="n">
         <v>79044</v>
@@ -4571,10 +4571,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>409241</v>
+        <v>409659</v>
       </c>
       <c r="R40" t="n">
-        <v>6782372</v>
+        <v>6782436</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4621,19 +4621,19 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129011399</v>
+        <v>129011394</v>
       </c>
       <c r="B41" t="n">
         <v>79044</v>
@@ -4668,10 +4668,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>409609</v>
+        <v>409543</v>
       </c>
       <c r="R41" t="n">
-        <v>6782404</v>
+        <v>6782361</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4703,7 +4703,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4713,7 +4713,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4740,7 +4740,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129032911</v>
+        <v>129011399</v>
       </c>
       <c r="B42" t="n">
         <v>79044</v>
@@ -4775,10 +4775,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>409777</v>
+        <v>409609</v>
       </c>
       <c r="R42" t="n">
-        <v>6782445</v>
+        <v>6782404</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4808,9 +4808,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4825,19 +4835,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129032407</v>
+        <v>129032891</v>
       </c>
       <c r="B43" t="n">
         <v>79044</v>
@@ -4872,10 +4882,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>409659</v>
+        <v>409241</v>
       </c>
       <c r="R43" t="n">
-        <v>6782436</v>
+        <v>6782372</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4922,19 +4932,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129011392</v>
+        <v>129032911</v>
       </c>
       <c r="B44" t="n">
         <v>79044</v>
@@ -4969,10 +4979,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>409361</v>
+        <v>409777</v>
       </c>
       <c r="R44" t="n">
-        <v>6782401</v>
+        <v>6782445</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5002,19 +5012,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>14:31</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>14:31</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5029,19 +5029,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129032906</v>
+        <v>129032910</v>
       </c>
       <c r="B45" t="n">
         <v>79044</v>
@@ -5076,10 +5076,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>409684</v>
+        <v>409744</v>
       </c>
       <c r="R45" t="n">
-        <v>6782322</v>
+        <v>6782394</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5138,10 +5138,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129032869</v>
+        <v>129011408</v>
       </c>
       <c r="B46" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5149,21 +5149,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5173,10 +5173,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>409754</v>
+        <v>409801</v>
       </c>
       <c r="R46" t="n">
-        <v>6782356</v>
+        <v>6782315</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5206,9 +5206,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5223,19 +5233,19 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129032884</v>
+        <v>129011380</v>
       </c>
       <c r="B47" t="n">
         <v>79044</v>
@@ -5270,10 +5280,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>409039</v>
+        <v>408984</v>
       </c>
       <c r="R47" t="n">
-        <v>6782290</v>
+        <v>6782385</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5303,9 +5313,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5320,19 +5340,19 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129032883</v>
+        <v>129032884</v>
       </c>
       <c r="B48" t="n">
         <v>79044</v>
@@ -5367,10 +5387,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>409010</v>
+        <v>409039</v>
       </c>
       <c r="R48" t="n">
-        <v>6782399</v>
+        <v>6782290</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5429,7 +5449,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129011408</v>
+        <v>129032883</v>
       </c>
       <c r="B49" t="n">
         <v>79044</v>
@@ -5464,10 +5484,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>409801</v>
+        <v>409010</v>
       </c>
       <c r="R49" t="n">
-        <v>6782315</v>
+        <v>6782399</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5497,19 +5517,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>11:08</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>11:08</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5524,22 +5534,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129011380</v>
+        <v>129032869</v>
       </c>
       <c r="B50" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5547,21 +5557,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5571,10 +5581,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>408984</v>
+        <v>409754</v>
       </c>
       <c r="R50" t="n">
-        <v>6782385</v>
+        <v>6782356</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5604,19 +5614,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>16:07</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>16:07</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5631,19 +5631,19 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129032899</v>
+        <v>129011401</v>
       </c>
       <c r="B51" t="n">
         <v>79044</v>
@@ -5678,10 +5678,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>409397</v>
+        <v>409663</v>
       </c>
       <c r="R51" t="n">
-        <v>6782272</v>
+        <v>6782385</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5711,9 +5711,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5728,12 +5738,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -5847,7 +5857,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129011396</v>
+        <v>129011409</v>
       </c>
       <c r="B53" t="n">
         <v>79044</v>
@@ -5882,10 +5892,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>409584</v>
+        <v>409202</v>
       </c>
       <c r="R53" t="n">
-        <v>6782395</v>
+        <v>6782367</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5917,7 +5927,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -5927,7 +5937,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5936,6 +5946,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -5954,7 +5965,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129011409</v>
+        <v>129011396</v>
       </c>
       <c r="B54" t="n">
         <v>79044</v>
@@ -5989,10 +6000,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>409202</v>
+        <v>409584</v>
       </c>
       <c r="R54" t="n">
-        <v>6782367</v>
+        <v>6782395</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6024,7 +6035,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6034,7 +6045,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6043,7 +6054,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6062,7 +6072,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129011401</v>
+        <v>129032899</v>
       </c>
       <c r="B55" t="n">
         <v>79044</v>
@@ -6097,10 +6107,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>409663</v>
+        <v>409397</v>
       </c>
       <c r="R55" t="n">
-        <v>6782385</v>
+        <v>6782272</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6130,19 +6140,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>12:58</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>12:58</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6157,12 +6157,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6266,10 +6266,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129011373</v>
+        <v>129011372</v>
       </c>
       <c r="B57" t="n">
-        <v>91571</v>
+        <v>57727</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6277,30 +6277,31 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -6308,10 +6309,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>409435</v>
+        <v>409796</v>
       </c>
       <c r="R57" t="n">
-        <v>6782383</v>
+        <v>6782327</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6343,7 +6344,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6353,12 +6354,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:14</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>4 st på samma tall</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6367,7 +6363,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6386,10 +6381,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129011372</v>
+        <v>129011373</v>
       </c>
       <c r="B58" t="n">
-        <v>57727</v>
+        <v>91574</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6397,31 +6392,30 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6429,10 +6423,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>409796</v>
+        <v>409435</v>
       </c>
       <c r="R58" t="n">
-        <v>6782327</v>
+        <v>6782383</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6464,7 +6458,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6474,7 +6468,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>4 st på samma tall</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6483,6 +6482,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6501,7 +6501,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129032889</v>
+        <v>129032403</v>
       </c>
       <c r="B59" t="n">
         <v>79044</v>
@@ -6536,10 +6536,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>409164</v>
+        <v>409021</v>
       </c>
       <c r="R59" t="n">
-        <v>6782308</v>
+        <v>6782365</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6586,19 +6586,19 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129032403</v>
+        <v>129032889</v>
       </c>
       <c r="B60" t="n">
         <v>79044</v>
@@ -6633,10 +6633,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>409021</v>
+        <v>409164</v>
       </c>
       <c r="R60" t="n">
-        <v>6782365</v>
+        <v>6782308</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6683,12 +6683,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -6802,53 +6802,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129032396</v>
+        <v>129032400</v>
       </c>
       <c r="B62" t="n">
-        <v>57727</v>
+        <v>92006</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>409753</v>
+        <v>409738</v>
       </c>
       <c r="R62" t="n">
-        <v>6782323</v>
+        <v>6782382</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6907,10 +6899,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129032867</v>
+        <v>129011387</v>
       </c>
       <c r="B63" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6918,21 +6910,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6942,10 +6934,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>409693</v>
+        <v>409232</v>
       </c>
       <c r="R63" t="n">
-        <v>6782357</v>
+        <v>6782353</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6975,9 +6967,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6992,19 +6994,19 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129032914</v>
+        <v>129011384</v>
       </c>
       <c r="B64" t="n">
         <v>79044</v>
@@ -7039,10 +7041,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>409759</v>
+        <v>409068</v>
       </c>
       <c r="R64" t="n">
-        <v>6782343</v>
+        <v>6782377</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7072,9 +7074,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7089,22 +7101,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129032872</v>
+        <v>129011379</v>
       </c>
       <c r="B65" t="n">
-        <v>78801</v>
+        <v>79044</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7112,21 +7124,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7136,10 +7148,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>409594</v>
+        <v>408991</v>
       </c>
       <c r="R65" t="n">
-        <v>6782294</v>
+        <v>6782360</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7169,9 +7181,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7186,22 +7208,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129011379</v>
+        <v>129032872</v>
       </c>
       <c r="B66" t="n">
-        <v>79044</v>
+        <v>78801</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7209,21 +7231,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7233,10 +7255,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>408991</v>
+        <v>409594</v>
       </c>
       <c r="R66" t="n">
-        <v>6782360</v>
+        <v>6782294</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7266,19 +7288,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>16:09</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>16:09</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7293,19 +7305,19 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129011387</v>
+        <v>129032886</v>
       </c>
       <c r="B67" t="n">
         <v>79044</v>
@@ -7340,10 +7352,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>409232</v>
+        <v>409108</v>
       </c>
       <c r="R67" t="n">
-        <v>6782353</v>
+        <v>6782395</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7373,19 +7385,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>15:22</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>15:22</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7400,22 +7402,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129032886</v>
+        <v>129032396</v>
       </c>
       <c r="B68" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7423,34 +7425,42 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>409108</v>
+        <v>409753</v>
       </c>
       <c r="R68" t="n">
-        <v>6782395</v>
+        <v>6782323</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7497,22 +7507,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129011384</v>
+        <v>129032867</v>
       </c>
       <c r="B69" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7520,21 +7530,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7544,10 +7554,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>409068</v>
+        <v>409693</v>
       </c>
       <c r="R69" t="n">
-        <v>6782377</v>
+        <v>6782357</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7577,19 +7587,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>15:43</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>15:43</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7604,46 +7604,42 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129032400</v>
+        <v>129032874</v>
       </c>
       <c r="B70" t="n">
-        <v>92003</v>
+        <v>91573</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1209</v>
+        <v>5432</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -7651,10 +7647,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>409738</v>
+        <v>409405</v>
       </c>
       <c r="R70" t="n">
-        <v>6782382</v>
+        <v>6782366</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7701,22 +7697,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129032874</v>
+        <v>129032914</v>
       </c>
       <c r="B71" t="n">
-        <v>91570</v>
+        <v>79044</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7724,19 +7720,23 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
@@ -7744,10 +7744,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>409405</v>
+        <v>409759</v>
       </c>
       <c r="R71" t="n">
-        <v>6782366</v>
+        <v>6782343</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7806,10 +7806,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129032900</v>
+        <v>129032873</v>
       </c>
       <c r="B72" t="n">
-        <v>79044</v>
+        <v>91553</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7817,34 +7817,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>409449</v>
+        <v>409075</v>
       </c>
       <c r="R72" t="n">
-        <v>6782286</v>
+        <v>6782317</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7885,6 +7888,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -7903,7 +7907,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129032917</v>
+        <v>129032896</v>
       </c>
       <c r="B73" t="n">
         <v>79044</v>
@@ -7938,10 +7942,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>409360</v>
+        <v>409331</v>
       </c>
       <c r="R73" t="n">
-        <v>6782355</v>
+        <v>6782342</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8000,7 +8004,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129032902</v>
+        <v>129032917</v>
       </c>
       <c r="B74" t="n">
         <v>79044</v>
@@ -8035,10 +8039,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>409549</v>
+        <v>409360</v>
       </c>
       <c r="R74" t="n">
-        <v>6782286</v>
+        <v>6782355</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8097,7 +8101,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129032896</v>
+        <v>129032902</v>
       </c>
       <c r="B75" t="n">
         <v>79044</v>
@@ -8132,10 +8136,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>409331</v>
+        <v>409549</v>
       </c>
       <c r="R75" t="n">
-        <v>6782342</v>
+        <v>6782286</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8194,10 +8198,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129032873</v>
+        <v>129032900</v>
       </c>
       <c r="B76" t="n">
-        <v>91550</v>
+        <v>79044</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8205,37 +8209,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>409075</v>
+        <v>409449</v>
       </c>
       <c r="R76" t="n">
-        <v>6782317</v>
+        <v>6782286</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8276,7 +8277,6 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8298,7 +8298,7 @@
         <v>129032402</v>
       </c>
       <c r="B77" t="n">
-        <v>91570</v>
+        <v>91573</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8388,7 +8388,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129011404</v>
+        <v>129032893</v>
       </c>
       <c r="B78" t="n">
         <v>79044</v>
@@ -8423,10 +8423,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>409736</v>
+        <v>409280</v>
       </c>
       <c r="R78" t="n">
-        <v>6782394</v>
+        <v>6782382</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8456,19 +8456,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>11:59</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>11:59</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8483,19 +8473,19 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129032901</v>
+        <v>129011404</v>
       </c>
       <c r="B79" t="n">
         <v>79044</v>
@@ -8530,10 +8520,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>409528</v>
+        <v>409736</v>
       </c>
       <c r="R79" t="n">
-        <v>6782292</v>
+        <v>6782394</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8563,9 +8553,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8580,19 +8580,19 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129032888</v>
+        <v>129032901</v>
       </c>
       <c r="B80" t="n">
         <v>79044</v>
@@ -8627,10 +8627,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>409127</v>
+        <v>409528</v>
       </c>
       <c r="R80" t="n">
-        <v>6782290</v>
+        <v>6782292</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8689,7 +8689,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129032893</v>
+        <v>129032888</v>
       </c>
       <c r="B81" t="n">
         <v>79044</v>
@@ -8724,10 +8724,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>409280</v>
+        <v>409127</v>
       </c>
       <c r="R81" t="n">
-        <v>6782382</v>
+        <v>6782290</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8786,7 +8786,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129032908</v>
+        <v>129032879</v>
       </c>
       <c r="B82" t="n">
         <v>79044</v>
@@ -8821,10 +8821,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>409715</v>
+        <v>408909</v>
       </c>
       <c r="R82" t="n">
-        <v>6782363</v>
+        <v>6782332</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8883,7 +8883,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129032879</v>
+        <v>129032409</v>
       </c>
       <c r="B83" t="n">
         <v>79044</v>
@@ -8918,10 +8918,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>408909</v>
+        <v>409782</v>
       </c>
       <c r="R83" t="n">
-        <v>6782332</v>
+        <v>6782339</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8968,19 +8968,19 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129032916</v>
+        <v>129032908</v>
       </c>
       <c r="B84" t="n">
         <v>79044</v>
@@ -9015,10 +9015,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>409812</v>
+        <v>409715</v>
       </c>
       <c r="R84" t="n">
-        <v>6782309</v>
+        <v>6782363</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9077,7 +9077,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129032409</v>
+        <v>129032916</v>
       </c>
       <c r="B85" t="n">
         <v>79044</v>
@@ -9112,10 +9112,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>409782</v>
+        <v>409812</v>
       </c>
       <c r="R85" t="n">
-        <v>6782339</v>
+        <v>6782309</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9162,22 +9162,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129032870</v>
+        <v>129032918</v>
       </c>
       <c r="B86" t="n">
-        <v>91571</v>
+        <v>79044</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9185,45 +9185,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>409530</v>
+        <v>409363</v>
       </c>
       <c r="R86" t="n">
-        <v>6782289</v>
+        <v>6782377</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9264,7 +9253,6 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9398,10 +9386,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129032918</v>
+        <v>129032870</v>
       </c>
       <c r="B88" t="n">
-        <v>79044</v>
+        <v>91574</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9409,34 +9397,45 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>409363</v>
+        <v>409530</v>
       </c>
       <c r="R88" t="n">
-        <v>6782377</v>
+        <v>6782289</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9477,6 +9476,7 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -9592,7 +9592,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129032895</v>
+        <v>129011393</v>
       </c>
       <c r="B90" t="n">
         <v>79044</v>
@@ -9627,10 +9627,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>409310</v>
+        <v>409472</v>
       </c>
       <c r="R90" t="n">
-        <v>6782326</v>
+        <v>6782351</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9660,9 +9660,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9677,19 +9687,19 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129032405</v>
+        <v>129032903</v>
       </c>
       <c r="B91" t="n">
         <v>79044</v>
@@ -9724,10 +9734,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>409048</v>
+        <v>409582</v>
       </c>
       <c r="R91" t="n">
-        <v>6782365</v>
+        <v>6782297</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9774,19 +9784,19 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129032880</v>
+        <v>129032405</v>
       </c>
       <c r="B92" t="n">
         <v>79044</v>
@@ -9821,10 +9831,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>408901</v>
+        <v>409048</v>
       </c>
       <c r="R92" t="n">
-        <v>6782390</v>
+        <v>6782365</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9871,19 +9881,19 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129011393</v>
+        <v>129032895</v>
       </c>
       <c r="B93" t="n">
         <v>79044</v>
@@ -9918,10 +9928,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>409472</v>
+        <v>409310</v>
       </c>
       <c r="R93" t="n">
-        <v>6782351</v>
+        <v>6782326</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9951,19 +9961,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>14:05</t>
-        </is>
-      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>14:05</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -9978,19 +9978,19 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129032903</v>
+        <v>129032880</v>
       </c>
       <c r="B94" t="n">
         <v>79044</v>
@@ -10025,10 +10025,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>409582</v>
+        <v>408901</v>
       </c>
       <c r="R94" t="n">
-        <v>6782297</v>
+        <v>6782390</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10087,7 +10087,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129032408</v>
+        <v>129011388</v>
       </c>
       <c r="B95" t="n">
         <v>79044</v>
@@ -10122,10 +10122,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>409749</v>
+        <v>409250</v>
       </c>
       <c r="R95" t="n">
-        <v>6782325</v>
+        <v>6782354</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10155,9 +10155,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10172,19 +10182,19 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129032890</v>
+        <v>129011406</v>
       </c>
       <c r="B96" t="n">
         <v>79044</v>
@@ -10219,10 +10229,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>409228</v>
+        <v>409759</v>
       </c>
       <c r="R96" t="n">
-        <v>6782298</v>
+        <v>6782314</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10252,9 +10262,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10269,19 +10289,19 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129032875</v>
+        <v>129032408</v>
       </c>
       <c r="B97" t="n">
         <v>79044</v>
@@ -10316,10 +10336,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>409034</v>
+        <v>409749</v>
       </c>
       <c r="R97" t="n">
-        <v>6782261</v>
+        <v>6782325</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10366,12 +10386,12 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
@@ -10475,7 +10495,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129011406</v>
+        <v>129032890</v>
       </c>
       <c r="B99" t="n">
         <v>79044</v>
@@ -10510,10 +10530,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>409759</v>
+        <v>409228</v>
       </c>
       <c r="R99" t="n">
-        <v>6782314</v>
+        <v>6782298</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10543,19 +10563,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>11:41</t>
-        </is>
-      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>11:41</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10570,19 +10580,19 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129011388</v>
+        <v>129011390</v>
       </c>
       <c r="B100" t="n">
         <v>79044</v>
@@ -10617,10 +10627,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>409250</v>
+        <v>409349</v>
       </c>
       <c r="R100" t="n">
-        <v>6782354</v>
+        <v>6782376</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10652,7 +10662,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -10662,7 +10672,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10689,7 +10699,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129011390</v>
+        <v>129032875</v>
       </c>
       <c r="B101" t="n">
         <v>79044</v>
@@ -10724,10 +10734,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>409349</v>
+        <v>409034</v>
       </c>
       <c r="R101" t="n">
-        <v>6782376</v>
+        <v>6782261</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10757,19 +10767,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z101" t="inlineStr">
-        <is>
-          <t>14:34</t>
-        </is>
-      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB101" t="inlineStr">
-        <is>
-          <t>14:34</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10784,22 +10784,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129011385</v>
+        <v>129032401</v>
       </c>
       <c r="B102" t="n">
-        <v>79044</v>
+        <v>91573</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10807,23 +10807,19 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
@@ -10831,10 +10827,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>409214</v>
+        <v>409226</v>
       </c>
       <c r="R102" t="n">
-        <v>6782345</v>
+        <v>6782376</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10864,19 +10860,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z102" t="inlineStr">
-        <is>
-          <t>15:29</t>
-        </is>
-      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB102" t="inlineStr">
-        <is>
-          <t>15:29</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10891,19 +10877,19 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129011377</v>
+        <v>129032915</v>
       </c>
       <c r="B103" t="n">
         <v>79044</v>
@@ -10938,10 +10924,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>408995</v>
+        <v>409765</v>
       </c>
       <c r="R103" t="n">
-        <v>6782299</v>
+        <v>6782330</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10971,19 +10957,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z103" t="inlineStr">
-        <is>
-          <t>16:13</t>
-        </is>
-      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB103" t="inlineStr">
-        <is>
-          <t>16:13</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10998,19 +10974,19 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129032915</v>
+        <v>129011377</v>
       </c>
       <c r="B104" t="n">
         <v>79044</v>
@@ -11045,10 +11021,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>409765</v>
+        <v>408995</v>
       </c>
       <c r="R104" t="n">
-        <v>6782330</v>
+        <v>6782299</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11078,9 +11054,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11095,19 +11081,19 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129032904</v>
+        <v>129011402</v>
       </c>
       <c r="B105" t="n">
         <v>79044</v>
@@ -11142,10 +11128,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>409568</v>
+        <v>409671</v>
       </c>
       <c r="R105" t="n">
-        <v>6782383</v>
+        <v>6782390</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11175,9 +11161,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11192,19 +11188,19 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129011402</v>
+        <v>129011385</v>
       </c>
       <c r="B106" t="n">
         <v>79044</v>
@@ -11239,10 +11235,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>409671</v>
+        <v>409214</v>
       </c>
       <c r="R106" t="n">
-        <v>6782390</v>
+        <v>6782345</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11274,7 +11270,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -11284,7 +11280,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11408,10 +11404,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129032401</v>
+        <v>129032904</v>
       </c>
       <c r="B108" t="n">
-        <v>91570</v>
+        <v>79044</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11419,19 +11415,23 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
@@ -11439,10 +11439,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>409226</v>
+        <v>409568</v>
       </c>
       <c r="R108" t="n">
-        <v>6782376</v>
+        <v>6782383</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11489,12 +11489,12 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>

--- a/artfynd/A 47938-2025 artfynd.xlsx
+++ b/artfynd/A 47938-2025 artfynd.xlsx
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129032905</v>
+        <v>129011405</v>
       </c>
       <c r="B3" t="n">
         <v>79044</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>409624</v>
+        <v>409747</v>
       </c>
       <c r="R3" t="n">
-        <v>6782292</v>
+        <v>6782328</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -840,9 +840,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -857,19 +867,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129011405</v>
+        <v>129032876</v>
       </c>
       <c r="B4" t="n">
         <v>79044</v>
@@ -904,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>409747</v>
+        <v>408997</v>
       </c>
       <c r="R4" t="n">
-        <v>6782328</v>
+        <v>6782283</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -937,19 +947,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>11:47</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>11:47</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -964,19 +964,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129032876</v>
+        <v>129011403</v>
       </c>
       <c r="B5" t="n">
         <v>79044</v>
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>408997</v>
+        <v>409706</v>
       </c>
       <c r="R5" t="n">
-        <v>6782283</v>
+        <v>6782359</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1044,9 +1044,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1061,19 +1071,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129011403</v>
+        <v>129032905</v>
       </c>
       <c r="B6" t="n">
         <v>79044</v>
@@ -1108,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>409706</v>
+        <v>409624</v>
       </c>
       <c r="R6" t="n">
-        <v>6782359</v>
+        <v>6782292</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1141,19 +1151,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>12:06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1168,19 +1168,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129032919</v>
+        <v>129032907</v>
       </c>
       <c r="B7" t="n">
         <v>79044</v>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>409358</v>
+        <v>409686</v>
       </c>
       <c r="R7" t="n">
-        <v>6782291</v>
+        <v>6782351</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1277,7 +1277,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129032907</v>
+        <v>129011389</v>
       </c>
       <c r="B8" t="n">
         <v>79044</v>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>409686</v>
+        <v>409278</v>
       </c>
       <c r="R8" t="n">
-        <v>6782351</v>
+        <v>6782361</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1345,9 +1345,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1362,19 +1372,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129011389</v>
+        <v>129032919</v>
       </c>
       <c r="B9" t="n">
         <v>79044</v>
@@ -1409,10 +1419,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>409278</v>
+        <v>409358</v>
       </c>
       <c r="R9" t="n">
-        <v>6782361</v>
+        <v>6782291</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1442,19 +1452,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>15:18</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>15:18</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1469,12 +1469,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1879,7 +1879,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129032909</v>
+        <v>129032897</v>
       </c>
       <c r="B14" t="n">
         <v>79044</v>
@@ -1914,10 +1914,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>409727</v>
+        <v>409469</v>
       </c>
       <c r="R14" t="n">
-        <v>6782352</v>
+        <v>6782371</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2073,7 +2073,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129011378</v>
+        <v>129032909</v>
       </c>
       <c r="B16" t="n">
         <v>79044</v>
@@ -2108,10 +2108,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>408984</v>
+        <v>409727</v>
       </c>
       <c r="R16" t="n">
-        <v>6782347</v>
+        <v>6782352</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2141,19 +2141,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>16:10</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>16:10</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2168,19 +2158,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129032897</v>
+        <v>129011378</v>
       </c>
       <c r="B17" t="n">
         <v>79044</v>
@@ -2215,10 +2205,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>409469</v>
+        <v>408984</v>
       </c>
       <c r="R17" t="n">
-        <v>6782371</v>
+        <v>6782347</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2248,9 +2238,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2265,12 +2265,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2778,10 +2778,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129032399</v>
+        <v>129011395</v>
       </c>
       <c r="B23" t="n">
-        <v>91574</v>
+        <v>79044</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2789,21 +2789,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2813,10 +2813,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>409492</v>
+        <v>409555</v>
       </c>
       <c r="R23" t="n">
-        <v>6782346</v>
+        <v>6782356</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2846,9 +2846,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2863,22 +2873,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129011374</v>
+        <v>129011407</v>
       </c>
       <c r="B24" t="n">
-        <v>91574</v>
+        <v>79044</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2886,41 +2896,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>409475</v>
+        <v>409795</v>
       </c>
       <c r="R24" t="n">
-        <v>6782342</v>
+        <v>6782327</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2952,7 +2955,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -2962,12 +2965,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:57</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>hackspetthål under tickorna</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2976,7 +2974,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3102,10 +3099,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129011395</v>
+        <v>129032393</v>
       </c>
       <c r="B26" t="n">
-        <v>79044</v>
+        <v>79634</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3113,21 +3110,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3137,10 +3134,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>409555</v>
+        <v>409554</v>
       </c>
       <c r="R26" t="n">
-        <v>6782356</v>
+        <v>6782380</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3170,19 +3167,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>13:17</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>13:17</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3197,22 +3184,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129011407</v>
+        <v>129032399</v>
       </c>
       <c r="B27" t="n">
-        <v>79044</v>
+        <v>91574</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3220,21 +3207,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3244,10 +3231,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>409795</v>
+        <v>409492</v>
       </c>
       <c r="R27" t="n">
-        <v>6782327</v>
+        <v>6782346</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3277,19 +3264,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>11:12</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>11:12</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3304,22 +3281,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129032393</v>
+        <v>129011374</v>
       </c>
       <c r="B28" t="n">
-        <v>79634</v>
+        <v>91574</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3327,34 +3304,41 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>229821</v>
+        <v>5442</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>409554</v>
+        <v>409475</v>
       </c>
       <c r="R28" t="n">
-        <v>6782380</v>
+        <v>6782342</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3384,29 +3368,45 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>hackspetthål under tickorna</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3518,10 +3518,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129032913</v>
+        <v>129011369</v>
       </c>
       <c r="B30" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3529,34 +3529,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>409757</v>
+        <v>409683</v>
       </c>
       <c r="R30" t="n">
-        <v>6782355</v>
+        <v>6782391</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3586,9 +3594,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3603,12 +3621,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -3712,7 +3730,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129011391</v>
+        <v>129032913</v>
       </c>
       <c r="B32" t="n">
         <v>79044</v>
@@ -3747,10 +3765,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>409349</v>
+        <v>409757</v>
       </c>
       <c r="R32" t="n">
-        <v>6782383</v>
+        <v>6782355</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3780,19 +3798,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>14:34</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>14:34</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3807,22 +3815,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129011369</v>
+        <v>129032882</v>
       </c>
       <c r="B33" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3830,42 +3838,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>409683</v>
+        <v>408992</v>
       </c>
       <c r="R33" t="n">
-        <v>6782391</v>
+        <v>6782394</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3895,19 +3895,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>12:56</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>12:56</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3922,19 +3912,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129032882</v>
+        <v>129011391</v>
       </c>
       <c r="B34" t="n">
         <v>79044</v>
@@ -3969,10 +3959,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>408992</v>
+        <v>409349</v>
       </c>
       <c r="R34" t="n">
-        <v>6782394</v>
+        <v>6782383</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4002,9 +3992,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4019,12 +4019,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4128,7 +4128,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129011381</v>
+        <v>129032887</v>
       </c>
       <c r="B36" t="n">
         <v>79044</v>
@@ -4163,10 +4163,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>409010</v>
+        <v>409176</v>
       </c>
       <c r="R36" t="n">
-        <v>6782383</v>
+        <v>6782420</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4196,19 +4196,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>16:06</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>16:06</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4223,19 +4213,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129032887</v>
+        <v>129011381</v>
       </c>
       <c r="B37" t="n">
         <v>79044</v>
@@ -4270,10 +4260,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>409176</v>
+        <v>409010</v>
       </c>
       <c r="R37" t="n">
-        <v>6782420</v>
+        <v>6782383</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4303,9 +4293,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4320,19 +4320,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129011392</v>
+        <v>129011394</v>
       </c>
       <c r="B38" t="n">
         <v>79044</v>
@@ -4367,10 +4367,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>409361</v>
+        <v>409543</v>
       </c>
       <c r="R38" t="n">
-        <v>6782401</v>
+        <v>6782361</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4402,7 +4402,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4439,7 +4439,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129032906</v>
+        <v>129011392</v>
       </c>
       <c r="B39" t="n">
         <v>79044</v>
@@ -4474,10 +4474,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>409684</v>
+        <v>409361</v>
       </c>
       <c r="R39" t="n">
-        <v>6782322</v>
+        <v>6782401</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4507,9 +4507,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4524,12 +4534,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4633,7 +4643,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129011394</v>
+        <v>129011399</v>
       </c>
       <c r="B41" t="n">
         <v>79044</v>
@@ -4668,10 +4678,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>409543</v>
+        <v>409609</v>
       </c>
       <c r="R41" t="n">
-        <v>6782361</v>
+        <v>6782404</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4703,7 +4713,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4713,7 +4723,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4740,7 +4750,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129011399</v>
+        <v>129032891</v>
       </c>
       <c r="B42" t="n">
         <v>79044</v>
@@ -4775,10 +4785,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>409609</v>
+        <v>409241</v>
       </c>
       <c r="R42" t="n">
-        <v>6782404</v>
+        <v>6782372</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4808,19 +4818,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>13:06</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>13:06</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4835,19 +4835,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129032891</v>
+        <v>129032911</v>
       </c>
       <c r="B43" t="n">
         <v>79044</v>
@@ -4882,10 +4882,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>409241</v>
+        <v>409777</v>
       </c>
       <c r="R43" t="n">
-        <v>6782372</v>
+        <v>6782445</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4944,7 +4944,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129032911</v>
+        <v>129032906</v>
       </c>
       <c r="B44" t="n">
         <v>79044</v>
@@ -4979,10 +4979,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>409777</v>
+        <v>409684</v>
       </c>
       <c r="R44" t="n">
-        <v>6782445</v>
+        <v>6782322</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5750,7 +5750,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129011386</v>
+        <v>129032899</v>
       </c>
       <c r="B52" t="n">
         <v>79044</v>
@@ -5785,10 +5785,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>409210</v>
+        <v>409397</v>
       </c>
       <c r="R52" t="n">
-        <v>6782365</v>
+        <v>6782272</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5818,19 +5818,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>15:26</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>15:26</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5845,12 +5835,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -5965,10 +5955,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129011396</v>
+        <v>129032866</v>
       </c>
       <c r="B54" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5976,21 +5966,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6000,10 +5990,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>409584</v>
+        <v>409757</v>
       </c>
       <c r="R54" t="n">
-        <v>6782395</v>
+        <v>6782386</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6033,19 +6023,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>13:11</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>13:11</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6060,19 +6040,19 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129032899</v>
+        <v>129011396</v>
       </c>
       <c r="B55" t="n">
         <v>79044</v>
@@ -6107,10 +6087,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>409397</v>
+        <v>409584</v>
       </c>
       <c r="R55" t="n">
-        <v>6782272</v>
+        <v>6782395</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6140,9 +6120,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6157,22 +6147,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129032866</v>
+        <v>129011386</v>
       </c>
       <c r="B56" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6180,21 +6170,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6204,10 +6194,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>409757</v>
+        <v>409210</v>
       </c>
       <c r="R56" t="n">
-        <v>6782386</v>
+        <v>6782365</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6237,9 +6227,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6254,22 +6254,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129011372</v>
+        <v>129032403</v>
       </c>
       <c r="B57" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6277,42 +6277,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>409796</v>
+        <v>409021</v>
       </c>
       <c r="R57" t="n">
-        <v>6782327</v>
+        <v>6782365</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6342,19 +6334,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>11:10</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6369,22 +6351,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129011373</v>
+        <v>129011372</v>
       </c>
       <c r="B58" t="n">
-        <v>91574</v>
+        <v>57727</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6392,30 +6374,31 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6423,10 +6406,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>409435</v>
+        <v>409796</v>
       </c>
       <c r="R58" t="n">
-        <v>6782383</v>
+        <v>6782327</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6458,7 +6441,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6468,12 +6451,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:14</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>4 st på samma tall</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6482,7 +6460,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6501,10 +6478,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129032403</v>
+        <v>129011373</v>
       </c>
       <c r="B59" t="n">
-        <v>79044</v>
+        <v>91574</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6512,34 +6489,41 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>409021</v>
+        <v>409435</v>
       </c>
       <c r="R59" t="n">
-        <v>6782365</v>
+        <v>6782383</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6569,29 +6553,45 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>4 st på samma tall</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -6802,45 +6802,53 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129032400</v>
+        <v>129032396</v>
       </c>
       <c r="B62" t="n">
-        <v>92006</v>
+        <v>57727</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>409738</v>
+        <v>409753</v>
       </c>
       <c r="R62" t="n">
-        <v>6782382</v>
+        <v>6782323</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6899,10 +6907,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129011387</v>
+        <v>129032867</v>
       </c>
       <c r="B63" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6910,21 +6918,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6934,10 +6942,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>409232</v>
+        <v>409693</v>
       </c>
       <c r="R63" t="n">
-        <v>6782353</v>
+        <v>6782357</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6967,19 +6975,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>15:22</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>15:22</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6994,19 +6992,19 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129011384</v>
+        <v>129032914</v>
       </c>
       <c r="B64" t="n">
         <v>79044</v>
@@ -7041,10 +7039,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>409068</v>
+        <v>409759</v>
       </c>
       <c r="R64" t="n">
-        <v>6782377</v>
+        <v>6782343</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7074,19 +7072,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>15:43</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>15:43</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7101,44 +7089,44 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129011379</v>
+        <v>129032400</v>
       </c>
       <c r="B65" t="n">
-        <v>79044</v>
+        <v>92006</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7148,10 +7136,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>408991</v>
+        <v>409738</v>
       </c>
       <c r="R65" t="n">
-        <v>6782360</v>
+        <v>6782382</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7181,19 +7169,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>16:09</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>16:09</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7208,22 +7186,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129032872</v>
+        <v>129011387</v>
       </c>
       <c r="B66" t="n">
-        <v>78801</v>
+        <v>79044</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7231,21 +7209,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7255,10 +7233,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>409594</v>
+        <v>409232</v>
       </c>
       <c r="R66" t="n">
-        <v>6782294</v>
+        <v>6782353</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7288,9 +7266,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7305,12 +7293,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -7414,10 +7402,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129032396</v>
+        <v>129011379</v>
       </c>
       <c r="B68" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7425,42 +7413,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>409753</v>
+        <v>408991</v>
       </c>
       <c r="R68" t="n">
-        <v>6782323</v>
+        <v>6782360</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7490,9 +7470,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7507,22 +7497,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129032867</v>
+        <v>129032874</v>
       </c>
       <c r="B69" t="n">
-        <v>57727</v>
+        <v>91573</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7530,23 +7520,19 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -7554,10 +7540,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>409693</v>
+        <v>409405</v>
       </c>
       <c r="R69" t="n">
-        <v>6782357</v>
+        <v>6782366</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7616,10 +7602,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129032874</v>
+        <v>129011384</v>
       </c>
       <c r="B70" t="n">
-        <v>91573</v>
+        <v>79044</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7627,19 +7613,23 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -7647,10 +7637,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>409405</v>
+        <v>409068</v>
       </c>
       <c r="R70" t="n">
-        <v>6782366</v>
+        <v>6782377</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7680,9 +7670,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7697,22 +7697,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129032914</v>
+        <v>129032872</v>
       </c>
       <c r="B71" t="n">
-        <v>79044</v>
+        <v>78801</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7720,21 +7720,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7744,10 +7744,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>409759</v>
+        <v>409594</v>
       </c>
       <c r="R71" t="n">
-        <v>6782343</v>
+        <v>6782294</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8101,7 +8101,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129032902</v>
+        <v>129032900</v>
       </c>
       <c r="B75" t="n">
         <v>79044</v>
@@ -8136,7 +8136,7 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>409549</v>
+        <v>409449</v>
       </c>
       <c r="R75" t="n">
         <v>6782286</v>
@@ -8198,7 +8198,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129032900</v>
+        <v>129032902</v>
       </c>
       <c r="B76" t="n">
         <v>79044</v>
@@ -8233,7 +8233,7 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>409449</v>
+        <v>409549</v>
       </c>
       <c r="R76" t="n">
         <v>6782286</v>
@@ -8295,10 +8295,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129032402</v>
+        <v>129032893</v>
       </c>
       <c r="B77" t="n">
-        <v>91573</v>
+        <v>79044</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8306,19 +8306,23 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
@@ -8326,10 +8330,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>409767</v>
+        <v>409280</v>
       </c>
       <c r="R77" t="n">
-        <v>6782352</v>
+        <v>6782382</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8376,19 +8380,19 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129032893</v>
+        <v>129011404</v>
       </c>
       <c r="B78" t="n">
         <v>79044</v>
@@ -8423,10 +8427,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>409280</v>
+        <v>409736</v>
       </c>
       <c r="R78" t="n">
-        <v>6782382</v>
+        <v>6782394</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8456,9 +8460,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8473,19 +8487,19 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129011404</v>
+        <v>129032901</v>
       </c>
       <c r="B79" t="n">
         <v>79044</v>
@@ -8520,10 +8534,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>409736</v>
+        <v>409528</v>
       </c>
       <c r="R79" t="n">
-        <v>6782394</v>
+        <v>6782292</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8553,19 +8567,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>11:59</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>11:59</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8580,19 +8584,19 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129032901</v>
+        <v>129032888</v>
       </c>
       <c r="B80" t="n">
         <v>79044</v>
@@ -8627,10 +8631,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>409528</v>
+        <v>409127</v>
       </c>
       <c r="R80" t="n">
-        <v>6782292</v>
+        <v>6782290</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8689,10 +8693,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129032888</v>
+        <v>129032402</v>
       </c>
       <c r="B81" t="n">
-        <v>79044</v>
+        <v>91573</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8700,23 +8704,19 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
@@ -8724,10 +8724,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>409127</v>
+        <v>409767</v>
       </c>
       <c r="R81" t="n">
-        <v>6782290</v>
+        <v>6782352</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8774,19 +8774,19 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129032879</v>
+        <v>129032908</v>
       </c>
       <c r="B82" t="n">
         <v>79044</v>
@@ -8821,10 +8821,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>408909</v>
+        <v>409715</v>
       </c>
       <c r="R82" t="n">
-        <v>6782332</v>
+        <v>6782363</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8883,7 +8883,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129032409</v>
+        <v>129032879</v>
       </c>
       <c r="B83" t="n">
         <v>79044</v>
@@ -8918,10 +8918,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>409782</v>
+        <v>408909</v>
       </c>
       <c r="R83" t="n">
-        <v>6782339</v>
+        <v>6782332</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8968,19 +8968,19 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129032908</v>
+        <v>129032916</v>
       </c>
       <c r="B84" t="n">
         <v>79044</v>
@@ -9015,10 +9015,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>409715</v>
+        <v>409812</v>
       </c>
       <c r="R84" t="n">
-        <v>6782363</v>
+        <v>6782309</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9077,7 +9077,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129032916</v>
+        <v>129032409</v>
       </c>
       <c r="B85" t="n">
         <v>79044</v>
@@ -9112,10 +9112,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>409812</v>
+        <v>409782</v>
       </c>
       <c r="R85" t="n">
-        <v>6782309</v>
+        <v>6782339</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9162,22 +9162,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129032918</v>
+        <v>129011370</v>
       </c>
       <c r="B86" t="n">
-        <v>79044</v>
+        <v>57727</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9185,34 +9185,42 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>409363</v>
+        <v>409759</v>
       </c>
       <c r="R86" t="n">
-        <v>6782377</v>
+        <v>6782330</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9242,9 +9250,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9259,22 +9277,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129011370</v>
+        <v>129032898</v>
       </c>
       <c r="B87" t="n">
-        <v>57727</v>
+        <v>79044</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9282,42 +9300,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>409759</v>
+        <v>409390</v>
       </c>
       <c r="R87" t="n">
-        <v>6782330</v>
+        <v>6782289</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9347,19 +9357,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>11:48</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>11:48</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9374,22 +9374,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129032870</v>
+        <v>129032918</v>
       </c>
       <c r="B88" t="n">
-        <v>91574</v>
+        <v>79044</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9397,45 +9397,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>409530</v>
+        <v>409363</v>
       </c>
       <c r="R88" t="n">
-        <v>6782289</v>
+        <v>6782377</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9476,7 +9465,6 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -9495,10 +9483,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129032898</v>
+        <v>129032870</v>
       </c>
       <c r="B89" t="n">
-        <v>79044</v>
+        <v>91574</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9506,31 +9494,42 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>409390</v>
+        <v>409530</v>
       </c>
       <c r="R89" t="n">
         <v>6782289</v>
@@ -9574,6 +9573,7 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -9796,7 +9796,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129032405</v>
+        <v>129032880</v>
       </c>
       <c r="B92" t="n">
         <v>79044</v>
@@ -9831,10 +9831,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>409048</v>
+        <v>408901</v>
       </c>
       <c r="R92" t="n">
-        <v>6782365</v>
+        <v>6782390</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9881,12 +9881,12 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
@@ -9990,7 +9990,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129032880</v>
+        <v>129032405</v>
       </c>
       <c r="B94" t="n">
         <v>79044</v>
@@ -10025,10 +10025,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>408901</v>
+        <v>409048</v>
       </c>
       <c r="R94" t="n">
-        <v>6782390</v>
+        <v>6782365</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10075,12 +10075,12 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
@@ -10301,7 +10301,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129032408</v>
+        <v>129032890</v>
       </c>
       <c r="B97" t="n">
         <v>79044</v>
@@ -10336,10 +10336,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>409749</v>
+        <v>409228</v>
       </c>
       <c r="R97" t="n">
-        <v>6782325</v>
+        <v>6782298</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10386,19 +10386,19 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129032912</v>
+        <v>129032875</v>
       </c>
       <c r="B98" t="n">
         <v>79044</v>
@@ -10433,10 +10433,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>409762</v>
+        <v>409034</v>
       </c>
       <c r="R98" t="n">
-        <v>6782335</v>
+        <v>6782261</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10495,7 +10495,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129032890</v>
+        <v>129011390</v>
       </c>
       <c r="B99" t="n">
         <v>79044</v>
@@ -10530,10 +10530,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>409228</v>
+        <v>409349</v>
       </c>
       <c r="R99" t="n">
-        <v>6782298</v>
+        <v>6782376</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10563,9 +10563,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10580,19 +10590,19 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129011390</v>
+        <v>129032408</v>
       </c>
       <c r="B100" t="n">
         <v>79044</v>
@@ -10627,10 +10637,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>409349</v>
+        <v>409749</v>
       </c>
       <c r="R100" t="n">
-        <v>6782376</v>
+        <v>6782325</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10660,19 +10670,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>14:34</t>
-        </is>
-      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>14:34</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10687,19 +10687,19 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129032875</v>
+        <v>129032912</v>
       </c>
       <c r="B101" t="n">
         <v>79044</v>
@@ -10734,10 +10734,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>409034</v>
+        <v>409762</v>
       </c>
       <c r="R101" t="n">
-        <v>6782261</v>
+        <v>6782335</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10889,7 +10889,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129032915</v>
+        <v>129011377</v>
       </c>
       <c r="B103" t="n">
         <v>79044</v>
@@ -10924,10 +10924,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>409765</v>
+        <v>408995</v>
       </c>
       <c r="R103" t="n">
-        <v>6782330</v>
+        <v>6782299</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10957,9 +10957,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -10974,19 +10984,19 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129011377</v>
+        <v>129011402</v>
       </c>
       <c r="B104" t="n">
         <v>79044</v>
@@ -11021,10 +11031,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>408995</v>
+        <v>409671</v>
       </c>
       <c r="R104" t="n">
-        <v>6782299</v>
+        <v>6782390</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11056,7 +11066,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11066,7 +11076,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11093,7 +11103,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129011402</v>
+        <v>129011385</v>
       </c>
       <c r="B105" t="n">
         <v>79044</v>
@@ -11128,10 +11138,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>409671</v>
+        <v>409214</v>
       </c>
       <c r="R105" t="n">
-        <v>6782390</v>
+        <v>6782345</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11163,7 +11173,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11173,7 +11183,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11200,7 +11210,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129011385</v>
+        <v>129032877</v>
       </c>
       <c r="B106" t="n">
         <v>79044</v>
@@ -11235,10 +11245,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>409214</v>
+        <v>408994</v>
       </c>
       <c r="R106" t="n">
-        <v>6782345</v>
+        <v>6782293</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11268,19 +11278,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z106" t="inlineStr">
-        <is>
-          <t>15:29</t>
-        </is>
-      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB106" t="inlineStr">
-        <is>
-          <t>15:29</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11295,19 +11295,19 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129032877</v>
+        <v>129032904</v>
       </c>
       <c r="B107" t="n">
         <v>79044</v>
@@ -11342,10 +11342,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>408994</v>
+        <v>409568</v>
       </c>
       <c r="R107" t="n">
-        <v>6782293</v>
+        <v>6782383</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11404,7 +11404,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129032904</v>
+        <v>129032915</v>
       </c>
       <c r="B108" t="n">
         <v>79044</v>
@@ -11439,10 +11439,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>409568</v>
+        <v>409765</v>
       </c>
       <c r="R108" t="n">
-        <v>6782383</v>
+        <v>6782330</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>

--- a/artfynd/A 47938-2025 artfynd.xlsx
+++ b/artfynd/A 47938-2025 artfynd.xlsx
@@ -2710,6 +2710,14 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
@@ -5575,6 +5583,14 @@
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
@@ -5984,6 +6000,14 @@
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
@@ -6936,6 +6960,14 @@
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>

--- a/artfynd/A 47938-2025 artfynd.xlsx
+++ b/artfynd/A 47938-2025 artfynd.xlsx
@@ -2684,7 +2684,7 @@
         <v>129032868</v>
       </c>
       <c r="B22" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -5557,7 +5557,7 @@
         <v>129032869</v>
       </c>
       <c r="B50" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5974,7 +5974,7 @@
         <v>129032866</v>
       </c>
       <c r="B54" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6934,7 +6934,7 @@
         <v>129032867</v>
       </c>
       <c r="B63" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 47938-2025 artfynd.xlsx
+++ b/artfynd/A 47938-2025 artfynd.xlsx
@@ -2684,7 +2684,7 @@
         <v>129032868</v>
       </c>
       <c r="B22" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -5557,7 +5557,7 @@
         <v>129032869</v>
       </c>
       <c r="B50" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5974,7 +5974,7 @@
         <v>129032866</v>
       </c>
       <c r="B54" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6934,7 +6934,7 @@
         <v>129032867</v>
       </c>
       <c r="B63" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 47938-2025 artfynd.xlsx
+++ b/artfynd/A 47938-2025 artfynd.xlsx
@@ -2684,7 +2684,7 @@
         <v>129032868</v>
       </c>
       <c r="B22" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -5557,7 +5557,7 @@
         <v>129032869</v>
       </c>
       <c r="B50" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5974,7 +5974,7 @@
         <v>129032866</v>
       </c>
       <c r="B54" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6934,7 +6934,7 @@
         <v>129032867</v>
       </c>
       <c r="B63" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 47938-2025 artfynd.xlsx
+++ b/artfynd/A 47938-2025 artfynd.xlsx
@@ -2684,7 +2684,7 @@
         <v>129032868</v>
       </c>
       <c r="B22" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -5557,7 +5557,7 @@
         <v>129032869</v>
       </c>
       <c r="B50" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5974,7 +5974,7 @@
         <v>129032866</v>
       </c>
       <c r="B54" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6934,7 +6934,7 @@
         <v>129032867</v>
       </c>
       <c r="B63" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 47938-2025 artfynd.xlsx
+++ b/artfynd/A 47938-2025 artfynd.xlsx
@@ -2684,7 +2684,7 @@
         <v>129032868</v>
       </c>
       <c r="B22" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3424,7 +3424,7 @@
         <v>129032395</v>
       </c>
       <c r="B29" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>129011369</v>
       </c>
       <c r="B30" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -5557,7 +5557,7 @@
         <v>129032869</v>
       </c>
       <c r="B50" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5974,7 +5974,7 @@
         <v>129032866</v>
       </c>
       <c r="B54" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6390,7 +6390,7 @@
         <v>129011372</v>
       </c>
       <c r="B58" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6829,7 +6829,7 @@
         <v>129032396</v>
       </c>
       <c r="B62" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6934,7 +6934,7 @@
         <v>129032867</v>
       </c>
       <c r="B63" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -9209,7 +9209,7 @@
         <v>129011370</v>
       </c>
       <c r="B86" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>

--- a/artfynd/A 47938-2025 artfynd.xlsx
+++ b/artfynd/A 47938-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY108"/>
+  <dimension ref="A1:AY104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129032920</v>
+        <v>129032870</v>
       </c>
       <c r="B2" t="n">
-        <v>79044</v>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,45 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>409793</v>
+        <v>409530</v>
       </c>
       <c r="R2" t="n">
-        <v>6782448</v>
+        <v>6782289</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,6 +765,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -772,14 +784,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129011405</v>
+        <v>129032875</v>
       </c>
       <c r="B3" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -807,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>409747</v>
+        <v>409034</v>
       </c>
       <c r="R3" t="n">
-        <v>6782328</v>
+        <v>6782261</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -840,19 +852,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>11:47</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:47</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,12 +869,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -882,11 +884,11 @@
         <v>129032876</v>
       </c>
       <c r="B4" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -976,14 +978,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129011403</v>
+        <v>129032878</v>
       </c>
       <c r="B5" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1011,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>409706</v>
+        <v>408966</v>
       </c>
       <c r="R5" t="n">
-        <v>6782359</v>
+        <v>6782283</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1044,19 +1046,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>12:06</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>12:06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,26 +1063,26 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129032905</v>
+        <v>129032884</v>
       </c>
       <c r="B6" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1118,10 +1110,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>409624</v>
+        <v>409039</v>
       </c>
       <c r="R6" t="n">
-        <v>6782292</v>
+        <v>6782290</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,14 +1172,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129032907</v>
+        <v>129032888</v>
       </c>
       <c r="B7" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1215,10 +1207,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>409686</v>
+        <v>409127</v>
       </c>
       <c r="R7" t="n">
-        <v>6782351</v>
+        <v>6782290</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1277,14 +1269,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129011389</v>
+        <v>129032898</v>
       </c>
       <c r="B8" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1312,10 +1304,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>409278</v>
+        <v>409390</v>
       </c>
       <c r="R8" t="n">
-        <v>6782361</v>
+        <v>6782289</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1345,19 +1337,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>15:18</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>15:18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1372,26 +1354,26 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129032919</v>
+        <v>129032899</v>
       </c>
       <c r="B9" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1419,10 +1401,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>409358</v>
+        <v>409397</v>
       </c>
       <c r="R9" t="n">
-        <v>6782291</v>
+        <v>6782272</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1481,32 +1463,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129032394</v>
+        <v>129032900</v>
       </c>
       <c r="B10" t="n">
-        <v>79634</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1516,10 +1498,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>409553</v>
+        <v>409449</v>
       </c>
       <c r="R10" t="n">
-        <v>6782378</v>
+        <v>6782286</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1566,22 +1548,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129032398</v>
+        <v>129032873</v>
       </c>
       <c r="B11" t="n">
-        <v>91574</v>
+        <v>91909</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1589,34 +1571,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>409482</v>
+        <v>409075</v>
       </c>
       <c r="R11" t="n">
-        <v>6782335</v>
+        <v>6782317</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1657,28 +1642,29 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129011398</v>
+        <v>129011373</v>
       </c>
       <c r="B12" t="n">
-        <v>79044</v>
+        <v>91930</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1686,34 +1672,41 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>409596</v>
+        <v>409435</v>
       </c>
       <c r="R12" t="n">
-        <v>6782395</v>
+        <v>6782383</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1745,7 +1738,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1755,7 +1748,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>4 st på samma tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1764,6 +1762,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1782,10 +1781,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129032894</v>
+        <v>129011374</v>
       </c>
       <c r="B13" t="n">
-        <v>79044</v>
+        <v>91930</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1793,34 +1792,41 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>409292</v>
+        <v>409475</v>
       </c>
       <c r="R13" t="n">
-        <v>6782306</v>
+        <v>6782342</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1850,39 +1856,55 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>hackspetthål under tickorna</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129032897</v>
+        <v>129032397</v>
       </c>
       <c r="B14" t="n">
-        <v>79044</v>
+        <v>91930</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1890,21 +1912,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1914,10 +1936,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>409469</v>
+        <v>409492</v>
       </c>
       <c r="R14" t="n">
-        <v>6782371</v>
+        <v>6782346</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1964,22 +1986,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129032392</v>
+        <v>129032398</v>
       </c>
       <c r="B15" t="n">
-        <v>79663</v>
+        <v>91930</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1987,21 +2009,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2011,10 +2033,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>409554</v>
+        <v>409482</v>
       </c>
       <c r="R15" t="n">
-        <v>6782380</v>
+        <v>6782335</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2073,14 +2095,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129032909</v>
+        <v>129011377</v>
       </c>
       <c r="B16" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2108,10 +2130,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>409727</v>
+        <v>408995</v>
       </c>
       <c r="R16" t="n">
-        <v>6782352</v>
+        <v>6782299</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2141,9 +2163,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2158,12 +2190,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2173,11 +2205,11 @@
         <v>129011378</v>
       </c>
       <c r="B17" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2277,30 +2309,34 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129011376</v>
+        <v>129011379</v>
       </c>
       <c r="B18" t="n">
-        <v>91573</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2308,10 +2344,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>409774</v>
+        <v>408991</v>
       </c>
       <c r="R18" t="n">
-        <v>6782323</v>
+        <v>6782360</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2343,7 +2379,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2353,7 +2389,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2380,14 +2416,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129032885</v>
+        <v>129011380</v>
       </c>
       <c r="B19" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2415,10 +2451,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>409078</v>
+        <v>408984</v>
       </c>
       <c r="R19" t="n">
-        <v>6782312</v>
+        <v>6782385</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2448,9 +2484,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2465,26 +2511,26 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129011400</v>
+        <v>129011381</v>
       </c>
       <c r="B20" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2512,10 +2558,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>409643</v>
+        <v>409010</v>
       </c>
       <c r="R20" t="n">
-        <v>6782378</v>
+        <v>6782383</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2547,7 +2593,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2557,7 +2603,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2584,14 +2630,14 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129032892</v>
+        <v>129011383</v>
       </c>
       <c r="B21" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2619,10 +2665,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>409244</v>
+        <v>409028</v>
       </c>
       <c r="R21" t="n">
-        <v>6782381</v>
+        <v>6782350</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2652,9 +2698,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2669,65 +2725,57 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129032868</v>
+        <v>129011384</v>
       </c>
       <c r="B22" t="n">
-        <v>57826</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>409688</v>
+        <v>409068</v>
       </c>
       <c r="R22" t="n">
-        <v>6782303</v>
+        <v>6782377</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2757,9 +2805,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2774,26 +2832,26 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129011395</v>
+        <v>129011385</v>
       </c>
       <c r="B23" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -2821,10 +2879,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>409555</v>
+        <v>409214</v>
       </c>
       <c r="R23" t="n">
-        <v>6782356</v>
+        <v>6782345</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2856,7 +2914,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2866,7 +2924,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2893,14 +2951,14 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129011407</v>
+        <v>129011386</v>
       </c>
       <c r="B24" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -2928,10 +2986,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>409795</v>
+        <v>409210</v>
       </c>
       <c r="R24" t="n">
-        <v>6782327</v>
+        <v>6782365</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2963,7 +3021,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -2973,7 +3031,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3000,14 +3058,14 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129011383</v>
+        <v>129011387</v>
       </c>
       <c r="B25" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -3035,10 +3093,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>409028</v>
+        <v>409232</v>
       </c>
       <c r="R25" t="n">
-        <v>6782350</v>
+        <v>6782353</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3070,7 +3128,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3080,7 +3138,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3107,32 +3165,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129032393</v>
+        <v>129011388</v>
       </c>
       <c r="B26" t="n">
-        <v>79634</v>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3142,10 +3200,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>409554</v>
+        <v>409250</v>
       </c>
       <c r="R26" t="n">
-        <v>6782380</v>
+        <v>6782354</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3175,9 +3233,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3192,44 +3260,44 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129032399</v>
+        <v>129011389</v>
       </c>
       <c r="B27" t="n">
-        <v>91574</v>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3239,10 +3307,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>409492</v>
+        <v>409278</v>
       </c>
       <c r="R27" t="n">
-        <v>6782346</v>
+        <v>6782361</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3272,9 +3340,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3289,64 +3367,57 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129011374</v>
+        <v>129011390</v>
       </c>
       <c r="B28" t="n">
-        <v>91574</v>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>409475</v>
+        <v>409349</v>
       </c>
       <c r="R28" t="n">
-        <v>6782342</v>
+        <v>6782376</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3378,7 +3449,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3388,12 +3459,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:57</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>hackspetthål under tickorna</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3402,7 +3468,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3421,53 +3486,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129032395</v>
+        <v>129011391</v>
       </c>
       <c r="B29" t="n">
-        <v>57826</v>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>409759</v>
+        <v>409349</v>
       </c>
       <c r="R29" t="n">
-        <v>6782358</v>
+        <v>6782383</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3497,9 +3554,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3514,65 +3581,57 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129011369</v>
+        <v>129011392</v>
       </c>
       <c r="B30" t="n">
-        <v>57826</v>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>409683</v>
+        <v>409361</v>
       </c>
       <c r="R30" t="n">
-        <v>6782391</v>
+        <v>6782401</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3604,7 +3663,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3614,7 +3673,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3641,14 +3700,14 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129032406</v>
+        <v>129011393</v>
       </c>
       <c r="B31" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -3676,10 +3735,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>409253</v>
+        <v>409472</v>
       </c>
       <c r="R31" t="n">
-        <v>6782372</v>
+        <v>6782351</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3709,9 +3768,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3726,26 +3795,26 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129032913</v>
+        <v>129011394</v>
       </c>
       <c r="B32" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -3773,10 +3842,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>409757</v>
+        <v>409543</v>
       </c>
       <c r="R32" t="n">
-        <v>6782355</v>
+        <v>6782361</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3806,9 +3875,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3823,26 +3902,26 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129032882</v>
+        <v>129011409</v>
       </c>
       <c r="B33" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -3870,10 +3949,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>408992</v>
+        <v>409202</v>
       </c>
       <c r="R33" t="n">
-        <v>6782394</v>
+        <v>6782367</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3903,43 +3982,54 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129011391</v>
+        <v>129032403</v>
       </c>
       <c r="B34" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -3967,10 +4057,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>409349</v>
+        <v>409021</v>
       </c>
       <c r="R34" t="n">
-        <v>6782383</v>
+        <v>6782365</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4000,19 +4090,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>14:34</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>14:34</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4027,26 +4107,26 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129032878</v>
+        <v>129032405</v>
       </c>
       <c r="B35" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -4074,10 +4154,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>408966</v>
+        <v>409048</v>
       </c>
       <c r="R35" t="n">
-        <v>6782283</v>
+        <v>6782365</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4124,26 +4204,26 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129032887</v>
+        <v>129032406</v>
       </c>
       <c r="B36" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -4171,10 +4251,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>409176</v>
+        <v>409253</v>
       </c>
       <c r="R36" t="n">
-        <v>6782420</v>
+        <v>6782372</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4221,26 +4301,26 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129011381</v>
+        <v>129032877</v>
       </c>
       <c r="B37" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -4268,10 +4348,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>409010</v>
+        <v>408994</v>
       </c>
       <c r="R37" t="n">
-        <v>6782383</v>
+        <v>6782293</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4301,19 +4381,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>16:06</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>16:06</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4328,26 +4398,26 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129011394</v>
+        <v>129032879</v>
       </c>
       <c r="B38" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -4375,10 +4445,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>409543</v>
+        <v>408909</v>
       </c>
       <c r="R38" t="n">
-        <v>6782361</v>
+        <v>6782332</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4408,19 +4478,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>13:27</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>13:27</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4435,26 +4495,26 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129011392</v>
+        <v>129032880</v>
       </c>
       <c r="B39" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -4482,10 +4542,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>409361</v>
+        <v>408901</v>
       </c>
       <c r="R39" t="n">
-        <v>6782401</v>
+        <v>6782390</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4515,19 +4575,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>14:31</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>14:31</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4542,26 +4592,26 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129032407</v>
+        <v>129032882</v>
       </c>
       <c r="B40" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -4589,10 +4639,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>409659</v>
+        <v>408992</v>
       </c>
       <c r="R40" t="n">
-        <v>6782436</v>
+        <v>6782394</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4639,26 +4689,26 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129011399</v>
+        <v>129032883</v>
       </c>
       <c r="B41" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -4686,10 +4736,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>409609</v>
+        <v>409010</v>
       </c>
       <c r="R41" t="n">
-        <v>6782404</v>
+        <v>6782399</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4719,19 +4769,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>13:06</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>13:06</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4746,26 +4786,26 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129032891</v>
+        <v>129032885</v>
       </c>
       <c r="B42" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -4793,10 +4833,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>409241</v>
+        <v>409078</v>
       </c>
       <c r="R42" t="n">
-        <v>6782372</v>
+        <v>6782312</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4855,14 +4895,14 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129032911</v>
+        <v>129032886</v>
       </c>
       <c r="B43" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -4890,10 +4930,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>409777</v>
+        <v>409108</v>
       </c>
       <c r="R43" t="n">
-        <v>6782445</v>
+        <v>6782395</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4952,14 +4992,14 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129032906</v>
+        <v>129032887</v>
       </c>
       <c r="B44" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -4987,10 +5027,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>409684</v>
+        <v>409176</v>
       </c>
       <c r="R44" t="n">
-        <v>6782322</v>
+        <v>6782420</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5049,14 +5089,14 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129032910</v>
+        <v>129032889</v>
       </c>
       <c r="B45" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -5084,10 +5124,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>409744</v>
+        <v>409164</v>
       </c>
       <c r="R45" t="n">
-        <v>6782394</v>
+        <v>6782308</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5146,14 +5186,14 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129011408</v>
+        <v>129032890</v>
       </c>
       <c r="B46" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -5181,10 +5221,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>409801</v>
+        <v>409228</v>
       </c>
       <c r="R46" t="n">
-        <v>6782315</v>
+        <v>6782298</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5214,19 +5254,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>11:08</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>11:08</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5241,26 +5271,26 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129011380</v>
+        <v>129032891</v>
       </c>
       <c r="B47" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -5288,10 +5318,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>408984</v>
+        <v>409241</v>
       </c>
       <c r="R47" t="n">
-        <v>6782385</v>
+        <v>6782372</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5321,19 +5351,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>16:07</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>16:07</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5348,26 +5368,26 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129032884</v>
+        <v>129032892</v>
       </c>
       <c r="B48" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -5395,10 +5415,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>409039</v>
+        <v>409244</v>
       </c>
       <c r="R48" t="n">
-        <v>6782290</v>
+        <v>6782381</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5457,14 +5477,14 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129032883</v>
+        <v>129032893</v>
       </c>
       <c r="B49" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -5492,10 +5512,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>409010</v>
+        <v>409280</v>
       </c>
       <c r="R49" t="n">
-        <v>6782399</v>
+        <v>6782382</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5554,53 +5574,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129032869</v>
+        <v>129032894</v>
       </c>
       <c r="B50" t="n">
-        <v>57826</v>
+        <v>79327</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>409754</v>
+        <v>409292</v>
       </c>
       <c r="R50" t="n">
-        <v>6782356</v>
+        <v>6782306</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5659,14 +5671,14 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129011401</v>
+        <v>129032895</v>
       </c>
       <c r="B51" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
@@ -5694,10 +5706,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>409663</v>
+        <v>409310</v>
       </c>
       <c r="R51" t="n">
-        <v>6782385</v>
+        <v>6782326</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5727,19 +5739,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>12:58</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>12:58</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5754,26 +5756,26 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129032899</v>
+        <v>129032896</v>
       </c>
       <c r="B52" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
@@ -5801,10 +5803,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>409397</v>
+        <v>409331</v>
       </c>
       <c r="R52" t="n">
-        <v>6782272</v>
+        <v>6782342</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5863,14 +5865,14 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129011409</v>
+        <v>129032897</v>
       </c>
       <c r="B53" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
@@ -5898,10 +5900,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>409202</v>
+        <v>409469</v>
       </c>
       <c r="R53" t="n">
-        <v>6782367</v>
+        <v>6782371</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5931,93 +5933,74 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>15:26</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>15:26</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129032866</v>
+        <v>129032901</v>
       </c>
       <c r="B54" t="n">
-        <v>57826</v>
+        <v>79327</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>409757</v>
+        <v>409528</v>
       </c>
       <c r="R54" t="n">
-        <v>6782386</v>
+        <v>6782292</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6076,14 +6059,14 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129011396</v>
+        <v>129032917</v>
       </c>
       <c r="B55" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
@@ -6111,10 +6094,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>409584</v>
+        <v>409360</v>
       </c>
       <c r="R55" t="n">
-        <v>6782395</v>
+        <v>6782355</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6144,19 +6127,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>13:11</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>13:11</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6171,26 +6144,26 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129011386</v>
+        <v>129032918</v>
       </c>
       <c r="B56" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
@@ -6218,10 +6191,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>409210</v>
+        <v>409363</v>
       </c>
       <c r="R56" t="n">
-        <v>6782365</v>
+        <v>6782377</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6251,19 +6224,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>15:26</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>15:26</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6278,26 +6241,26 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129032403</v>
+        <v>129032919</v>
       </c>
       <c r="B57" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
@@ -6325,10 +6288,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>409021</v>
+        <v>409358</v>
       </c>
       <c r="R57" t="n">
-        <v>6782365</v>
+        <v>6782291</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6375,22 +6338,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129011372</v>
+        <v>129011375</v>
       </c>
       <c r="B58" t="n">
-        <v>57826</v>
+        <v>79084</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6398,42 +6361,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>409796</v>
+        <v>409335</v>
       </c>
       <c r="R58" t="n">
-        <v>6782327</v>
+        <v>6782352</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6465,7 +6420,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6475,7 +6430,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6502,52 +6457,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129011373</v>
+        <v>129032902</v>
       </c>
       <c r="B59" t="n">
-        <v>91574</v>
+        <v>79327</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>409435</v>
+        <v>409549</v>
       </c>
       <c r="R59" t="n">
-        <v>6782383</v>
+        <v>6782286</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6577,55 +6525,39 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>4 st på samma tall</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129032889</v>
+        <v>129032400</v>
       </c>
       <c r="B60" t="n">
-        <v>79044</v>
+        <v>92369</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6633,21 +6565,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6657,10 +6589,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>409164</v>
+        <v>409738</v>
       </c>
       <c r="R60" t="n">
-        <v>6782308</v>
+        <v>6782382</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6707,44 +6639,44 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129011375</v>
+        <v>129011395</v>
       </c>
       <c r="B61" t="n">
-        <v>78801</v>
+        <v>79327</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6754,10 +6686,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>409335</v>
+        <v>409555</v>
       </c>
       <c r="R61" t="n">
-        <v>6782352</v>
+        <v>6782356</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6789,7 +6721,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -6799,7 +6731,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6826,53 +6758,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129032396</v>
+        <v>129011396</v>
       </c>
       <c r="B62" t="n">
-        <v>57826</v>
+        <v>79327</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>409753</v>
+        <v>409584</v>
       </c>
       <c r="R62" t="n">
-        <v>6782323</v>
+        <v>6782395</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6902,9 +6826,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6919,65 +6853,57 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129032867</v>
+        <v>129011398</v>
       </c>
       <c r="B63" t="n">
-        <v>57826</v>
+        <v>79327</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>409693</v>
+        <v>409596</v>
       </c>
       <c r="R63" t="n">
-        <v>6782357</v>
+        <v>6782395</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7007,9 +6933,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7024,26 +6960,26 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129032914</v>
+        <v>129011399</v>
       </c>
       <c r="B64" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
@@ -7071,10 +7007,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>409759</v>
+        <v>409609</v>
       </c>
       <c r="R64" t="n">
-        <v>6782343</v>
+        <v>6782404</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7104,9 +7040,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7121,22 +7067,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129032400</v>
+        <v>129011400</v>
       </c>
       <c r="B65" t="n">
-        <v>92006</v>
+        <v>79327</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7144,21 +7090,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7168,10 +7114,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>409738</v>
+        <v>409643</v>
       </c>
       <c r="R65" t="n">
-        <v>6782382</v>
+        <v>6782378</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7201,9 +7147,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7218,26 +7174,26 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129011387</v>
+        <v>129011401</v>
       </c>
       <c r="B66" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
@@ -7265,10 +7221,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>409232</v>
+        <v>409663</v>
       </c>
       <c r="R66" t="n">
-        <v>6782353</v>
+        <v>6782385</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7300,7 +7256,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7310,7 +7266,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7337,14 +7293,14 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129032886</v>
+        <v>129011402</v>
       </c>
       <c r="B67" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
@@ -7372,10 +7328,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>409108</v>
+        <v>409671</v>
       </c>
       <c r="R67" t="n">
-        <v>6782395</v>
+        <v>6782390</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7405,9 +7361,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7422,26 +7388,26 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129011379</v>
+        <v>129011403</v>
       </c>
       <c r="B68" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
@@ -7469,10 +7435,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>408991</v>
+        <v>409706</v>
       </c>
       <c r="R68" t="n">
-        <v>6782360</v>
+        <v>6782359</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7504,7 +7470,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7514,7 +7480,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7541,30 +7507,34 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129032874</v>
+        <v>129011404</v>
       </c>
       <c r="B69" t="n">
-        <v>91573</v>
+        <v>79327</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
@@ -7572,10 +7542,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>409405</v>
+        <v>409736</v>
       </c>
       <c r="R69" t="n">
-        <v>6782366</v>
+        <v>6782394</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7605,9 +7575,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7622,26 +7602,26 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129011384</v>
+        <v>129011405</v>
       </c>
       <c r="B70" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
@@ -7669,10 +7649,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>409068</v>
+        <v>409747</v>
       </c>
       <c r="R70" t="n">
-        <v>6782377</v>
+        <v>6782328</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7704,7 +7684,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -7714,7 +7694,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7741,32 +7721,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129032872</v>
+        <v>129011406</v>
       </c>
       <c r="B71" t="n">
-        <v>78801</v>
+        <v>79327</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7776,10 +7756,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>409594</v>
+        <v>409759</v>
       </c>
       <c r="R71" t="n">
-        <v>6782294</v>
+        <v>6782314</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7809,9 +7789,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7826,60 +7816,57 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129032873</v>
+        <v>129011407</v>
       </c>
       <c r="B72" t="n">
-        <v>91553</v>
+        <v>79327</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Hästtjärnåsen, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>409075</v>
+        <v>409795</v>
       </c>
       <c r="R72" t="n">
-        <v>6782317</v>
+        <v>6782327</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7909,44 +7896,53 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129032896</v>
+        <v>129011408</v>
       </c>
       <c r="B73" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
@@ -7974,10 +7970,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>409331</v>
+        <v>409801</v>
       </c>
       <c r="R73" t="n">
-        <v>6782342</v>
+        <v>6782315</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8007,9 +8003,19 @@
           <t>2025-10-09</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8024,26 +8030,26 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129032917</v>
+        <v>129032407</v>
       </c>
       <c r="B74" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
@@ -8071,10 +8077,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>409360</v>
+        <v>409659</v>
       </c>
       <c r="R74" t="n">
-        <v>6782355</v>
+        <v>6782436</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8121,26 +8127,26 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129032900</v>
+        <v>129032408</v>
       </c>
       <c r="B75" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
@@ -8168,10 +8174,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>409449</v>
+        <v>409749</v>
       </c>
       <c r="R75" t="n">
-        <v>6782286</v>
+        <v>6782325</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8218,26 +8224,26 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129032902</v>
+        <v>129032409</v>
       </c>
       <c r="B76" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
@@ -8265,10 +8271,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>409549</v>
+        <v>409782</v>
       </c>
       <c r="R76" t="n">
-        <v>6782286</v>
+        <v>6782339</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8315,26 +8321,26 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129032893</v>
+        <v>129032903</v>
       </c>
       <c r="B77" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
@@ -8362,10 +8368,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>409280</v>
+        <v>409582</v>
       </c>
       <c r="R77" t="n">
-        <v>6782382</v>
+        <v>6782297</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8424,14 +8430,14 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129011404</v>
+        <v>129032904</v>
       </c>
       <c r="B78" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
@@ -8459,10 +8465,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>409736</v>
+        <v>409568</v>
       </c>
       <c r="R78" t="n">
-        <v>6782394</v>
+        <v>6782383</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8492,19 +8498,9 @@
           <t>2025-10-09</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>11:59</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-09</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>11:59</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8519,26 +8515,26 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129032901</v>
+        <v>129032905</v>
       </c>
       <c r="B79" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
@@ -8566,7 +8562,7 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>409528</v>
+        <v>409624</v>
       </c>
       <c r="R79" t="n">
         <v>6782292</v>
@@ -8628,14 +8624,14 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129032888</v>
+        <v>129032906</v>
       </c>
       <c r="B80" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
@@ -8663,10 +8659,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>409127</v>
+        <v>409684</v>
       </c>
       <c r="R80" t="n">
-        <v>6782290</v>
+        <v>6782322</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8725,30 +8721,34 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129032402</v>
+        <v>129032907</v>
       </c>
       <c r="B81" t="n">
-        <v>91573</v>
+        <v>79327</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
@@ -8756,10 +8756,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>409767</v>
+        <v>409686</v>
       </c>
       <c r="R81" t="n">
-        <v>6782352</v>
+        <v>6782351</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8806,12 +8806,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
@@ -8821,11 +8821,11 @@
         <v>129032908</v>
       </c>
       <c r="B82" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
@@ -8915,14 +8915,14 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129032879</v>
+        <v>129032909</v>
       </c>
       <c r="B83" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
@@ -8950,10 +8950,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>408909</v>
+        <v>409727</v>
       </c>
       <c r="R83" t="n">
-        <v>6782332</v>
+        <v>6782352</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9012,14 +9012,14 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129032916</v>
+        <v>129032910</v>
       </c>
       <c r="B84" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
@@ -9047,10 +9047,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>409812</v>
+        <v>409744</v>
       </c>
       <c r="R84" t="n">
-        <v>6782309</v>
+        <v>6782394</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9109,14 +9109,14 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129032409</v>
+        <v>129032911</v>
       </c>
       <c r="B85" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t=